--- a/Financial Analysis/MSFT.xlsx
+++ b/Financial Analysis/MSFT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197304FC-6695-4F0A-A390-F31A7A017CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEDF5F8-82DE-47CE-9EAA-F0F34D0078F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{61E89E8F-0FF3-456B-A54B-AD32D916470B}"/>
   </bookViews>
@@ -1176,14 +1176,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="19">
-        <v>435.28</v>
+        <v>454.26</v>
       </c>
       <c r="E3" s="2">
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="2">
         <v>45868</v>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>3235218.5999999996</v>
+        <v>3376287.4499999997</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>3193052.5999999996</v>
+        <v>3334121.4499999997</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="BI27" s="19">
         <f>Main!D3</f>
-        <v>435.28</v>
+        <v>454.26</v>
       </c>
     </row>
     <row r="28" spans="2:179" x14ac:dyDescent="0.3">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="BI28" s="18">
         <f>BI26/BI27-1</f>
-        <v>-0.1306971479613509</v>
+        <v>-0.16701856770267431</v>
       </c>
     </row>
     <row r="29" spans="2:179" x14ac:dyDescent="0.3">

--- a/Financial Analysis/MSFT.xlsx
+++ b/Financial Analysis/MSFT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEDF5F8-82DE-47CE-9EAA-F0F34D0078F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93D2327-2A19-4A7A-B7FB-7A8CF3BDAAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{61E89E8F-0FF3-456B-A54B-AD32D916470B}"/>
   </bookViews>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO16" authorId="0" shapeId="0" xr:uid="{23CEF960-23D3-4234-9A71-9F5F76A023AD}">
+    <comment ref="AT16" authorId="0" shapeId="0" xr:uid="{23CEF960-23D3-4234-9A71-9F5F76A023AD}">
       <text>
         <r>
           <rPr>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="140">
   <si>
     <t>MSFT</t>
   </si>
@@ -492,6 +492,18 @@
   </si>
   <si>
     <t>Slightly overvalued</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -736,14 +748,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
@@ -760,7 +772,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27172920" y="0"/>
+          <a:off x="27889200" y="0"/>
           <a:ext cx="0" cy="6088380"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -786,14 +798,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -810,7 +822,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="33482280" y="0"/>
+          <a:off x="37688520" y="0"/>
           <a:ext cx="0" cy="6118860"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1176,17 +1188,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="19">
-        <v>454.26</v>
+        <v>520.79999999999995</v>
       </c>
       <c r="E3" s="2">
-        <v>45804</v>
+        <v>45887</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45887</v>
       </c>
       <c r="G3" s="2">
-        <v>45868</v>
+        <v>45960</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>43</v>
@@ -1207,11 +1219,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>7432.5</f>
-        <v>7432.5</v>
+        <v>7432</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F4" s="1"/>
       <c r="I4" s="13"/>
@@ -1232,7 +1243,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>3376287.4499999997</v>
+        <v>3870585.5999999996</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1253,11 +1264,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>17482+54073+15581</f>
-        <v>87136</v>
+        <f>30242+64323+15405</f>
+        <v>109970</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F6" s="1"/>
       <c r="I6" s="11" t="s">
@@ -1279,11 +1290,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>5248+39722</f>
-        <v>44970</v>
+        <f>2999+40152</f>
+        <v>43151</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F7" s="1"/>
       <c r="I7" s="13"/>
@@ -1304,7 +1315,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>42166</v>
+        <v>66819</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -1328,7 +1339,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>3334121.4499999997</v>
+        <v>3803766.5999999996</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1383,21 +1394,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F890206B-862E-4016-AB7D-796014A07090}">
-  <dimension ref="A1:FW54"/>
+  <dimension ref="A1:GB54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="10.5546875" customWidth="1"/>
     <col min="7" max="22" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="38" width="10.5546875" customWidth="1"/>
-    <col min="41" max="41" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="8.88671875" customWidth="1"/>
-    <col min="60" max="60" width="12" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="23" max="43" width="10.5546875" customWidth="1"/>
+    <col min="46" max="46" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="8.88671875" customWidth="1"/>
+    <col min="65" max="65" width="12" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:63" x14ac:dyDescent="0.3">
       <c r="C1" s="17">
         <v>42643</v>
       </c>
@@ -1506,11 +1517,24 @@
       <c r="AL1" s="17">
         <v>45838</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AM1" s="17">
+        <v>45930</v>
+      </c>
+      <c r="AN1" s="17">
+        <v>46022</v>
+      </c>
+      <c r="AO1" s="17">
+        <v>46112</v>
+      </c>
+      <c r="AP1" s="17">
+        <v>46203</v>
+      </c>
+      <c r="AQ1" s="17"/>
+      <c r="AT1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:63" x14ac:dyDescent="0.3">
       <c r="C2" s="3" t="s">
         <v>80</v>
       </c>
@@ -1619,65 +1643,78 @@
       <c r="AL2" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AN2">
+      <c r="AM2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="AQ2" s="3"/>
+      <c r="AS2">
         <v>2017</v>
       </c>
-      <c r="AO2">
+      <c r="AT2">
         <v>2018</v>
       </c>
-      <c r="AP2">
+      <c r="AU2">
         <v>2019</v>
       </c>
-      <c r="AQ2">
+      <c r="AV2">
         <v>2020</v>
       </c>
-      <c r="AR2">
+      <c r="AW2">
         <v>2021</v>
       </c>
-      <c r="AS2">
+      <c r="AX2">
         <v>2022</v>
       </c>
-      <c r="AT2">
+      <c r="AY2">
         <v>2023</v>
       </c>
-      <c r="AU2">
+      <c r="AZ2">
         <v>2024</v>
       </c>
-      <c r="AV2">
+      <c r="BA2">
         <v>2025</v>
       </c>
-      <c r="AW2">
+      <c r="BB2">
         <v>2026</v>
       </c>
-      <c r="AX2">
+      <c r="BC2">
         <v>2027</v>
       </c>
-      <c r="AY2">
+      <c r="BD2">
         <v>2028</v>
       </c>
-      <c r="AZ2">
+      <c r="BE2">
         <v>2029</v>
       </c>
-      <c r="BA2">
+      <c r="BF2">
         <v>2030</v>
       </c>
-      <c r="BB2">
+      <c r="BG2">
         <v>2031</v>
       </c>
-      <c r="BC2">
+      <c r="BH2">
         <v>2032</v>
       </c>
-      <c r="BD2">
+      <c r="BI2">
         <v>2033</v>
       </c>
-      <c r="BE2">
+      <c r="BJ2">
         <v>2034</v>
       </c>
-      <c r="BF2">
+      <c r="BK2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:63" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>30</v>
       </c>
@@ -1787,87 +1824,91 @@
         <v>15319</v>
       </c>
       <c r="AL3" s="4">
-        <f t="shared" ref="AL3" si="0">AH3*0.99</f>
-        <v>13084.83</v>
-      </c>
-      <c r="AN3" s="5">
+        <v>17136</v>
+      </c>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="4"/>
+      <c r="AS3" s="5">
         <f>SUM(C3:F3)</f>
         <v>63541</v>
       </c>
-      <c r="AO3" s="5">
+      <c r="AT3" s="5">
         <f>SUM(G3:J3)</f>
         <v>64497</v>
       </c>
-      <c r="AP3" s="5">
+      <c r="AU3" s="5">
         <f>SUM(K3:N3)</f>
         <v>66069</v>
       </c>
-      <c r="AQ3" s="5">
+      <c r="AV3" s="5">
         <f>SUM(O3:R3)</f>
         <v>68041</v>
       </c>
-      <c r="AR3" s="5">
+      <c r="AW3" s="5">
         <f>SUM(S3:V3)</f>
         <v>71074</v>
       </c>
-      <c r="AS3" s="5">
+      <c r="AX3" s="5">
         <f>SUM(W3:Z3)</f>
         <v>72732</v>
       </c>
-      <c r="AT3" s="5">
+      <c r="AY3" s="5">
         <f>SUM(AA3:AD3)</f>
         <v>64699</v>
       </c>
-      <c r="AU3" s="5">
+      <c r="AZ3" s="5">
         <f>SUM(AE3:AH3)</f>
         <v>63228</v>
       </c>
-      <c r="AV3" s="5">
+      <c r="BA3" s="5">
         <f>SUM(AI3:AL3)</f>
-        <v>59894.83</v>
-      </c>
-      <c r="AW3" s="5">
-        <f>AV3*1.01</f>
-        <v>60493.778300000005</v>
-      </c>
-      <c r="AX3" s="5">
-        <f t="shared" ref="AX3:BF3" si="1">AW3*1.01</f>
-        <v>61098.716083000007</v>
-      </c>
-      <c r="AY3" s="5">
-        <f t="shared" si="1"/>
-        <v>61709.703243830008</v>
-      </c>
-      <c r="AZ3" s="5">
-        <f t="shared" si="1"/>
-        <v>62326.80027626831</v>
-      </c>
-      <c r="BA3" s="5">
-        <f t="shared" si="1"/>
-        <v>62950.068279030995</v>
+        <v>63946</v>
       </c>
       <c r="BB3" s="5">
-        <f t="shared" si="1"/>
-        <v>63579.568961821307</v>
+        <f>BA3*1.01</f>
+        <v>64585.46</v>
       </c>
       <c r="BC3" s="5">
-        <f t="shared" si="1"/>
-        <v>64215.364651439522</v>
+        <f t="shared" ref="BC3:BK3" si="0">BB3*1.01</f>
+        <v>65231.314599999998</v>
       </c>
       <c r="BD3" s="5">
-        <f t="shared" si="1"/>
-        <v>64857.518297953917</v>
+        <f t="shared" si="0"/>
+        <v>65883.627745999998</v>
       </c>
       <c r="BE3" s="5">
-        <f t="shared" si="1"/>
-        <v>65506.093480933458</v>
+        <f t="shared" si="0"/>
+        <v>66542.464023459994</v>
       </c>
       <c r="BF3" s="5">
-        <f t="shared" si="1"/>
-        <v>66161.1544157428</v>
+        <f t="shared" si="0"/>
+        <v>67207.888663694597</v>
+      </c>
+      <c r="BG3" s="5">
+        <f t="shared" si="0"/>
+        <v>67879.967550331537</v>
+      </c>
+      <c r="BH3" s="5">
+        <f t="shared" si="0"/>
+        <v>68558.767225834847</v>
+      </c>
+      <c r="BI3" s="5">
+        <f t="shared" si="0"/>
+        <v>69244.354898093196</v>
+      </c>
+      <c r="BJ3" s="5">
+        <f t="shared" si="0"/>
+        <v>69936.798447074121</v>
+      </c>
+      <c r="BK3" s="5">
+        <f t="shared" si="0"/>
+        <v>70636.166431544858</v>
       </c>
     </row>
-    <row r="4" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:63" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>31</v>
       </c>
@@ -1977,312 +2018,321 @@
         <v>54747</v>
       </c>
       <c r="AL4" s="4">
-        <f>AH4*1.2</f>
-        <v>61812</v>
-      </c>
-      <c r="AN4" s="5">
+        <v>59305</v>
+      </c>
+      <c r="AM4" s="4"/>
+      <c r="AN4" s="4"/>
+      <c r="AO4" s="4"/>
+      <c r="AP4" s="4"/>
+      <c r="AQ4" s="4"/>
+      <c r="AS4" s="5">
         <f>SUM(C4:F4)</f>
         <v>32760</v>
       </c>
-      <c r="AO4" s="5">
+      <c r="AT4" s="5">
         <f>SUM(G4:J4)</f>
         <v>45863</v>
       </c>
-      <c r="AP4" s="5">
+      <c r="AU4" s="5">
         <f>SUM(K4:N4)</f>
         <v>59774</v>
       </c>
-      <c r="AQ4" s="5">
+      <c r="AV4" s="5">
         <f>SUM(O4:R4)</f>
         <v>74974</v>
       </c>
-      <c r="AR4" s="5">
+      <c r="AW4" s="5">
         <f>SUM(S4:V4)</f>
         <v>97014</v>
       </c>
-      <c r="AS4" s="5">
+      <c r="AX4" s="5">
         <f>SUM(W4:Z4)</f>
         <v>125538</v>
       </c>
-      <c r="AT4" s="5">
+      <c r="AY4" s="5">
         <f>SUM(AA4:AD4)</f>
         <v>147216</v>
       </c>
-      <c r="AU4" s="5">
+      <c r="AZ4" s="5">
         <f>SUM(AE4:AH4)</f>
         <v>176553</v>
       </c>
-      <c r="AV4" s="5">
+      <c r="BA4" s="5">
         <f>SUM(AI4:AL4)</f>
-        <v>220285</v>
-      </c>
-      <c r="AW4" s="5">
-        <f>AV4*1.15</f>
-        <v>253327.74999999997</v>
-      </c>
-      <c r="AX4" s="5">
-        <f>AW4*1.08</f>
-        <v>273593.96999999997</v>
-      </c>
-      <c r="AY4" s="5">
-        <f>AX4*1.06</f>
-        <v>290009.60819999996</v>
-      </c>
-      <c r="AZ4" s="5">
-        <f>AY4*1.05</f>
-        <v>304510.08860999998</v>
-      </c>
-      <c r="BA4" s="5">
-        <f>AZ4*1.04</f>
-        <v>316690.49215439998</v>
+        <v>217778</v>
       </c>
       <c r="BB4" s="5">
-        <f>BA4*1.03</f>
-        <v>326191.20691903197</v>
+        <f>BA4*1.15</f>
+        <v>250444.69999999998</v>
       </c>
       <c r="BC4" s="5">
-        <f>BB4*1.03</f>
-        <v>335976.94312660291</v>
+        <f>BB4*1.08</f>
+        <v>270480.27600000001</v>
       </c>
       <c r="BD4" s="5">
-        <f>BC4*1.02</f>
-        <v>342696.48198913498</v>
+        <f>BC4*1.06</f>
+        <v>286709.09256000002</v>
       </c>
       <c r="BE4" s="5">
-        <f t="shared" ref="BE4:BF4" si="2">BD4*1.02</f>
-        <v>349550.41162891767</v>
+        <f>BD4*1.05</f>
+        <v>301044.54718800006</v>
       </c>
       <c r="BF4" s="5">
-        <f t="shared" si="2"/>
-        <v>356541.41986149602</v>
+        <f>BE4*1.04</f>
+        <v>313086.32907552004</v>
+      </c>
+      <c r="BG4" s="5">
+        <f>BF4*1.03</f>
+        <v>322478.91894778563</v>
+      </c>
+      <c r="BH4" s="5">
+        <f>BG4*1.03</f>
+        <v>332153.2865162192</v>
+      </c>
+      <c r="BI4" s="5">
+        <f>BH4*1.02</f>
+        <v>338796.35224654357</v>
+      </c>
+      <c r="BJ4" s="5">
+        <f t="shared" ref="BJ4:BK4" si="1">BI4*1.02</f>
+        <v>345572.27929147444</v>
+      </c>
+      <c r="BK4" s="5">
+        <f t="shared" si="1"/>
+        <v>352483.72487730393</v>
       </c>
     </row>
-    <row r="5" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:R5" si="3">C3+C4</f>
+        <f t="shared" ref="C5:R5" si="2">C3+C4</f>
         <v>21658</v>
       </c>
       <c r="D5" s="7">
+        <f t="shared" si="2"/>
+        <v>25826</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" si="2"/>
+        <v>23212</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" si="2"/>
+        <v>25605</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="2"/>
+        <v>24538</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="2"/>
+        <v>28918</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="2"/>
+        <v>26819</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" si="2"/>
+        <v>30085</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="2"/>
+        <v>29084</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="2"/>
+        <v>32471</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="2"/>
+        <v>30571</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="2"/>
+        <v>33717</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="2"/>
+        <v>33055</v>
+      </c>
+      <c r="P5" s="7">
+        <f t="shared" si="2"/>
+        <v>36906</v>
+      </c>
+      <c r="Q5" s="7">
+        <f t="shared" si="2"/>
+        <v>35021</v>
+      </c>
+      <c r="R5" s="7">
+        <f t="shared" si="2"/>
+        <v>38033</v>
+      </c>
+      <c r="S5" s="7">
+        <f t="shared" ref="S5:V5" si="3">S3+S4</f>
+        <v>37154</v>
+      </c>
+      <c r="T5" s="7">
         <f t="shared" si="3"/>
-        <v>25826</v>
-      </c>
-      <c r="E5" s="7">
+        <v>43076</v>
+      </c>
+      <c r="U5" s="7">
         <f t="shared" si="3"/>
-        <v>23212</v>
-      </c>
-      <c r="F5" s="7">
+        <v>41706</v>
+      </c>
+      <c r="V5" s="7">
         <f t="shared" si="3"/>
-        <v>25605</v>
-      </c>
-      <c r="G5" s="7">
-        <f t="shared" si="3"/>
-        <v>24538</v>
-      </c>
-      <c r="H5" s="7">
-        <f t="shared" si="3"/>
-        <v>28918</v>
-      </c>
-      <c r="I5" s="7">
-        <f t="shared" si="3"/>
-        <v>26819</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="3"/>
-        <v>30085</v>
-      </c>
-      <c r="K5" s="7">
-        <f t="shared" si="3"/>
-        <v>29084</v>
-      </c>
-      <c r="L5" s="7">
-        <f t="shared" si="3"/>
-        <v>32471</v>
-      </c>
-      <c r="M5" s="7">
-        <f t="shared" si="3"/>
-        <v>30571</v>
-      </c>
-      <c r="N5" s="7">
-        <f t="shared" si="3"/>
-        <v>33717</v>
-      </c>
-      <c r="O5" s="7">
-        <f t="shared" si="3"/>
-        <v>33055</v>
-      </c>
-      <c r="P5" s="7">
-        <f t="shared" si="3"/>
-        <v>36906</v>
-      </c>
-      <c r="Q5" s="7">
-        <f t="shared" si="3"/>
-        <v>35021</v>
-      </c>
-      <c r="R5" s="7">
-        <f t="shared" si="3"/>
-        <v>38033</v>
-      </c>
-      <c r="S5" s="7">
-        <f t="shared" ref="S5:V5" si="4">S3+S4</f>
-        <v>37154</v>
-      </c>
-      <c r="T5" s="7">
+        <v>46152</v>
+      </c>
+      <c r="W5" s="7">
+        <f t="shared" ref="W5:X5" si="4">W3+W4</f>
+        <v>45317</v>
+      </c>
+      <c r="X5" s="7">
         <f t="shared" si="4"/>
-        <v>43076</v>
-      </c>
-      <c r="U5" s="7">
-        <f t="shared" si="4"/>
-        <v>41706</v>
-      </c>
-      <c r="V5" s="7">
-        <f t="shared" si="4"/>
-        <v>46152</v>
-      </c>
-      <c r="W5" s="7">
-        <f t="shared" ref="W5:X5" si="5">W3+W4</f>
-        <v>45317</v>
-      </c>
-      <c r="X5" s="7">
-        <f t="shared" si="5"/>
         <v>51728</v>
       </c>
       <c r="Y5" s="7">
-        <f t="shared" ref="Y5" si="6">Y3+Y4</f>
+        <f t="shared" ref="Y5" si="5">Y3+Y4</f>
         <v>49360</v>
       </c>
       <c r="Z5" s="7">
-        <f t="shared" ref="Z5" si="7">Z3+Z4</f>
+        <f t="shared" ref="Z5" si="6">Z3+Z4</f>
         <v>51865</v>
       </c>
       <c r="AA5" s="7">
-        <f t="shared" ref="AA5" si="8">AA3+AA4</f>
+        <f t="shared" ref="AA5" si="7">AA3+AA4</f>
         <v>50122</v>
       </c>
       <c r="AB5" s="7">
-        <f t="shared" ref="AB5:AC5" si="9">AB3+AB4</f>
+        <f t="shared" ref="AB5:AC5" si="8">AB3+AB4</f>
         <v>52747</v>
       </c>
       <c r="AC5" s="7">
+        <f t="shared" si="8"/>
+        <v>52857</v>
+      </c>
+      <c r="AD5" s="7">
+        <f t="shared" ref="AD5:AE5" si="9">AD3+AD4</f>
+        <v>56189</v>
+      </c>
+      <c r="AE5" s="7">
         <f t="shared" si="9"/>
-        <v>52857</v>
-      </c>
-      <c r="AD5" s="7">
-        <f t="shared" ref="AD5:AE5" si="10">AD3+AD4</f>
-        <v>56189</v>
-      </c>
-      <c r="AE5" s="7">
+        <v>56517</v>
+      </c>
+      <c r="AF5" s="7">
+        <f t="shared" ref="AF5:AL5" si="10">AF3+AF4</f>
+        <v>56517</v>
+      </c>
+      <c r="AG5" s="7">
         <f t="shared" si="10"/>
-        <v>56517</v>
-      </c>
-      <c r="AF5" s="7">
-        <f t="shared" ref="AF5:AL5" si="11">AF3+AF4</f>
-        <v>56517</v>
-      </c>
-      <c r="AG5" s="7">
+        <v>62020</v>
+      </c>
+      <c r="AH5" s="7">
+        <f t="shared" si="10"/>
+        <v>64727</v>
+      </c>
+      <c r="AI5" s="7">
+        <f t="shared" si="10"/>
+        <v>65585</v>
+      </c>
+      <c r="AJ5" s="7">
+        <f t="shared" si="10"/>
+        <v>69632</v>
+      </c>
+      <c r="AK5" s="7">
+        <f t="shared" si="10"/>
+        <v>70066</v>
+      </c>
+      <c r="AL5" s="7">
+        <f t="shared" si="10"/>
+        <v>76441</v>
+      </c>
+      <c r="AM5" s="7"/>
+      <c r="AN5" s="7"/>
+      <c r="AO5" s="7"/>
+      <c r="AP5" s="7"/>
+      <c r="AQ5" s="7"/>
+      <c r="AS5" s="7">
+        <f t="shared" ref="AS5:AW5" si="11">AS3+AS4</f>
+        <v>96301</v>
+      </c>
+      <c r="AT5" s="7">
         <f t="shared" si="11"/>
-        <v>62020</v>
-      </c>
-      <c r="AH5" s="7">
+        <v>110360</v>
+      </c>
+      <c r="AU5" s="7">
         <f t="shared" si="11"/>
-        <v>64727</v>
-      </c>
-      <c r="AI5" s="7">
+        <v>125843</v>
+      </c>
+      <c r="AV5" s="7">
         <f t="shared" si="11"/>
-        <v>65585</v>
-      </c>
-      <c r="AJ5" s="7">
+        <v>143015</v>
+      </c>
+      <c r="AW5" s="7">
         <f t="shared" si="11"/>
-        <v>69632</v>
-      </c>
-      <c r="AK5" s="7">
-        <f t="shared" si="11"/>
-        <v>70066</v>
-      </c>
-      <c r="AL5" s="7">
-        <f t="shared" si="11"/>
-        <v>74896.83</v>
-      </c>
-      <c r="AN5" s="7">
-        <f t="shared" ref="AN5:AR5" si="12">AN3+AN4</f>
-        <v>96301</v>
-      </c>
-      <c r="AO5" s="7">
+        <v>168088</v>
+      </c>
+      <c r="AX5" s="7">
+        <f t="shared" ref="AX5:AY5" si="12">AX3+AX4</f>
+        <v>198270</v>
+      </c>
+      <c r="AY5" s="7">
         <f t="shared" si="12"/>
-        <v>110360</v>
-      </c>
-      <c r="AP5" s="7">
-        <f t="shared" si="12"/>
-        <v>125843</v>
-      </c>
-      <c r="AQ5" s="7">
-        <f t="shared" si="12"/>
-        <v>143015</v>
-      </c>
-      <c r="AR5" s="7">
-        <f t="shared" si="12"/>
-        <v>168088</v>
-      </c>
-      <c r="AS5" s="7">
-        <f t="shared" ref="AS5:AT5" si="13">AS3+AS4</f>
-        <v>198270</v>
-      </c>
-      <c r="AT5" s="7">
-        <f t="shared" si="13"/>
         <v>211915</v>
       </c>
-      <c r="AU5" s="7">
-        <f t="shared" ref="AU5" si="14">AU3+AU4</f>
+      <c r="AZ5" s="7">
+        <f t="shared" ref="AZ5" si="13">AZ3+AZ4</f>
         <v>239781</v>
       </c>
-      <c r="AV5" s="7">
-        <f t="shared" ref="AV5:BA5" si="15">AV3+AV4</f>
-        <v>280179.83</v>
-      </c>
-      <c r="AW5" s="7">
+      <c r="BA5" s="7">
+        <f t="shared" ref="BA5:BF5" si="14">BA3+BA4</f>
+        <v>281724</v>
+      </c>
+      <c r="BB5" s="7">
+        <f t="shared" si="14"/>
+        <v>315030.15999999997</v>
+      </c>
+      <c r="BC5" s="7">
+        <f t="shared" si="14"/>
+        <v>335711.5906</v>
+      </c>
+      <c r="BD5" s="7">
+        <f t="shared" si="14"/>
+        <v>352592.72030600003</v>
+      </c>
+      <c r="BE5" s="7">
+        <f t="shared" si="14"/>
+        <v>367587.01121146005</v>
+      </c>
+      <c r="BF5" s="7">
+        <f t="shared" si="14"/>
+        <v>380294.21773921466</v>
+      </c>
+      <c r="BG5" s="7">
+        <f t="shared" ref="BG5:BI5" si="15">BG3+BG4</f>
+        <v>390358.88649811718</v>
+      </c>
+      <c r="BH5" s="7">
         <f t="shared" si="15"/>
-        <v>313821.52830000001</v>
-      </c>
-      <c r="AX5" s="7">
+        <v>400712.05374205403</v>
+      </c>
+      <c r="BI5" s="7">
         <f t="shared" si="15"/>
-        <v>334692.68608299998</v>
-      </c>
-      <c r="AY5" s="7">
-        <f t="shared" si="15"/>
-        <v>351719.31144382997</v>
-      </c>
-      <c r="AZ5" s="7">
-        <f t="shared" si="15"/>
-        <v>366836.88888626831</v>
-      </c>
-      <c r="BA5" s="7">
-        <f t="shared" si="15"/>
-        <v>379640.56043343095</v>
-      </c>
-      <c r="BB5" s="7">
-        <f t="shared" ref="BB5:BD5" si="16">BB3+BB4</f>
-        <v>389770.7758808533</v>
-      </c>
-      <c r="BC5" s="7">
+        <v>408040.70714463678</v>
+      </c>
+      <c r="BJ5" s="7">
+        <f t="shared" ref="BJ5:BK5" si="16">BJ3+BJ4</f>
+        <v>415509.07773854857</v>
+      </c>
+      <c r="BK5" s="7">
         <f t="shared" si="16"/>
-        <v>400192.30777804245</v>
-      </c>
-      <c r="BD5" s="7">
-        <f t="shared" si="16"/>
-        <v>407554.00028708891</v>
-      </c>
-      <c r="BE5" s="7">
-        <f t="shared" ref="BE5:BF5" si="17">BE3+BE4</f>
-        <v>415056.50510985113</v>
-      </c>
-      <c r="BF5" s="7">
-        <f t="shared" si="17"/>
-        <v>422702.5742772388</v>
+        <v>423119.8913088488</v>
       </c>
     </row>
-    <row r="6" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:63" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>28</v>
       </c>
@@ -2392,87 +2442,91 @@
         <v>3037</v>
       </c>
       <c r="AL6" s="5">
-        <f t="shared" ref="AL6" si="18">AL3*0.22</f>
-        <v>2878.6626000000001</v>
-      </c>
-      <c r="AN6" s="5">
+        <v>3314</v>
+      </c>
+      <c r="AM6" s="5"/>
+      <c r="AN6" s="5"/>
+      <c r="AO6" s="5"/>
+      <c r="AP6" s="5"/>
+      <c r="AQ6" s="5"/>
+      <c r="AS6" s="5">
         <f>SUM(C6:F6)</f>
         <v>15175</v>
       </c>
-      <c r="AO6" s="5">
+      <c r="AT6" s="5">
         <f>SUM(G6:J6)</f>
         <v>15420</v>
       </c>
-      <c r="AP6" s="5">
+      <c r="AU6" s="5">
         <f>SUM(K6:N6)</f>
         <v>16273</v>
       </c>
-      <c r="AQ6" s="5">
+      <c r="AV6" s="5">
         <f>SUM(O6:R6)</f>
         <v>16017</v>
       </c>
-      <c r="AR6" s="5">
+      <c r="AW6" s="5">
         <f>SUM(S6:V6)</f>
         <v>18219</v>
       </c>
-      <c r="AS6" s="5">
+      <c r="AX6" s="5">
         <f>SUM(W6:Z6)</f>
         <v>19064</v>
       </c>
-      <c r="AT6" s="5">
+      <c r="AY6" s="5">
         <f>SUM(AA6:AD6)</f>
         <v>17804</v>
       </c>
-      <c r="AU6" s="5">
+      <c r="AZ6" s="5">
         <f>SUM(AE6:AH6)</f>
         <v>14464</v>
       </c>
-      <c r="AV6" s="5">
+      <c r="BA6" s="5">
         <f>SUM(AI6:AL6)</f>
-        <v>13065.6626</v>
-      </c>
-      <c r="AW6" s="5">
-        <f t="shared" ref="AW6:BD6" si="19">AW3*0.23</f>
-        <v>13913.569009000003</v>
-      </c>
-      <c r="AX6" s="5">
-        <f t="shared" si="19"/>
-        <v>14052.704699090002</v>
-      </c>
-      <c r="AY6" s="5">
-        <f t="shared" si="19"/>
-        <v>14193.231746080903</v>
-      </c>
-      <c r="AZ6" s="5">
-        <f t="shared" si="19"/>
-        <v>14335.164063541712</v>
-      </c>
-      <c r="BA6" s="5">
-        <f t="shared" si="19"/>
-        <v>14478.515704177129</v>
+        <v>13501</v>
       </c>
       <c r="BB6" s="5">
-        <f t="shared" si="19"/>
-        <v>14623.300861218901</v>
+        <f t="shared" ref="BB6:BI6" si="17">BB3*0.23</f>
+        <v>14854.6558</v>
       </c>
       <c r="BC6" s="5">
-        <f t="shared" si="19"/>
-        <v>14769.533869831092</v>
+        <f t="shared" si="17"/>
+        <v>15003.202358</v>
       </c>
       <c r="BD6" s="5">
-        <f t="shared" si="19"/>
-        <v>14917.229208529401</v>
+        <f t="shared" si="17"/>
+        <v>15153.23438158</v>
       </c>
       <c r="BE6" s="5">
-        <f t="shared" ref="BE6:BF6" si="20">BE3*0.23</f>
-        <v>15066.401500614696</v>
+        <f t="shared" si="17"/>
+        <v>15304.766725395799</v>
       </c>
       <c r="BF6" s="5">
-        <f t="shared" si="20"/>
-        <v>15217.065515620845</v>
+        <f t="shared" si="17"/>
+        <v>15457.814392649758</v>
+      </c>
+      <c r="BG6" s="5">
+        <f t="shared" si="17"/>
+        <v>15612.392536576253</v>
+      </c>
+      <c r="BH6" s="5">
+        <f t="shared" si="17"/>
+        <v>15768.516461942016</v>
+      </c>
+      <c r="BI6" s="5">
+        <f t="shared" si="17"/>
+        <v>15926.201626561437</v>
+      </c>
+      <c r="BJ6" s="5">
+        <f t="shared" ref="BJ6:BK6" si="18">BJ3*0.23</f>
+        <v>16085.463642827048</v>
+      </c>
+      <c r="BK6" s="5">
+        <f t="shared" si="18"/>
+        <v>16246.318279255318</v>
       </c>
     </row>
-    <row r="7" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:63" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -2582,537 +2636,551 @@
         <v>18882</v>
       </c>
       <c r="AL7" s="5">
-        <f>AL4*0.35</f>
-        <v>21634.199999999997</v>
-      </c>
-      <c r="AN7" s="5">
+        <v>20700</v>
+      </c>
+      <c r="AM7" s="5"/>
+      <c r="AN7" s="5"/>
+      <c r="AO7" s="5"/>
+      <c r="AP7" s="5"/>
+      <c r="AQ7" s="5"/>
+      <c r="AS7" s="5">
         <f>SUM(C7:F7)</f>
         <v>19086</v>
       </c>
-      <c r="AO7" s="5">
+      <c r="AT7" s="5">
         <f>SUM(G7:J7)</f>
         <v>22933</v>
       </c>
-      <c r="AP7" s="5">
+      <c r="AU7" s="5">
         <f>SUM(K7:N7)</f>
         <v>26637</v>
       </c>
-      <c r="AQ7" s="5">
+      <c r="AV7" s="5">
         <f>SUM(O7:R7)</f>
         <v>30061</v>
       </c>
-      <c r="AR7" s="5">
+      <c r="AW7" s="5">
         <f>SUM(S7:V7)</f>
         <v>34013</v>
       </c>
-      <c r="AS7" s="5">
+      <c r="AX7" s="5">
         <f>SUM(W7:Z7)</f>
         <v>44755</v>
       </c>
-      <c r="AT7" s="5">
+      <c r="AY7" s="5">
         <f>SUM(AA7:AD7)</f>
         <v>48059</v>
       </c>
-      <c r="AU7" s="5">
+      <c r="AZ7" s="5">
         <f>SUM(AE7:AH7)</f>
         <v>57447</v>
       </c>
-      <c r="AV7" s="5">
+      <c r="BA7" s="5">
         <f>SUM(AI7:AL7)</f>
-        <v>75264.2</v>
-      </c>
-      <c r="AW7" s="5">
-        <f>AW4*0.33</f>
-        <v>83598.157500000001</v>
-      </c>
-      <c r="AX7" s="5">
-        <f t="shared" ref="AX7:BF7" si="21">AX4*0.33</f>
-        <v>90286.0101</v>
-      </c>
-      <c r="AY7" s="5">
-        <f t="shared" si="21"/>
-        <v>95703.17070599999</v>
-      </c>
-      <c r="AZ7" s="5">
-        <f t="shared" si="21"/>
-        <v>100488.3292413</v>
-      </c>
-      <c r="BA7" s="5">
-        <f t="shared" si="21"/>
-        <v>104507.862410952</v>
+        <v>74330</v>
       </c>
       <c r="BB7" s="5">
-        <f t="shared" si="21"/>
-        <v>107643.09828328056</v>
+        <f>BB4*0.33</f>
+        <v>82646.751000000004</v>
       </c>
       <c r="BC7" s="5">
-        <f t="shared" si="21"/>
-        <v>110872.39123177897</v>
+        <f t="shared" ref="BC7:BK7" si="19">BC4*0.33</f>
+        <v>89258.491080000007</v>
       </c>
       <c r="BD7" s="5">
-        <f t="shared" si="21"/>
-        <v>113089.83905641455</v>
+        <f t="shared" si="19"/>
+        <v>94614.000544800016</v>
       </c>
       <c r="BE7" s="5">
-        <f t="shared" si="21"/>
-        <v>115351.63583754284</v>
+        <f t="shared" si="19"/>
+        <v>99344.700572040019</v>
       </c>
       <c r="BF7" s="5">
-        <f t="shared" si="21"/>
-        <v>117658.66855429369</v>
+        <f t="shared" si="19"/>
+        <v>103318.48859492163</v>
+      </c>
+      <c r="BG7" s="5">
+        <f t="shared" si="19"/>
+        <v>106418.04325276926</v>
+      </c>
+      <c r="BH7" s="5">
+        <f t="shared" si="19"/>
+        <v>109610.58455035235</v>
+      </c>
+      <c r="BI7" s="5">
+        <f t="shared" si="19"/>
+        <v>111802.79624135938</v>
+      </c>
+      <c r="BJ7" s="5">
+        <f t="shared" si="19"/>
+        <v>114038.85216618657</v>
+      </c>
+      <c r="BK7" s="5">
+        <f t="shared" si="19"/>
+        <v>116319.6292095103</v>
       </c>
     </row>
-    <row r="8" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:63" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="5">
-        <f t="shared" ref="C8:R8" si="22">C6+C7</f>
+        <f t="shared" ref="C8:R8" si="20">C6+C7</f>
         <v>7844</v>
       </c>
       <c r="D8" s="5">
+        <f t="shared" si="20"/>
+        <v>9901</v>
+      </c>
+      <c r="E8" s="5">
+        <f t="shared" si="20"/>
+        <v>8060</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="20"/>
+        <v>8456</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" si="20"/>
+        <v>8278</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="20"/>
+        <v>11064</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="20"/>
+        <v>9269</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="20"/>
+        <v>9742</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="20"/>
+        <v>9905</v>
+      </c>
+      <c r="L8" s="5">
+        <f t="shared" si="20"/>
+        <v>12423</v>
+      </c>
+      <c r="M8" s="5">
+        <f t="shared" si="20"/>
+        <v>10170</v>
+      </c>
+      <c r="N8" s="5">
+        <f t="shared" si="20"/>
+        <v>10412</v>
+      </c>
+      <c r="O8" s="5">
+        <f t="shared" si="20"/>
+        <v>10406</v>
+      </c>
+      <c r="P8" s="5">
+        <f t="shared" si="20"/>
+        <v>12358</v>
+      </c>
+      <c r="Q8" s="5">
+        <f t="shared" si="20"/>
+        <v>10975</v>
+      </c>
+      <c r="R8" s="5">
+        <f t="shared" si="20"/>
+        <v>12339</v>
+      </c>
+      <c r="S8" s="5">
+        <f t="shared" ref="S8:V8" si="21">S6+S7</f>
+        <v>11002</v>
+      </c>
+      <c r="T8" s="5">
+        <f t="shared" si="21"/>
+        <v>14194</v>
+      </c>
+      <c r="U8" s="5">
+        <f t="shared" si="21"/>
+        <v>13045</v>
+      </c>
+      <c r="V8" s="5">
+        <f t="shared" si="21"/>
+        <v>13991</v>
+      </c>
+      <c r="W8" s="5">
+        <f t="shared" ref="W8:X8" si="22">W6+W7</f>
+        <v>13646</v>
+      </c>
+      <c r="X8" s="5">
         <f t="shared" si="22"/>
-        <v>9901</v>
-      </c>
-      <c r="E8" s="5">
-        <f t="shared" si="22"/>
-        <v>8060</v>
-      </c>
-      <c r="F8" s="5">
-        <f t="shared" si="22"/>
-        <v>8456</v>
-      </c>
-      <c r="G8" s="5">
-        <f t="shared" si="22"/>
-        <v>8278</v>
-      </c>
-      <c r="H8" s="5">
-        <f t="shared" si="22"/>
-        <v>11064</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="22"/>
-        <v>9269</v>
-      </c>
-      <c r="J8" s="5">
-        <f t="shared" si="22"/>
-        <v>9742</v>
-      </c>
-      <c r="K8" s="5">
-        <f t="shared" si="22"/>
-        <v>9905</v>
-      </c>
-      <c r="L8" s="5">
-        <f t="shared" si="22"/>
-        <v>12423</v>
-      </c>
-      <c r="M8" s="5">
-        <f t="shared" si="22"/>
-        <v>10170</v>
-      </c>
-      <c r="N8" s="5">
-        <f t="shared" si="22"/>
-        <v>10412</v>
-      </c>
-      <c r="O8" s="5">
-        <f t="shared" si="22"/>
-        <v>10406</v>
-      </c>
-      <c r="P8" s="5">
-        <f t="shared" si="22"/>
-        <v>12358</v>
-      </c>
-      <c r="Q8" s="5">
-        <f t="shared" si="22"/>
-        <v>10975</v>
-      </c>
-      <c r="R8" s="5">
-        <f t="shared" si="22"/>
-        <v>12339</v>
-      </c>
-      <c r="S8" s="5">
-        <f t="shared" ref="S8:V8" si="23">S6+S7</f>
-        <v>11002</v>
-      </c>
-      <c r="T8" s="5">
-        <f t="shared" si="23"/>
-        <v>14194</v>
-      </c>
-      <c r="U8" s="5">
-        <f t="shared" si="23"/>
-        <v>13045</v>
-      </c>
-      <c r="V8" s="5">
-        <f t="shared" si="23"/>
-        <v>13991</v>
-      </c>
-      <c r="W8" s="5">
-        <f t="shared" ref="W8:X8" si="24">W6+W7</f>
-        <v>13646</v>
-      </c>
-      <c r="X8" s="5">
-        <f t="shared" si="24"/>
         <v>18129</v>
       </c>
       <c r="Y8" s="5">
-        <f t="shared" ref="Y8" si="25">Y6+Y7</f>
+        <f t="shared" ref="Y8" si="23">Y6+Y7</f>
         <v>15615</v>
       </c>
       <c r="Z8" s="5">
-        <f t="shared" ref="Z8" si="26">Z6+Z7</f>
+        <f t="shared" ref="Z8" si="24">Z6+Z7</f>
         <v>16429</v>
       </c>
       <c r="AA8" s="5">
-        <f t="shared" ref="AA8" si="27">AA6+AA7</f>
+        <f t="shared" ref="AA8" si="25">AA6+AA7</f>
         <v>15452</v>
       </c>
       <c r="AB8" s="5">
-        <f t="shared" ref="AB8:AC8" si="28">AB6+AB7</f>
+        <f t="shared" ref="AB8:AC8" si="26">AB6+AB7</f>
         <v>17488</v>
       </c>
       <c r="AC8" s="5">
+        <f t="shared" si="26"/>
+        <v>16128</v>
+      </c>
+      <c r="AD8" s="5">
+        <f t="shared" ref="AD8:AE8" si="27">AD6+AD7</f>
+        <v>16795</v>
+      </c>
+      <c r="AE8" s="5">
+        <f t="shared" si="27"/>
+        <v>16302</v>
+      </c>
+      <c r="AF8" s="5">
+        <f t="shared" ref="AF8:AG8" si="28">AF6+AF7</f>
+        <v>16302</v>
+      </c>
+      <c r="AG8" s="5">
         <f t="shared" si="28"/>
-        <v>16128</v>
-      </c>
-      <c r="AD8" s="5">
-        <f t="shared" ref="AD8:AE8" si="29">AD6+AD7</f>
-        <v>16795</v>
-      </c>
-      <c r="AE8" s="5">
+        <v>19623</v>
+      </c>
+      <c r="AH8" s="5">
+        <f t="shared" ref="AH8:AI8" si="29">AH6+AH7</f>
+        <v>19684</v>
+      </c>
+      <c r="AI8" s="5">
         <f t="shared" si="29"/>
-        <v>16302</v>
-      </c>
-      <c r="AF8" s="5">
-        <f t="shared" ref="AF8:AG8" si="30">AF6+AF7</f>
-        <v>16302</v>
-      </c>
-      <c r="AG8" s="5">
+        <v>20099</v>
+      </c>
+      <c r="AJ8" s="5">
+        <f t="shared" ref="AJ8:AL8" si="30">AJ6+AJ7</f>
+        <v>21799</v>
+      </c>
+      <c r="AK8" s="5">
         <f t="shared" si="30"/>
-        <v>19623</v>
-      </c>
-      <c r="AH8" s="5">
-        <f t="shared" ref="AH8:AI8" si="31">AH6+AH7</f>
-        <v>19684</v>
-      </c>
-      <c r="AI8" s="5">
+        <v>21919</v>
+      </c>
+      <c r="AL8" s="5">
+        <f t="shared" si="30"/>
+        <v>24014</v>
+      </c>
+      <c r="AM8" s="5"/>
+      <c r="AN8" s="5"/>
+      <c r="AO8" s="5"/>
+      <c r="AP8" s="5"/>
+      <c r="AQ8" s="5"/>
+      <c r="AS8" s="5">
+        <f t="shared" ref="AS8:AZ8" si="31">AS6+AS7</f>
+        <v>34261</v>
+      </c>
+      <c r="AT8" s="5">
         <f t="shared" si="31"/>
-        <v>20099</v>
-      </c>
-      <c r="AJ8" s="5">
-        <f t="shared" ref="AJ8:AL8" si="32">AJ6+AJ7</f>
-        <v>21799</v>
-      </c>
-      <c r="AK8" s="5">
+        <v>38353</v>
+      </c>
+      <c r="AU8" s="5">
+        <f t="shared" si="31"/>
+        <v>42910</v>
+      </c>
+      <c r="AV8" s="5">
+        <f t="shared" si="31"/>
+        <v>46078</v>
+      </c>
+      <c r="AW8" s="5">
+        <f t="shared" si="31"/>
+        <v>52232</v>
+      </c>
+      <c r="AX8" s="5">
+        <f t="shared" si="31"/>
+        <v>63819</v>
+      </c>
+      <c r="AY8" s="5">
+        <f t="shared" si="31"/>
+        <v>65863</v>
+      </c>
+      <c r="AZ8" s="5">
+        <f t="shared" si="31"/>
+        <v>71911</v>
+      </c>
+      <c r="BA8" s="5">
+        <f t="shared" ref="BA8:BI8" si="32">BA6+BA7</f>
+        <v>87831</v>
+      </c>
+      <c r="BB8" s="5">
         <f t="shared" si="32"/>
-        <v>21919</v>
-      </c>
-      <c r="AL8" s="5">
+        <v>97501.406799999997</v>
+      </c>
+      <c r="BC8" s="5">
         <f t="shared" si="32"/>
-        <v>24512.862599999997</v>
-      </c>
-      <c r="AN8" s="5">
-        <f t="shared" ref="AN8:AU8" si="33">AN6+AN7</f>
-        <v>34261</v>
-      </c>
-      <c r="AO8" s="5">
+        <v>104261.693438</v>
+      </c>
+      <c r="BD8" s="5">
+        <f t="shared" si="32"/>
+        <v>109767.23492638001</v>
+      </c>
+      <c r="BE8" s="5">
+        <f t="shared" si="32"/>
+        <v>114649.46729743583</v>
+      </c>
+      <c r="BF8" s="5">
+        <f t="shared" si="32"/>
+        <v>118776.30298757138</v>
+      </c>
+      <c r="BG8" s="5">
+        <f t="shared" si="32"/>
+        <v>122030.43578934552</v>
+      </c>
+      <c r="BH8" s="5">
+        <f t="shared" si="32"/>
+        <v>125379.10101229436</v>
+      </c>
+      <c r="BI8" s="5">
+        <f t="shared" si="32"/>
+        <v>127728.99786792081</v>
+      </c>
+      <c r="BJ8" s="5">
+        <f t="shared" ref="BJ8:BK8" si="33">BJ6+BJ7</f>
+        <v>130124.31580901361</v>
+      </c>
+      <c r="BK8" s="5">
         <f t="shared" si="33"/>
-        <v>38353</v>
-      </c>
-      <c r="AP8" s="5">
-        <f t="shared" si="33"/>
-        <v>42910</v>
-      </c>
-      <c r="AQ8" s="5">
-        <f t="shared" si="33"/>
-        <v>46078</v>
-      </c>
-      <c r="AR8" s="5">
-        <f t="shared" si="33"/>
-        <v>52232</v>
-      </c>
-      <c r="AS8" s="5">
-        <f t="shared" si="33"/>
-        <v>63819</v>
-      </c>
-      <c r="AT8" s="5">
-        <f t="shared" si="33"/>
-        <v>65863</v>
-      </c>
-      <c r="AU8" s="5">
-        <f t="shared" si="33"/>
-        <v>71911</v>
-      </c>
-      <c r="AV8" s="5">
-        <f t="shared" ref="AV8:BD8" si="34">AV6+AV7</f>
-        <v>88329.862599999993</v>
-      </c>
-      <c r="AW8" s="5">
-        <f t="shared" si="34"/>
-        <v>97511.726509</v>
-      </c>
-      <c r="AX8" s="5">
-        <f t="shared" si="34"/>
-        <v>104338.71479909</v>
-      </c>
-      <c r="AY8" s="5">
-        <f t="shared" si="34"/>
-        <v>109896.40245208089</v>
-      </c>
-      <c r="AZ8" s="5">
-        <f t="shared" si="34"/>
-        <v>114823.49330484172</v>
-      </c>
-      <c r="BA8" s="5">
-        <f t="shared" si="34"/>
-        <v>118986.37811512913</v>
-      </c>
-      <c r="BB8" s="5">
-        <f t="shared" si="34"/>
-        <v>122266.39914449946</v>
-      </c>
-      <c r="BC8" s="5">
-        <f t="shared" si="34"/>
-        <v>125641.92510161006</v>
-      </c>
-      <c r="BD8" s="5">
-        <f t="shared" si="34"/>
-        <v>128007.06826494396</v>
-      </c>
-      <c r="BE8" s="5">
-        <f t="shared" ref="BE8:BF8" si="35">BE6+BE7</f>
-        <v>130418.03733815753</v>
-      </c>
-      <c r="BF8" s="5">
-        <f t="shared" si="35"/>
-        <v>132875.73406991453</v>
+        <v>132565.94748876561</v>
       </c>
     </row>
-    <row r="9" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="7">
-        <f t="shared" ref="C9:R9" si="36">C5-C8</f>
+        <f t="shared" ref="C9:R9" si="34">C5-C8</f>
         <v>13814</v>
       </c>
       <c r="D9" s="7">
+        <f t="shared" si="34"/>
+        <v>15925</v>
+      </c>
+      <c r="E9" s="7">
+        <f t="shared" si="34"/>
+        <v>15152</v>
+      </c>
+      <c r="F9" s="7">
+        <f t="shared" si="34"/>
+        <v>17149</v>
+      </c>
+      <c r="G9" s="7">
+        <f t="shared" si="34"/>
+        <v>16260</v>
+      </c>
+      <c r="H9" s="7">
+        <f t="shared" si="34"/>
+        <v>17854</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="34"/>
+        <v>17550</v>
+      </c>
+      <c r="J9" s="7">
+        <f t="shared" si="34"/>
+        <v>20343</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="34"/>
+        <v>19179</v>
+      </c>
+      <c r="L9" s="7">
+        <f t="shared" si="34"/>
+        <v>20048</v>
+      </c>
+      <c r="M9" s="7">
+        <f t="shared" si="34"/>
+        <v>20401</v>
+      </c>
+      <c r="N9" s="7">
+        <f t="shared" si="34"/>
+        <v>23305</v>
+      </c>
+      <c r="O9" s="7">
+        <f t="shared" si="34"/>
+        <v>22649</v>
+      </c>
+      <c r="P9" s="7">
+        <f t="shared" si="34"/>
+        <v>24548</v>
+      </c>
+      <c r="Q9" s="7">
+        <f t="shared" si="34"/>
+        <v>24046</v>
+      </c>
+      <c r="R9" s="7">
+        <f t="shared" si="34"/>
+        <v>25694</v>
+      </c>
+      <c r="S9" s="7">
+        <f t="shared" ref="S9:V9" si="35">S5-S8</f>
+        <v>26152</v>
+      </c>
+      <c r="T9" s="7">
+        <f t="shared" si="35"/>
+        <v>28882</v>
+      </c>
+      <c r="U9" s="7">
+        <f t="shared" si="35"/>
+        <v>28661</v>
+      </c>
+      <c r="V9" s="7">
+        <f t="shared" si="35"/>
+        <v>32161</v>
+      </c>
+      <c r="W9" s="7">
+        <f t="shared" ref="W9:X9" si="36">W5-W8</f>
+        <v>31671</v>
+      </c>
+      <c r="X9" s="7">
         <f t="shared" si="36"/>
-        <v>15925</v>
-      </c>
-      <c r="E9" s="7">
-        <f t="shared" si="36"/>
-        <v>15152</v>
-      </c>
-      <c r="F9" s="7">
-        <f t="shared" si="36"/>
-        <v>17149</v>
-      </c>
-      <c r="G9" s="7">
-        <f t="shared" si="36"/>
-        <v>16260</v>
-      </c>
-      <c r="H9" s="7">
-        <f t="shared" si="36"/>
-        <v>17854</v>
-      </c>
-      <c r="I9" s="7">
-        <f t="shared" si="36"/>
-        <v>17550</v>
-      </c>
-      <c r="J9" s="7">
-        <f t="shared" si="36"/>
-        <v>20343</v>
-      </c>
-      <c r="K9" s="7">
-        <f t="shared" si="36"/>
-        <v>19179</v>
-      </c>
-      <c r="L9" s="7">
-        <f t="shared" si="36"/>
-        <v>20048</v>
-      </c>
-      <c r="M9" s="7">
-        <f t="shared" si="36"/>
-        <v>20401</v>
-      </c>
-      <c r="N9" s="7">
-        <f t="shared" si="36"/>
-        <v>23305</v>
-      </c>
-      <c r="O9" s="7">
-        <f t="shared" si="36"/>
-        <v>22649</v>
-      </c>
-      <c r="P9" s="7">
-        <f t="shared" si="36"/>
-        <v>24548</v>
-      </c>
-      <c r="Q9" s="7">
-        <f t="shared" si="36"/>
-        <v>24046</v>
-      </c>
-      <c r="R9" s="7">
-        <f t="shared" si="36"/>
-        <v>25694</v>
-      </c>
-      <c r="S9" s="7">
-        <f t="shared" ref="S9:V9" si="37">S5-S8</f>
-        <v>26152</v>
-      </c>
-      <c r="T9" s="7">
-        <f t="shared" si="37"/>
-        <v>28882</v>
-      </c>
-      <c r="U9" s="7">
-        <f t="shared" si="37"/>
-        <v>28661</v>
-      </c>
-      <c r="V9" s="7">
-        <f t="shared" si="37"/>
-        <v>32161</v>
-      </c>
-      <c r="W9" s="7">
-        <f t="shared" ref="W9:X9" si="38">W5-W8</f>
-        <v>31671</v>
-      </c>
-      <c r="X9" s="7">
-        <f t="shared" si="38"/>
         <v>33599</v>
       </c>
       <c r="Y9" s="7">
-        <f t="shared" ref="Y9" si="39">Y5-Y8</f>
+        <f t="shared" ref="Y9" si="37">Y5-Y8</f>
         <v>33745</v>
       </c>
       <c r="Z9" s="7">
-        <f t="shared" ref="Z9" si="40">Z5-Z8</f>
+        <f t="shared" ref="Z9" si="38">Z5-Z8</f>
         <v>35436</v>
       </c>
       <c r="AA9" s="7">
-        <f t="shared" ref="AA9" si="41">AA5-AA8</f>
+        <f t="shared" ref="AA9" si="39">AA5-AA8</f>
         <v>34670</v>
       </c>
       <c r="AB9" s="7">
-        <f t="shared" ref="AB9:AC9" si="42">AB5-AB8</f>
+        <f t="shared" ref="AB9:AC9" si="40">AB5-AB8</f>
         <v>35259</v>
       </c>
       <c r="AC9" s="7">
+        <f t="shared" si="40"/>
+        <v>36729</v>
+      </c>
+      <c r="AD9" s="7">
+        <f t="shared" ref="AD9:AE9" si="41">AD5-AD8</f>
+        <v>39394</v>
+      </c>
+      <c r="AE9" s="7">
+        <f t="shared" si="41"/>
+        <v>40215</v>
+      </c>
+      <c r="AF9" s="7">
+        <f t="shared" ref="AF9:AG9" si="42">AF5-AF8</f>
+        <v>40215</v>
+      </c>
+      <c r="AG9" s="7">
         <f t="shared" si="42"/>
-        <v>36729</v>
-      </c>
-      <c r="AD9" s="7">
-        <f t="shared" ref="AD9:AE9" si="43">AD5-AD8</f>
-        <v>39394</v>
-      </c>
-      <c r="AE9" s="7">
+        <v>42397</v>
+      </c>
+      <c r="AH9" s="7">
+        <f t="shared" ref="AH9:AI9" si="43">AH5-AH8</f>
+        <v>45043</v>
+      </c>
+      <c r="AI9" s="7">
         <f t="shared" si="43"/>
-        <v>40215</v>
-      </c>
-      <c r="AF9" s="7">
-        <f t="shared" ref="AF9:AG9" si="44">AF5-AF8</f>
-        <v>40215</v>
-      </c>
-      <c r="AG9" s="7">
+        <v>45486</v>
+      </c>
+      <c r="AJ9" s="7">
+        <f t="shared" ref="AJ9:AL9" si="44">AJ5-AJ8</f>
+        <v>47833</v>
+      </c>
+      <c r="AK9" s="7">
         <f t="shared" si="44"/>
-        <v>42397</v>
-      </c>
-      <c r="AH9" s="7">
-        <f t="shared" ref="AH9:AI9" si="45">AH5-AH8</f>
-        <v>45043</v>
-      </c>
-      <c r="AI9" s="7">
+        <v>48147</v>
+      </c>
+      <c r="AL9" s="7">
+        <f t="shared" si="44"/>
+        <v>52427</v>
+      </c>
+      <c r="AM9" s="7"/>
+      <c r="AN9" s="7"/>
+      <c r="AO9" s="7"/>
+      <c r="AP9" s="7"/>
+      <c r="AQ9" s="7"/>
+      <c r="AS9" s="7">
+        <f t="shared" ref="AS9:AZ9" si="45">AS5-AS8</f>
+        <v>62040</v>
+      </c>
+      <c r="AT9" s="7">
         <f t="shared" si="45"/>
-        <v>45486</v>
-      </c>
-      <c r="AJ9" s="7">
-        <f t="shared" ref="AJ9:AL9" si="46">AJ5-AJ8</f>
-        <v>47833</v>
-      </c>
-      <c r="AK9" s="7">
+        <v>72007</v>
+      </c>
+      <c r="AU9" s="7">
+        <f t="shared" si="45"/>
+        <v>82933</v>
+      </c>
+      <c r="AV9" s="7">
+        <f t="shared" si="45"/>
+        <v>96937</v>
+      </c>
+      <c r="AW9" s="7">
+        <f t="shared" si="45"/>
+        <v>115856</v>
+      </c>
+      <c r="AX9" s="7">
+        <f t="shared" si="45"/>
+        <v>134451</v>
+      </c>
+      <c r="AY9" s="7">
+        <f t="shared" si="45"/>
+        <v>146052</v>
+      </c>
+      <c r="AZ9" s="7">
+        <f t="shared" si="45"/>
+        <v>167870</v>
+      </c>
+      <c r="BA9" s="7">
+        <f t="shared" ref="BA9:BI9" si="46">BA5-BA8</f>
+        <v>193893</v>
+      </c>
+      <c r="BB9" s="7">
         <f t="shared" si="46"/>
-        <v>48147</v>
-      </c>
-      <c r="AL9" s="7">
+        <v>217528.75319999998</v>
+      </c>
+      <c r="BC9" s="7">
         <f t="shared" si="46"/>
-        <v>50383.967400000009</v>
-      </c>
-      <c r="AN9" s="7">
-        <f t="shared" ref="AN9:AU9" si="47">AN5-AN8</f>
-        <v>62040</v>
-      </c>
-      <c r="AO9" s="7">
+        <v>231449.89716200001</v>
+      </c>
+      <c r="BD9" s="7">
+        <f t="shared" si="46"/>
+        <v>242825.48537962002</v>
+      </c>
+      <c r="BE9" s="7">
+        <f t="shared" si="46"/>
+        <v>252937.54391402422</v>
+      </c>
+      <c r="BF9" s="7">
+        <f t="shared" si="46"/>
+        <v>261517.91475164326</v>
+      </c>
+      <c r="BG9" s="7">
+        <f t="shared" si="46"/>
+        <v>268328.45070877165</v>
+      </c>
+      <c r="BH9" s="7">
+        <f t="shared" si="46"/>
+        <v>275332.95272975968</v>
+      </c>
+      <c r="BI9" s="7">
+        <f t="shared" si="46"/>
+        <v>280311.70927671599</v>
+      </c>
+      <c r="BJ9" s="7">
+        <f t="shared" ref="BJ9:BK9" si="47">BJ5-BJ8</f>
+        <v>285384.76192953496</v>
+      </c>
+      <c r="BK9" s="7">
         <f t="shared" si="47"/>
-        <v>72007</v>
-      </c>
-      <c r="AP9" s="7">
-        <f t="shared" si="47"/>
-        <v>82933</v>
-      </c>
-      <c r="AQ9" s="7">
-        <f t="shared" si="47"/>
-        <v>96937</v>
-      </c>
-      <c r="AR9" s="7">
-        <f t="shared" si="47"/>
-        <v>115856</v>
-      </c>
-      <c r="AS9" s="7">
-        <f t="shared" si="47"/>
-        <v>134451</v>
-      </c>
-      <c r="AT9" s="7">
-        <f t="shared" si="47"/>
-        <v>146052</v>
-      </c>
-      <c r="AU9" s="7">
-        <f t="shared" si="47"/>
-        <v>167870</v>
-      </c>
-      <c r="AV9" s="7">
-        <f t="shared" ref="AV9:BD9" si="48">AV5-AV8</f>
-        <v>191849.96740000002</v>
-      </c>
-      <c r="AW9" s="7">
-        <f t="shared" si="48"/>
-        <v>216309.80179100001</v>
-      </c>
-      <c r="AX9" s="7">
-        <f t="shared" si="48"/>
-        <v>230353.97128390998</v>
-      </c>
-      <c r="AY9" s="7">
-        <f t="shared" si="48"/>
-        <v>241822.90899174908</v>
-      </c>
-      <c r="AZ9" s="7">
-        <f t="shared" si="48"/>
-        <v>252013.39558142659</v>
-      </c>
-      <c r="BA9" s="7">
-        <f t="shared" si="48"/>
-        <v>260654.18231830181</v>
-      </c>
-      <c r="BB9" s="7">
-        <f t="shared" si="48"/>
-        <v>267504.37673635385</v>
-      </c>
-      <c r="BC9" s="7">
-        <f t="shared" si="48"/>
-        <v>274550.38267643237</v>
-      </c>
-      <c r="BD9" s="7">
-        <f t="shared" si="48"/>
-        <v>279546.93202214496</v>
-      </c>
-      <c r="BE9" s="7">
-        <f t="shared" ref="BE9:BF9" si="49">BE5-BE8</f>
-        <v>284638.4677716936</v>
-      </c>
-      <c r="BF9" s="7">
-        <f t="shared" si="49"/>
-        <v>289826.84020732425</v>
+        <v>290553.94382008316</v>
       </c>
     </row>
-    <row r="10" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:63" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>33</v>
       </c>
@@ -3222,87 +3290,91 @@
         <v>8198</v>
       </c>
       <c r="AL10" s="5">
-        <f>AH10*1.07</f>
-        <v>8619.92</v>
-      </c>
-      <c r="AN10" s="5">
+        <v>8829</v>
+      </c>
+      <c r="AM10" s="5"/>
+      <c r="AN10" s="5"/>
+      <c r="AO10" s="5"/>
+      <c r="AP10" s="5"/>
+      <c r="AQ10" s="5"/>
+      <c r="AS10" s="5">
         <f>SUM(C10:F10)</f>
         <v>13037</v>
       </c>
-      <c r="AO10" s="5">
+      <c r="AT10" s="5">
         <f>SUM(G10:J10)</f>
         <v>14726</v>
       </c>
-      <c r="AP10" s="5">
+      <c r="AU10" s="5">
         <f>SUM(K10:N10)</f>
         <v>16876</v>
       </c>
-      <c r="AQ10" s="5">
+      <c r="AV10" s="5">
         <f>SUM(O10:R10)</f>
         <v>19269</v>
       </c>
-      <c r="AR10" s="5">
+      <c r="AW10" s="5">
         <f>SUM(S10:V10)</f>
         <v>20716</v>
       </c>
-      <c r="AS10" s="5">
+      <c r="AX10" s="5">
         <f>SUM(W10:Z10)</f>
         <v>24512</v>
       </c>
-      <c r="AT10" s="5">
+      <c r="AY10" s="5">
         <f>SUM(AA10:AD10)</f>
         <v>27195</v>
       </c>
-      <c r="AU10" s="5">
+      <c r="AZ10" s="5">
         <f>SUM(AE10:AH10)</f>
         <v>28516</v>
       </c>
-      <c r="AV10" s="5">
+      <c r="BA10" s="5">
         <f>SUM(AI10:AL10)</f>
-        <v>32278.92</v>
-      </c>
-      <c r="AW10" s="5">
-        <f>AV10*1.06</f>
-        <v>34215.655200000001</v>
-      </c>
-      <c r="AX10" s="5">
-        <f>AW10*1.04</f>
-        <v>35584.281408000003</v>
-      </c>
-      <c r="AY10" s="5">
-        <f>AX10*1.02</f>
-        <v>36295.96703616</v>
-      </c>
-      <c r="AZ10" s="5">
-        <f t="shared" ref="AZ10:BD10" si="50">AY10*1.01</f>
-        <v>36658.926706521597</v>
-      </c>
-      <c r="BA10" s="5">
-        <f t="shared" si="50"/>
-        <v>37025.515973586815</v>
+        <v>32488</v>
       </c>
       <c r="BB10" s="5">
-        <f t="shared" si="50"/>
-        <v>37395.771133322683</v>
+        <f>BA10*1.06</f>
+        <v>34437.279999999999</v>
       </c>
       <c r="BC10" s="5">
-        <f t="shared" si="50"/>
-        <v>37769.728844655911</v>
+        <f>BB10*1.04</f>
+        <v>35814.771200000003</v>
       </c>
       <c r="BD10" s="5">
-        <f t="shared" si="50"/>
-        <v>38147.426133102468</v>
+        <f>BC10*1.02</f>
+        <v>36531.066624000006</v>
       </c>
       <c r="BE10" s="5">
-        <f t="shared" ref="BE10" si="51">BD10*1.01</f>
-        <v>38528.900394433491</v>
+        <f t="shared" ref="BE10:BI10" si="48">BD10*1.01</f>
+        <v>36896.377290240009</v>
       </c>
       <c r="BF10" s="5">
-        <f t="shared" ref="BF10" si="52">BE10*1.01</f>
-        <v>38914.189398377828</v>
+        <f t="shared" si="48"/>
+        <v>37265.341063142412</v>
+      </c>
+      <c r="BG10" s="5">
+        <f t="shared" si="48"/>
+        <v>37637.994473773833</v>
+      </c>
+      <c r="BH10" s="5">
+        <f t="shared" si="48"/>
+        <v>38014.374418511572</v>
+      </c>
+      <c r="BI10" s="5">
+        <f t="shared" si="48"/>
+        <v>38394.518162696688</v>
+      </c>
+      <c r="BJ10" s="5">
+        <f t="shared" ref="BJ10" si="49">BI10*1.01</f>
+        <v>38778.463344323653</v>
+      </c>
+      <c r="BK10" s="5">
+        <f t="shared" ref="BK10" si="50">BJ10*1.01</f>
+        <v>39166.247977766892</v>
       </c>
     </row>
-    <row r="11" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:63" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>34</v>
       </c>
@@ -3412,87 +3484,91 @@
         <v>6212</v>
       </c>
       <c r="AL11" s="5">
-        <f>AL5*0.1</f>
-        <v>7489.6830000000009</v>
-      </c>
-      <c r="AN11" s="5">
+        <v>7285</v>
+      </c>
+      <c r="AM11" s="5"/>
+      <c r="AN11" s="5"/>
+      <c r="AO11" s="5"/>
+      <c r="AP11" s="5"/>
+      <c r="AQ11" s="5"/>
+      <c r="AS11" s="5">
         <f>SUM(C11:F11)</f>
         <v>15461</v>
       </c>
-      <c r="AO11" s="5">
+      <c r="AT11" s="5">
         <f>SUM(G11:J11)</f>
         <v>17469</v>
       </c>
-      <c r="AP11" s="5">
+      <c r="AU11" s="5">
         <f>SUM(K11:N11)</f>
         <v>18213</v>
       </c>
-      <c r="AQ11" s="5">
+      <c r="AV11" s="5">
         <f>SUM(O11:R11)</f>
         <v>19598</v>
       </c>
-      <c r="AR11" s="5">
+      <c r="AW11" s="5">
         <f>SUM(S11:V11)</f>
         <v>20117</v>
       </c>
-      <c r="AS11" s="5">
+      <c r="AX11" s="5">
         <f>SUM(W11:Z11)</f>
         <v>21825</v>
       </c>
-      <c r="AT11" s="5">
+      <c r="AY11" s="5">
         <f>SUM(AA11:AD11)</f>
         <v>22759</v>
       </c>
-      <c r="AU11" s="5">
+      <c r="AZ11" s="5">
         <f>SUM(AE11:AH11)</f>
         <v>23436</v>
       </c>
-      <c r="AV11" s="5">
+      <c r="BA11" s="5">
         <f>SUM(AI11:AL11)</f>
-        <v>25858.683000000001</v>
-      </c>
-      <c r="AW11" s="5">
-        <f>AV11*1.02</f>
-        <v>26375.856660000001</v>
-      </c>
-      <c r="AX11" s="5">
-        <f t="shared" ref="AX11:BD11" si="53">AW11*1.02</f>
-        <v>26903.3737932</v>
-      </c>
-      <c r="AY11" s="5">
-        <f t="shared" si="53"/>
-        <v>27441.441269064002</v>
-      </c>
-      <c r="AZ11" s="5">
-        <f t="shared" si="53"/>
-        <v>27990.270094445281</v>
-      </c>
-      <c r="BA11" s="5">
-        <f t="shared" si="53"/>
-        <v>28550.075496334186</v>
+        <v>25654</v>
       </c>
       <c r="BB11" s="5">
-        <f t="shared" si="53"/>
-        <v>29121.077006260872</v>
+        <f>BA11*1.02</f>
+        <v>26167.08</v>
       </c>
       <c r="BC11" s="5">
-        <f t="shared" si="53"/>
-        <v>29703.49854638609</v>
+        <f t="shared" ref="BC11:BI11" si="51">BB11*1.02</f>
+        <v>26690.421600000001</v>
       </c>
       <c r="BD11" s="5">
-        <f t="shared" si="53"/>
-        <v>30297.568517313812</v>
+        <f t="shared" si="51"/>
+        <v>27224.230032000003</v>
       </c>
       <c r="BE11" s="5">
-        <f t="shared" ref="BE11" si="54">BD11*1.02</f>
-        <v>30903.519887660088</v>
+        <f t="shared" si="51"/>
+        <v>27768.714632640003</v>
       </c>
       <c r="BF11" s="5">
-        <f t="shared" ref="BF11" si="55">BE11*1.02</f>
-        <v>31521.590285413291</v>
+        <f t="shared" si="51"/>
+        <v>28324.088925292803</v>
+      </c>
+      <c r="BG11" s="5">
+        <f t="shared" si="51"/>
+        <v>28890.570703798658</v>
+      </c>
+      <c r="BH11" s="5">
+        <f t="shared" si="51"/>
+        <v>29468.382117874633</v>
+      </c>
+      <c r="BI11" s="5">
+        <f t="shared" si="51"/>
+        <v>30057.749760232127</v>
+      </c>
+      <c r="BJ11" s="5">
+        <f t="shared" ref="BJ11" si="52">BI11*1.02</f>
+        <v>30658.904755436772</v>
+      </c>
+      <c r="BK11" s="5">
+        <f t="shared" ref="BK11" si="53">BJ11*1.02</f>
+        <v>31272.082850545507</v>
       </c>
     </row>
-    <row r="12" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:63" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>35</v>
       </c>
@@ -3602,312 +3678,321 @@
         <v>1737</v>
       </c>
       <c r="AL12" s="5">
-        <f>AH12*1.06</f>
-        <v>2380.7600000000002</v>
-      </c>
-      <c r="AN12" s="5">
+        <v>1990</v>
+      </c>
+      <c r="AM12" s="5"/>
+      <c r="AN12" s="5"/>
+      <c r="AO12" s="5"/>
+      <c r="AP12" s="5"/>
+      <c r="AQ12" s="5"/>
+      <c r="AS12" s="5">
         <f>SUM(C12:F12)</f>
         <v>4481</v>
       </c>
-      <c r="AO12" s="5">
+      <c r="AT12" s="5">
         <f>SUM(G12:J12)</f>
         <v>4754</v>
       </c>
-      <c r="AP12" s="5">
+      <c r="AU12" s="5">
         <f>SUM(K12:N12)</f>
         <v>4885</v>
       </c>
-      <c r="AQ12" s="5">
+      <c r="AV12" s="5">
         <f>SUM(O12:R12)</f>
         <v>5111</v>
       </c>
-      <c r="AR12" s="5">
+      <c r="AW12" s="5">
         <f>SUM(S12:V12)</f>
         <v>5107</v>
       </c>
-      <c r="AS12" s="5">
+      <c r="AX12" s="5">
         <f>SUM(W12:Z12)</f>
         <v>5900</v>
       </c>
-      <c r="AT12" s="5">
+      <c r="AY12" s="5">
         <f>SUM(AA12:AD12)</f>
         <v>7575</v>
       </c>
-      <c r="AU12" s="5">
+      <c r="AZ12" s="5">
         <f>SUM(AE12:AH12)</f>
         <v>7171</v>
       </c>
-      <c r="AV12" s="5">
+      <c r="BA12" s="5">
         <f>SUM(AI12:AL12)</f>
-        <v>7613.76</v>
-      </c>
-      <c r="AW12" s="5">
-        <f>AV12*1.05</f>
-        <v>7994.4480000000003</v>
-      </c>
-      <c r="AX12" s="5">
-        <f>AW12*1.04</f>
-        <v>8314.2259200000008</v>
-      </c>
-      <c r="AY12" s="5">
-        <f>AX12*1.03</f>
-        <v>8563.6526976000005</v>
-      </c>
-      <c r="AZ12" s="5">
-        <f>AY12*1.02</f>
-        <v>8734.9257515520003</v>
-      </c>
-      <c r="BA12" s="5">
-        <f>AZ12*1.02</f>
-        <v>8909.6242665830396</v>
+        <v>7223</v>
       </c>
       <c r="BB12" s="5">
-        <f>BA12*1.01</f>
-        <v>8998.7205092488693</v>
+        <f>BA12*1.05</f>
+        <v>7584.1500000000005</v>
       </c>
       <c r="BC12" s="5">
-        <f t="shared" ref="BC12:BF12" si="56">BB12*1.01</f>
-        <v>9088.707714341359</v>
+        <f>BB12*1.04</f>
+        <v>7887.5160000000005</v>
       </c>
       <c r="BD12" s="5">
-        <f t="shared" si="56"/>
-        <v>9179.5947914847729</v>
+        <f>BC12*1.03</f>
+        <v>8124.1414800000011</v>
       </c>
       <c r="BE12" s="5">
-        <f t="shared" si="56"/>
-        <v>9271.3907393996215</v>
+        <f>BD12*1.02</f>
+        <v>8286.6243096000017</v>
       </c>
       <c r="BF12" s="5">
-        <f t="shared" si="56"/>
-        <v>9364.1046467936176</v>
+        <f>BE12*1.02</f>
+        <v>8452.3567957920022</v>
+      </c>
+      <c r="BG12" s="5">
+        <f>BF12*1.01</f>
+        <v>8536.8803637499223</v>
+      </c>
+      <c r="BH12" s="5">
+        <f t="shared" ref="BH12:BK12" si="54">BG12*1.01</f>
+        <v>8622.249167387421</v>
+      </c>
+      <c r="BI12" s="5">
+        <f t="shared" si="54"/>
+        <v>8708.4716590612952</v>
+      </c>
+      <c r="BJ12" s="5">
+        <f t="shared" si="54"/>
+        <v>8795.5563756519077</v>
+      </c>
+      <c r="BK12" s="5">
+        <f t="shared" si="54"/>
+        <v>8883.5119394084268</v>
       </c>
     </row>
-    <row r="13" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:R13" si="57">C9-C10-C11-C12</f>
+        <f t="shared" ref="C13:R13" si="55">C9-C10-C11-C12</f>
         <v>6445</v>
       </c>
       <c r="D13" s="7">
+        <f t="shared" si="55"/>
+        <v>7905</v>
+      </c>
+      <c r="E13" s="7">
+        <f t="shared" si="55"/>
+        <v>6723</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="55"/>
+        <v>7988</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="55"/>
+        <v>7708</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="55"/>
+        <v>8679</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="55"/>
+        <v>8292</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="55"/>
+        <v>10379</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="55"/>
+        <v>9955</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="55"/>
+        <v>10258</v>
+      </c>
+      <c r="M13" s="7">
+        <f t="shared" si="55"/>
+        <v>10341</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="55"/>
+        <v>12405</v>
+      </c>
+      <c r="O13" s="7">
+        <f t="shared" si="55"/>
+        <v>12686</v>
+      </c>
+      <c r="P13" s="7">
+        <f t="shared" si="55"/>
+        <v>13891</v>
+      </c>
+      <c r="Q13" s="7">
+        <f t="shared" si="55"/>
+        <v>12975</v>
+      </c>
+      <c r="R13" s="7">
+        <f t="shared" si="55"/>
+        <v>13407</v>
+      </c>
+      <c r="S13" s="7">
+        <f t="shared" ref="S13:V13" si="56">S9-S10-S11-S12</f>
+        <v>15876</v>
+      </c>
+      <c r="T13" s="7">
+        <f t="shared" si="56"/>
+        <v>17897</v>
+      </c>
+      <c r="U13" s="7">
+        <f t="shared" si="56"/>
+        <v>17048</v>
+      </c>
+      <c r="V13" s="7">
+        <f t="shared" si="56"/>
+        <v>19095</v>
+      </c>
+      <c r="W13" s="7">
+        <f t="shared" ref="W13:X13" si="57">W9-W10-W11-W12</f>
+        <v>20238</v>
+      </c>
+      <c r="X13" s="7">
         <f t="shared" si="57"/>
-        <v>7905</v>
-      </c>
-      <c r="E13" s="7">
-        <f t="shared" si="57"/>
-        <v>6723</v>
-      </c>
-      <c r="F13" s="7">
-        <f t="shared" si="57"/>
-        <v>7988</v>
-      </c>
-      <c r="G13" s="7">
-        <f t="shared" si="57"/>
-        <v>7708</v>
-      </c>
-      <c r="H13" s="7">
-        <f t="shared" si="57"/>
-        <v>8679</v>
-      </c>
-      <c r="I13" s="7">
-        <f t="shared" si="57"/>
-        <v>8292</v>
-      </c>
-      <c r="J13" s="7">
-        <f t="shared" si="57"/>
-        <v>10379</v>
-      </c>
-      <c r="K13" s="7">
-        <f t="shared" si="57"/>
-        <v>9955</v>
-      </c>
-      <c r="L13" s="7">
-        <f t="shared" si="57"/>
-        <v>10258</v>
-      </c>
-      <c r="M13" s="7">
-        <f t="shared" si="57"/>
-        <v>10341</v>
-      </c>
-      <c r="N13" s="7">
-        <f t="shared" si="57"/>
-        <v>12405</v>
-      </c>
-      <c r="O13" s="7">
-        <f t="shared" si="57"/>
-        <v>12686</v>
-      </c>
-      <c r="P13" s="7">
-        <f t="shared" si="57"/>
-        <v>13891</v>
-      </c>
-      <c r="Q13" s="7">
-        <f t="shared" si="57"/>
-        <v>12975</v>
-      </c>
-      <c r="R13" s="7">
-        <f t="shared" si="57"/>
-        <v>13407</v>
-      </c>
-      <c r="S13" s="7">
-        <f t="shared" ref="S13:V13" si="58">S9-S10-S11-S12</f>
-        <v>15876</v>
-      </c>
-      <c r="T13" s="7">
-        <f t="shared" si="58"/>
-        <v>17897</v>
-      </c>
-      <c r="U13" s="7">
-        <f t="shared" si="58"/>
-        <v>17048</v>
-      </c>
-      <c r="V13" s="7">
-        <f t="shared" si="58"/>
-        <v>19095</v>
-      </c>
-      <c r="W13" s="7">
-        <f t="shared" ref="W13:X13" si="59">W9-W10-W11-W12</f>
-        <v>20238</v>
-      </c>
-      <c r="X13" s="7">
-        <f t="shared" si="59"/>
         <v>21078</v>
       </c>
       <c r="Y13" s="7">
-        <f t="shared" ref="Y13" si="60">Y9-Y10-Y11-Y12</f>
+        <f t="shared" ref="Y13" si="58">Y9-Y10-Y11-Y12</f>
         <v>20364</v>
       </c>
       <c r="Z13" s="7">
-        <f t="shared" ref="Z13" si="61">Z9-Z10-Z11-Z12</f>
+        <f t="shared" ref="Z13" si="59">Z9-Z10-Z11-Z12</f>
         <v>20534</v>
       </c>
       <c r="AA13" s="7">
-        <f t="shared" ref="AA13" si="62">AA9-AA10-AA11-AA12</f>
+        <f t="shared" ref="AA13" si="60">AA9-AA10-AA11-AA12</f>
         <v>21518</v>
       </c>
       <c r="AB13" s="7">
-        <f t="shared" ref="AB13:AC13" si="63">AB9-AB10-AB11-AB12</f>
+        <f t="shared" ref="AB13:AC13" si="61">AB9-AB10-AB11-AB12</f>
         <v>20399</v>
       </c>
       <c r="AC13" s="7">
+        <f t="shared" si="61"/>
+        <v>22352</v>
+      </c>
+      <c r="AD13" s="7">
+        <f t="shared" ref="AD13:AE13" si="62">AD9-AD10-AD11-AD12</f>
+        <v>24254</v>
+      </c>
+      <c r="AE13" s="7">
+        <f t="shared" si="62"/>
+        <v>26895</v>
+      </c>
+      <c r="AF13" s="7">
+        <f t="shared" ref="AF13:AG13" si="63">AF9-AF10-AF11-AF12</f>
+        <v>26895</v>
+      </c>
+      <c r="AG13" s="7">
         <f t="shared" si="63"/>
-        <v>22352</v>
-      </c>
-      <c r="AD13" s="7">
-        <f t="shared" ref="AD13:AE13" si="64">AD9-AD10-AD11-AD12</f>
-        <v>24254</v>
-      </c>
-      <c r="AE13" s="7">
+        <v>27032</v>
+      </c>
+      <c r="AH13" s="7">
+        <f t="shared" ref="AH13:AL13" si="64">AH9-AH10-AH11-AH12</f>
+        <v>27925</v>
+      </c>
+      <c r="AI13" s="7">
         <f t="shared" si="64"/>
-        <v>26895</v>
-      </c>
-      <c r="AF13" s="7">
-        <f t="shared" ref="AF13:AG13" si="65">AF9-AF10-AF11-AF12</f>
-        <v>26895</v>
-      </c>
-      <c r="AG13" s="7">
+        <v>30552</v>
+      </c>
+      <c r="AJ13" s="7">
+        <f t="shared" si="64"/>
+        <v>31653</v>
+      </c>
+      <c r="AK13" s="7">
+        <f t="shared" si="64"/>
+        <v>32000</v>
+      </c>
+      <c r="AL13" s="7">
+        <f t="shared" si="64"/>
+        <v>34323</v>
+      </c>
+      <c r="AM13" s="7"/>
+      <c r="AN13" s="7"/>
+      <c r="AO13" s="7"/>
+      <c r="AP13" s="7"/>
+      <c r="AQ13" s="7"/>
+      <c r="AS13" s="7">
+        <f>AS9-AS10-AS11-AS12</f>
+        <v>29061</v>
+      </c>
+      <c r="AT13" s="7">
+        <f>AT9-AT10-AT11-AT12</f>
+        <v>35058</v>
+      </c>
+      <c r="AU13" s="7">
+        <f>AU9-AU10-AU11-AU12</f>
+        <v>42959</v>
+      </c>
+      <c r="AV13" s="7">
+        <f>AV9-AV10-AV11-AV12</f>
+        <v>52959</v>
+      </c>
+      <c r="AW13" s="7">
+        <f t="shared" ref="AW13:BF13" si="65">AW9-AW10-AW11-AW12</f>
+        <v>69916</v>
+      </c>
+      <c r="AX13" s="7">
+        <f t="shared" ref="AX13:AY13" si="66">AX9-AX10-AX11-AX12</f>
+        <v>82214</v>
+      </c>
+      <c r="AY13" s="7">
+        <f t="shared" si="66"/>
+        <v>88523</v>
+      </c>
+      <c r="AZ13" s="7">
+        <f t="shared" ref="AZ13" si="67">AZ9-AZ10-AZ11-AZ12</f>
+        <v>108747</v>
+      </c>
+      <c r="BA13" s="7">
         <f t="shared" si="65"/>
-        <v>27032</v>
-      </c>
-      <c r="AH13" s="7">
-        <f t="shared" ref="AH13:AL13" si="66">AH9-AH10-AH11-AH12</f>
-        <v>27925</v>
-      </c>
-      <c r="AI13" s="7">
-        <f t="shared" si="66"/>
-        <v>30552</v>
-      </c>
-      <c r="AJ13" s="7">
-        <f t="shared" si="66"/>
-        <v>31653</v>
-      </c>
-      <c r="AK13" s="7">
-        <f t="shared" si="66"/>
-        <v>32000</v>
-      </c>
-      <c r="AL13" s="7">
-        <f t="shared" si="66"/>
-        <v>31893.604400000004</v>
-      </c>
-      <c r="AN13" s="7">
-        <f>AN9-AN10-AN11-AN12</f>
-        <v>29061</v>
-      </c>
-      <c r="AO13" s="7">
-        <f>AO9-AO10-AO11-AO12</f>
-        <v>35058</v>
-      </c>
-      <c r="AP13" s="7">
-        <f>AP9-AP10-AP11-AP12</f>
-        <v>42959</v>
-      </c>
-      <c r="AQ13" s="7">
-        <f>AQ9-AQ10-AQ11-AQ12</f>
-        <v>52959</v>
-      </c>
-      <c r="AR13" s="7">
-        <f t="shared" ref="AR13:BA13" si="67">AR9-AR10-AR11-AR12</f>
-        <v>69916</v>
-      </c>
-      <c r="AS13" s="7">
-        <f t="shared" ref="AS13:AT13" si="68">AS9-AS10-AS11-AS12</f>
-        <v>82214</v>
-      </c>
-      <c r="AT13" s="7">
+        <v>128528</v>
+      </c>
+      <c r="BB13" s="7">
+        <f t="shared" si="65"/>
+        <v>149340.2432</v>
+      </c>
+      <c r="BC13" s="7">
+        <f t="shared" si="65"/>
+        <v>161057.18836199999</v>
+      </c>
+      <c r="BD13" s="7">
+        <f t="shared" si="65"/>
+        <v>170946.04724362004</v>
+      </c>
+      <c r="BE13" s="7">
+        <f t="shared" si="65"/>
+        <v>179985.82768154421</v>
+      </c>
+      <c r="BF13" s="7">
+        <f t="shared" si="65"/>
+        <v>187476.12796741605</v>
+      </c>
+      <c r="BG13" s="7">
+        <f t="shared" ref="BG13:BI13" si="68">BG9-BG10-BG11-BG12</f>
+        <v>193263.00516744924</v>
+      </c>
+      <c r="BH13" s="7">
         <f t="shared" si="68"/>
-        <v>88523</v>
-      </c>
-      <c r="AU13" s="7">
-        <f t="shared" ref="AU13" si="69">AU9-AU10-AU11-AU12</f>
-        <v>108747</v>
-      </c>
-      <c r="AV13" s="7">
-        <f t="shared" si="67"/>
-        <v>126098.60440000005</v>
-      </c>
-      <c r="AW13" s="7">
-        <f t="shared" si="67"/>
-        <v>147723.841931</v>
-      </c>
-      <c r="AX13" s="7">
-        <f t="shared" si="67"/>
-        <v>159552.09016270997</v>
-      </c>
-      <c r="AY13" s="7">
-        <f t="shared" si="67"/>
-        <v>169521.84798892509</v>
-      </c>
-      <c r="AZ13" s="7">
-        <f t="shared" si="67"/>
-        <v>178629.27302890772</v>
-      </c>
-      <c r="BA13" s="7">
-        <f t="shared" si="67"/>
-        <v>186168.96658179778</v>
-      </c>
-      <c r="BB13" s="7">
-        <f t="shared" ref="BB13:BD13" si="70">BB9-BB10-BB11-BB12</f>
-        <v>191988.80808752144</v>
-      </c>
-      <c r="BC13" s="7">
-        <f t="shared" si="70"/>
-        <v>197988.44757104904</v>
-      </c>
-      <c r="BD13" s="7">
-        <f t="shared" si="70"/>
-        <v>201922.34258024392</v>
-      </c>
-      <c r="BE13" s="7">
-        <f t="shared" ref="BE13:BF13" si="71">BE9-BE10-BE11-BE12</f>
-        <v>205934.6567502004</v>
-      </c>
-      <c r="BF13" s="7">
-        <f t="shared" si="71"/>
-        <v>210026.95587673949</v>
+        <v>199227.94702598604</v>
+      </c>
+      <c r="BI13" s="7">
+        <f t="shared" si="68"/>
+        <v>203150.96969472588</v>
+      </c>
+      <c r="BJ13" s="7">
+        <f t="shared" ref="BJ13:BK13" si="69">BJ9-BJ10-BJ11-BJ12</f>
+        <v>207151.83745412261</v>
+      </c>
+      <c r="BK13" s="7">
+        <f t="shared" si="69"/>
+        <v>211232.10105236233</v>
       </c>
     </row>
-    <row r="14" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:63" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>37</v>
       </c>
@@ -4018,311 +4103,321 @@
         <v>623</v>
       </c>
       <c r="AL14" s="5">
-        <v>200</v>
-      </c>
-      <c r="AN14" s="5">
+        <v>1707</v>
+      </c>
+      <c r="AM14" s="5"/>
+      <c r="AN14" s="5"/>
+      <c r="AO14" s="5"/>
+      <c r="AP14" s="5"/>
+      <c r="AQ14" s="5"/>
+      <c r="AS14" s="5">
         <f>SUM(C14:F14)</f>
         <v>-570</v>
       </c>
-      <c r="AO14" s="5">
+      <c r="AT14" s="5">
         <f>SUM(G14:J14)</f>
         <v>-1416</v>
       </c>
-      <c r="AP14" s="5">
+      <c r="AU14" s="5">
         <f>SUM(K14:N14)</f>
         <v>-729</v>
       </c>
-      <c r="AQ14" s="5">
+      <c r="AV14" s="5">
         <f>SUM(O14:R14)</f>
         <v>-77</v>
       </c>
-      <c r="AR14" s="5">
+      <c r="AW14" s="5">
         <f>SUM(S14:V14)</f>
         <v>-1186</v>
       </c>
-      <c r="AS14" s="5">
+      <c r="AX14" s="5">
         <f>SUM(W14:Z14)</f>
         <v>-333</v>
       </c>
-      <c r="AT14" s="5">
+      <c r="AY14" s="5">
         <f>SUM(AA14:AD14)</f>
         <v>-788</v>
       </c>
-      <c r="AU14" s="5">
+      <c r="AZ14" s="5">
         <f>SUM(AE14:AH14)</f>
         <v>403</v>
       </c>
-      <c r="AV14" s="5">
+      <c r="BA14" s="5">
         <f>SUM(AI14:AL14)</f>
-        <v>3394</v>
-      </c>
-      <c r="AW14" s="5">
-        <f t="shared" ref="AW14:BD14" si="72">AV14*1.01</f>
-        <v>3427.94</v>
-      </c>
-      <c r="AX14" s="5">
-        <f t="shared" si="72"/>
-        <v>3462.2194</v>
-      </c>
-      <c r="AY14" s="5">
-        <f t="shared" si="72"/>
-        <v>3496.841594</v>
-      </c>
-      <c r="AZ14" s="5">
-        <f t="shared" si="72"/>
-        <v>3531.8100099399999</v>
-      </c>
-      <c r="BA14" s="5">
-        <f t="shared" si="72"/>
-        <v>3567.1281100393999</v>
+        <v>4901</v>
       </c>
       <c r="BB14" s="5">
-        <f t="shared" si="72"/>
-        <v>3602.7993911397939</v>
+        <f t="shared" ref="BB14:BI14" si="70">BA14*1.01</f>
+        <v>4950.01</v>
       </c>
       <c r="BC14" s="5">
-        <f t="shared" si="72"/>
-        <v>3638.8273850511919</v>
+        <f t="shared" si="70"/>
+        <v>4999.5101000000004</v>
       </c>
       <c r="BD14" s="5">
-        <f t="shared" si="72"/>
-        <v>3675.215658901704</v>
+        <f t="shared" si="70"/>
+        <v>5049.5052010000009</v>
       </c>
       <c r="BE14" s="5">
-        <f t="shared" ref="BE14" si="73">BD14*1.01</f>
-        <v>3711.967815490721</v>
+        <f t="shared" si="70"/>
+        <v>5100.000253010001</v>
       </c>
       <c r="BF14" s="5">
-        <f t="shared" ref="BF14" si="74">BE14*1.01</f>
-        <v>3749.0874936456285</v>
+        <f t="shared" si="70"/>
+        <v>5151.0002555401006</v>
+      </c>
+      <c r="BG14" s="5">
+        <f t="shared" si="70"/>
+        <v>5202.5102580955017</v>
+      </c>
+      <c r="BH14" s="5">
+        <f t="shared" si="70"/>
+        <v>5254.5353606764565</v>
+      </c>
+      <c r="BI14" s="5">
+        <f t="shared" si="70"/>
+        <v>5307.0807142832209</v>
+      </c>
+      <c r="BJ14" s="5">
+        <f t="shared" ref="BJ14" si="71">BI14*1.01</f>
+        <v>5360.1515214260535</v>
+      </c>
+      <c r="BK14" s="5">
+        <f t="shared" ref="BK14" si="72">BJ14*1.01</f>
+        <v>5413.7530366403143</v>
       </c>
     </row>
-    <row r="15" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:R15" si="75">C13-C14</f>
+        <f t="shared" ref="C15:R15" si="73">C13-C14</f>
         <v>6557</v>
       </c>
       <c r="D15" s="7">
+        <f t="shared" si="73"/>
+        <v>8022</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="73"/>
+        <v>7094</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="73"/>
+        <v>7958</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="73"/>
+        <v>7984</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="73"/>
+        <v>9169</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="73"/>
+        <v>8641</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="73"/>
+        <v>10680</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="73"/>
+        <v>10221</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="73"/>
+        <v>10385</v>
+      </c>
+      <c r="M15" s="7">
+        <f t="shared" si="73"/>
+        <v>10486</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="73"/>
+        <v>12596</v>
+      </c>
+      <c r="O15" s="7">
+        <f t="shared" si="73"/>
+        <v>12686</v>
+      </c>
+      <c r="P15" s="7">
+        <f t="shared" si="73"/>
+        <v>14085</v>
+      </c>
+      <c r="Q15" s="7">
+        <f t="shared" si="73"/>
+        <v>12843</v>
+      </c>
+      <c r="R15" s="7">
+        <f t="shared" si="73"/>
+        <v>13422</v>
+      </c>
+      <c r="S15" s="7">
+        <f t="shared" ref="S15:V15" si="74">S13-S14</f>
+        <v>16124</v>
+      </c>
+      <c r="T15" s="7">
+        <f t="shared" si="74"/>
+        <v>18337</v>
+      </c>
+      <c r="U15" s="7">
+        <f t="shared" si="74"/>
+        <v>17236</v>
+      </c>
+      <c r="V15" s="7">
+        <f t="shared" si="74"/>
+        <v>19405</v>
+      </c>
+      <c r="W15" s="7">
+        <f t="shared" ref="W15:X15" si="75">W13-W14</f>
+        <v>20524</v>
+      </c>
+      <c r="X15" s="7">
         <f t="shared" si="75"/>
-        <v>8022</v>
-      </c>
-      <c r="E15" s="7">
-        <f t="shared" si="75"/>
-        <v>7094</v>
-      </c>
-      <c r="F15" s="7">
-        <f t="shared" si="75"/>
-        <v>7958</v>
-      </c>
-      <c r="G15" s="7">
-        <f t="shared" si="75"/>
-        <v>7984</v>
-      </c>
-      <c r="H15" s="7">
-        <f t="shared" si="75"/>
-        <v>9169</v>
-      </c>
-      <c r="I15" s="7">
-        <f t="shared" si="75"/>
-        <v>8641</v>
-      </c>
-      <c r="J15" s="7">
-        <f t="shared" si="75"/>
-        <v>10680</v>
-      </c>
-      <c r="K15" s="7">
-        <f t="shared" si="75"/>
-        <v>10221</v>
-      </c>
-      <c r="L15" s="7">
-        <f t="shared" si="75"/>
-        <v>10385</v>
-      </c>
-      <c r="M15" s="7">
-        <f t="shared" si="75"/>
-        <v>10486</v>
-      </c>
-      <c r="N15" s="7">
-        <f t="shared" si="75"/>
-        <v>12596</v>
-      </c>
-      <c r="O15" s="7">
-        <f t="shared" si="75"/>
-        <v>12686</v>
-      </c>
-      <c r="P15" s="7">
-        <f t="shared" si="75"/>
-        <v>14085</v>
-      </c>
-      <c r="Q15" s="7">
-        <f t="shared" si="75"/>
-        <v>12843</v>
-      </c>
-      <c r="R15" s="7">
-        <f t="shared" si="75"/>
-        <v>13422</v>
-      </c>
-      <c r="S15" s="7">
-        <f t="shared" ref="S15:V15" si="76">S13-S14</f>
-        <v>16124</v>
-      </c>
-      <c r="T15" s="7">
-        <f t="shared" si="76"/>
-        <v>18337</v>
-      </c>
-      <c r="U15" s="7">
-        <f t="shared" si="76"/>
-        <v>17236</v>
-      </c>
-      <c r="V15" s="7">
-        <f t="shared" si="76"/>
-        <v>19405</v>
-      </c>
-      <c r="W15" s="7">
-        <f t="shared" ref="W15:X15" si="77">W13-W14</f>
-        <v>20524</v>
-      </c>
-      <c r="X15" s="7">
-        <f t="shared" si="77"/>
         <v>21346</v>
       </c>
       <c r="Y15" s="7">
-        <f t="shared" ref="Y15" si="78">Y13-Y14</f>
+        <f t="shared" ref="Y15" si="76">Y13-Y14</f>
         <v>20190</v>
       </c>
       <c r="Z15" s="7">
-        <f t="shared" ref="Z15" si="79">Z13-Z14</f>
+        <f t="shared" ref="Z15" si="77">Z13-Z14</f>
         <v>20487</v>
       </c>
       <c r="AA15" s="7">
-        <f t="shared" ref="AA15" si="80">AA13-AA14</f>
+        <f t="shared" ref="AA15" si="78">AA13-AA14</f>
         <v>21572</v>
       </c>
       <c r="AB15" s="7">
-        <f t="shared" ref="AB15:AC15" si="81">AB13-AB14</f>
+        <f t="shared" ref="AB15:AC15" si="79">AB13-AB14</f>
         <v>20339</v>
       </c>
       <c r="AC15" s="7">
+        <f t="shared" si="79"/>
+        <v>22673</v>
+      </c>
+      <c r="AD15" s="7">
+        <f t="shared" ref="AD15:AE15" si="80">AD13-AD14</f>
+        <v>24727</v>
+      </c>
+      <c r="AE15" s="7">
+        <f t="shared" si="80"/>
+        <v>27284</v>
+      </c>
+      <c r="AF15" s="7">
+        <f t="shared" ref="AF15:AG15" si="81">AF13-AF14</f>
+        <v>27284</v>
+      </c>
+      <c r="AG15" s="7">
         <f t="shared" si="81"/>
-        <v>22673</v>
-      </c>
-      <c r="AD15" s="7">
-        <f t="shared" ref="AD15:AE15" si="82">AD13-AD14</f>
-        <v>24727</v>
-      </c>
-      <c r="AE15" s="7">
+        <v>26526</v>
+      </c>
+      <c r="AH15" s="7">
+        <f t="shared" ref="AH15:AL15" si="82">AH13-AH14</f>
+        <v>27250</v>
+      </c>
+      <c r="AI15" s="7">
         <f t="shared" si="82"/>
-        <v>27284</v>
-      </c>
-      <c r="AF15" s="7">
-        <f t="shared" ref="AF15:AG15" si="83">AF13-AF14</f>
-        <v>27284</v>
-      </c>
-      <c r="AG15" s="7">
+        <v>30269</v>
+      </c>
+      <c r="AJ15" s="7">
+        <f t="shared" si="82"/>
+        <v>29365</v>
+      </c>
+      <c r="AK15" s="7">
+        <f t="shared" si="82"/>
+        <v>31377</v>
+      </c>
+      <c r="AL15" s="7">
+        <f t="shared" si="82"/>
+        <v>32616</v>
+      </c>
+      <c r="AM15" s="7"/>
+      <c r="AN15" s="7"/>
+      <c r="AO15" s="7"/>
+      <c r="AP15" s="7"/>
+      <c r="AQ15" s="7"/>
+      <c r="AS15" s="7">
+        <f>AS13-AS14</f>
+        <v>29631</v>
+      </c>
+      <c r="AT15" s="7">
+        <f>AT13-AT14</f>
+        <v>36474</v>
+      </c>
+      <c r="AU15" s="7">
+        <f>AU13-AU14</f>
+        <v>43688</v>
+      </c>
+      <c r="AV15" s="7">
+        <f>AV13-AV14</f>
+        <v>53036</v>
+      </c>
+      <c r="AW15" s="7">
+        <f t="shared" ref="AW15:BF15" si="83">AW13-AW14</f>
+        <v>71102</v>
+      </c>
+      <c r="AX15" s="7">
+        <f t="shared" ref="AX15:AY15" si="84">AX13-AX14</f>
+        <v>82547</v>
+      </c>
+      <c r="AY15" s="7">
+        <f t="shared" si="84"/>
+        <v>89311</v>
+      </c>
+      <c r="AZ15" s="7">
+        <f t="shared" ref="AZ15" si="85">AZ13-AZ14</f>
+        <v>108344</v>
+      </c>
+      <c r="BA15" s="7">
         <f t="shared" si="83"/>
-        <v>26526</v>
-      </c>
-      <c r="AH15" s="7">
-        <f t="shared" ref="AH15:AL15" si="84">AH13-AH14</f>
-        <v>27250</v>
-      </c>
-      <c r="AI15" s="7">
-        <f t="shared" si="84"/>
-        <v>30269</v>
-      </c>
-      <c r="AJ15" s="7">
-        <f t="shared" si="84"/>
-        <v>29365</v>
-      </c>
-      <c r="AK15" s="7">
-        <f t="shared" si="84"/>
-        <v>31377</v>
-      </c>
-      <c r="AL15" s="7">
-        <f t="shared" si="84"/>
-        <v>31693.604400000004</v>
-      </c>
-      <c r="AN15" s="7">
-        <f>AN13-AN14</f>
-        <v>29631</v>
-      </c>
-      <c r="AO15" s="7">
-        <f>AO13-AO14</f>
-        <v>36474</v>
-      </c>
-      <c r="AP15" s="7">
-        <f>AP13-AP14</f>
-        <v>43688</v>
-      </c>
-      <c r="AQ15" s="7">
-        <f>AQ13-AQ14</f>
-        <v>53036</v>
-      </c>
-      <c r="AR15" s="7">
-        <f t="shared" ref="AR15:BA15" si="85">AR13-AR14</f>
-        <v>71102</v>
-      </c>
-      <c r="AS15" s="7">
-        <f t="shared" ref="AS15:AT15" si="86">AS13-AS14</f>
-        <v>82547</v>
-      </c>
-      <c r="AT15" s="7">
+        <v>123627</v>
+      </c>
+      <c r="BB15" s="7">
+        <f t="shared" si="83"/>
+        <v>144390.23319999999</v>
+      </c>
+      <c r="BC15" s="7">
+        <f t="shared" si="83"/>
+        <v>156057.67826199997</v>
+      </c>
+      <c r="BD15" s="7">
+        <f t="shared" si="83"/>
+        <v>165896.54204262004</v>
+      </c>
+      <c r="BE15" s="7">
+        <f t="shared" si="83"/>
+        <v>174885.82742853422</v>
+      </c>
+      <c r="BF15" s="7">
+        <f t="shared" si="83"/>
+        <v>182325.12771187595</v>
+      </c>
+      <c r="BG15" s="7">
+        <f t="shared" ref="BG15:BI15" si="86">BG13-BG14</f>
+        <v>188060.49490935373</v>
+      </c>
+      <c r="BH15" s="7">
         <f t="shared" si="86"/>
-        <v>89311</v>
-      </c>
-      <c r="AU15" s="7">
-        <f t="shared" ref="AU15" si="87">AU13-AU14</f>
-        <v>108344</v>
-      </c>
-      <c r="AV15" s="7">
-        <f t="shared" si="85"/>
-        <v>122704.60440000005</v>
-      </c>
-      <c r="AW15" s="7">
-        <f t="shared" si="85"/>
-        <v>144295.901931</v>
-      </c>
-      <c r="AX15" s="7">
-        <f t="shared" si="85"/>
-        <v>156089.87076270996</v>
-      </c>
-      <c r="AY15" s="7">
-        <f t="shared" si="85"/>
-        <v>166025.00639492509</v>
-      </c>
-      <c r="AZ15" s="7">
-        <f t="shared" si="85"/>
-        <v>175097.46301896771</v>
-      </c>
-      <c r="BA15" s="7">
-        <f t="shared" si="85"/>
-        <v>182601.83847175838</v>
-      </c>
-      <c r="BB15" s="7">
-        <f t="shared" ref="BB15:BD15" si="88">BB13-BB14</f>
-        <v>188386.00869638164</v>
-      </c>
-      <c r="BC15" s="7">
-        <f t="shared" si="88"/>
-        <v>194349.62018599783</v>
-      </c>
-      <c r="BD15" s="7">
-        <f t="shared" si="88"/>
-        <v>198247.12692134222</v>
-      </c>
-      <c r="BE15" s="7">
-        <f t="shared" ref="BE15:BF15" si="89">BE13-BE14</f>
-        <v>202222.68893470967</v>
-      </c>
-      <c r="BF15" s="7">
-        <f t="shared" si="89"/>
-        <v>206277.86838309385</v>
+        <v>193973.41166530957</v>
+      </c>
+      <c r="BI15" s="7">
+        <f t="shared" si="86"/>
+        <v>197843.88898044266</v>
+      </c>
+      <c r="BJ15" s="7">
+        <f t="shared" ref="BJ15:BK15" si="87">BJ13-BJ14</f>
+        <v>201791.68593269656</v>
+      </c>
+      <c r="BK15" s="7">
+        <f t="shared" si="87"/>
+        <v>205818.348015722</v>
       </c>
     </row>
-    <row r="16" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:63" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>39</v>
       </c>
@@ -4433,796 +4528,805 @@
         <v>5553</v>
       </c>
       <c r="AL16" s="5">
-        <f t="shared" ref="AL16" si="90">AL15*0.19</f>
-        <v>6021.7848360000007</v>
-      </c>
-      <c r="AN16" s="5">
+        <v>5383</v>
+      </c>
+      <c r="AM16" s="5"/>
+      <c r="AN16" s="5"/>
+      <c r="AO16" s="5"/>
+      <c r="AP16" s="5"/>
+      <c r="AQ16" s="5"/>
+      <c r="AS16" s="5">
         <f>SUM(C16:F16)</f>
         <v>4412</v>
       </c>
-      <c r="AO16" s="5">
+      <c r="AT16" s="5">
         <f>SUM(G16:J16)-13800</f>
         <v>6103</v>
       </c>
-      <c r="AP16" s="5">
+      <c r="AU16" s="5">
         <f>SUM(K16:N16)</f>
         <v>4448</v>
       </c>
-      <c r="AQ16" s="5">
+      <c r="AV16" s="5">
         <f>SUM(O16:R16)</f>
         <v>8755</v>
       </c>
-      <c r="AR16" s="5">
+      <c r="AW16" s="5">
         <f>SUM(S16:V16)</f>
         <v>9831</v>
       </c>
-      <c r="AS16" s="5">
+      <c r="AX16" s="5">
         <f>SUM(W16:Z16)</f>
         <v>10978</v>
       </c>
-      <c r="AT16" s="5">
+      <c r="AY16" s="5">
         <f>SUM(AA16:AD16)</f>
         <v>16950</v>
       </c>
-      <c r="AU16" s="5">
+      <c r="AZ16" s="5">
         <f>SUM(AE16:AH16)</f>
         <v>19856</v>
       </c>
-      <c r="AV16" s="5">
+      <c r="BA16" s="5">
         <f>SUM(AI16:AL16)</f>
-        <v>22433.784835999999</v>
-      </c>
-      <c r="AW16" s="5">
-        <f t="shared" ref="AW16:BD16" si="91">AW15*0.19</f>
-        <v>27416.22136689</v>
-      </c>
-      <c r="AX16" s="5">
-        <f t="shared" si="91"/>
-        <v>29657.075444914895</v>
-      </c>
-      <c r="AY16" s="5">
-        <f t="shared" si="91"/>
-        <v>31544.751215035769</v>
-      </c>
-      <c r="AZ16" s="5">
-        <f t="shared" si="91"/>
-        <v>33268.517973603863</v>
-      </c>
-      <c r="BA16" s="5">
-        <f t="shared" si="91"/>
-        <v>34694.34930963409</v>
+        <v>21795</v>
       </c>
       <c r="BB16" s="5">
-        <f t="shared" si="91"/>
-        <v>35793.341652312512</v>
+        <f t="shared" ref="BB16:BI16" si="88">BB15*0.19</f>
+        <v>27434.144307999999</v>
       </c>
       <c r="BC16" s="5">
-        <f t="shared" si="91"/>
-        <v>36926.427835339586</v>
+        <f t="shared" si="88"/>
+        <v>29650.958869779995</v>
       </c>
       <c r="BD16" s="5">
-        <f t="shared" si="91"/>
-        <v>37666.954115055021</v>
+        <f t="shared" si="88"/>
+        <v>31520.342988097807</v>
       </c>
       <c r="BE16" s="5">
-        <f t="shared" ref="BE16:BF16" si="92">BE15*0.19</f>
-        <v>38422.310897594842</v>
+        <f t="shared" si="88"/>
+        <v>33228.307211421503</v>
       </c>
       <c r="BF16" s="5">
-        <f t="shared" si="92"/>
-        <v>39192.794992787836</v>
+        <f t="shared" si="88"/>
+        <v>34641.774265256427</v>
+      </c>
+      <c r="BG16" s="5">
+        <f t="shared" si="88"/>
+        <v>35731.494032777206</v>
+      </c>
+      <c r="BH16" s="5">
+        <f t="shared" si="88"/>
+        <v>36854.948216408819</v>
+      </c>
+      <c r="BI16" s="5">
+        <f t="shared" si="88"/>
+        <v>37590.338906284109</v>
+      </c>
+      <c r="BJ16" s="5">
+        <f t="shared" ref="BJ16:BK16" si="89">BJ15*0.19</f>
+        <v>38340.420327212349</v>
+      </c>
+      <c r="BK16" s="5">
+        <f t="shared" si="89"/>
+        <v>39105.486122987182</v>
       </c>
     </row>
-    <row r="17" spans="2:179" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:184" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:R17" si="93">C15-C16</f>
+        <f t="shared" ref="C17:R17" si="90">C15-C16</f>
         <v>5397</v>
       </c>
       <c r="D17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>6267</v>
       </c>
       <c r="E17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>5486</v>
       </c>
       <c r="F17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>8069</v>
       </c>
       <c r="G17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>6576</v>
       </c>
       <c r="H17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>-6302</v>
       </c>
       <c r="I17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>7424</v>
       </c>
       <c r="J17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>8873</v>
       </c>
       <c r="K17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>8824</v>
       </c>
       <c r="L17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>8420</v>
       </c>
       <c r="M17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>8809</v>
       </c>
       <c r="N17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>13187</v>
       </c>
       <c r="O17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>10678</v>
       </c>
       <c r="P17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>11649</v>
       </c>
       <c r="Q17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>10752</v>
       </c>
       <c r="R17" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="90"/>
         <v>11202</v>
       </c>
       <c r="S17" s="7">
-        <f t="shared" ref="S17:V17" si="94">S15-S16</f>
+        <f t="shared" ref="S17:V17" si="91">S15-S16</f>
         <v>13893</v>
       </c>
       <c r="T17" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="91"/>
         <v>15463</v>
       </c>
       <c r="U17" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="91"/>
         <v>15457</v>
       </c>
       <c r="V17" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="91"/>
         <v>16458</v>
       </c>
       <c r="W17" s="7">
-        <f t="shared" ref="W17:X17" si="95">W15-W16</f>
+        <f t="shared" ref="W17:X17" si="92">W15-W16</f>
         <v>20505</v>
       </c>
       <c r="X17" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>17596</v>
       </c>
       <c r="Y17" s="7">
-        <f t="shared" ref="Y17" si="96">Y15-Y16</f>
+        <f t="shared" ref="Y17" si="93">Y15-Y16</f>
         <v>16728</v>
       </c>
       <c r="Z17" s="7">
-        <f t="shared" ref="Z17" si="97">Z15-Z16</f>
+        <f t="shared" ref="Z17" si="94">Z15-Z16</f>
         <v>16740</v>
       </c>
       <c r="AA17" s="7">
-        <f t="shared" ref="AA17" si="98">AA15-AA16</f>
+        <f t="shared" ref="AA17" si="95">AA15-AA16</f>
         <v>17556</v>
       </c>
       <c r="AB17" s="7">
-        <f t="shared" ref="AB17:AC17" si="99">AB15-AB16</f>
+        <f t="shared" ref="AB17:AC17" si="96">AB15-AB16</f>
         <v>16425</v>
       </c>
       <c r="AC17" s="7">
+        <f t="shared" si="96"/>
+        <v>18299</v>
+      </c>
+      <c r="AD17" s="7">
+        <f t="shared" ref="AD17:AE17" si="97">AD15-AD16</f>
+        <v>20081</v>
+      </c>
+      <c r="AE17" s="7">
+        <f t="shared" si="97"/>
+        <v>22291</v>
+      </c>
+      <c r="AF17" s="7">
+        <f t="shared" ref="AF17:AG17" si="98">AF15-AF16</f>
+        <v>22291</v>
+      </c>
+      <c r="AG17" s="7">
+        <f t="shared" si="98"/>
+        <v>21870</v>
+      </c>
+      <c r="AH17" s="7">
+        <f t="shared" ref="AH17:AI17" si="99">AH15-AH16</f>
+        <v>22036</v>
+      </c>
+      <c r="AI17" s="7">
         <f t="shared" si="99"/>
-        <v>18299</v>
-      </c>
-      <c r="AD17" s="7">
-        <f t="shared" ref="AD17:AE17" si="100">AD15-AD16</f>
-        <v>20081</v>
-      </c>
-      <c r="AE17" s="7">
+        <v>24667</v>
+      </c>
+      <c r="AJ17" s="7">
+        <f t="shared" ref="AJ17:AL17" si="100">AJ15-AJ16</f>
+        <v>24108</v>
+      </c>
+      <c r="AK17" s="7">
         <f t="shared" si="100"/>
-        <v>22291</v>
-      </c>
-      <c r="AF17" s="7">
-        <f t="shared" ref="AF17:AG17" si="101">AF15-AF16</f>
-        <v>22291</v>
-      </c>
-      <c r="AG17" s="7">
+        <v>25824</v>
+      </c>
+      <c r="AL17" s="7">
+        <f t="shared" si="100"/>
+        <v>27233</v>
+      </c>
+      <c r="AM17" s="7"/>
+      <c r="AN17" s="7"/>
+      <c r="AO17" s="7"/>
+      <c r="AP17" s="7"/>
+      <c r="AQ17" s="7"/>
+      <c r="AS17" s="7">
+        <f>AS15-AS16</f>
+        <v>25219</v>
+      </c>
+      <c r="AT17" s="7">
+        <f>AT15-AT16</f>
+        <v>30371</v>
+      </c>
+      <c r="AU17" s="7">
+        <f>AU15-AU16</f>
+        <v>39240</v>
+      </c>
+      <c r="AV17" s="7">
+        <f>AV15-AV16</f>
+        <v>44281</v>
+      </c>
+      <c r="AW17" s="7">
+        <f t="shared" ref="AW17:BF17" si="101">AW15-AW16</f>
+        <v>61271</v>
+      </c>
+      <c r="AX17" s="7">
+        <f t="shared" ref="AX17:AY17" si="102">AX15-AX16</f>
+        <v>71569</v>
+      </c>
+      <c r="AY17" s="7">
+        <f t="shared" si="102"/>
+        <v>72361</v>
+      </c>
+      <c r="AZ17" s="7">
+        <f t="shared" ref="AZ17" si="103">AZ15-AZ16</f>
+        <v>88488</v>
+      </c>
+      <c r="BA17" s="7">
         <f t="shared" si="101"/>
-        <v>21870</v>
-      </c>
-      <c r="AH17" s="7">
-        <f t="shared" ref="AH17:AI17" si="102">AH15-AH16</f>
-        <v>22036</v>
-      </c>
-      <c r="AI17" s="7">
-        <f t="shared" si="102"/>
-        <v>24667</v>
-      </c>
-      <c r="AJ17" s="7">
-        <f t="shared" ref="AJ17:AL17" si="103">AJ15-AJ16</f>
-        <v>24108</v>
-      </c>
-      <c r="AK17" s="7">
-        <f t="shared" si="103"/>
-        <v>25824</v>
-      </c>
-      <c r="AL17" s="7">
-        <f t="shared" si="103"/>
-        <v>25671.819564000005</v>
-      </c>
-      <c r="AN17" s="7">
-        <f>AN15-AN16</f>
-        <v>25219</v>
-      </c>
-      <c r="AO17" s="7">
-        <f>AO15-AO16</f>
-        <v>30371</v>
-      </c>
-      <c r="AP17" s="7">
-        <f>AP15-AP16</f>
-        <v>39240</v>
-      </c>
-      <c r="AQ17" s="7">
-        <f>AQ15-AQ16</f>
-        <v>44281</v>
-      </c>
-      <c r="AR17" s="7">
-        <f t="shared" ref="AR17:BA17" si="104">AR15-AR16</f>
-        <v>61271</v>
-      </c>
-      <c r="AS17" s="7">
-        <f t="shared" ref="AS17:AT17" si="105">AS15-AS16</f>
-        <v>71569</v>
-      </c>
-      <c r="AT17" s="7">
+        <v>101832</v>
+      </c>
+      <c r="BB17" s="7">
+        <f t="shared" si="101"/>
+        <v>116956.08889199999</v>
+      </c>
+      <c r="BC17" s="7">
+        <f t="shared" si="101"/>
+        <v>126406.71939221998</v>
+      </c>
+      <c r="BD17" s="7">
+        <f t="shared" si="101"/>
+        <v>134376.19905452224</v>
+      </c>
+      <c r="BE17" s="7">
+        <f t="shared" si="101"/>
+        <v>141657.52021711273</v>
+      </c>
+      <c r="BF17" s="7">
+        <f t="shared" si="101"/>
+        <v>147683.35344661953</v>
+      </c>
+      <c r="BG17" s="7">
+        <f t="shared" ref="BG17:BI17" si="104">BG15-BG16</f>
+        <v>152329.00087657652</v>
+      </c>
+      <c r="BH17" s="7">
+        <f t="shared" si="104"/>
+        <v>157118.46344890076</v>
+      </c>
+      <c r="BI17" s="7">
+        <f t="shared" si="104"/>
+        <v>160253.55007415856</v>
+      </c>
+      <c r="BJ17" s="7">
+        <f t="shared" ref="BJ17:BK17" si="105">BJ15-BJ16</f>
+        <v>163451.26560548422</v>
+      </c>
+      <c r="BK17" s="7">
         <f t="shared" si="105"/>
-        <v>72361</v>
-      </c>
-      <c r="AU17" s="7">
-        <f t="shared" ref="AU17" si="106">AU15-AU16</f>
-        <v>88488</v>
-      </c>
-      <c r="AV17" s="7">
-        <f t="shared" si="104"/>
-        <v>100270.81956400006</v>
-      </c>
-      <c r="AW17" s="7">
-        <f t="shared" si="104"/>
-        <v>116879.68056410999</v>
-      </c>
-      <c r="AX17" s="7">
-        <f t="shared" si="104"/>
-        <v>126432.79531779507</v>
-      </c>
-      <c r="AY17" s="7">
-        <f t="shared" si="104"/>
-        <v>134480.25517988933</v>
-      </c>
-      <c r="AZ17" s="7">
-        <f t="shared" si="104"/>
-        <v>141828.94504536386</v>
-      </c>
-      <c r="BA17" s="7">
-        <f t="shared" si="104"/>
-        <v>147907.48916212429</v>
-      </c>
-      <c r="BB17" s="7">
-        <f t="shared" ref="BB17:BD17" si="107">BB15-BB16</f>
-        <v>152592.66704406912</v>
-      </c>
-      <c r="BC17" s="7">
+        <v>166712.86189273483</v>
+      </c>
+      <c r="BL17" s="6">
+        <f>BK17*(1+$BN$21)</f>
+        <v>165045.73327380748</v>
+      </c>
+      <c r="BM17" s="6">
+        <f t="shared" ref="BM17:DX17" si="106">BL17*(1+$BN$21)</f>
+        <v>163395.27594106941</v>
+      </c>
+      <c r="BN17" s="6">
+        <f t="shared" si="106"/>
+        <v>161761.32318165872</v>
+      </c>
+      <c r="BO17" s="6">
+        <f t="shared" si="106"/>
+        <v>160143.70994984213</v>
+      </c>
+      <c r="BP17" s="6">
+        <f t="shared" si="106"/>
+        <v>158542.2728503437</v>
+      </c>
+      <c r="BQ17" s="6">
+        <f t="shared" si="106"/>
+        <v>156956.85012184025</v>
+      </c>
+      <c r="BR17" s="6">
+        <f t="shared" si="106"/>
+        <v>155387.28162062186</v>
+      </c>
+      <c r="BS17" s="6">
+        <f t="shared" si="106"/>
+        <v>153833.40880441564</v>
+      </c>
+      <c r="BT17" s="6">
+        <f t="shared" si="106"/>
+        <v>152295.07471637148</v>
+      </c>
+      <c r="BU17" s="6">
+        <f t="shared" si="106"/>
+        <v>150772.12396920778</v>
+      </c>
+      <c r="BV17" s="6">
+        <f t="shared" si="106"/>
+        <v>149264.40272951571</v>
+      </c>
+      <c r="BW17" s="6">
+        <f t="shared" si="106"/>
+        <v>147771.75870222057</v>
+      </c>
+      <c r="BX17" s="6">
+        <f t="shared" si="106"/>
+        <v>146294.04111519837</v>
+      </c>
+      <c r="BY17" s="6">
+        <f t="shared" si="106"/>
+        <v>144831.10070404637</v>
+      </c>
+      <c r="BZ17" s="6">
+        <f t="shared" si="106"/>
+        <v>143382.78969700591</v>
+      </c>
+      <c r="CA17" s="6">
+        <f t="shared" si="106"/>
+        <v>141948.96180003585</v>
+      </c>
+      <c r="CB17" s="6">
+        <f t="shared" si="106"/>
+        <v>140529.47218203548</v>
+      </c>
+      <c r="CC17" s="6">
+        <f t="shared" si="106"/>
+        <v>139124.17746021511</v>
+      </c>
+      <c r="CD17" s="6">
+        <f t="shared" si="106"/>
+        <v>137732.93568561296</v>
+      </c>
+      <c r="CE17" s="6">
+        <f t="shared" si="106"/>
+        <v>136355.60632875684</v>
+      </c>
+      <c r="CF17" s="6">
+        <f t="shared" si="106"/>
+        <v>134992.05026546927</v>
+      </c>
+      <c r="CG17" s="6">
+        <f t="shared" si="106"/>
+        <v>133642.12976281458</v>
+      </c>
+      <c r="CH17" s="6">
+        <f t="shared" si="106"/>
+        <v>132305.70846518644</v>
+      </c>
+      <c r="CI17" s="6">
+        <f t="shared" si="106"/>
+        <v>130982.65138053457</v>
+      </c>
+      <c r="CJ17" s="6">
+        <f t="shared" si="106"/>
+        <v>129672.82486672922</v>
+      </c>
+      <c r="CK17" s="6">
+        <f t="shared" si="106"/>
+        <v>128376.09661806193</v>
+      </c>
+      <c r="CL17" s="6">
+        <f t="shared" si="106"/>
+        <v>127092.33565188131</v>
+      </c>
+      <c r="CM17" s="6">
+        <f t="shared" si="106"/>
+        <v>125821.41229536249</v>
+      </c>
+      <c r="CN17" s="6">
+        <f t="shared" si="106"/>
+        <v>124563.19817240887</v>
+      </c>
+      <c r="CO17" s="6">
+        <f t="shared" si="106"/>
+        <v>123317.56619068478</v>
+      </c>
+      <c r="CP17" s="6">
+        <f t="shared" si="106"/>
+        <v>122084.39052877793</v>
+      </c>
+      <c r="CQ17" s="6">
+        <f t="shared" si="106"/>
+        <v>120863.54662349015</v>
+      </c>
+      <c r="CR17" s="6">
+        <f t="shared" si="106"/>
+        <v>119654.91115725525</v>
+      </c>
+      <c r="CS17" s="6">
+        <f t="shared" si="106"/>
+        <v>118458.36204568269</v>
+      </c>
+      <c r="CT17" s="6">
+        <f t="shared" si="106"/>
+        <v>117273.77842522586</v>
+      </c>
+      <c r="CU17" s="6">
+        <f t="shared" si="106"/>
+        <v>116101.0406409736</v>
+      </c>
+      <c r="CV17" s="6">
+        <f t="shared" si="106"/>
+        <v>114940.03023456386</v>
+      </c>
+      <c r="CW17" s="6">
+        <f t="shared" si="106"/>
+        <v>113790.62993221822</v>
+      </c>
+      <c r="CX17" s="6">
+        <f t="shared" si="106"/>
+        <v>112652.72363289603</v>
+      </c>
+      <c r="CY17" s="6">
+        <f t="shared" si="106"/>
+        <v>111526.19639656707</v>
+      </c>
+      <c r="CZ17" s="6">
+        <f t="shared" si="106"/>
+        <v>110410.9344326014</v>
+      </c>
+      <c r="DA17" s="6">
+        <f t="shared" si="106"/>
+        <v>109306.82508827538</v>
+      </c>
+      <c r="DB17" s="6">
+        <f t="shared" si="106"/>
+        <v>108213.75683739262</v>
+      </c>
+      <c r="DC17" s="6">
+        <f t="shared" si="106"/>
+        <v>107131.61926901869</v>
+      </c>
+      <c r="DD17" s="6">
+        <f t="shared" si="106"/>
+        <v>106060.30307632851</v>
+      </c>
+      <c r="DE17" s="6">
+        <f t="shared" si="106"/>
+        <v>104999.70004556522</v>
+      </c>
+      <c r="DF17" s="6">
+        <f t="shared" si="106"/>
+        <v>103949.70304510956</v>
+      </c>
+      <c r="DG17" s="6">
+        <f t="shared" si="106"/>
+        <v>102910.20601465847</v>
+      </c>
+      <c r="DH17" s="6">
+        <f t="shared" si="106"/>
+        <v>101881.10395451188</v>
+      </c>
+      <c r="DI17" s="6">
+        <f t="shared" si="106"/>
+        <v>100862.29291496676</v>
+      </c>
+      <c r="DJ17" s="6">
+        <f t="shared" si="106"/>
+        <v>99853.66998581709</v>
+      </c>
+      <c r="DK17" s="6">
+        <f t="shared" si="106"/>
+        <v>98855.133285958917</v>
+      </c>
+      <c r="DL17" s="6">
+        <f t="shared" si="106"/>
+        <v>97866.581953099332</v>
+      </c>
+      <c r="DM17" s="6">
+        <f t="shared" si="106"/>
+        <v>96887.916133568331</v>
+      </c>
+      <c r="DN17" s="6">
+        <f t="shared" si="106"/>
+        <v>95919.036972232643</v>
+      </c>
+      <c r="DO17" s="6">
+        <f t="shared" si="106"/>
+        <v>94959.846602510312</v>
+      </c>
+      <c r="DP17" s="6">
+        <f t="shared" si="106"/>
+        <v>94010.248136485214</v>
+      </c>
+      <c r="DQ17" s="6">
+        <f t="shared" si="106"/>
+        <v>93070.145655120359</v>
+      </c>
+      <c r="DR17" s="6">
+        <f t="shared" si="106"/>
+        <v>92139.444198569152</v>
+      </c>
+      <c r="DS17" s="6">
+        <f t="shared" si="106"/>
+        <v>91218.049756583467</v>
+      </c>
+      <c r="DT17" s="6">
+        <f t="shared" si="106"/>
+        <v>90305.869259017636</v>
+      </c>
+      <c r="DU17" s="6">
+        <f t="shared" si="106"/>
+        <v>89402.810566427463</v>
+      </c>
+      <c r="DV17" s="6">
+        <f t="shared" si="106"/>
+        <v>88508.782460763192</v>
+      </c>
+      <c r="DW17" s="6">
+        <f t="shared" si="106"/>
+        <v>87623.69463615556</v>
+      </c>
+      <c r="DX17" s="6">
+        <f t="shared" si="106"/>
+        <v>86747.457689793999</v>
+      </c>
+      <c r="DY17" s="6">
+        <f t="shared" ref="DY17:GB17" si="107">DX17*(1+$BN$21)</f>
+        <v>85879.983112896065</v>
+      </c>
+      <c r="DZ17" s="6">
         <f t="shared" si="107"/>
-        <v>157423.19235065824</v>
-      </c>
-      <c r="BD17" s="7">
+        <v>85021.183281767109</v>
+      </c>
+      <c r="EA17" s="6">
         <f t="shared" si="107"/>
-        <v>160580.17280628718</v>
-      </c>
-      <c r="BE17" s="7">
-        <f t="shared" ref="BE17:BF17" si="108">BE15-BE16</f>
-        <v>163800.37803711483</v>
-      </c>
-      <c r="BF17" s="7">
-        <f t="shared" si="108"/>
-        <v>167085.07339030603</v>
-      </c>
-      <c r="BG17" s="6">
-        <f>BF17*(1+$BI$21)</f>
-        <v>165414.22265640297</v>
-      </c>
-      <c r="BH17" s="6">
-        <f t="shared" ref="BH17:DS17" si="109">BG17*(1+$BI$21)</f>
-        <v>163760.08042983894</v>
-      </c>
-      <c r="BI17" s="6">
-        <f t="shared" si="109"/>
-        <v>162122.47962554055</v>
-      </c>
-      <c r="BJ17" s="6">
-        <f t="shared" si="109"/>
-        <v>160501.25482928514</v>
-      </c>
-      <c r="BK17" s="6">
-        <f t="shared" si="109"/>
-        <v>158896.2422809923</v>
-      </c>
-      <c r="BL17" s="6">
-        <f t="shared" si="109"/>
-        <v>157307.27985818239</v>
-      </c>
-      <c r="BM17" s="6">
-        <f t="shared" si="109"/>
-        <v>155734.20705960057</v>
-      </c>
-      <c r="BN17" s="6">
-        <f t="shared" si="109"/>
-        <v>154176.86498900456</v>
-      </c>
-      <c r="BO17" s="6">
-        <f t="shared" si="109"/>
-        <v>152635.09633911451</v>
-      </c>
-      <c r="BP17" s="6">
-        <f t="shared" si="109"/>
-        <v>151108.74537572335</v>
-      </c>
-      <c r="BQ17" s="6">
-        <f t="shared" si="109"/>
-        <v>149597.65792196611</v>
-      </c>
-      <c r="BR17" s="6">
-        <f t="shared" si="109"/>
-        <v>148101.68134274645</v>
-      </c>
-      <c r="BS17" s="6">
-        <f t="shared" si="109"/>
-        <v>146620.66452931898</v>
-      </c>
-      <c r="BT17" s="6">
-        <f t="shared" si="109"/>
-        <v>145154.45788402579</v>
-      </c>
-      <c r="BU17" s="6">
-        <f t="shared" si="109"/>
-        <v>143702.91330518553</v>
-      </c>
-      <c r="BV17" s="6">
-        <f t="shared" si="109"/>
-        <v>142265.88417213366</v>
-      </c>
-      <c r="BW17" s="6">
-        <f t="shared" si="109"/>
-        <v>140843.22533041233</v>
-      </c>
-      <c r="BX17" s="6">
-        <f t="shared" si="109"/>
-        <v>139434.79307710822</v>
-      </c>
-      <c r="BY17" s="6">
-        <f t="shared" si="109"/>
-        <v>138040.44514633712</v>
-      </c>
-      <c r="BZ17" s="6">
-        <f t="shared" si="109"/>
-        <v>136660.04069487375</v>
-      </c>
-      <c r="CA17" s="6">
-        <f t="shared" si="109"/>
-        <v>135293.44028792501</v>
-      </c>
-      <c r="CB17" s="6">
-        <f t="shared" si="109"/>
-        <v>133940.50588504577</v>
-      </c>
-      <c r="CC17" s="6">
-        <f t="shared" si="109"/>
-        <v>132601.10082619532</v>
-      </c>
-      <c r="CD17" s="6">
-        <f t="shared" si="109"/>
-        <v>131275.08981793336</v>
-      </c>
-      <c r="CE17" s="6">
-        <f t="shared" si="109"/>
-        <v>129962.33891975402</v>
-      </c>
-      <c r="CF17" s="6">
-        <f t="shared" si="109"/>
-        <v>128662.71553055648</v>
-      </c>
-      <c r="CG17" s="6">
-        <f t="shared" si="109"/>
-        <v>127376.08837525091</v>
-      </c>
-      <c r="CH17" s="6">
-        <f t="shared" si="109"/>
-        <v>126102.32749149841</v>
-      </c>
-      <c r="CI17" s="6">
-        <f t="shared" si="109"/>
-        <v>124841.30421658342</v>
-      </c>
-      <c r="CJ17" s="6">
-        <f t="shared" si="109"/>
-        <v>123592.89117441759</v>
-      </c>
-      <c r="CK17" s="6">
-        <f t="shared" si="109"/>
-        <v>122356.96226267341</v>
-      </c>
-      <c r="CL17" s="6">
-        <f t="shared" si="109"/>
-        <v>121133.39264004667</v>
-      </c>
-      <c r="CM17" s="6">
-        <f t="shared" si="109"/>
-        <v>119922.05871364621</v>
-      </c>
-      <c r="CN17" s="6">
-        <f t="shared" si="109"/>
-        <v>118722.83812650976</v>
-      </c>
-      <c r="CO17" s="6">
-        <f t="shared" si="109"/>
-        <v>117535.60974524466</v>
-      </c>
-      <c r="CP17" s="6">
-        <f t="shared" si="109"/>
-        <v>116360.25364779221</v>
-      </c>
-      <c r="CQ17" s="6">
-        <f t="shared" si="109"/>
-        <v>115196.65111131429</v>
-      </c>
-      <c r="CR17" s="6">
-        <f t="shared" si="109"/>
-        <v>114044.68460020114</v>
-      </c>
-      <c r="CS17" s="6">
-        <f t="shared" si="109"/>
-        <v>112904.23775419913</v>
-      </c>
-      <c r="CT17" s="6">
-        <f t="shared" si="109"/>
-        <v>111775.19537665714</v>
-      </c>
-      <c r="CU17" s="6">
-        <f t="shared" si="109"/>
-        <v>110657.44342289056</v>
-      </c>
-      <c r="CV17" s="6">
-        <f t="shared" si="109"/>
-        <v>109550.86898866165</v>
-      </c>
-      <c r="CW17" s="6">
-        <f t="shared" si="109"/>
-        <v>108455.36029877503</v>
-      </c>
-      <c r="CX17" s="6">
-        <f t="shared" si="109"/>
-        <v>107370.80669578728</v>
-      </c>
-      <c r="CY17" s="6">
-        <f t="shared" si="109"/>
-        <v>106297.09862882941</v>
-      </c>
-      <c r="CZ17" s="6">
-        <f t="shared" si="109"/>
-        <v>105234.12764254112</v>
-      </c>
-      <c r="DA17" s="6">
-        <f t="shared" si="109"/>
-        <v>104181.7863661157</v>
-      </c>
-      <c r="DB17" s="6">
-        <f t="shared" si="109"/>
-        <v>103139.96850245455</v>
-      </c>
-      <c r="DC17" s="6">
-        <f t="shared" si="109"/>
-        <v>102108.56881743</v>
-      </c>
-      <c r="DD17" s="6">
-        <f t="shared" si="109"/>
-        <v>101087.48312925571</v>
-      </c>
-      <c r="DE17" s="6">
-        <f t="shared" si="109"/>
-        <v>100076.60829796315</v>
-      </c>
-      <c r="DF17" s="6">
-        <f t="shared" si="109"/>
-        <v>99075.84221498351</v>
-      </c>
-      <c r="DG17" s="6">
-        <f t="shared" si="109"/>
-        <v>98085.08379283367</v>
-      </c>
-      <c r="DH17" s="6">
-        <f t="shared" si="109"/>
-        <v>97104.232954905339</v>
-      </c>
-      <c r="DI17" s="6">
-        <f t="shared" si="109"/>
-        <v>96133.190625356292</v>
-      </c>
-      <c r="DJ17" s="6">
-        <f t="shared" si="109"/>
-        <v>95171.858719102733</v>
-      </c>
-      <c r="DK17" s="6">
-        <f t="shared" si="109"/>
-        <v>94220.140131911699</v>
-      </c>
-      <c r="DL17" s="6">
-        <f t="shared" si="109"/>
-        <v>93277.938730592577</v>
-      </c>
-      <c r="DM17" s="6">
-        <f t="shared" si="109"/>
-        <v>92345.15934328665</v>
-      </c>
-      <c r="DN17" s="6">
-        <f t="shared" si="109"/>
-        <v>91421.707749853784</v>
-      </c>
-      <c r="DO17" s="6">
-        <f t="shared" si="109"/>
-        <v>90507.490672355241</v>
-      </c>
-      <c r="DP17" s="6">
-        <f t="shared" si="109"/>
-        <v>89602.415765631682</v>
-      </c>
-      <c r="DQ17" s="6">
-        <f t="shared" si="109"/>
-        <v>88706.391607975369</v>
-      </c>
-      <c r="DR17" s="6">
-        <f t="shared" si="109"/>
-        <v>87819.327691895611</v>
-      </c>
-      <c r="DS17" s="6">
-        <f t="shared" si="109"/>
-        <v>86941.134414976652</v>
-      </c>
-      <c r="DT17" s="6">
-        <f t="shared" ref="DT17:FW17" si="110">DS17*(1+$BI$21)</f>
-        <v>86071.723070826891</v>
-      </c>
-      <c r="DU17" s="6">
-        <f t="shared" si="110"/>
-        <v>85211.005840118625</v>
-      </c>
-      <c r="DV17" s="6">
-        <f t="shared" si="110"/>
-        <v>84358.895781717438</v>
-      </c>
-      <c r="DW17" s="6">
-        <f t="shared" si="110"/>
-        <v>83515.30682390026</v>
-      </c>
-      <c r="DX17" s="6">
-        <f t="shared" si="110"/>
-        <v>82680.15375566126</v>
-      </c>
-      <c r="DY17" s="6">
-        <f t="shared" si="110"/>
-        <v>81853.352218104643</v>
-      </c>
-      <c r="DZ17" s="6">
-        <f t="shared" si="110"/>
-        <v>81034.81869592359</v>
-      </c>
-      <c r="EA17" s="6">
-        <f t="shared" si="110"/>
-        <v>80224.470508964354</v>
+        <v>84170.971448949436</v>
       </c>
       <c r="EB17" s="6">
-        <f t="shared" si="110"/>
-        <v>79422.22580387471</v>
+        <f t="shared" si="107"/>
+        <v>83329.261734459942</v>
       </c>
       <c r="EC17" s="6">
-        <f t="shared" si="110"/>
-        <v>78628.003545835963</v>
+        <f t="shared" si="107"/>
+        <v>82495.969117115339</v>
       </c>
       <c r="ED17" s="6">
-        <f t="shared" si="110"/>
-        <v>77841.723510377604</v>
+        <f t="shared" si="107"/>
+        <v>81671.009425944183</v>
       </c>
       <c r="EE17" s="6">
-        <f t="shared" si="110"/>
-        <v>77063.306275273833</v>
+        <f t="shared" si="107"/>
+        <v>80854.299331684742</v>
       </c>
       <c r="EF17" s="6">
-        <f t="shared" si="110"/>
-        <v>76292.673212521098</v>
+        <f t="shared" si="107"/>
+        <v>80045.756338367893</v>
       </c>
       <c r="EG17" s="6">
-        <f t="shared" si="110"/>
-        <v>75529.746480395886</v>
+        <f t="shared" si="107"/>
+        <v>79245.298774984214</v>
       </c>
       <c r="EH17" s="6">
-        <f t="shared" si="110"/>
-        <v>74774.449015591934</v>
+        <f t="shared" si="107"/>
+        <v>78452.845787234372</v>
       </c>
       <c r="EI17" s="6">
-        <f t="shared" si="110"/>
-        <v>74026.704525436013</v>
+        <f t="shared" si="107"/>
+        <v>77668.31732936202</v>
       </c>
       <c r="EJ17" s="6">
-        <f t="shared" si="110"/>
-        <v>73286.437480181645</v>
+        <f t="shared" si="107"/>
+        <v>76891.634156068394</v>
       </c>
       <c r="EK17" s="6">
-        <f t="shared" si="110"/>
-        <v>72553.573105379823</v>
+        <f t="shared" si="107"/>
+        <v>76122.717814507705</v>
       </c>
       <c r="EL17" s="6">
-        <f t="shared" si="110"/>
-        <v>71828.037374326028</v>
+        <f t="shared" si="107"/>
+        <v>75361.490636362621</v>
       </c>
       <c r="EM17" s="6">
-        <f t="shared" si="110"/>
-        <v>71109.757000582773</v>
+        <f t="shared" si="107"/>
+        <v>74607.875729998996</v>
       </c>
       <c r="EN17" s="6">
-        <f t="shared" si="110"/>
-        <v>70398.659430576939</v>
+        <f t="shared" si="107"/>
+        <v>73861.796972699012</v>
       </c>
       <c r="EO17" s="6">
-        <f t="shared" si="110"/>
-        <v>69694.672836271173</v>
+        <f t="shared" si="107"/>
+        <v>73123.179002972029</v>
       </c>
       <c r="EP17" s="6">
-        <f t="shared" si="110"/>
-        <v>68997.726107908456</v>
+        <f t="shared" si="107"/>
+        <v>72391.947212942308</v>
       </c>
       <c r="EQ17" s="6">
-        <f t="shared" si="110"/>
-        <v>68307.748846829374</v>
+        <f t="shared" si="107"/>
+        <v>71668.02774081289</v>
       </c>
       <c r="ER17" s="6">
-        <f t="shared" si="110"/>
-        <v>67624.671358361084</v>
+        <f t="shared" si="107"/>
+        <v>70951.34746340476</v>
       </c>
       <c r="ES17" s="6">
-        <f t="shared" si="110"/>
-        <v>66948.424644777479</v>
+        <f t="shared" si="107"/>
+        <v>70241.833988770712</v>
       </c>
       <c r="ET17" s="6">
-        <f t="shared" si="110"/>
-        <v>66278.940398329709</v>
+        <f t="shared" si="107"/>
+        <v>69539.415648883005</v>
       </c>
       <c r="EU17" s="6">
-        <f t="shared" si="110"/>
-        <v>65616.150994346404</v>
+        <f t="shared" si="107"/>
+        <v>68844.021492394168</v>
       </c>
       <c r="EV17" s="6">
-        <f t="shared" si="110"/>
-        <v>64959.98948440294</v>
+        <f t="shared" si="107"/>
+        <v>68155.581277470221</v>
       </c>
       <c r="EW17" s="6">
-        <f t="shared" si="110"/>
-        <v>64310.389589558908</v>
+        <f t="shared" si="107"/>
+        <v>67474.025464695515</v>
       </c>
       <c r="EX17" s="6">
-        <f t="shared" si="110"/>
-        <v>63667.285693663318</v>
+        <f t="shared" si="107"/>
+        <v>66799.285210048562</v>
       </c>
       <c r="EY17" s="6">
-        <f t="shared" si="110"/>
-        <v>63030.612836726687</v>
+        <f t="shared" si="107"/>
+        <v>66131.29235794807</v>
       </c>
       <c r="EZ17" s="6">
-        <f t="shared" si="110"/>
-        <v>62400.306708359421</v>
+        <f t="shared" si="107"/>
+        <v>65469.979434368586</v>
       </c>
       <c r="FA17" s="6">
-        <f t="shared" si="110"/>
-        <v>61776.30364127583</v>
+        <f t="shared" si="107"/>
+        <v>64815.279640024899</v>
       </c>
       <c r="FB17" s="6">
-        <f t="shared" si="110"/>
-        <v>61158.540604863068</v>
+        <f t="shared" si="107"/>
+        <v>64167.126843624646</v>
       </c>
       <c r="FC17" s="6">
-        <f t="shared" si="110"/>
-        <v>60546.955198814438</v>
+        <f t="shared" si="107"/>
+        <v>63525.455575188396</v>
       </c>
       <c r="FD17" s="6">
-        <f t="shared" si="110"/>
-        <v>59941.485646826295</v>
+        <f t="shared" si="107"/>
+        <v>62890.201019436514</v>
       </c>
       <c r="FE17" s="6">
-        <f t="shared" si="110"/>
-        <v>59342.070790358033</v>
+        <f t="shared" si="107"/>
+        <v>62261.299009242146</v>
       </c>
       <c r="FF17" s="6">
-        <f t="shared" si="110"/>
-        <v>58748.650082454449</v>
+        <f t="shared" si="107"/>
+        <v>61638.686019149725</v>
       </c>
       <c r="FG17" s="6">
-        <f t="shared" si="110"/>
-        <v>58161.163581629902</v>
+        <f t="shared" si="107"/>
+        <v>61022.299158958231</v>
       </c>
       <c r="FH17" s="6">
-        <f t="shared" si="110"/>
-        <v>57579.551945813604</v>
+        <f t="shared" si="107"/>
+        <v>60412.07616736865</v>
       </c>
       <c r="FI17" s="6">
-        <f t="shared" si="110"/>
-        <v>57003.756426355467</v>
+        <f t="shared" si="107"/>
+        <v>59807.955405694964</v>
       </c>
       <c r="FJ17" s="6">
-        <f t="shared" si="110"/>
-        <v>56433.718862091911</v>
+        <f t="shared" si="107"/>
+        <v>59209.875851638011</v>
       </c>
       <c r="FK17" s="6">
-        <f t="shared" si="110"/>
-        <v>55869.381673470991</v>
+        <f t="shared" si="107"/>
+        <v>58617.777093121629</v>
       </c>
       <c r="FL17" s="6">
-        <f t="shared" si="110"/>
-        <v>55310.68785673628</v>
+        <f t="shared" si="107"/>
+        <v>58031.599322190414</v>
       </c>
       <c r="FM17" s="6">
-        <f t="shared" si="110"/>
-        <v>54757.580978168917</v>
+        <f t="shared" si="107"/>
+        <v>57451.283328968508</v>
       </c>
       <c r="FN17" s="6">
-        <f t="shared" si="110"/>
-        <v>54210.00516838723</v>
+        <f t="shared" si="107"/>
+        <v>56876.770495678822</v>
       </c>
       <c r="FO17" s="6">
-        <f t="shared" si="110"/>
-        <v>53667.905116703354</v>
+        <f t="shared" si="107"/>
+        <v>56308.002790722036</v>
       </c>
       <c r="FP17" s="6">
-        <f t="shared" si="110"/>
-        <v>53131.226065536321</v>
+        <f t="shared" si="107"/>
+        <v>55744.922762814815</v>
       </c>
       <c r="FQ17" s="6">
-        <f t="shared" si="110"/>
-        <v>52599.913804880955</v>
+        <f t="shared" si="107"/>
+        <v>55187.473535186669</v>
       </c>
       <c r="FR17" s="6">
-        <f t="shared" si="110"/>
-        <v>52073.914666832141</v>
+        <f t="shared" si="107"/>
+        <v>54635.598799834799</v>
       </c>
       <c r="FS17" s="6">
-        <f t="shared" si="110"/>
-        <v>51553.175520163823</v>
+        <f t="shared" si="107"/>
+        <v>54089.242811836448</v>
       </c>
       <c r="FT17" s="6">
-        <f t="shared" si="110"/>
-        <v>51037.64376496218</v>
+        <f t="shared" si="107"/>
+        <v>53548.350383718083</v>
       </c>
       <c r="FU17" s="6">
-        <f t="shared" si="110"/>
-        <v>50527.267327312555</v>
+        <f t="shared" si="107"/>
+        <v>53012.866879880901</v>
       </c>
       <c r="FV17" s="6">
-        <f t="shared" si="110"/>
-        <v>50021.99465403943</v>
+        <f t="shared" si="107"/>
+        <v>52482.738211082091</v>
       </c>
       <c r="FW17" s="6">
-        <f t="shared" si="110"/>
-        <v>49521.774707499033</v>
+        <f t="shared" si="107"/>
+        <v>51957.910828971268</v>
+      </c>
+      <c r="FX17" s="6">
+        <f t="shared" si="107"/>
+        <v>51438.331720681555</v>
+      </c>
+      <c r="FY17" s="6">
+        <f t="shared" si="107"/>
+        <v>50923.948403474737</v>
+      </c>
+      <c r="FZ17" s="6">
+        <f t="shared" si="107"/>
+        <v>50414.708919439989</v>
+      </c>
+      <c r="GA17" s="6">
+        <f t="shared" si="107"/>
+        <v>49910.561830245591</v>
+      </c>
+      <c r="GB17" s="6">
+        <f t="shared" si="107"/>
+        <v>49411.456211943136</v>
       </c>
     </row>
-    <row r="18" spans="2:179" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:184" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>2</v>
       </c>
@@ -5333,726 +5437,734 @@
         <v>7432.5</v>
       </c>
       <c r="AL18" s="5">
-        <f>7432.5</f>
-        <v>7432.5</v>
-      </c>
-      <c r="AN18" s="5">
+        <v>7432</v>
+      </c>
+      <c r="AM18" s="5"/>
+      <c r="AN18" s="5"/>
+      <c r="AO18" s="5"/>
+      <c r="AP18" s="5"/>
+      <c r="AQ18" s="5"/>
+      <c r="AS18" s="5">
         <v>7567</v>
       </c>
-      <c r="AO18" s="5">
+      <c r="AT18" s="5">
         <v>7567</v>
       </c>
-      <c r="AP18" s="5">
+      <c r="AU18" s="5">
         <v>7567</v>
       </c>
-      <c r="AQ18" s="5">
+      <c r="AV18" s="5">
         <v>7567</v>
       </c>
-      <c r="AR18" s="5">
+      <c r="AW18" s="5">
         <v>7531.6</v>
       </c>
-      <c r="AS18" s="5">
+      <c r="AX18" s="5">
         <v>7432.3</v>
       </c>
-      <c r="AT18" s="5">
+      <c r="AY18" s="5">
         <v>7432.3</v>
       </c>
-      <c r="AU18" s="5">
+      <c r="AZ18" s="5">
         <v>7433</v>
       </c>
-      <c r="AV18" s="5">
-        <f t="shared" ref="AV18:BF18" si="111">7432.5</f>
-        <v>7432.5</v>
-      </c>
-      <c r="AW18" s="5">
-        <f t="shared" si="111"/>
-        <v>7432.5</v>
-      </c>
-      <c r="AX18" s="5">
-        <f t="shared" si="111"/>
-        <v>7432.5</v>
-      </c>
-      <c r="AY18" s="5">
-        <f t="shared" si="111"/>
-        <v>7432.5</v>
-      </c>
-      <c r="AZ18" s="5">
-        <f t="shared" si="111"/>
-        <v>7432.5</v>
-      </c>
       <c r="BA18" s="5">
-        <f t="shared" si="111"/>
-        <v>7432.5</v>
+        <v>7432</v>
       </c>
       <c r="BB18" s="5">
-        <f t="shared" si="111"/>
-        <v>7432.5</v>
+        <v>7432</v>
       </c>
       <c r="BC18" s="5">
-        <f t="shared" si="111"/>
-        <v>7432.5</v>
+        <v>7432</v>
       </c>
       <c r="BD18" s="5">
-        <f t="shared" si="111"/>
-        <v>7432.5</v>
+        <v>7432</v>
       </c>
       <c r="BE18" s="5">
-        <f t="shared" si="111"/>
-        <v>7432.5</v>
+        <v>7432</v>
       </c>
       <c r="BF18" s="5">
-        <f t="shared" si="111"/>
-        <v>7432.5</v>
+        <v>7432</v>
+      </c>
+      <c r="BG18" s="5">
+        <v>7432</v>
+      </c>
+      <c r="BH18" s="5">
+        <v>7432</v>
+      </c>
+      <c r="BI18" s="5">
+        <v>7432</v>
+      </c>
+      <c r="BJ18" s="5">
+        <v>7432</v>
+      </c>
+      <c r="BK18" s="5">
+        <v>7432</v>
       </c>
     </row>
-    <row r="19" spans="2:179" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:184" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="8">
-        <f t="shared" ref="C19:R19" si="112">C17/C18</f>
+        <f t="shared" ref="C19:R19" si="108">C17/C18</f>
         <v>0.71322849213691031</v>
       </c>
       <c r="D19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>0.82820140081934712</v>
       </c>
       <c r="E19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>0.72499008854235492</v>
       </c>
       <c r="F19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>1.0663406898374521</v>
       </c>
       <c r="G19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>0.86903660631690238</v>
       </c>
       <c r="H19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>-0.83282674772036469</v>
       </c>
       <c r="I19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>0.98110215409012824</v>
       </c>
       <c r="J19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>1.172591515792256</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>1.1661160301308313</v>
       </c>
       <c r="L19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>1.1127263116162283</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>1.1641337386018238</v>
       </c>
       <c r="N19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>1.7426985595348223</v>
       </c>
       <c r="O19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>1.4111272631161622</v>
       </c>
       <c r="P19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>1.5394476014272498</v>
       </c>
       <c r="Q19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>1.4209065679925994</v>
       </c>
       <c r="R19" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>1.4803753138628255</v>
       </c>
       <c r="S19" s="8">
-        <f t="shared" ref="S19:V19" si="113">S17/S18</f>
+        <f t="shared" ref="S19:V19" si="109">S17/S18</f>
         <v>1.8359984141667769</v>
       </c>
       <c r="T19" s="8">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v>2.0434782608695654</v>
       </c>
       <c r="U19" s="8">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v>2.052286366774656</v>
       </c>
       <c r="V19" s="8">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v>2.1851930532688937</v>
       </c>
       <c r="W19" s="8">
-        <f t="shared" ref="W19:X19" si="114">W17/W18</f>
+        <f t="shared" ref="W19:X19" si="110">W17/W18</f>
         <v>2.7589037041023641</v>
       </c>
       <c r="X19" s="8">
+        <f t="shared" si="110"/>
+        <v>2.3675040027985954</v>
+      </c>
+      <c r="Y19" s="8">
+        <f t="shared" ref="Y19" si="111">Y17/Y18</f>
+        <v>2.2507164673115994</v>
+      </c>
+      <c r="Z19" s="8">
+        <f t="shared" ref="Z19" si="112">Z17/Z18</f>
+        <v>2.252331041534922</v>
+      </c>
+      <c r="AA19" s="8">
+        <f t="shared" ref="AA19" si="113">AA17/AA18</f>
+        <v>2.3621220887208536</v>
+      </c>
+      <c r="AB19" s="8">
+        <f t="shared" ref="AB19:AC19" si="114">AB17/AB18</f>
+        <v>2.2099484681727057</v>
+      </c>
+      <c r="AC19" s="8">
         <f t="shared" si="114"/>
-        <v>2.3675040027985954</v>
-      </c>
-      <c r="Y19" s="8">
-        <f t="shared" ref="Y19" si="115">Y17/Y18</f>
-        <v>2.2507164673115994</v>
-      </c>
-      <c r="Z19" s="8">
-        <f t="shared" ref="Z19" si="116">Z17/Z18</f>
-        <v>2.252331041534922</v>
-      </c>
-      <c r="AA19" s="8">
-        <f t="shared" ref="AA19" si="117">AA17/AA18</f>
-        <v>2.3621220887208536</v>
-      </c>
-      <c r="AB19" s="8">
-        <f t="shared" ref="AB19:AC19" si="118">AB17/AB18</f>
-        <v>2.2099484681727057</v>
-      </c>
-      <c r="AC19" s="8">
+        <v>2.4620911427149066</v>
+      </c>
+      <c r="AD19" s="8">
+        <f t="shared" ref="AD19:AE19" si="115">AD17/AD18</f>
+        <v>2.7018554148783016</v>
+      </c>
+      <c r="AE19" s="8">
+        <f t="shared" si="115"/>
+        <v>2.9992061676735329</v>
+      </c>
+      <c r="AF19" s="8">
+        <f t="shared" ref="AF19:AG19" si="116">AF17/AF18</f>
+        <v>2.9992061676735329</v>
+      </c>
+      <c r="AG19" s="8">
+        <f t="shared" si="116"/>
+        <v>2.9425615220053012</v>
+      </c>
+      <c r="AH19" s="8">
+        <f t="shared" ref="AH19:AI19" si="117">AH17/AH18</f>
+        <v>2.9646172474101977</v>
+      </c>
+      <c r="AI19" s="8">
+        <f t="shared" si="117"/>
+        <v>3.3185793084891699</v>
+      </c>
+      <c r="AJ19" s="8">
+        <f t="shared" ref="AJ19:AL19" si="118">AJ17/AJ18</f>
+        <v>3.2429378531073447</v>
+      </c>
+      <c r="AK19" s="8">
         <f t="shared" si="118"/>
-        <v>2.4620911427149066</v>
-      </c>
-      <c r="AD19" s="8">
-        <f t="shared" ref="AD19:AE19" si="119">AD17/AD18</f>
-        <v>2.7018554148783016</v>
-      </c>
-      <c r="AE19" s="8">
+        <v>3.474470232088799</v>
+      </c>
+      <c r="AL19" s="8">
+        <f t="shared" si="118"/>
+        <v>3.6642895586652315</v>
+      </c>
+      <c r="AM19" s="8"/>
+      <c r="AN19" s="8"/>
+      <c r="AO19" s="8"/>
+      <c r="AP19" s="8"/>
+      <c r="AQ19" s="8"/>
+      <c r="AS19" s="8">
+        <f>AS17/AS18</f>
+        <v>3.3327606713360645</v>
+      </c>
+      <c r="AT19" s="8">
+        <f>AT17/AT18</f>
+        <v>4.0136117351658518</v>
+      </c>
+      <c r="AU19" s="8">
+        <f>AU17/AU18</f>
+        <v>5.1856746398837057</v>
+      </c>
+      <c r="AV19" s="8">
+        <f>AV17/AV18</f>
+        <v>5.8518567463988367</v>
+      </c>
+      <c r="AW19" s="8">
+        <f t="shared" ref="AW19:BF19" si="119">AW17/AW18</f>
+        <v>8.135190397790641</v>
+      </c>
+      <c r="AX19" s="8">
+        <f t="shared" ref="AX19:AY19" si="120">AX17/AX18</f>
+        <v>9.6294552157474804</v>
+      </c>
+      <c r="AY19" s="8">
+        <f t="shared" si="120"/>
+        <v>9.7360171144867671</v>
+      </c>
+      <c r="AZ19" s="8">
+        <f t="shared" ref="AZ19" si="121">AZ17/AZ18</f>
+        <v>11.904749091887529</v>
+      </c>
+      <c r="BA19" s="8">
         <f t="shared" si="119"/>
-        <v>2.9992061676735329</v>
-      </c>
-      <c r="AF19" s="8">
-        <f t="shared" ref="AF19:AG19" si="120">AF17/AF18</f>
-        <v>2.9992061676735329</v>
-      </c>
-      <c r="AG19" s="8">
-        <f t="shared" si="120"/>
-        <v>2.9425615220053012</v>
-      </c>
-      <c r="AH19" s="8">
-        <f t="shared" ref="AH19:AI19" si="121">AH17/AH18</f>
-        <v>2.9646172474101977</v>
-      </c>
-      <c r="AI19" s="8">
-        <f t="shared" si="121"/>
-        <v>3.3185793084891699</v>
-      </c>
-      <c r="AJ19" s="8">
-        <f t="shared" ref="AJ19:AL19" si="122">AJ17/AJ18</f>
-        <v>3.2429378531073447</v>
-      </c>
-      <c r="AK19" s="8">
+        <v>13.701829924650161</v>
+      </c>
+      <c r="BB19" s="8">
+        <f t="shared" si="119"/>
+        <v>15.736825738966628</v>
+      </c>
+      <c r="BC19" s="8">
+        <f t="shared" si="119"/>
+        <v>17.008439100137242</v>
+      </c>
+      <c r="BD19" s="8">
+        <f t="shared" si="119"/>
+        <v>18.080758753299548</v>
+      </c>
+      <c r="BE19" s="8">
+        <f t="shared" si="119"/>
+        <v>19.060484421032392</v>
+      </c>
+      <c r="BF19" s="8">
+        <f t="shared" si="119"/>
+        <v>19.871280065476256</v>
+      </c>
+      <c r="BG19" s="8">
+        <f t="shared" ref="BG19:BI19" si="122">BG17/BG18</f>
+        <v>20.496367179302545</v>
+      </c>
+      <c r="BH19" s="8">
         <f t="shared" si="122"/>
-        <v>3.474470232088799</v>
-      </c>
-      <c r="AL19" s="8">
+        <v>21.14080509269386</v>
+      </c>
+      <c r="BI19" s="8">
         <f t="shared" si="122"/>
-        <v>3.453995232290616</v>
-      </c>
-      <c r="AN19" s="8">
-        <f>AN17/AN18</f>
-        <v>3.3327606713360645</v>
-      </c>
-      <c r="AO19" s="8">
-        <f>AO17/AO18</f>
-        <v>4.0136117351658518</v>
-      </c>
-      <c r="AP19" s="8">
-        <f>AP17/AP18</f>
-        <v>5.1856746398837057</v>
-      </c>
-      <c r="AQ19" s="8">
-        <f>AQ17/AQ18</f>
-        <v>5.8518567463988367</v>
-      </c>
-      <c r="AR19" s="8">
-        <f t="shared" ref="AR19:BA19" si="123">AR17/AR18</f>
-        <v>8.135190397790641</v>
-      </c>
-      <c r="AS19" s="8">
-        <f t="shared" ref="AS19:AT19" si="124">AS17/AS18</f>
-        <v>9.6294552157474804</v>
-      </c>
-      <c r="AT19" s="8">
-        <f t="shared" si="124"/>
-        <v>9.7360171144867671</v>
-      </c>
-      <c r="AU19" s="8">
-        <f t="shared" ref="AU19" si="125">AU17/AU18</f>
-        <v>11.904749091887529</v>
-      </c>
-      <c r="AV19" s="8">
+        <v>21.562641290925534</v>
+      </c>
+      <c r="BJ19" s="8">
+        <f t="shared" ref="BJ19:BK19" si="123">BJ17/BJ18</f>
+        <v>21.992904414085604</v>
+      </c>
+      <c r="BK19" s="8">
         <f t="shared" si="123"/>
-        <v>13.490860351698629</v>
-      </c>
-      <c r="AW19" s="8">
-        <f t="shared" si="123"/>
-        <v>15.725486789654893</v>
-      </c>
-      <c r="AX19" s="8">
-        <f t="shared" si="123"/>
-        <v>17.010803271819047</v>
-      </c>
-      <c r="AY19" s="8">
-        <f t="shared" si="123"/>
-        <v>18.093542573816258</v>
-      </c>
-      <c r="AZ19" s="8">
-        <f t="shared" si="123"/>
-        <v>19.082266403681651</v>
-      </c>
-      <c r="BA19" s="8">
-        <f t="shared" si="123"/>
-        <v>19.900099449999903</v>
-      </c>
-      <c r="BB19" s="8">
-        <f t="shared" ref="BB19:BD19" si="126">BB17/BB18</f>
-        <v>20.53046310717378</v>
-      </c>
-      <c r="BC19" s="8">
-        <f t="shared" si="126"/>
-        <v>21.180382421884726</v>
-      </c>
-      <c r="BD19" s="8">
-        <f t="shared" si="126"/>
-        <v>21.605135930882906</v>
-      </c>
-      <c r="BE19" s="8">
-        <f t="shared" ref="BE19:BF19" si="127">BE17/BE18</f>
-        <v>22.038395968666645</v>
-      </c>
-      <c r="BF19" s="8">
-        <f t="shared" si="127"/>
-        <v>22.480332780397717</v>
+        <v>22.431762902682298</v>
       </c>
     </row>
-    <row r="21" spans="2:179" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:184" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>99</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" ref="G21:V22" si="128">G3/C3-1</f>
+        <f t="shared" ref="G21:V22" si="124">G3/C3-1</f>
         <v>-2.7214587018641989E-2</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>-1.898976632189564E-2</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>4.141114862537032E-2</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>6.8630503830105161E-2</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>0.20988949503427046</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>-9.5224813120606933E-2</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>2.2098716421860454E-2</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>-3.2635934495016672E-3</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>-8.8502225562171244E-2</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>0.12553178371046303</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>2.7382185396167769E-2</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>6.1041922469742049E-2</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>2.2196854388634168E-3</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>6.6009312517118612E-2</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>6.3134018020288618E-2</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>4.3588471923734051E-2</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" ref="W21:X23" si="129">W3/S3-1</f>
+        <f t="shared" ref="W21:X23" si="125">W3/S3-1</f>
         <v>5.2395114851610414E-2</v>
       </c>
       <c r="X21" s="9">
+        <f t="shared" si="125"/>
+        <v>6.7780061664953761E-2</v>
+      </c>
+      <c r="Y21" s="9">
+        <f t="shared" ref="Y21:Y23" si="126">Y3/U3-1</f>
+        <v>2.9218277721803965E-2</v>
+      </c>
+      <c r="Z21" s="9">
+        <f t="shared" ref="Z21:Z23" si="127">Z3/V3-1</f>
+        <v>-5.1853416411447917E-2</v>
+      </c>
+      <c r="AA21" s="9">
+        <f t="shared" ref="AA21:AA23" si="128">AA3/W3-1</f>
+        <v>-5.3514521075100685E-2</v>
+      </c>
+      <c r="AB21" s="9">
+        <f t="shared" ref="AB21:AL23" si="129">AB3/X3-1</f>
+        <v>-0.20511092930362385</v>
+      </c>
+      <c r="AC21" s="9">
         <f t="shared" si="129"/>
-        <v>6.7780061664953761E-2</v>
-      </c>
-      <c r="Y21" s="9">
-        <f t="shared" ref="Y21:Y23" si="130">Y3/U3-1</f>
-        <v>2.9218277721803965E-2</v>
-      </c>
-      <c r="Z21" s="9">
-        <f t="shared" ref="Z21:Z23" si="131">Z3/V3-1</f>
-        <v>-5.1853416411447917E-2</v>
-      </c>
-      <c r="AA21" s="9">
-        <f t="shared" ref="AA21:AA23" si="132">AA3/W3-1</f>
-        <v>-5.3514521075100685E-2</v>
-      </c>
-      <c r="AB21" s="9">
-        <f t="shared" ref="AB21:AL23" si="133">AB3/X3-1</f>
-        <v>-0.20511092930362385</v>
-      </c>
-      <c r="AC21" s="9">
-        <f t="shared" si="133"/>
         <v>-0.10238396867442123</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>-6.142793495210519E-2</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>-1.3086843275522564E-2</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>-5.9453895985953853E-2</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>0.21510136002052871</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>-0.2157479380525722</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>-1.6929514000643686E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>4.4029610556807208E-2</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>-0.1912253840874294</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="133"/>
-        <v>-1.0000000000000009E-2</v>
-      </c>
-      <c r="AO21" s="9">
-        <f t="shared" ref="AO21:BD21" si="134">AO3/AN3-1</f>
+        <f t="shared" si="129"/>
+        <v>0.29651206779148076</v>
+      </c>
+      <c r="AM21" s="9"/>
+      <c r="AN21" s="9"/>
+      <c r="AO21" s="9"/>
+      <c r="AP21" s="9"/>
+      <c r="AQ21" s="9"/>
+      <c r="AT21" s="9">
+        <f t="shared" ref="AT21:BI21" si="130">AT3/AS3-1</f>
         <v>1.5045403755055808E-2</v>
       </c>
-      <c r="AP21" s="9">
-        <f t="shared" si="134"/>
+      <c r="AU21" s="9">
+        <f t="shared" si="130"/>
         <v>2.4373226661705161E-2</v>
       </c>
-      <c r="AQ21" s="9">
-        <f t="shared" si="134"/>
+      <c r="AV21" s="9">
+        <f t="shared" si="130"/>
         <v>2.984758358685613E-2</v>
       </c>
-      <c r="AR21" s="9">
-        <f t="shared" si="134"/>
+      <c r="AW21" s="9">
+        <f t="shared" si="130"/>
         <v>4.457606443173967E-2</v>
       </c>
-      <c r="AS21" s="9">
-        <f t="shared" si="134"/>
+      <c r="AX21" s="9">
+        <f t="shared" si="130"/>
         <v>2.3327799195205001E-2</v>
       </c>
-      <c r="AT21" s="9">
-        <f t="shared" si="134"/>
+      <c r="AY21" s="9">
+        <f t="shared" si="130"/>
         <v>-0.11044657097288679</v>
       </c>
-      <c r="AU21" s="9">
-        <f t="shared" si="134"/>
+      <c r="AZ21" s="9">
+        <f t="shared" si="130"/>
         <v>-2.2736054653085813E-2</v>
       </c>
-      <c r="AV21" s="9">
-        <f t="shared" si="134"/>
-        <v>-5.2716676156133291E-2</v>
-      </c>
-      <c r="AW21" s="9">
-        <f t="shared" si="134"/>
+      <c r="BA21" s="9">
+        <f t="shared" si="130"/>
+        <v>1.1355728474726323E-2</v>
+      </c>
+      <c r="BB21" s="9">
+        <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AX21" s="9">
-        <f t="shared" si="134"/>
+      <c r="BC21" s="9">
+        <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AY21" s="9">
-        <f t="shared" si="134"/>
+      <c r="BD21" s="9">
+        <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AZ21" s="9">
-        <f t="shared" si="134"/>
+      <c r="BE21" s="9">
+        <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BA21" s="9">
-        <f t="shared" si="134"/>
+      <c r="BF21" s="9">
+        <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BB21" s="9">
-        <f t="shared" si="134"/>
+      <c r="BG21" s="9">
+        <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BC21" s="9">
-        <f t="shared" si="134"/>
+      <c r="BH21" s="9">
+        <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BD21" s="9">
-        <f t="shared" si="134"/>
+      <c r="BI21" s="9">
+        <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BE21" s="9">
-        <f t="shared" ref="BE21:BE23" si="135">BE3/BD3-1</f>
+      <c r="BJ21" s="9">
+        <f t="shared" ref="BJ21:BJ23" si="131">BJ3/BI3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BF21" s="9">
-        <f t="shared" ref="BF21:BF23" si="136">BF3/BE3-1</f>
+      <c r="BK21" s="9">
+        <f t="shared" ref="BK21:BK23" si="132">BK3/BJ3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BH21" t="s">
+      <c r="BM21" t="s">
         <v>86</v>
       </c>
-      <c r="BI21" s="9">
+      <c r="BN21" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="22" spans="2:179" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:184" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>85</v>
       </c>
       <c r="G22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.47126436781609193</v>
+      </c>
+      <c r="H22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.45531576856878053</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.34555696057018048</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.35379136992040228</v>
+      </c>
+      <c r="K22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.15087890625</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.47852983988355158</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.29201196070055535</v>
+      </c>
+      <c r="N22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.28531641652483364</v>
+      </c>
+      <c r="O22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.46686465846414937</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.147612601525966</v>
+      </c>
+      <c r="Q22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.26628314487866156</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.19694233778740822</v>
+      </c>
+      <c r="S22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.23508995198704219</v>
+      </c>
+      <c r="T22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.26620556538523399</v>
+      </c>
+      <c r="U22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.29676240208877291</v>
+      </c>
+      <c r="V22" s="9">
+        <f t="shared" si="124"/>
+        <v>0.36850045257970421</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" si="125"/>
+        <v>0.34354362793311788</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" si="125"/>
+        <v>0.31050982384823844</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" si="126"/>
+        <v>0.2883662867957959</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" si="127"/>
+        <v>0.24601308150216794</v>
+      </c>
+      <c r="AA22" s="9">
         <f t="shared" si="128"/>
-        <v>0.47126436781609193</v>
-      </c>
-      <c r="H22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.45531576856878053</v>
-      </c>
-      <c r="I22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.34555696057018048</v>
-      </c>
-      <c r="J22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.35379136992040228</v>
-      </c>
-      <c r="K22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.15087890625</v>
-      </c>
-      <c r="L22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.47852983988355158</v>
-      </c>
-      <c r="M22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.29201196070055535</v>
-      </c>
-      <c r="N22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.28531641652483364</v>
-      </c>
-      <c r="O22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.46686465846414937</v>
-      </c>
-      <c r="P22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.147612601525966</v>
-      </c>
-      <c r="Q22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.26628314487866156</v>
-      </c>
-      <c r="R22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.19694233778740822</v>
-      </c>
-      <c r="S22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.23508995198704219</v>
-      </c>
-      <c r="T22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.26620556538523399</v>
-      </c>
-      <c r="U22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.29676240208877291</v>
-      </c>
-      <c r="V22" s="9">
-        <f t="shared" si="128"/>
-        <v>0.36850045257970421</v>
-      </c>
-      <c r="W22" s="9">
+        <v>0.19852889911455063</v>
+      </c>
+      <c r="AB22" s="9">
         <f t="shared" si="129"/>
-        <v>0.34354362793311788</v>
-      </c>
-      <c r="X22" s="9">
+        <v>0.17063556173058902</v>
+      </c>
+      <c r="AC22" s="9">
         <f t="shared" si="129"/>
-        <v>0.31050982384823844</v>
-      </c>
-      <c r="Y22" s="9">
-        <f t="shared" si="130"/>
-        <v>0.2883662867957959</v>
-      </c>
-      <c r="Z22" s="9">
+        <v>0.16487466399950002</v>
+      </c>
+      <c r="AD22" s="9">
+        <f t="shared" si="129"/>
+        <v>0.16004600548526948</v>
+      </c>
+      <c r="AE22" s="9">
+        <f t="shared" si="129"/>
+        <v>0.19199557895349173</v>
+      </c>
+      <c r="AF22" s="9">
+        <f t="shared" si="129"/>
+        <v>0.13116202042506209</v>
+      </c>
+      <c r="AG22" s="9">
+        <f t="shared" si="129"/>
+        <v>0.15589363814430213</v>
+      </c>
+      <c r="AH22" s="9">
+        <f t="shared" si="129"/>
+        <v>0.30948749237339834</v>
+      </c>
+      <c r="AI22" s="9">
+        <f t="shared" si="129"/>
+        <v>0.22768532526475038</v>
+      </c>
+      <c r="AJ22" s="9">
+        <f t="shared" si="129"/>
+        <v>0.30332829046898646</v>
+      </c>
+      <c r="AK22" s="9">
+        <f t="shared" si="129"/>
+        <v>0.27085122681585005</v>
+      </c>
+      <c r="AL22" s="9">
+        <f t="shared" si="129"/>
+        <v>0.15132983886623963</v>
+      </c>
+      <c r="AM22" s="9"/>
+      <c r="AN22" s="9"/>
+      <c r="AO22" s="9"/>
+      <c r="AP22" s="9"/>
+      <c r="AQ22" s="9"/>
+      <c r="AT22" s="9">
+        <f t="shared" ref="AT22:BI22" si="133">AT4/AS4-1</f>
+        <v>0.39996947496947488</v>
+      </c>
+      <c r="AU22" s="9">
+        <f t="shared" si="133"/>
+        <v>0.30331639884002359</v>
+      </c>
+      <c r="AV22" s="9">
+        <f t="shared" si="133"/>
+        <v>0.25429116338207258</v>
+      </c>
+      <c r="AW22" s="9">
+        <f t="shared" si="133"/>
+        <v>0.29396857577293467</v>
+      </c>
+      <c r="AX22" s="9">
+        <f t="shared" si="133"/>
+        <v>0.29401941987754343</v>
+      </c>
+      <c r="AY22" s="9">
+        <f t="shared" si="133"/>
+        <v>0.17268078191463943</v>
+      </c>
+      <c r="AZ22" s="9">
+        <f t="shared" si="133"/>
+        <v>0.19927861102054134</v>
+      </c>
+      <c r="BA22" s="9">
+        <f t="shared" si="133"/>
+        <v>0.23349928916529317</v>
+      </c>
+      <c r="BB22" s="9">
+        <f t="shared" si="133"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="BC22" s="9">
+        <f t="shared" si="133"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="BD22" s="9">
+        <f t="shared" si="133"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="BE22" s="9">
+        <f t="shared" si="133"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="BF22" s="9">
+        <f t="shared" si="133"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="BG22" s="9">
+        <f t="shared" si="133"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="BH22" s="9">
+        <f t="shared" si="133"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="BI22" s="9">
+        <f t="shared" si="133"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BJ22" s="9">
         <f t="shared" si="131"/>
-        <v>0.24601308150216794</v>
-      </c>
-      <c r="AA22" s="9">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BK22" s="9">
         <f t="shared" si="132"/>
-        <v>0.19852889911455063</v>
-      </c>
-      <c r="AB22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.17063556173058902</v>
-      </c>
-      <c r="AC22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.16487466399950002</v>
-      </c>
-      <c r="AD22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.16004600548526948</v>
-      </c>
-      <c r="AE22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.19199557895349173</v>
-      </c>
-      <c r="AF22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.13116202042506209</v>
-      </c>
-      <c r="AG22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.15589363814430213</v>
-      </c>
-      <c r="AH22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.30948749237339834</v>
-      </c>
-      <c r="AI22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.22768532526475038</v>
-      </c>
-      <c r="AJ22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.30332829046898646</v>
-      </c>
-      <c r="AK22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.27085122681585005</v>
-      </c>
-      <c r="AL22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AO22" s="9">
-        <f t="shared" ref="AO22:BD22" si="137">AO4/AN4-1</f>
-        <v>0.39996947496947488</v>
-      </c>
-      <c r="AP22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.30331639884002359</v>
-      </c>
-      <c r="AQ22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.25429116338207258</v>
-      </c>
-      <c r="AR22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.29396857577293467</v>
-      </c>
-      <c r="AS22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.29401941987754343</v>
-      </c>
-      <c r="AT22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.17268078191463943</v>
-      </c>
-      <c r="AU22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.19927861102054134</v>
-      </c>
-      <c r="AV22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.24769899123775874</v>
-      </c>
-      <c r="AW22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AX22" s="9">
-        <f t="shared" si="137"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AY22" s="9">
-        <f t="shared" si="137"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="AZ22" s="9">
-        <f t="shared" si="137"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="BA22" s="9">
-        <f t="shared" si="137"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="BB22" s="9">
-        <f t="shared" si="137"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="BC22" s="9">
-        <f t="shared" si="137"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="BD22" s="9">
-        <f t="shared" si="137"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE22" s="9">
-        <f t="shared" si="135"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="BF22" s="9">
-        <f t="shared" si="136"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="BH22" t="s">
+      <c r="BM22" t="s">
         <v>87</v>
       </c>
-      <c r="BI22" s="9">
+      <c r="BN22" s="9">
         <v>0.05</v>
       </c>
     </row>
-    <row r="23" spans="2:179" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:184" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
         <v>79</v>
       </c>
@@ -6061,19 +6173,19 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="9">
-        <f t="shared" ref="G23:J23" si="138">G5/C5-1</f>
+        <f t="shared" ref="G23:J23" si="134">G5/C5-1</f>
         <v>0.13297626743004898</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>0.11972430883605667</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>0.15539376184732046</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>0.17496582698691654</v>
       </c>
       <c r="K23" s="9">
@@ -6081,194 +6193,199 @@
         <v>0.18526367267095933</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" ref="L23:V23" si="139">L5/H5-1</f>
+        <f t="shared" ref="L23:V23" si="135">L5/H5-1</f>
         <v>0.12286465177398154</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="135"/>
         <v>0.13990081658525666</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="135"/>
         <v>0.12072461359481479</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="135"/>
         <v>0.13653555219364599</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="135"/>
         <v>0.13658341289150311</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="135"/>
         <v>0.14556278826338698</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="135"/>
         <v>0.12800664353293589</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="135"/>
         <v>0.12400544546967174</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="135"/>
         <v>0.16718148810491518</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="135"/>
         <v>0.19088546871876866</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="135"/>
         <v>0.21347251071437956</v>
       </c>
       <c r="W23" s="9">
+        <f t="shared" si="125"/>
+        <v>0.21970716477364483</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" si="125"/>
+        <v>0.2008543040208004</v>
+      </c>
+      <c r="Y23" s="9">
+        <f t="shared" si="126"/>
+        <v>0.18352275451973332</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" si="127"/>
+        <v>0.12378661813139202</v>
+      </c>
+      <c r="AA23" s="9">
+        <f t="shared" si="128"/>
+        <v>0.1060308493501334</v>
+      </c>
+      <c r="AB23" s="9">
         <f t="shared" si="129"/>
-        <v>0.21970716477364483</v>
-      </c>
-      <c r="X23" s="9">
+        <v>1.9699195793380753E-2</v>
+      </c>
+      <c r="AC23" s="9">
         <f t="shared" si="129"/>
-        <v>0.2008543040208004</v>
-      </c>
-      <c r="Y23" s="9">
-        <f t="shared" si="130"/>
-        <v>0.18352275451973332</v>
-      </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="131"/>
-        <v>0.12378661813139202</v>
-      </c>
-      <c r="AA23" s="9">
-        <f t="shared" si="132"/>
-        <v>0.1060308493501334</v>
-      </c>
-      <c r="AB23" s="9">
-        <f t="shared" si="133"/>
-        <v>1.9699195793380753E-2</v>
-      </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="133"/>
         <v>7.0846839546191198E-2</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>8.3370288248336921E-2</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>0.12758868361198683</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>7.1473259142700085E-2</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>0.17335452257979078</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>0.15195144957198026</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>0.16044729904276589</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>0.23205407222605579</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>0.12973234440503068</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="133"/>
-        <v>0.1571188221298685</v>
-      </c>
-      <c r="AO23" s="9">
-        <f>AO5/AN5-1</f>
+        <f t="shared" si="129"/>
+        <v>0.18097548163826538</v>
+      </c>
+      <c r="AM23" s="9"/>
+      <c r="AN23" s="9"/>
+      <c r="AO23" s="9"/>
+      <c r="AP23" s="9"/>
+      <c r="AQ23" s="9"/>
+      <c r="AT23" s="9">
+        <f>AT5/AS5-1</f>
         <v>0.14599017663367975</v>
       </c>
-      <c r="AP23" s="9">
-        <f t="shared" ref="AP23:BD23" si="140">AP5/AO5-1</f>
+      <c r="AU23" s="9">
+        <f t="shared" ref="AU23:BI23" si="136">AU5/AT5-1</f>
         <v>0.14029539688292858</v>
       </c>
-      <c r="AQ23" s="9">
-        <f t="shared" si="140"/>
+      <c r="AV23" s="9">
+        <f t="shared" si="136"/>
         <v>0.13645574247276371</v>
       </c>
-      <c r="AR23" s="9">
-        <f t="shared" si="140"/>
+      <c r="AW23" s="9">
+        <f t="shared" si="136"/>
         <v>0.17531727441177503</v>
       </c>
-      <c r="AS23" s="9">
-        <f t="shared" si="140"/>
+      <c r="AX23" s="9">
+        <f t="shared" si="136"/>
         <v>0.17956070629670173</v>
       </c>
-      <c r="AT23" s="9">
-        <f t="shared" si="140"/>
+      <c r="AY23" s="9">
+        <f t="shared" si="136"/>
         <v>6.8820295556564215E-2</v>
       </c>
-      <c r="AU23" s="9">
-        <f t="shared" si="140"/>
+      <c r="AZ23" s="9">
+        <f t="shared" si="136"/>
         <v>0.13149611872684797</v>
       </c>
-      <c r="AV23" s="9">
-        <f t="shared" si="140"/>
-        <v>0.1684821983393181</v>
-      </c>
-      <c r="AW23" s="9">
-        <f t="shared" si="140"/>
-        <v>0.12007180638235093</v>
-      </c>
-      <c r="AX23" s="9">
-        <f t="shared" si="140"/>
-        <v>6.6506456380035273E-2</v>
-      </c>
-      <c r="AY23" s="9">
-        <f t="shared" si="140"/>
-        <v>5.0872415409183969E-2</v>
-      </c>
-      <c r="AZ23" s="9">
-        <f t="shared" si="140"/>
-        <v>4.2981937444320995E-2</v>
-      </c>
       <c r="BA23" s="9">
-        <f t="shared" si="140"/>
-        <v>3.4902900812497695E-2</v>
+        <f t="shared" si="136"/>
+        <v>0.17492211643124356</v>
       </c>
       <c r="BB23" s="9">
-        <f t="shared" si="140"/>
-        <v>2.6683701646253999E-2</v>
+        <f t="shared" si="136"/>
+        <v>0.11822265763655193</v>
       </c>
       <c r="BC23" s="9">
-        <f t="shared" si="140"/>
-        <v>2.6737591790039206E-2</v>
+        <f t="shared" si="136"/>
+        <v>6.5649049602108045E-2</v>
       </c>
       <c r="BD23" s="9">
-        <f t="shared" si="140"/>
-        <v>1.8395387332455826E-2</v>
+        <f t="shared" si="136"/>
+        <v>5.0284619830460064E-2</v>
       </c>
       <c r="BE23" s="9">
-        <f t="shared" si="135"/>
-        <v>1.8408615342941914E-2</v>
+        <f t="shared" si="136"/>
+        <v>4.2525809643622514E-2</v>
       </c>
       <c r="BF23" s="9">
         <f t="shared" si="136"/>
-        <v>1.8421754805081347E-2</v>
-      </c>
-      <c r="BH23" t="s">
+        <v>3.4569247933639913E-2</v>
+      </c>
+      <c r="BG23" s="9">
+        <f t="shared" si="136"/>
+        <v>2.646547933001786E-2</v>
+      </c>
+      <c r="BH23" s="9">
+        <f t="shared" si="136"/>
+        <v>2.6522176392125729E-2</v>
+      </c>
+      <c r="BI23" s="9">
+        <f t="shared" si="136"/>
+        <v>1.828907649306788E-2</v>
+      </c>
+      <c r="BJ23" s="9">
+        <f t="shared" si="131"/>
+        <v>1.8303003752183189E-2</v>
+      </c>
+      <c r="BK23" s="9">
+        <f t="shared" si="132"/>
+        <v>1.8316840661395162E-2</v>
+      </c>
+      <c r="BM23" t="s">
         <v>88</v>
       </c>
-      <c r="BI23" s="23">
-        <f>NPV(BI22,AV17:FW17)</f>
-        <v>2770218.7559484853</v>
+      <c r="BN23" s="23">
+        <f>NPV(BN22,BB17:GB17)</f>
+        <v>2803246.2306998842</v>
       </c>
     </row>
-    <row r="24" spans="2:179" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:184" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>95</v>
       </c>
@@ -6277,711 +6394,726 @@
         <v>0.75636140971560761</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" ref="D24:V24" si="141">(D3-D6)/D3</f>
+        <f t="shared" ref="D24:V24" si="137">(D3-D6)/D3</f>
         <v>0.70568598478629674</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.78812099497002686</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.8043843806439559</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.79157924185200723</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.69329465580720739</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.77338891094349604</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.79503467568040098</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.78906295161570028</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.63715395523768414</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.77725271879854996</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.80716833304098701</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.79039827498731607</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.72796494111202414</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.78728498519311951</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.75918884664131814</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.77238499019173579</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.68869475847893113</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.74651810584958223</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>0.7736297391488014</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" ref="W24:X24" si="142">(W3-W6)/W3</f>
+        <f t="shared" ref="W24:X24" si="138">(W3-W6)/W3</f>
         <v>0.77199206301485179</v>
       </c>
       <c r="X24" s="9">
+        <f t="shared" si="138"/>
+        <v>0.69531738774724483</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" ref="Y24:Y25" si="139">(Y3-Y6)/Y3</f>
+        <v>0.73603593228146957</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" ref="Z24" si="140">(Z3-Z6)/Z3</f>
+        <v>0.75735130318556476</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" ref="AA24:AA25" si="141">(AA3-AA6)/AA3</f>
+        <v>0.72670097198399086</v>
+      </c>
+      <c r="AB24" s="9">
+        <f t="shared" ref="AB24:AC24" si="142">(AB3-AB6)/AB3</f>
+        <v>0.65550644790216139</v>
+      </c>
+      <c r="AC24" s="9">
         <f t="shared" si="142"/>
-        <v>0.69531738774724483</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" ref="Y24:Y25" si="143">(Y3-Y6)/Y3</f>
-        <v>0.73603593228146957</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" ref="Z24" si="144">(Z3-Z6)/Z3</f>
-        <v>0.75735130318556476</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" ref="AA24:AA25" si="145">(AA3-AA6)/AA3</f>
-        <v>0.72670097198399086</v>
-      </c>
-      <c r="AB24" s="9">
-        <f t="shared" ref="AB24:AC24" si="146">(AB3-AB6)/AB3</f>
-        <v>0.65550644790216139</v>
-      </c>
-      <c r="AC24" s="9">
+        <v>0.74717731588401337</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" ref="AD24:AE24" si="143">(AD3-AD6)/AD3</f>
+        <v>0.77030795704028954</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" si="143"/>
+        <v>0.77270679111683294</v>
+      </c>
+      <c r="AF24" s="9">
+        <f t="shared" ref="AF24:AG24" si="144">(AF3-AF6)/AF3</f>
+        <v>0.77270679111683294</v>
+      </c>
+      <c r="AG24" s="9">
+        <f t="shared" si="144"/>
+        <v>0.68512750118789922</v>
+      </c>
+      <c r="AH24" s="9">
+        <f t="shared" ref="AH24:AI24" si="145">(AH3-AH6)/AH3</f>
+        <v>0.89120072633729286</v>
+      </c>
+      <c r="AI24" s="9">
+        <f t="shared" si="145"/>
+        <v>0.78431115767417492</v>
+      </c>
+      <c r="AJ24" s="9">
+        <f t="shared" ref="AJ24:AL24" si="146">(AJ3-AJ6)/AJ3</f>
+        <v>0.76225414637153954</v>
+      </c>
+      <c r="AK24" s="9">
         <f t="shared" si="146"/>
-        <v>0.74717731588401337</v>
-      </c>
-      <c r="AD24" s="9">
-        <f t="shared" ref="AD24:AE24" si="147">(AD3-AD6)/AD3</f>
-        <v>0.77030795704028954</v>
-      </c>
-      <c r="AE24" s="9">
+        <v>0.80174946145309745</v>
+      </c>
+      <c r="AL24" s="9">
+        <f t="shared" si="146"/>
+        <v>0.8066059757236228</v>
+      </c>
+      <c r="AM24" s="9"/>
+      <c r="AN24" s="9"/>
+      <c r="AO24" s="9"/>
+      <c r="AP24" s="9"/>
+      <c r="AQ24" s="9"/>
+      <c r="AS24" s="9">
+        <f t="shared" ref="AS24:AW24" si="147">(AS3-AS6)/AS3</f>
+        <v>0.76117782219354435</v>
+      </c>
+      <c r="AT24" s="9">
         <f t="shared" si="147"/>
-        <v>0.77270679111683294</v>
-      </c>
-      <c r="AF24" s="9">
-        <f t="shared" ref="AF24:AG24" si="148">(AF3-AF6)/AF3</f>
-        <v>0.77270679111683294</v>
-      </c>
-      <c r="AG24" s="9">
+        <v>0.76091911251686128</v>
+      </c>
+      <c r="AU24" s="9">
+        <f t="shared" si="147"/>
+        <v>0.75369689264254036</v>
+      </c>
+      <c r="AV24" s="9">
+        <f t="shared" si="147"/>
+        <v>0.76459781602269217</v>
+      </c>
+      <c r="AW24" s="9">
+        <f t="shared" si="147"/>
+        <v>0.74366153586402906</v>
+      </c>
+      <c r="AX24" s="9">
+        <f t="shared" ref="AX24:AY24" si="148">(AX3-AX6)/AX3</f>
+        <v>0.73788703734257277</v>
+      </c>
+      <c r="AY24" s="9">
         <f t="shared" si="148"/>
-        <v>0.68512750118789922</v>
-      </c>
-      <c r="AH24" s="9">
-        <f t="shared" ref="AH24:AI24" si="149">(AH3-AH6)/AH3</f>
-        <v>0.89120072633729286</v>
-      </c>
-      <c r="AI24" s="9">
+        <v>0.72481800336944935</v>
+      </c>
+      <c r="AZ24" s="9">
+        <f t="shared" ref="AZ24:BI24" si="149">(AZ3-AZ6)/AZ3</f>
+        <v>0.7712405896121971</v>
+      </c>
+      <c r="BA24" s="9">
         <f t="shared" si="149"/>
-        <v>0.78431115767417492</v>
-      </c>
-      <c r="AJ24" s="9">
-        <f t="shared" ref="AJ24:AL24" si="150">(AJ3-AJ6)/AJ3</f>
-        <v>0.76225414637153954</v>
-      </c>
-      <c r="AK24" s="9">
+        <v>0.78886873299346327</v>
+      </c>
+      <c r="BB24" s="9">
+        <f t="shared" si="149"/>
+        <v>0.77</v>
+      </c>
+      <c r="BC24" s="9">
+        <f t="shared" si="149"/>
+        <v>0.76999999999999991</v>
+      </c>
+      <c r="BD24" s="9">
+        <f t="shared" si="149"/>
+        <v>0.77</v>
+      </c>
+      <c r="BE24" s="9">
+        <f t="shared" si="149"/>
+        <v>0.77</v>
+      </c>
+      <c r="BF24" s="9">
+        <f t="shared" si="149"/>
+        <v>0.77</v>
+      </c>
+      <c r="BG24" s="9">
+        <f t="shared" si="149"/>
+        <v>0.77</v>
+      </c>
+      <c r="BH24" s="9">
+        <f t="shared" si="149"/>
+        <v>0.76999999999999991</v>
+      </c>
+      <c r="BI24" s="9">
+        <f t="shared" si="149"/>
+        <v>0.77</v>
+      </c>
+      <c r="BJ24" s="9">
+        <f t="shared" ref="BJ24:BK24" si="150">(BJ3-BJ6)/BJ3</f>
+        <v>0.77</v>
+      </c>
+      <c r="BK24" s="9">
         <f t="shared" si="150"/>
-        <v>0.80174946145309745</v>
-      </c>
-      <c r="AL24" s="9">
-        <f t="shared" si="150"/>
-        <v>0.78</v>
-      </c>
-      <c r="AN24" s="9">
-        <f t="shared" ref="AN24:AR24" si="151">(AN3-AN6)/AN3</f>
-        <v>0.76117782219354435</v>
-      </c>
-      <c r="AO24" s="9">
-        <f t="shared" si="151"/>
-        <v>0.76091911251686128</v>
-      </c>
-      <c r="AP24" s="9">
-        <f t="shared" si="151"/>
-        <v>0.75369689264254036</v>
-      </c>
-      <c r="AQ24" s="9">
-        <f t="shared" si="151"/>
-        <v>0.76459781602269217</v>
-      </c>
-      <c r="AR24" s="9">
-        <f t="shared" si="151"/>
-        <v>0.74366153586402906</v>
-      </c>
-      <c r="AS24" s="9">
-        <f t="shared" ref="AS24:AT24" si="152">(AS3-AS6)/AS3</f>
-        <v>0.73788703734257277</v>
-      </c>
-      <c r="AT24" s="9">
-        <f t="shared" si="152"/>
-        <v>0.72481800336944935</v>
-      </c>
-      <c r="AU24" s="9">
-        <f t="shared" ref="AU24:BD24" si="153">(AU3-AU6)/AU3</f>
-        <v>0.7712405896121971</v>
-      </c>
-      <c r="AV24" s="9">
-        <f t="shared" si="153"/>
-        <v>0.7818565876220035</v>
-      </c>
-      <c r="AW24" s="9">
-        <f t="shared" si="153"/>
         <v>0.77</v>
       </c>
-      <c r="AX24" s="9">
-        <f t="shared" si="153"/>
-        <v>0.77</v>
-      </c>
-      <c r="AY24" s="9">
-        <f t="shared" si="153"/>
-        <v>0.77</v>
-      </c>
-      <c r="AZ24" s="9">
-        <f t="shared" si="153"/>
-        <v>0.77</v>
-      </c>
-      <c r="BA24" s="9">
-        <f t="shared" si="153"/>
-        <v>0.77</v>
-      </c>
-      <c r="BB24" s="9">
-        <f t="shared" si="153"/>
-        <v>0.77</v>
-      </c>
-      <c r="BC24" s="9">
-        <f t="shared" si="153"/>
-        <v>0.76999999999999991</v>
-      </c>
-      <c r="BD24" s="9">
-        <f t="shared" si="153"/>
-        <v>0.77</v>
-      </c>
-      <c r="BE24" s="9">
-        <f t="shared" ref="BE24:BF24" si="154">(BE3-BE6)/BE3</f>
-        <v>0.77</v>
-      </c>
-      <c r="BF24" s="9">
-        <f t="shared" si="154"/>
-        <v>0.77</v>
-      </c>
-      <c r="BH24" t="s">
+      <c r="BM24" t="s">
         <v>91</v>
       </c>
-      <c r="BI24" s="23">
+      <c r="BN24" s="23">
         <f>Main!D8</f>
-        <v>42166</v>
+        <v>66819</v>
       </c>
     </row>
-    <row r="25" spans="2:179" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:184" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>96</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:V25" si="155">(C4-C7)/C4</f>
+        <f t="shared" ref="C25:V25" si="151">(C4-C7)/C4</f>
         <v>0.38750000000000001</v>
       </c>
       <c r="D25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.40116509996028066</v>
+      </c>
+      <c r="E25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.42694562593401542</v>
+      </c>
+      <c r="F25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.44333891914537077</v>
+      </c>
+      <c r="G25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.48261718749999999</v>
+      </c>
+      <c r="H25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.49363173216885009</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.50072618539085856</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.51841250193408639</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.46915570640644888</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.59771105094757571</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.55504860146796275</v>
+      </c>
+      <c r="N25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.57180690983507887</v>
+      </c>
+      <c r="O25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.58922890032972752</v>
+      </c>
+      <c r="P25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.60366736368023166</v>
+      </c>
+      <c r="Q25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.60318537859007837</v>
+      </c>
+      <c r="R25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.59926581514633415</v>
+      </c>
+      <c r="S25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.65317783710364852</v>
+      </c>
+      <c r="T25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.65548780487804881</v>
+      </c>
+      <c r="U25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.64692143518704948</v>
+      </c>
+      <c r="V25" s="9">
+        <f t="shared" si="151"/>
+        <v>0.64341882854413168</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" ref="W25:X25" si="152">(W4-W7)/W4</f>
+        <v>0.65648748518441047</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="152"/>
+        <v>0.618792206533329</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="139"/>
+        <v>0.65521660311308372</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" ref="Z25" si="153">(Z4-Z7)/Z4</f>
+        <v>0.64398832168450859</v>
+      </c>
+      <c r="AA25" s="9">
+        <f t="shared" si="141"/>
+        <v>0.67569296995433525</v>
+      </c>
+      <c r="AB25" s="9">
+        <f t="shared" ref="AB25:AC25" si="154">(AB4-AB7)/AB4</f>
+        <v>0.67435826662986476</v>
+      </c>
+      <c r="AC25" s="9">
+        <f t="shared" si="154"/>
+        <v>0.67299900721779493</v>
+      </c>
+      <c r="AD25" s="9">
+        <f t="shared" ref="AD25:AE25" si="155">(AD4-AD7)/AD4</f>
+        <v>0.67144600366076879</v>
+      </c>
+      <c r="AE25" s="9">
         <f t="shared" si="155"/>
-        <v>0.40116509996028066</v>
-      </c>
-      <c r="E25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.42694562593401542</v>
-      </c>
-      <c r="F25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.44333891914537077</v>
-      </c>
-      <c r="G25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.48261718749999999</v>
-      </c>
-      <c r="H25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.49363173216885009</v>
-      </c>
-      <c r="I25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.50072618539085856</v>
-      </c>
-      <c r="J25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.51841250193408639</v>
-      </c>
-      <c r="K25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.46915570640644888</v>
-      </c>
-      <c r="L25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.59771105094757571</v>
-      </c>
-      <c r="M25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.55504860146796275</v>
-      </c>
-      <c r="N25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.57180690983507887</v>
-      </c>
-      <c r="O25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.58922890032972752</v>
-      </c>
-      <c r="P25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.60366736368023166</v>
-      </c>
-      <c r="Q25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.60318537859007837</v>
-      </c>
-      <c r="R25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.59926581514633415</v>
-      </c>
-      <c r="S25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.65317783710364852</v>
-      </c>
-      <c r="T25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.65548780487804881</v>
-      </c>
-      <c r="U25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.64692143518704948</v>
-      </c>
-      <c r="V25" s="9">
-        <f t="shared" si="155"/>
-        <v>0.64341882854413168</v>
-      </c>
-      <c r="W25" s="9">
-        <f t="shared" ref="W25:X25" si="156">(W4-W7)/W4</f>
-        <v>0.65648748518441047</v>
-      </c>
-      <c r="X25" s="9">
+        <v>0.68837538431506518</v>
+      </c>
+      <c r="AF25" s="9">
+        <f t="shared" ref="AF25:AG25" si="156">(AF4-AF7)/AF4</f>
+        <v>0.68837538431506518</v>
+      </c>
+      <c r="AG25" s="9">
         <f t="shared" si="156"/>
-        <v>0.618792206533329</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="143"/>
-        <v>0.65521660311308372</v>
-      </c>
-      <c r="Z25" s="9">
-        <f t="shared" ref="Z25" si="157">(Z4-Z7)/Z4</f>
-        <v>0.64398832168450859</v>
-      </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="145"/>
-        <v>0.67569296995433525</v>
-      </c>
-      <c r="AB25" s="9">
-        <f t="shared" ref="AB25:AC25" si="158">(AB4-AB7)/AB4</f>
-        <v>0.67435826662986476</v>
-      </c>
-      <c r="AC25" s="9">
+        <v>0.68293135866663568</v>
+      </c>
+      <c r="AH25" s="9">
+        <f t="shared" ref="AH25:AI25" si="157">(AH4-AH7)/AH4</f>
+        <v>0.64577751892836344</v>
+      </c>
+      <c r="AI25" s="9">
+        <f t="shared" si="157"/>
+        <v>0.66599089698487468</v>
+      </c>
+      <c r="AJ25" s="9">
+        <f t="shared" ref="AJ25:AL25" si="158">(AJ4-AJ7)/AJ4</f>
+        <v>0.66407054462396797</v>
+      </c>
+      <c r="AK25" s="9">
         <f t="shared" si="158"/>
-        <v>0.67299900721779493</v>
-      </c>
-      <c r="AD25" s="9">
-        <f t="shared" ref="AD25:AE25" si="159">(AD4-AD7)/AD4</f>
-        <v>0.67144600366076879</v>
-      </c>
-      <c r="AE25" s="9">
+        <v>0.65510438928160453</v>
+      </c>
+      <c r="AL25" s="9">
+        <f t="shared" si="158"/>
+        <v>0.65095691762920493</v>
+      </c>
+      <c r="AM25" s="9"/>
+      <c r="AN25" s="9"/>
+      <c r="AO25" s="9"/>
+      <c r="AP25" s="9"/>
+      <c r="AQ25" s="9"/>
+      <c r="AS25" s="9">
+        <f t="shared" ref="AS25:AW25" si="159">(AS4-AS7)/AS4</f>
+        <v>0.41739926739926742</v>
+      </c>
+      <c r="AT25" s="9">
         <f t="shared" si="159"/>
-        <v>0.68837538431506518</v>
-      </c>
-      <c r="AF25" s="9">
-        <f t="shared" ref="AF25:AG25" si="160">(AF4-AF7)/AF4</f>
-        <v>0.68837538431506518</v>
-      </c>
-      <c r="AG25" s="9">
+        <v>0.4999672938970412</v>
+      </c>
+      <c r="AU25" s="9">
+        <f t="shared" si="159"/>
+        <v>0.55437146585471941</v>
+      </c>
+      <c r="AV25" s="9">
+        <f t="shared" si="159"/>
+        <v>0.59904766985888447</v>
+      </c>
+      <c r="AW25" s="9">
+        <f t="shared" si="159"/>
+        <v>0.64940111736450412</v>
+      </c>
+      <c r="AX25" s="9">
+        <f t="shared" ref="AX25:AY25" si="160">(AX4-AX7)/AX4</f>
+        <v>0.64349440010196113</v>
+      </c>
+      <c r="AY25" s="9">
         <f t="shared" si="160"/>
-        <v>0.68293135866663568</v>
-      </c>
-      <c r="AH25" s="9">
-        <f t="shared" ref="AH25:AI25" si="161">(AH4-AH7)/AH4</f>
-        <v>0.64577751892836344</v>
-      </c>
-      <c r="AI25" s="9">
+        <v>0.67354771220519505</v>
+      </c>
+      <c r="AZ25" s="9">
+        <f t="shared" ref="AZ25:BI25" si="161">(AZ4-AZ7)/AZ4</f>
+        <v>0.67461895294897278</v>
+      </c>
+      <c r="BA25" s="9">
         <f t="shared" si="161"/>
-        <v>0.66599089698487468</v>
-      </c>
-      <c r="AJ25" s="9">
-        <f t="shared" ref="AJ25:AL25" si="162">(AJ4-AJ7)/AJ4</f>
-        <v>0.66407054462396797</v>
-      </c>
-      <c r="AK25" s="9">
+        <v>0.65868912378660838</v>
+      </c>
+      <c r="BB25" s="9">
+        <f t="shared" si="161"/>
+        <v>0.66999999999999993</v>
+      </c>
+      <c r="BC25" s="9">
+        <f t="shared" si="161"/>
+        <v>0.67</v>
+      </c>
+      <c r="BD25" s="9">
+        <f t="shared" si="161"/>
+        <v>0.66999999999999993</v>
+      </c>
+      <c r="BE25" s="9">
+        <f t="shared" si="161"/>
+        <v>0.67</v>
+      </c>
+      <c r="BF25" s="9">
+        <f t="shared" si="161"/>
+        <v>0.66999999999999993</v>
+      </c>
+      <c r="BG25" s="9">
+        <f t="shared" si="161"/>
+        <v>0.66999999999999993</v>
+      </c>
+      <c r="BH25" s="9">
+        <f t="shared" si="161"/>
+        <v>0.66999999999999993</v>
+      </c>
+      <c r="BI25" s="9">
+        <f t="shared" si="161"/>
+        <v>0.67</v>
+      </c>
+      <c r="BJ25" s="9">
+        <f t="shared" ref="BJ25:BK25" si="162">(BJ4-BJ7)/BJ4</f>
+        <v>0.67</v>
+      </c>
+      <c r="BK25" s="9">
         <f t="shared" si="162"/>
-        <v>0.65510438928160453</v>
-      </c>
-      <c r="AL25" s="9">
-        <f t="shared" si="162"/>
-        <v>0.65</v>
-      </c>
-      <c r="AN25" s="9">
-        <f t="shared" ref="AN25:AR25" si="163">(AN4-AN7)/AN4</f>
-        <v>0.41739926739926742</v>
-      </c>
-      <c r="AO25" s="9">
-        <f t="shared" si="163"/>
-        <v>0.4999672938970412</v>
-      </c>
-      <c r="AP25" s="9">
-        <f t="shared" si="163"/>
-        <v>0.55437146585471941</v>
-      </c>
-      <c r="AQ25" s="9">
-        <f t="shared" si="163"/>
-        <v>0.59904766985888447</v>
-      </c>
-      <c r="AR25" s="9">
-        <f t="shared" si="163"/>
-        <v>0.64940111736450412</v>
-      </c>
-      <c r="AS25" s="9">
-        <f t="shared" ref="AS25:AT25" si="164">(AS4-AS7)/AS4</f>
-        <v>0.64349440010196113</v>
-      </c>
-      <c r="AT25" s="9">
-        <f t="shared" si="164"/>
-        <v>0.67354771220519505</v>
-      </c>
-      <c r="AU25" s="9">
-        <f t="shared" ref="AU25:BD25" si="165">(AU4-AU7)/AU4</f>
-        <v>0.67461895294897278</v>
-      </c>
-      <c r="AV25" s="9">
-        <f t="shared" si="165"/>
-        <v>0.65833261456749204</v>
-      </c>
-      <c r="AW25" s="9">
-        <f t="shared" si="165"/>
-        <v>0.66999999999999993</v>
-      </c>
-      <c r="AX25" s="9">
-        <f t="shared" si="165"/>
-        <v>0.66999999999999993</v>
-      </c>
-      <c r="AY25" s="9">
-        <f t="shared" si="165"/>
-        <v>0.66999999999999993</v>
-      </c>
-      <c r="AZ25" s="9">
-        <f t="shared" si="165"/>
-        <v>0.66999999999999993</v>
-      </c>
-      <c r="BA25" s="9">
-        <f t="shared" si="165"/>
         <v>0.67</v>
       </c>
-      <c r="BB25" s="9">
-        <f t="shared" si="165"/>
-        <v>0.66999999999999993</v>
-      </c>
-      <c r="BC25" s="9">
-        <f t="shared" si="165"/>
-        <v>0.67</v>
-      </c>
-      <c r="BD25" s="9">
-        <f t="shared" si="165"/>
-        <v>0.66999999999999993</v>
-      </c>
-      <c r="BE25" s="9">
-        <f t="shared" ref="BE25:BF25" si="166">(BE4-BE7)/BE4</f>
-        <v>0.67</v>
-      </c>
-      <c r="BF25" s="9">
-        <f t="shared" si="166"/>
-        <v>0.67</v>
-      </c>
-      <c r="BH25" t="s">
+      <c r="BM25" t="s">
         <v>89</v>
       </c>
-      <c r="BI25" s="23">
-        <f>BI23+BI24</f>
-        <v>2812384.7559484853</v>
+      <c r="BN25" s="23">
+        <f>BN23+BN24</f>
+        <v>2870065.2306998842</v>
       </c>
     </row>
-    <row r="26" spans="2:179" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:184" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:F26" si="167">C9/C5</f>
+        <f t="shared" ref="C26:F26" si="163">C9/C5</f>
         <v>0.63782436051343616</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>0.61662665530860372</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>0.65276581078752371</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>0.66975200156219483</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" ref="G26" si="168">G9/G5</f>
+        <f t="shared" ref="G26" si="164">G9/G5</f>
         <v>0.66264569239546822</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ref="H26:V26" si="169">H9/H5</f>
+        <f t="shared" ref="H26:V26" si="165">H9/H5</f>
         <v>0.6174009267584204</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.65438681531749876</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.67618414492271894</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.65943474075092834</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.61741246034923469</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.66733178502502366</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.69119435299700449</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.6851913477537438</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.66514929821709212</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.68661660146769077</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.67557121447164303</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.70388114334930285</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.67048936762930633</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.68721526878626582</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.69684954064829263</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" ref="W26:X26" si="170">W9/W5</f>
+        <f t="shared" ref="W26:X26" si="166">W9/W5</f>
         <v>0.6988768012004325</v>
       </c>
       <c r="X26" s="9">
+        <f t="shared" si="166"/>
+        <v>0.64953216826476956</v>
+      </c>
+      <c r="Y26" s="9">
+        <f t="shared" ref="Y26" si="167">Y9/Y5</f>
+        <v>0.68365072933549431</v>
+      </c>
+      <c r="Z26" s="9">
+        <f t="shared" ref="Z26" si="168">Z9/Z5</f>
+        <v>0.68323532247180174</v>
+      </c>
+      <c r="AA26" s="9">
+        <f t="shared" ref="AA26" si="169">AA9/AA5</f>
+        <v>0.69171222217788597</v>
+      </c>
+      <c r="AB26" s="9">
+        <f t="shared" ref="AB26:AC26" si="170">AB9/AB5</f>
+        <v>0.66845507801391546</v>
+      </c>
+      <c r="AC26" s="9">
         <f t="shared" si="170"/>
-        <v>0.64953216826476956</v>
-      </c>
-      <c r="Y26" s="9">
-        <f t="shared" ref="Y26" si="171">Y9/Y5</f>
-        <v>0.68365072933549431</v>
-      </c>
-      <c r="Z26" s="9">
-        <f t="shared" ref="Z26" si="172">Z9/Z5</f>
-        <v>0.68323532247180174</v>
-      </c>
-      <c r="AA26" s="9">
-        <f t="shared" ref="AA26" si="173">AA9/AA5</f>
-        <v>0.69171222217788597</v>
-      </c>
-      <c r="AB26" s="9">
-        <f t="shared" ref="AB26:AC26" si="174">AB9/AB5</f>
-        <v>0.66845507801391546</v>
-      </c>
-      <c r="AC26" s="9">
+        <v>0.69487485101311086</v>
+      </c>
+      <c r="AD26" s="9">
+        <f t="shared" ref="AD26:AE26" si="171">AD9/AD5</f>
+        <v>0.70109807969531401</v>
+      </c>
+      <c r="AE26" s="9">
+        <f t="shared" si="171"/>
+        <v>0.71155581506449384</v>
+      </c>
+      <c r="AF26" s="9">
+        <f t="shared" ref="AF26:AG26" si="172">AF9/AF5</f>
+        <v>0.71155581506449384</v>
+      </c>
+      <c r="AG26" s="9">
+        <f t="shared" si="172"/>
+        <v>0.68360206385037081</v>
+      </c>
+      <c r="AH26" s="9">
+        <f t="shared" ref="AH26:AI26" si="173">AH9/AH5</f>
+        <v>0.69589197707293715</v>
+      </c>
+      <c r="AI26" s="9">
+        <f t="shared" si="173"/>
+        <v>0.69354273080734929</v>
+      </c>
+      <c r="AJ26" s="9">
+        <f t="shared" ref="AJ26:AL26" si="174">AJ9/AJ5</f>
+        <v>0.68693991268382348</v>
+      </c>
+      <c r="AK26" s="9">
         <f t="shared" si="174"/>
-        <v>0.69487485101311086</v>
-      </c>
-      <c r="AD26" s="9">
-        <f t="shared" ref="AD26:AE26" si="175">AD9/AD5</f>
-        <v>0.70109807969531401</v>
-      </c>
-      <c r="AE26" s="9">
+        <v>0.6871663859789342</v>
+      </c>
+      <c r="AL26" s="9">
+        <f t="shared" si="174"/>
+        <v>0.68584921704320978</v>
+      </c>
+      <c r="AM26" s="9"/>
+      <c r="AN26" s="9"/>
+      <c r="AO26" s="9"/>
+      <c r="AP26" s="9"/>
+      <c r="AQ26" s="9"/>
+      <c r="AS26" s="9">
+        <f t="shared" ref="AS26:AU26" si="175">AS9/AS5</f>
+        <v>0.64423007030041224</v>
+      </c>
+      <c r="AT26" s="9">
         <f t="shared" si="175"/>
-        <v>0.71155581506449384</v>
-      </c>
-      <c r="AF26" s="9">
-        <f t="shared" ref="AF26:AG26" si="176">AF9/AF5</f>
-        <v>0.71155581506449384</v>
-      </c>
-      <c r="AG26" s="9">
+        <v>0.65247372236317502</v>
+      </c>
+      <c r="AU26" s="9">
+        <f t="shared" si="175"/>
+        <v>0.65901957200638894</v>
+      </c>
+      <c r="AV26" s="9">
+        <f t="shared" ref="AV26:BF26" si="176">AV9/AV5</f>
+        <v>0.67781001992797962</v>
+      </c>
+      <c r="AW26" s="9">
         <f t="shared" si="176"/>
-        <v>0.68360206385037081</v>
-      </c>
-      <c r="AH26" s="9">
-        <f t="shared" ref="AH26:AI26" si="177">AH9/AH5</f>
-        <v>0.69589197707293715</v>
-      </c>
-      <c r="AI26" s="9">
-        <f t="shared" si="177"/>
-        <v>0.69354273080734929</v>
-      </c>
-      <c r="AJ26" s="9">
-        <f t="shared" ref="AJ26:AL26" si="178">AJ9/AJ5</f>
-        <v>0.68693991268382348</v>
-      </c>
-      <c r="AK26" s="9">
-        <f t="shared" si="178"/>
-        <v>0.6871663859789342</v>
-      </c>
-      <c r="AL26" s="9">
-        <f t="shared" si="178"/>
-        <v>0.67271161409635105</v>
-      </c>
-      <c r="AN26" s="9">
-        <f t="shared" ref="AN26:AP26" si="179">AN9/AN5</f>
-        <v>0.64423007030041224</v>
-      </c>
-      <c r="AO26" s="9">
+        <v>0.68925800771024703</v>
+      </c>
+      <c r="AX26" s="9">
+        <f t="shared" ref="AX26" si="177">AX9/AX5</f>
+        <v>0.67812074443940085</v>
+      </c>
+      <c r="AY26" s="9">
+        <f t="shared" si="176"/>
+        <v>0.68920085883491022</v>
+      </c>
+      <c r="AZ26" s="9">
+        <f t="shared" ref="AZ26" si="178">AZ9/AZ5</f>
+        <v>0.70009717200278587</v>
+      </c>
+      <c r="BA26" s="9">
+        <f t="shared" si="176"/>
+        <v>0.68823742386165188</v>
+      </c>
+      <c r="BB26" s="9">
+        <f t="shared" si="176"/>
+        <v>0.69050135771127441</v>
+      </c>
+      <c r="BC26" s="9">
+        <f t="shared" si="176"/>
+        <v>0.68943076033908024</v>
+      </c>
+      <c r="BD26" s="9">
+        <f t="shared" si="176"/>
+        <v>0.68868547589094364</v>
+      </c>
+      <c r="BE26" s="9">
+        <f t="shared" si="176"/>
+        <v>0.68810250688786723</v>
+      </c>
+      <c r="BF26" s="9">
+        <f t="shared" si="176"/>
+        <v>0.68767260334990998</v>
+      </c>
+      <c r="BG26" s="9">
+        <f t="shared" ref="BG26:BI26" si="179">BG9/BG5</f>
+        <v>0.68738911803937086</v>
+      </c>
+      <c r="BH26" s="9">
         <f t="shared" si="179"/>
-        <v>0.65247372236317502</v>
-      </c>
-      <c r="AP26" s="9">
+        <v>0.68710923506932176</v>
+      </c>
+      <c r="BI26" s="9">
         <f t="shared" si="179"/>
-        <v>0.65901957200638894</v>
-      </c>
-      <c r="AQ26" s="9">
-        <f t="shared" ref="AQ26:BA26" si="180">AQ9/AQ5</f>
-        <v>0.67781001992797962</v>
-      </c>
-      <c r="AR26" s="9">
+        <v>0.68696996247816733</v>
+      </c>
+      <c r="BJ26" s="9">
+        <f t="shared" ref="BJ26:BK26" si="180">BJ9/BJ5</f>
+        <v>0.68683159338604882</v>
+      </c>
+      <c r="BK26" s="9">
         <f t="shared" si="180"/>
-        <v>0.68925800771024703</v>
-      </c>
-      <c r="AS26" s="9">
-        <f t="shared" ref="AS26" si="181">AS9/AS5</f>
-        <v>0.67812074443940085</v>
-      </c>
-      <c r="AT26" s="9">
-        <f t="shared" si="180"/>
-        <v>0.68920085883491022</v>
-      </c>
-      <c r="AU26" s="9">
-        <f t="shared" ref="AU26" si="182">AU9/AU5</f>
-        <v>0.70009717200278587</v>
-      </c>
-      <c r="AV26" s="9">
-        <f t="shared" si="180"/>
-        <v>0.68473868158175422</v>
-      </c>
-      <c r="AW26" s="9">
-        <f t="shared" si="180"/>
-        <v>0.68927649088566367</v>
-      </c>
-      <c r="AX26" s="9">
-        <f t="shared" si="180"/>
-        <v>0.68825516918163199</v>
-      </c>
-      <c r="AY26" s="9">
-        <f t="shared" si="180"/>
-        <v>0.68754515638919789</v>
-      </c>
-      <c r="AZ26" s="9">
-        <f t="shared" si="180"/>
-        <v>0.68699033062500747</v>
-      </c>
-      <c r="BA26" s="9">
-        <f t="shared" si="180"/>
-        <v>0.68658149176873029</v>
-      </c>
-      <c r="BB26" s="9">
-        <f t="shared" ref="BB26:BD26" si="183">BB9/BB5</f>
-        <v>0.68631204104980326</v>
-      </c>
-      <c r="BC26" s="9">
-        <f t="shared" si="183"/>
-        <v>0.68604612667544196</v>
-      </c>
-      <c r="BD26" s="9">
-        <f t="shared" si="183"/>
-        <v>0.6859138465705813</v>
-      </c>
-      <c r="BE26" s="9">
-        <f t="shared" ref="BE26:BF26" si="184">BE9/BE5</f>
-        <v>0.68578245194918608</v>
-      </c>
-      <c r="BF26" s="9">
-        <f t="shared" si="184"/>
-        <v>0.68565194026293041</v>
-      </c>
-      <c r="BH26" t="s">
+        <v>0.68669412567985022</v>
+      </c>
+      <c r="BM26" t="s">
         <v>90</v>
       </c>
-      <c r="BI26" s="19">
-        <f>BI25/BA18</f>
-        <v>378.39014543538315</v>
+      <c r="BN26" s="19">
+        <f>BN25/BF18</f>
+        <v>386.1766995021373</v>
       </c>
     </row>
-    <row r="27" spans="2:179" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:184" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>76</v>
       </c>
       <c r="C27" s="9">
-        <f t="shared" ref="C27:F27" si="185">C13/C5</f>
+        <f t="shared" ref="C27:F27" si="181">C13/C5</f>
         <v>0.29758057068981436</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.30608688918144505</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.28963467172152335</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.31197031829720756</v>
       </c>
       <c r="G27" s="9">
@@ -6989,214 +7121,219 @@
         <v>0.3141250305648382</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:V27" si="186">H13/H5</f>
+        <f t="shared" ref="H27:V27" si="182">H13/H5</f>
         <v>0.30012448993706342</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.30918378761325926</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.3449891972743892</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.34228441754916794</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.3159126605278556</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.3382617513329626</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.3679152949550672</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.38378460142187265</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.37638866309001245</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.37049199051997372</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.35250966266137301</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.42730257845723207</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.41547497446373849</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.40876612477820939</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.41374154966198645</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" ref="W27:X27" si="187">W13/W5</f>
+        <f t="shared" ref="W27:X27" si="183">W13/W5</f>
         <v>0.44658737339188381</v>
       </c>
       <c r="X27" s="9">
+        <f t="shared" si="183"/>
+        <v>0.40747757500773274</v>
+      </c>
+      <c r="Y27" s="9">
+        <f t="shared" ref="Y27" si="184">Y13/Y5</f>
+        <v>0.41256077795786061</v>
+      </c>
+      <c r="Z27" s="9">
+        <f t="shared" ref="Z27" si="185">Z13/Z5</f>
+        <v>0.3959124650535043</v>
+      </c>
+      <c r="AA27" s="9">
+        <f t="shared" ref="AA27" si="186">AA13/AA5</f>
+        <v>0.42931247755476637</v>
+      </c>
+      <c r="AB27" s="9">
+        <f t="shared" ref="AB27:AC27" si="187">AB13/AB5</f>
+        <v>0.3867328947617874</v>
+      </c>
+      <c r="AC27" s="9">
         <f t="shared" si="187"/>
-        <v>0.40747757500773274</v>
-      </c>
-      <c r="Y27" s="9">
-        <f t="shared" ref="Y27" si="188">Y13/Y5</f>
-        <v>0.41256077795786061</v>
-      </c>
-      <c r="Z27" s="9">
-        <f t="shared" ref="Z27" si="189">Z13/Z5</f>
-        <v>0.3959124650535043</v>
-      </c>
-      <c r="AA27" s="9">
-        <f t="shared" ref="AA27" si="190">AA13/AA5</f>
-        <v>0.42931247755476637</v>
-      </c>
-      <c r="AB27" s="9">
-        <f t="shared" ref="AB27:AC27" si="191">AB13/AB5</f>
-        <v>0.3867328947617874</v>
-      </c>
-      <c r="AC27" s="9">
+        <v>0.42287681858599618</v>
+      </c>
+      <c r="AD27" s="9">
+        <f t="shared" ref="AD27:AE27" si="188">AD13/AD5</f>
+        <v>0.4316503230169606</v>
+      </c>
+      <c r="AE27" s="9">
+        <f t="shared" si="188"/>
+        <v>0.47587451563246458</v>
+      </c>
+      <c r="AF27" s="9">
+        <f t="shared" ref="AF27:AG27" si="189">AF13/AF5</f>
+        <v>0.47587451563246458</v>
+      </c>
+      <c r="AG27" s="9">
+        <f t="shared" si="189"/>
+        <v>0.43585940019348596</v>
+      </c>
+      <c r="AH27" s="9">
+        <f t="shared" ref="AH27:AI27" si="190">AH13/AH5</f>
+        <v>0.43142737960974553</v>
+      </c>
+      <c r="AI27" s="9">
+        <f t="shared" si="190"/>
+        <v>0.46583822520393381</v>
+      </c>
+      <c r="AJ27" s="9">
+        <f t="shared" ref="AJ27:AL27" si="191">AJ13/AJ5</f>
+        <v>0.45457548253676472</v>
+      </c>
+      <c r="AK27" s="9">
         <f t="shared" si="191"/>
-        <v>0.42287681858599618</v>
-      </c>
-      <c r="AD27" s="9">
-        <f t="shared" ref="AD27:AE27" si="192">AD13/AD5</f>
-        <v>0.4316503230169606</v>
-      </c>
-      <c r="AE27" s="9">
+        <v>0.45671224274255701</v>
+      </c>
+      <c r="AL27" s="9">
+        <f t="shared" si="191"/>
+        <v>0.44901296424693554</v>
+      </c>
+      <c r="AM27" s="9"/>
+      <c r="AN27" s="9"/>
+      <c r="AO27" s="9"/>
+      <c r="AP27" s="9"/>
+      <c r="AQ27" s="9"/>
+      <c r="AS27" s="9">
+        <f t="shared" ref="AS27:AU27" si="192">AS13/AS5</f>
+        <v>0.30177256726306062</v>
+      </c>
+      <c r="AT27" s="9">
         <f t="shared" si="192"/>
-        <v>0.47587451563246458</v>
-      </c>
-      <c r="AF27" s="9">
-        <f t="shared" ref="AF27:AG27" si="193">AF13/AF5</f>
-        <v>0.47587451563246458</v>
-      </c>
-      <c r="AG27" s="9">
+        <v>0.31766944545125048</v>
+      </c>
+      <c r="AU27" s="9">
+        <f t="shared" si="192"/>
+        <v>0.3413698020549415</v>
+      </c>
+      <c r="AV27" s="9">
+        <f t="shared" ref="AV27:BF27" si="193">AV13/AV5</f>
+        <v>0.37030381428521486</v>
+      </c>
+      <c r="AW27" s="9">
         <f t="shared" si="193"/>
-        <v>0.43585940019348596</v>
-      </c>
-      <c r="AH27" s="9">
-        <f t="shared" ref="AH27:AI27" si="194">AH13/AH5</f>
-        <v>0.43142737960974553</v>
-      </c>
-      <c r="AI27" s="9">
-        <f t="shared" si="194"/>
-        <v>0.46583822520393381</v>
-      </c>
-      <c r="AJ27" s="9">
-        <f t="shared" ref="AJ27:AL27" si="195">AJ13/AJ5</f>
-        <v>0.45457548253676472</v>
-      </c>
-      <c r="AK27" s="9">
-        <f t="shared" si="195"/>
-        <v>0.45671224274255701</v>
-      </c>
-      <c r="AL27" s="9">
-        <f t="shared" si="195"/>
-        <v>0.42583383569104333</v>
-      </c>
-      <c r="AN27" s="9">
-        <f t="shared" ref="AN27:AP27" si="196">AN13/AN5</f>
-        <v>0.30177256726306062</v>
-      </c>
-      <c r="AO27" s="9">
+        <v>0.41594878872971303</v>
+      </c>
+      <c r="AX27" s="9">
+        <f t="shared" ref="AX27" si="194">AX13/AX5</f>
+        <v>0.4146567811570081</v>
+      </c>
+      <c r="AY27" s="9">
+        <f t="shared" si="193"/>
+        <v>0.41772880636104098</v>
+      </c>
+      <c r="AZ27" s="9">
+        <f t="shared" ref="AZ27" si="195">AZ13/AZ5</f>
+        <v>0.45352634278779386</v>
+      </c>
+      <c r="BA27" s="9">
+        <f t="shared" si="193"/>
+        <v>0.45621956240859851</v>
+      </c>
+      <c r="BB27" s="9">
+        <f t="shared" si="193"/>
+        <v>0.47405062169285633</v>
+      </c>
+      <c r="BC27" s="9">
+        <f t="shared" si="193"/>
+        <v>0.47974866781975201</v>
+      </c>
+      <c r="BD27" s="9">
+        <f t="shared" si="193"/>
+        <v>0.48482579871547921</v>
+      </c>
+      <c r="BE27" s="9">
+        <f t="shared" si="193"/>
+        <v>0.48964142418515599</v>
+      </c>
+      <c r="BF27" s="9">
+        <f t="shared" si="193"/>
+        <v>0.49297654085284331</v>
+      </c>
+      <c r="BG27" s="9">
+        <f t="shared" ref="BG27:BI27" si="196">BG13/BG5</f>
+        <v>0.4950905739618186</v>
+      </c>
+      <c r="BH27" s="9">
         <f t="shared" si="196"/>
-        <v>0.31766944545125048</v>
-      </c>
-      <c r="AP27" s="9">
+        <v>0.4971848118006274</v>
+      </c>
+      <c r="BI27" s="9">
         <f t="shared" si="196"/>
-        <v>0.3413698020549415</v>
-      </c>
-      <c r="AQ27" s="9">
-        <f t="shared" ref="AQ27:BA27" si="197">AQ13/AQ5</f>
-        <v>0.37030381428521486</v>
-      </c>
-      <c r="AR27" s="9">
+        <v>0.4978693697408863</v>
+      </c>
+      <c r="BJ27" s="9">
+        <f t="shared" ref="BJ27:BK27" si="197">BJ13/BJ5</f>
+        <v>0.49854948676829891</v>
+      </c>
+      <c r="BK27" s="9">
         <f t="shared" si="197"/>
-        <v>0.41594878872971303</v>
-      </c>
-      <c r="AS27" s="9">
-        <f t="shared" ref="AS27" si="198">AS13/AS5</f>
-        <v>0.4146567811570081</v>
-      </c>
-      <c r="AT27" s="9">
-        <f t="shared" si="197"/>
-        <v>0.41772880636104098</v>
-      </c>
-      <c r="AU27" s="9">
-        <f t="shared" ref="AU27" si="199">AU13/AU5</f>
-        <v>0.45352634278779386</v>
-      </c>
-      <c r="AV27" s="9">
-        <f t="shared" si="197"/>
-        <v>0.45006310554189444</v>
-      </c>
-      <c r="AW27" s="9">
-        <f t="shared" si="197"/>
-        <v>0.47072564693452867</v>
-      </c>
-      <c r="AX27" s="9">
-        <f t="shared" si="197"/>
-        <v>0.47671221032640931</v>
-      </c>
-      <c r="AY27" s="9">
-        <f t="shared" si="197"/>
-        <v>0.48198049544970167</v>
-      </c>
-      <c r="AZ27" s="9">
-        <f t="shared" si="197"/>
-        <v>0.48694468424708715</v>
-      </c>
-      <c r="BA27" s="9">
-        <f t="shared" si="197"/>
-        <v>0.49038218247610571</v>
-      </c>
-      <c r="BB27" s="9">
-        <f t="shared" ref="BB27:BD27" si="200">BB13/BB5</f>
-        <v>0.49256850427957521</v>
-      </c>
-      <c r="BC27" s="9">
-        <f t="shared" si="200"/>
-        <v>0.49473326628971293</v>
-      </c>
-      <c r="BD27" s="9">
-        <f t="shared" si="200"/>
-        <v>0.49544929613745886</v>
-      </c>
-      <c r="BE27" s="9">
-        <f t="shared" ref="BE27:BF27" si="201">BE13/BE5</f>
-        <v>0.49616053287900308</v>
-      </c>
-      <c r="BF27" s="9">
-        <f t="shared" si="201"/>
-        <v>0.49686699030838805</v>
-      </c>
-      <c r="BH27" t="s">
+        <v>0.49922517326933519</v>
+      </c>
+      <c r="BM27" t="s">
         <v>92</v>
       </c>
-      <c r="BI27" s="19">
+      <c r="BN27" s="19">
         <f>Main!D3</f>
-        <v>454.26</v>
+        <v>520.79999999999995</v>
       </c>
     </row>
-    <row r="28" spans="2:179" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:184" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>97</v>
       </c>
@@ -7205,446 +7342,456 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9">
-        <f t="shared" ref="G28:G30" si="202">G10/C10-1</f>
+        <f t="shared" ref="G28:G30" si="198">G10/C10-1</f>
         <v>0.1506761107533805</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" ref="H28" si="203">H10/D10-1</f>
+        <f t="shared" ref="H28" si="199">H10/D10-1</f>
         <v>0.14435009797517973</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" ref="I28" si="204">I10/E10-1</f>
+        <f t="shared" ref="I28" si="200">I10/E10-1</f>
         <v>0.10730253353204167</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" ref="J28" si="205">J10/F10-1</f>
+        <f t="shared" ref="J28" si="201">J10/F10-1</f>
         <v>0.1192373363688104</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" ref="K28" si="206">K10/G10-1</f>
+        <f t="shared" ref="K28" si="202">K10/G10-1</f>
         <v>0.11275881365416907</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" ref="L28" si="207">L10/H10-1</f>
+        <f t="shared" ref="L28" si="203">L10/H10-1</f>
         <v>0.1615296803652968</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" ref="M28" si="208">M10/I10-1</f>
+        <f t="shared" ref="M28" si="204">M10/I10-1</f>
         <v>0.16177658142664875</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" ref="N28" si="209">N10/J10-1</f>
+        <f t="shared" ref="N28" si="205">N10/J10-1</f>
         <v>0.14747012458682929</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28" si="210">O10/K10-1</f>
+        <f t="shared" ref="O28" si="206">O10/K10-1</f>
         <v>0.14785013829519733</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" ref="P28" si="211">P10/L10-1</f>
+        <f t="shared" ref="P28" si="207">P10/L10-1</f>
         <v>0.13095823095823089</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" ref="Q28" si="212">Q10/M10-1</f>
+        <f t="shared" ref="Q28" si="208">Q10/M10-1</f>
         <v>0.13229842446709927</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" ref="R28" si="213">R10/N10-1</f>
+        <f t="shared" ref="R28" si="209">R10/N10-1</f>
         <v>0.15532904941280745</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" ref="S28" si="214">S10/O10-1</f>
+        <f t="shared" ref="S28" si="210">S10/O10-1</f>
         <v>7.9079956188389922E-2</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" ref="T28" si="215">T10/P10-1</f>
+        <f t="shared" ref="T28" si="211">T10/P10-1</f>
         <v>6.4305887464696898E-2</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" ref="U28" si="216">U10/Q10-1</f>
+        <f t="shared" ref="U28" si="212">U10/Q10-1</f>
         <v>6.4865970943319029E-2</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" ref="V28" si="217">V10/R10-1</f>
+        <f t="shared" ref="V28" si="213">V10/R10-1</f>
         <v>9.0717299578058963E-2</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" ref="W28:X28" si="218">W10/S10-1</f>
+        <f t="shared" ref="W28:X28" si="214">W10/S10-1</f>
         <v>0.13662200568412497</v>
       </c>
       <c r="X28" s="9">
+        <f t="shared" si="214"/>
+        <v>0.17534190651153292</v>
+      </c>
+      <c r="Y28" s="9">
+        <f t="shared" ref="Y28" si="215">Y10/U10-1</f>
+        <v>0.21176018447348199</v>
+      </c>
+      <c r="Z28" s="9">
+        <f t="shared" ref="Z28" si="216">Z10/V10-1</f>
+        <v>0.20432565500263755</v>
+      </c>
+      <c r="AA28" s="9">
+        <f t="shared" ref="AA28" si="217">AA10/W10-1</f>
+        <v>0.18378281836042154</v>
+      </c>
+      <c r="AB28" s="9">
+        <f t="shared" ref="AB28:AL28" si="218">AB10/X10-1</f>
+        <v>0.18860715526224392</v>
+      </c>
+      <c r="AC28" s="9">
         <f t="shared" si="218"/>
-        <v>0.17534190651153292</v>
-      </c>
-      <c r="Y28" s="9">
-        <f t="shared" ref="Y28" si="219">Y10/U10-1</f>
-        <v>0.21176018447348199</v>
-      </c>
-      <c r="Z28" s="9">
-        <f t="shared" ref="Z28" si="220">Z10/V10-1</f>
-        <v>0.20432565500263755</v>
-      </c>
-      <c r="AA28" s="9">
-        <f t="shared" ref="AA28" si="221">AA10/W10-1</f>
-        <v>0.18378281836042154</v>
-      </c>
-      <c r="AB28" s="9">
-        <f t="shared" ref="AB28:AL28" si="222">AB10/X10-1</f>
-        <v>0.18860715526224392</v>
-      </c>
-      <c r="AC28" s="9">
-        <f t="shared" si="222"/>
         <v>0.1075166508087535</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="218"/>
         <v>-1.6060738793984508E-2</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="218"/>
         <v>4.6771273385637357E-3</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="218"/>
         <v>-2.7030976037405008E-2</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="218"/>
         <v>2.2623138602519965E-2</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="218"/>
         <v>0.19542958895978635</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="218"/>
         <v>0.13290283826400362</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="218"/>
         <v>0.18891725484306954</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="218"/>
         <v>0.14785774292915144</v>
       </c>
       <c r="AL28" s="9">
-        <f t="shared" si="222"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
+        <f t="shared" si="218"/>
+        <v>9.5953326713009046E-2</v>
+      </c>
+      <c r="AM28" s="9"/>
       <c r="AN28" s="9"/>
-      <c r="AO28" s="9">
-        <f>AO10/AN10-1</f>
+      <c r="AO28" s="9"/>
+      <c r="AP28" s="9"/>
+      <c r="AQ28" s="9"/>
+      <c r="AS28" s="9"/>
+      <c r="AT28" s="9">
+        <f>AT10/AS10-1</f>
         <v>0.12955434532484467</v>
       </c>
-      <c r="AP28" s="9">
-        <f t="shared" ref="AP28:BD28" si="223">AP10/AO10-1</f>
+      <c r="AU28" s="9">
+        <f t="shared" ref="AU28:BI28" si="219">AU10/AT10-1</f>
         <v>0.14600027162841234</v>
       </c>
-      <c r="AQ28" s="9">
-        <f t="shared" si="223"/>
+      <c r="AV28" s="9">
+        <f t="shared" si="219"/>
         <v>0.14179900450343674</v>
       </c>
-      <c r="AR28" s="9">
-        <f t="shared" si="223"/>
+      <c r="AW28" s="9">
+        <f t="shared" si="219"/>
         <v>7.5094711713114437E-2</v>
       </c>
-      <c r="AS28" s="9">
-        <f t="shared" si="223"/>
+      <c r="AX28" s="9">
+        <f t="shared" si="219"/>
         <v>0.1832400077234988</v>
       </c>
-      <c r="AT28" s="9">
-        <f t="shared" si="223"/>
+      <c r="AY28" s="9">
+        <f t="shared" si="219"/>
         <v>0.10945659268929497</v>
       </c>
-      <c r="AU28" s="9">
-        <f t="shared" si="223"/>
+      <c r="AZ28" s="9">
+        <f t="shared" si="219"/>
         <v>4.8575105717962863E-2</v>
       </c>
-      <c r="AV28" s="9">
-        <f t="shared" si="223"/>
-        <v>0.13195819890587734</v>
-      </c>
-      <c r="AW28" s="9">
-        <f t="shared" si="223"/>
+      <c r="BA28" s="9">
+        <f t="shared" si="219"/>
+        <v>0.13929022303268335</v>
+      </c>
+      <c r="BB28" s="9">
+        <f t="shared" si="219"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AX28" s="9">
-        <f t="shared" si="223"/>
+      <c r="BC28" s="9">
+        <f t="shared" si="219"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AY28" s="9">
-        <f t="shared" si="223"/>
+      <c r="BD28" s="9">
+        <f t="shared" si="219"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AZ28" s="9">
-        <f t="shared" si="223"/>
+      <c r="BE28" s="9">
+        <f t="shared" si="219"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BA28" s="9">
-        <f t="shared" si="223"/>
+      <c r="BF28" s="9">
+        <f t="shared" si="219"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BB28" s="9">
-        <f t="shared" si="223"/>
+      <c r="BG28" s="9">
+        <f t="shared" si="219"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BC28" s="9">
-        <f t="shared" si="223"/>
+      <c r="BH28" s="9">
+        <f t="shared" si="219"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BD28" s="9">
-        <f t="shared" si="223"/>
+      <c r="BI28" s="9">
+        <f t="shared" si="219"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BE28" s="9">
-        <f t="shared" ref="BE28" si="224">BE10/BD10-1</f>
+      <c r="BJ28" s="9">
+        <f t="shared" ref="BJ28" si="220">BJ10/BI10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BF28" s="9">
-        <f t="shared" ref="BF28" si="225">BF10/BE10-1</f>
+      <c r="BK28" s="9">
+        <f t="shared" ref="BK28" si="221">BK10/BJ10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BH28" s="6" t="s">
+      <c r="BM28" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="BI28" s="18">
-        <f>BI26/BI27-1</f>
-        <v>-0.16701856770267431</v>
+      <c r="BN28" s="18">
+        <f>BN26/BN27-1</f>
+        <v>-0.25849328052584997</v>
       </c>
     </row>
-    <row r="29" spans="2:179" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:184" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>77</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:F29" si="226">C11/C$5</f>
+        <f t="shared" ref="C29:F29" si="222">C11/C$5</f>
         <v>0.14858250992704775</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="226"/>
+        <f t="shared" si="222"/>
         <v>0.1579416092310075</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="226"/>
+        <f t="shared" si="222"/>
         <v>0.16681027054971567</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="226"/>
+        <f t="shared" si="222"/>
         <v>0.16762351103300135</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" ref="G29:V29" si="227">G11/G$5</f>
+        <f t="shared" ref="G29:V29" si="223">G11/G$5</f>
         <v>0.15535088434265221</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.15775641468981258</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.16163913643312577</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.15821838125311616</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.14090221427589053</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.14129530966092821</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.14932452324098</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.14716611798202686</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.13120556648010892</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.13366390288841923</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.14023014762571029</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.14242894328609365</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.11387737524896377</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.11484353236140775</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.12185297079556898</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="223"/>
         <v>0.12690674293638413</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" ref="W29:X29" si="228">W11/W$5</f>
+        <f t="shared" ref="W29:X29" si="224">W11/W$5</f>
         <v>0.100337621643092</v>
       </c>
       <c r="X29" s="9">
+        <f t="shared" si="224"/>
+        <v>0.10398623569440149</v>
+      </c>
+      <c r="Y29" s="9">
+        <f t="shared" ref="Y29" si="225">Y11/Y$5</f>
+        <v>0.11335089141004863</v>
+      </c>
+      <c r="Z29" s="9">
+        <f t="shared" ref="Z29" si="226">Z11/Z$5</f>
+        <v>0.12154632218258941</v>
+      </c>
+      <c r="AA29" s="9">
+        <f t="shared" ref="AA29" si="227">AA11/AA$5</f>
+        <v>0.10227046007741111</v>
+      </c>
+      <c r="AB29" s="9">
+        <f t="shared" ref="AB29:AC29" si="228">AB11/AB$5</f>
+        <v>0.10766489089426887</v>
+      </c>
+      <c r="AC29" s="9">
         <f t="shared" si="228"/>
-        <v>0.10398623569440149</v>
-      </c>
-      <c r="Y29" s="9">
-        <f t="shared" ref="Y29" si="229">Y11/Y$5</f>
-        <v>0.11335089141004863</v>
-      </c>
-      <c r="Z29" s="9">
-        <f t="shared" ref="Z29" si="230">Z11/Z$5</f>
-        <v>0.12154632218258941</v>
-      </c>
-      <c r="AA29" s="9">
-        <f t="shared" ref="AA29" si="231">AA11/AA$5</f>
-        <v>0.10227046007741111</v>
-      </c>
-      <c r="AB29" s="9">
-        <f t="shared" ref="AB29:AC29" si="232">AB11/AB$5</f>
-        <v>0.10766489089426887</v>
-      </c>
-      <c r="AC29" s="9">
+        <v>0.10878407779480485</v>
+      </c>
+      <c r="AD29" s="9">
+        <f t="shared" ref="AD29:AE29" si="229">AD11/AD$5</f>
+        <v>0.11041307017387746</v>
+      </c>
+      <c r="AE29" s="9">
+        <f t="shared" si="229"/>
+        <v>9.1777695206751955E-2</v>
+      </c>
+      <c r="AF29" s="9">
+        <f t="shared" ref="AF29:AG29" si="230">AF11/AF$5</f>
+        <v>9.1777695206751955E-2</v>
+      </c>
+      <c r="AG29" s="9">
+        <f t="shared" si="230"/>
+        <v>0.10070944856497904</v>
+      </c>
+      <c r="AH29" s="9">
+        <f t="shared" ref="AH29:AI29" si="231">AH11/AH$5</f>
+        <v>0.10530381448236439</v>
+      </c>
+      <c r="AI29" s="9">
+        <f t="shared" si="231"/>
+        <v>8.716932225356408E-2</v>
+      </c>
+      <c r="AJ29" s="9">
+        <f t="shared" ref="AJ29:AL29" si="232">AJ11/AJ$5</f>
+        <v>9.2486213235294115E-2</v>
+      </c>
+      <c r="AK29" s="9">
         <f t="shared" si="232"/>
-        <v>0.10878407779480485</v>
-      </c>
-      <c r="AD29" s="9">
-        <f t="shared" ref="AD29:AE29" si="233">AD11/AD$5</f>
-        <v>0.11041307017387746</v>
-      </c>
-      <c r="AE29" s="9">
+        <v>8.8659264122398884E-2</v>
+      </c>
+      <c r="AL29" s="9">
+        <f t="shared" si="232"/>
+        <v>9.5302259258774738E-2</v>
+      </c>
+      <c r="AM29" s="9"/>
+      <c r="AN29" s="9"/>
+      <c r="AO29" s="9"/>
+      <c r="AP29" s="9"/>
+      <c r="AQ29" s="9"/>
+      <c r="AS29" s="9">
+        <f t="shared" ref="AS29:AU29" si="233">AS11/AS$5</f>
+        <v>0.16054869627522039</v>
+      </c>
+      <c r="AT29" s="9">
         <f t="shared" si="233"/>
-        <v>9.1777695206751955E-2</v>
-      </c>
-      <c r="AF29" s="9">
-        <f t="shared" ref="AF29:AG29" si="234">AF11/AF$5</f>
-        <v>9.1777695206751955E-2</v>
-      </c>
-      <c r="AG29" s="9">
+        <v>0.15829104748097136</v>
+      </c>
+      <c r="AU29" s="9">
+        <f t="shared" si="233"/>
+        <v>0.14472795467368069</v>
+      </c>
+      <c r="AV29" s="9">
+        <f t="shared" ref="AV29:BF29" si="234">AV11/AV$5</f>
+        <v>0.13703457679264414</v>
+      </c>
+      <c r="AW29" s="9">
         <f t="shared" si="234"/>
-        <v>0.10070944856497904</v>
-      </c>
-      <c r="AH29" s="9">
-        <f t="shared" ref="AH29:AI29" si="235">AH11/AH$5</f>
-        <v>0.10530381448236439</v>
-      </c>
-      <c r="AI29" s="9">
-        <f t="shared" si="235"/>
-        <v>8.716932225356408E-2</v>
-      </c>
-      <c r="AJ29" s="9">
-        <f t="shared" ref="AJ29:AL29" si="236">AJ11/AJ$5</f>
-        <v>9.2486213235294115E-2</v>
-      </c>
-      <c r="AK29" s="9">
-        <f t="shared" si="236"/>
-        <v>8.8659264122398884E-2</v>
-      </c>
-      <c r="AL29" s="9">
-        <f t="shared" si="236"/>
-        <v>0.1</v>
-      </c>
-      <c r="AN29" s="9">
-        <f t="shared" ref="AN29:AP29" si="237">AN11/AN$5</f>
-        <v>0.16054869627522039</v>
-      </c>
-      <c r="AO29" s="9">
+        <v>0.1196813573842273</v>
+      </c>
+      <c r="AX29" s="9">
+        <f t="shared" ref="AX29" si="235">AX11/AX$5</f>
+        <v>0.11007716749886519</v>
+      </c>
+      <c r="AY29" s="9">
+        <f t="shared" si="234"/>
+        <v>0.10739683363612769</v>
+      </c>
+      <c r="AZ29" s="9">
+        <f t="shared" ref="AZ29" si="236">AZ11/AZ$5</f>
+        <v>9.7739187008144934E-2</v>
+      </c>
+      <c r="BA29" s="9">
+        <f t="shared" si="234"/>
+        <v>9.1060754497309424E-2</v>
+      </c>
+      <c r="BB29" s="9">
+        <f t="shared" si="234"/>
+        <v>8.3062142367575226E-2</v>
+      </c>
+      <c r="BC29" s="9">
+        <f t="shared" si="234"/>
+        <v>7.9504021747648299E-2</v>
+      </c>
+      <c r="BD29" s="9">
+        <f t="shared" si="234"/>
+        <v>7.7211548804448568E-2</v>
+      </c>
+      <c r="BE29" s="9">
+        <f t="shared" si="234"/>
+        <v>7.554324224112921E-2</v>
+      </c>
+      <c r="BF29" s="9">
+        <f t="shared" si="234"/>
+        <v>7.4479409899195312E-2</v>
+      </c>
+      <c r="BG29" s="9">
+        <f t="shared" ref="BG29:BI29" si="237">BG11/BG$5</f>
+        <v>7.4010280547149795E-2</v>
+      </c>
+      <c r="BH29" s="9">
         <f t="shared" si="237"/>
-        <v>0.15829104748097136</v>
-      </c>
-      <c r="AP29" s="9">
+        <v>7.3540044135642579E-2</v>
+      </c>
+      <c r="BI29" s="9">
         <f t="shared" si="237"/>
-        <v>0.14472795467368069</v>
-      </c>
-      <c r="AQ29" s="9">
-        <f t="shared" ref="AQ29:BA29" si="238">AQ11/AQ$5</f>
-        <v>0.13703457679264414</v>
-      </c>
-      <c r="AR29" s="9">
+        <v>7.3663605698971749E-2</v>
+      </c>
+      <c r="BJ29" s="9">
+        <f t="shared" ref="BJ29:BK29" si="238">BJ11/BJ$5</f>
+        <v>7.3786365684959415E-2</v>
+      </c>
+      <c r="BK29" s="9">
         <f t="shared" si="238"/>
-        <v>0.1196813573842273</v>
-      </c>
-      <c r="AS29" s="9">
-        <f t="shared" ref="AS29" si="239">AS11/AS$5</f>
-        <v>0.11007716749886519</v>
-      </c>
-      <c r="AT29" s="9">
-        <f t="shared" si="238"/>
-        <v>0.10739683363612769</v>
-      </c>
-      <c r="AU29" s="9">
-        <f t="shared" ref="AU29" si="240">AU11/AU$5</f>
-        <v>9.7739187008144934E-2</v>
-      </c>
-      <c r="AV29" s="9">
-        <f t="shared" si="238"/>
-        <v>9.2293164001134562E-2</v>
-      </c>
-      <c r="AW29" s="9">
-        <f t="shared" si="238"/>
-        <v>8.4047314417466629E-2</v>
-      </c>
-      <c r="AX29" s="9">
-        <f t="shared" si="238"/>
-        <v>8.0382317606212256E-2</v>
-      </c>
-      <c r="AY29" s="9">
-        <f t="shared" si="238"/>
-        <v>7.8020854630970235E-2</v>
-      </c>
-      <c r="AZ29" s="9">
-        <f t="shared" si="238"/>
-        <v>7.6301677782255967E-2</v>
-      </c>
-      <c r="BA29" s="9">
-        <f t="shared" si="238"/>
-        <v>7.5202911574408476E-2</v>
-      </c>
-      <c r="BB29" s="9">
-        <f t="shared" ref="BB29:BD29" si="241">BB11/BB$5</f>
-        <v>7.4713341297713717E-2</v>
-      </c>
-      <c r="BC29" s="9">
-        <f t="shared" si="241"/>
-        <v>7.4223062185544197E-2</v>
-      </c>
-      <c r="BD29" s="9">
-        <f t="shared" si="241"/>
-        <v>7.4340010148278804E-2</v>
-      </c>
-      <c r="BE29" s="9">
-        <f t="shared" ref="BE29:BF29" si="242">BE11/BE$5</f>
-        <v>7.4456175260958726E-2</v>
-      </c>
-      <c r="BF29" s="9">
-        <f t="shared" si="242"/>
-        <v>7.4571559776541979E-2</v>
-      </c>
-      <c r="BH29" t="s">
+        <v>7.3908325968345956E-2</v>
+      </c>
+      <c r="BM29" t="s">
         <v>94</v>
       </c>
-      <c r="BI29" s="3" t="s">
+      <c r="BN29" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="30" spans="2:179" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:184" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>98</v>
       </c>
@@ -7653,225 +7800,230 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="198"/>
         <v>0.11578947368421044</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" ref="H30" si="243">H12/D12-1</f>
+        <f t="shared" ref="H30" si="239">H12/D12-1</f>
         <v>0.26166097838452784</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" ref="I30" si="244">I12/E12-1</f>
+        <f t="shared" ref="I30" si="240">I12/E12-1</f>
         <v>4.991680532445919E-3</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" ref="J30" si="245">J12/F12-1</f>
+        <f t="shared" ref="J30" si="241">J12/F12-1</f>
         <v>-6.199261992619931E-2</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" ref="K30" si="246">K12/G12-1</f>
+        <f t="shared" ref="K30" si="242">K12/G12-1</f>
         <v>-1.4579759862778707E-2</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" ref="L30" si="247">L12/H12-1</f>
+        <f t="shared" ref="L30" si="243">L12/H12-1</f>
         <v>2.0739404869251521E-2</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" ref="M30" si="248">M12/I12-1</f>
+        <f t="shared" ref="M30" si="244">M12/I12-1</f>
         <v>-2.4006622516556275E-2</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" ref="N30" si="249">N12/J12-1</f>
+        <f t="shared" ref="N30" si="245">N12/J12-1</f>
         <v>0.12116443745082606</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" ref="O30" si="250">O12/K12-1</f>
+        <f t="shared" ref="O30" si="246">O12/K12-1</f>
         <v>-7.6588337684943442E-2</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" ref="P30" si="251">P12/L12-1</f>
+        <f t="shared" ref="P30" si="247">P12/L12-1</f>
         <v>-9.7173144876324669E-3</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" ref="Q30" si="252">Q12/M12-1</f>
+        <f t="shared" ref="Q30" si="248">Q12/M12-1</f>
         <v>7.9728583545377374E-2</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" ref="R30" si="253">R12/N12-1</f>
+        <f t="shared" ref="R30" si="249">R12/N12-1</f>
         <v>0.16210526315789475</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" ref="S30" si="254">S12/O12-1</f>
+        <f t="shared" ref="S30" si="250">S12/O12-1</f>
         <v>5.4665409990575009E-2</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" ref="T30" si="255">T12/P12-1</f>
+        <f t="shared" ref="T30" si="251">T12/P12-1</f>
         <v>1.605709188224802E-2</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" ref="U30" si="256">U12/Q12-1</f>
+        <f t="shared" ref="U30" si="252">U12/Q12-1</f>
         <v>4.2419481539670123E-2</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" ref="V30" si="257">V12/R12-1</f>
+        <f t="shared" ref="V30" si="253">V12/R12-1</f>
         <v>-8.0917874396135292E-2</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" ref="W30:X30" si="258">W12/S12-1</f>
+        <f t="shared" ref="W30:X30" si="254">W12/S12-1</f>
         <v>0.15013404825737275</v>
       </c>
       <c r="X30" s="9">
+        <f t="shared" si="254"/>
+        <v>0.21510096575943805</v>
+      </c>
+      <c r="Y30" s="9">
+        <f t="shared" ref="Y30" si="255">Y12/U12-1</f>
+        <v>0.1152976639035419</v>
+      </c>
+      <c r="Z30" s="9">
+        <f t="shared" ref="Z30" si="256">Z12/V12-1</f>
+        <v>0.14914586070959257</v>
+      </c>
+      <c r="AA30" s="9">
+        <f t="shared" ref="AA30" si="257">AA12/W12-1</f>
+        <v>8.6247086247086324E-2</v>
+      </c>
+      <c r="AB30" s="9">
+        <f t="shared" ref="AB30:AL30" si="258">AB12/X12-1</f>
+        <v>0.68858381502890165</v>
+      </c>
+      <c r="AC30" s="9">
         <f t="shared" si="258"/>
-        <v>0.21510096575943805</v>
-      </c>
-      <c r="Y30" s="9">
-        <f t="shared" ref="Y30" si="259">Y12/U12-1</f>
-        <v>0.1152976639035419</v>
-      </c>
-      <c r="Z30" s="9">
-        <f t="shared" ref="Z30" si="260">Z12/V12-1</f>
-        <v>0.14914586070959257</v>
-      </c>
-      <c r="AA30" s="9">
-        <f t="shared" ref="AA30" si="261">AA12/W12-1</f>
-        <v>8.6247086247086324E-2</v>
-      </c>
-      <c r="AB30" s="9">
-        <f t="shared" ref="AB30:AL30" si="262">AB12/X12-1</f>
-        <v>0.68858381502890165</v>
-      </c>
-      <c r="AC30" s="9">
-        <f t="shared" si="262"/>
         <v>0.11013513513513518</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="262"/>
+        <f t="shared" si="258"/>
         <v>0.25614636935391655</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="262"/>
+        <f t="shared" si="258"/>
         <v>5.4363376251788331E-2</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="262"/>
+        <f t="shared" si="258"/>
         <v>-0.36927685066324345</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="262"/>
+        <f t="shared" si="258"/>
         <v>0.20328667072428486</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="262"/>
+        <f t="shared" si="258"/>
         <v>2.2303140646335873E-2</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="262"/>
+        <f t="shared" si="258"/>
         <v>0.1350067842605156</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="262"/>
+        <f t="shared" si="258"/>
         <v>0.23677069199457268</v>
       </c>
       <c r="AK30" s="9">
-        <f t="shared" si="262"/>
+        <f t="shared" si="258"/>
         <v>-0.12139605462822456</v>
       </c>
       <c r="AL30" s="9">
-        <f t="shared" si="262"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
+        <f t="shared" si="258"/>
+        <v>-0.1139804096170971</v>
+      </c>
+      <c r="AM30" s="9"/>
       <c r="AN30" s="9"/>
-      <c r="AO30" s="9">
-        <f t="shared" ref="AO30:BD30" si="263">AO12/AN12-1</f>
+      <c r="AO30" s="9"/>
+      <c r="AP30" s="9"/>
+      <c r="AQ30" s="9"/>
+      <c r="AS30" s="9"/>
+      <c r="AT30" s="9">
+        <f t="shared" ref="AT30:BI30" si="259">AT12/AS12-1</f>
         <v>6.0923900914974238E-2</v>
       </c>
-      <c r="AP30" s="9">
-        <f t="shared" si="263"/>
+      <c r="AU30" s="9">
+        <f t="shared" si="259"/>
         <v>2.7555742532604066E-2</v>
       </c>
-      <c r="AQ30" s="9">
-        <f t="shared" si="263"/>
+      <c r="AV30" s="9">
+        <f t="shared" si="259"/>
         <v>4.6264073694984642E-2</v>
       </c>
-      <c r="AR30" s="9">
-        <f t="shared" si="263"/>
+      <c r="AW30" s="9">
+        <f t="shared" si="259"/>
         <v>-7.8262570925458075E-4</v>
       </c>
-      <c r="AS30" s="9">
-        <f t="shared" si="263"/>
+      <c r="AX30" s="9">
+        <f t="shared" si="259"/>
         <v>0.15527707068729191</v>
       </c>
-      <c r="AT30" s="9">
-        <f t="shared" si="263"/>
+      <c r="AY30" s="9">
+        <f t="shared" si="259"/>
         <v>0.28389830508474567</v>
       </c>
-      <c r="AU30" s="9">
-        <f t="shared" si="263"/>
+      <c r="AZ30" s="9">
+        <f t="shared" si="259"/>
         <v>-5.3333333333333344E-2</v>
       </c>
-      <c r="AV30" s="9">
-        <f t="shared" si="263"/>
-        <v>6.1743132059684847E-2</v>
-      </c>
-      <c r="AW30" s="9">
-        <f t="shared" si="263"/>
+      <c r="BA30" s="9">
+        <f t="shared" si="259"/>
+        <v>7.2514293682890418E-3</v>
+      </c>
+      <c r="BB30" s="9">
+        <f t="shared" si="259"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AX30" s="9">
-        <f t="shared" si="263"/>
+      <c r="BC30" s="9">
+        <f t="shared" si="259"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AY30" s="9">
-        <f t="shared" si="263"/>
+      <c r="BD30" s="9">
+        <f t="shared" si="259"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AZ30" s="9">
-        <f t="shared" si="263"/>
+      <c r="BE30" s="9">
+        <f t="shared" si="259"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BA30" s="9">
-        <f t="shared" si="263"/>
+      <c r="BF30" s="9">
+        <f t="shared" si="259"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB30" s="9">
-        <f t="shared" si="263"/>
+      <c r="BG30" s="9">
+        <f t="shared" si="259"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BC30" s="9">
-        <f t="shared" si="263"/>
+      <c r="BH30" s="9">
+        <f t="shared" si="259"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BD30" s="9">
-        <f t="shared" si="263"/>
+      <c r="BI30" s="9">
+        <f t="shared" si="259"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BE30" s="9">
-        <f t="shared" ref="BE30" si="264">BE12/BD12-1</f>
+      <c r="BJ30" s="9">
+        <f t="shared" ref="BJ30" si="260">BJ12/BI12-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BF30" s="9">
-        <f t="shared" ref="BF30" si="265">BF12/BE12-1</f>
+      <c r="BK30" s="9">
+        <f t="shared" ref="BK30" si="261">BK12/BJ12-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:179" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:184" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>78</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="266">C16/C15</f>
+        <f t="shared" ref="C31:F31" si="262">C16/C15</f>
         <v>0.17691017233490924</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="266"/>
+        <f t="shared" si="262"/>
         <v>0.21877337322363499</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="266"/>
+        <f t="shared" si="262"/>
         <v>0.22667042571186918</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="266"/>
+        <f t="shared" si="262"/>
         <v>-1.3948228198039708E-2</v>
       </c>
       <c r="G31" s="9">
@@ -7883,200 +8035,205 @@
         <v>0.18224451957683499</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" ref="I31:V31" si="267">I16/I15</f>
+        <f t="shared" ref="I31:V31" si="263">I16/I15</f>
         <v>0.14084018053466035</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.16919475655430713</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.13667938557871051</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.18921521425132404</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.15992752241083349</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>-4.6919657033979038E-2</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.15828472331704241</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.17294994675186368</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.16281242700303666</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.16540008940545373</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.13836516993301909</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.15673228990565524</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.10321420283128337</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="267"/>
+        <f t="shared" si="263"/>
         <v>0.15186807523834064</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" ref="W31:X31" si="268">W16/W15</f>
+        <f t="shared" ref="W31:X31" si="264">W16/W15</f>
         <v>9.2574546871954783E-4</v>
       </c>
       <c r="X31" s="9">
+        <f t="shared" si="264"/>
+        <v>0.17567694181579688</v>
+      </c>
+      <c r="Y31" s="9">
+        <f t="shared" ref="Y31" si="265">Y16/Y15</f>
+        <v>0.17147102526002972</v>
+      </c>
+      <c r="Z31" s="9">
+        <f t="shared" ref="Z31" si="266">Z16/Z15</f>
+        <v>0.18289647093278666</v>
+      </c>
+      <c r="AA31" s="9">
+        <f t="shared" ref="AA31" si="267">AA16/AA15</f>
+        <v>0.18616725384758021</v>
+      </c>
+      <c r="AB31" s="9">
+        <f t="shared" ref="AB31:AC31" si="268">AB16/AB15</f>
+        <v>0.19243817296818919</v>
+      </c>
+      <c r="AC31" s="9">
         <f t="shared" si="268"/>
-        <v>0.17567694181579688</v>
-      </c>
-      <c r="Y31" s="9">
-        <f t="shared" ref="Y31" si="269">Y16/Y15</f>
-        <v>0.17147102526002972</v>
-      </c>
-      <c r="Z31" s="9">
-        <f t="shared" ref="Z31" si="270">Z16/Z15</f>
-        <v>0.18289647093278666</v>
-      </c>
-      <c r="AA31" s="9">
-        <f t="shared" ref="AA31" si="271">AA16/AA15</f>
-        <v>0.18616725384758021</v>
-      </c>
-      <c r="AB31" s="9">
-        <f t="shared" ref="AB31:AC31" si="272">AB16/AB15</f>
-        <v>0.19243817296818919</v>
-      </c>
-      <c r="AC31" s="9">
+        <v>0.19291668504388479</v>
+      </c>
+      <c r="AD31" s="9">
+        <f t="shared" ref="AD31:AE31" si="269">AD16/AD15</f>
+        <v>0.18789177821814212</v>
+      </c>
+      <c r="AE31" s="9">
+        <f t="shared" si="269"/>
+        <v>0.18300102624248643</v>
+      </c>
+      <c r="AF31" s="9">
+        <f t="shared" ref="AF31:AG31" si="270">AF16/AF15</f>
+        <v>0.18300102624248643</v>
+      </c>
+      <c r="AG31" s="9">
+        <f t="shared" si="270"/>
+        <v>0.17552589911784663</v>
+      </c>
+      <c r="AH31" s="9">
+        <f t="shared" ref="AH31:AI31" si="271">AH16/AH15</f>
+        <v>0.1913394495412844</v>
+      </c>
+      <c r="AI31" s="9">
+        <f t="shared" si="271"/>
+        <v>0.18507383791998414</v>
+      </c>
+      <c r="AJ31" s="9">
+        <f t="shared" ref="AJ31:AL31" si="272">AJ16/AJ15</f>
+        <v>0.17902264600715137</v>
+      </c>
+      <c r="AK31" s="9">
         <f t="shared" si="272"/>
-        <v>0.19291668504388479</v>
-      </c>
-      <c r="AD31" s="9">
-        <f t="shared" ref="AD31:AE31" si="273">AD16/AD15</f>
-        <v>0.18789177821814212</v>
-      </c>
-      <c r="AE31" s="9">
+        <v>0.17697676642126398</v>
+      </c>
+      <c r="AL31" s="9">
+        <f t="shared" si="272"/>
+        <v>0.16504169732646554</v>
+      </c>
+      <c r="AM31" s="9"/>
+      <c r="AN31" s="9"/>
+      <c r="AO31" s="9"/>
+      <c r="AP31" s="9"/>
+      <c r="AQ31" s="9"/>
+      <c r="AS31" s="9">
+        <f t="shared" ref="AS31:AU31" si="273">AS16/AS15</f>
+        <v>0.14889811346225237</v>
+      </c>
+      <c r="AT31" s="9">
         <f t="shared" si="273"/>
-        <v>0.18300102624248643</v>
-      </c>
-      <c r="AF31" s="9">
-        <f t="shared" ref="AF31:AG31" si="274">AF16/AF15</f>
-        <v>0.18300102624248643</v>
-      </c>
-      <c r="AG31" s="9">
+        <v>0.16732466962768</v>
+      </c>
+      <c r="AU31" s="9">
+        <f t="shared" si="273"/>
+        <v>0.10181285478850027</v>
+      </c>
+      <c r="AV31" s="9">
+        <f t="shared" ref="AV31:BF31" si="274">AV16/AV15</f>
+        <v>0.16507655177615205</v>
+      </c>
+      <c r="AW31" s="9">
         <f t="shared" si="274"/>
-        <v>0.17552589911784663</v>
-      </c>
-      <c r="AH31" s="9">
-        <f t="shared" ref="AH31:AI31" si="275">AH16/AH15</f>
-        <v>0.1913394495412844</v>
-      </c>
-      <c r="AI31" s="9">
-        <f t="shared" si="275"/>
-        <v>0.18507383791998414</v>
-      </c>
-      <c r="AJ31" s="9">
-        <f t="shared" ref="AJ31:AL31" si="276">AJ16/AJ15</f>
-        <v>0.17902264600715137</v>
-      </c>
-      <c r="AK31" s="9">
-        <f t="shared" si="276"/>
-        <v>0.17697676642126398</v>
-      </c>
-      <c r="AL31" s="9">
-        <f t="shared" si="276"/>
+        <v>0.13826615285083402</v>
+      </c>
+      <c r="AX31" s="9">
+        <f t="shared" ref="AX31" si="275">AX16/AX15</f>
+        <v>0.132990902152713</v>
+      </c>
+      <c r="AY31" s="9">
+        <f t="shared" si="274"/>
+        <v>0.18978625253328257</v>
+      </c>
+      <c r="AZ31" s="9">
+        <f t="shared" ref="AZ31" si="276">AZ16/AZ15</f>
+        <v>0.18326810898619214</v>
+      </c>
+      <c r="BA31" s="9">
+        <f t="shared" si="274"/>
+        <v>0.17629644009803683</v>
+      </c>
+      <c r="BB31" s="9">
+        <f t="shared" si="274"/>
         <v>0.19</v>
       </c>
-      <c r="AN31" s="9">
-        <f t="shared" ref="AN31:AP31" si="277">AN16/AN15</f>
-        <v>0.14889811346225237</v>
-      </c>
-      <c r="AO31" s="9">
+      <c r="BC31" s="9">
+        <f t="shared" si="274"/>
+        <v>0.19</v>
+      </c>
+      <c r="BD31" s="9">
+        <f t="shared" si="274"/>
+        <v>0.19</v>
+      </c>
+      <c r="BE31" s="9">
+        <f t="shared" si="274"/>
+        <v>0.19</v>
+      </c>
+      <c r="BF31" s="9">
+        <f t="shared" si="274"/>
+        <v>0.18999999999999997</v>
+      </c>
+      <c r="BG31" s="9">
+        <f t="shared" ref="BG31:BI31" si="277">BG16/BG15</f>
+        <v>0.18999999999999997</v>
+      </c>
+      <c r="BH31" s="9">
         <f t="shared" si="277"/>
-        <v>0.16732466962768</v>
-      </c>
-      <c r="AP31" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="BI31" s="9">
         <f t="shared" si="277"/>
-        <v>0.10181285478850027</v>
-      </c>
-      <c r="AQ31" s="9">
-        <f t="shared" ref="AQ31:BA31" si="278">AQ16/AQ15</f>
-        <v>0.16507655177615205</v>
-      </c>
-      <c r="AR31" s="9">
-        <f t="shared" si="278"/>
-        <v>0.13826615285083402</v>
-      </c>
-      <c r="AS31" s="9">
-        <f t="shared" ref="AS31" si="279">AS16/AS15</f>
-        <v>0.132990902152713</v>
-      </c>
-      <c r="AT31" s="9">
-        <f t="shared" si="278"/>
-        <v>0.18978625253328257</v>
-      </c>
-      <c r="AU31" s="9">
-        <f t="shared" ref="AU31" si="280">AU16/AU15</f>
-        <v>0.18326810898619214</v>
-      </c>
-      <c r="AV31" s="9">
-        <f t="shared" si="278"/>
-        <v>0.18282757151368959</v>
-      </c>
-      <c r="AW31" s="9">
+        <v>0.19000000000000003</v>
+      </c>
+      <c r="BJ31" s="9">
+        <f t="shared" ref="BJ31:BK31" si="278">BJ16/BJ15</f>
+        <v>0.19</v>
+      </c>
+      <c r="BK31" s="9">
         <f t="shared" si="278"/>
         <v>0.19</v>
-      </c>
-      <c r="AX31" s="9">
-        <f t="shared" si="278"/>
-        <v>0.19</v>
-      </c>
-      <c r="AY31" s="9">
-        <f t="shared" si="278"/>
-        <v>0.19</v>
-      </c>
-      <c r="AZ31" s="9">
-        <f t="shared" si="278"/>
-        <v>0.18999999999999997</v>
-      </c>
-      <c r="BA31" s="9">
-        <f t="shared" si="278"/>
-        <v>0.18999999999999997</v>
-      </c>
-      <c r="BB31" s="9">
-        <f t="shared" ref="BB31:BD31" si="281">BB16/BB15</f>
-        <v>0.19</v>
-      </c>
-      <c r="BC31" s="9">
-        <f t="shared" si="281"/>
-        <v>0.18999999999999997</v>
-      </c>
-      <c r="BD31" s="9">
-        <f t="shared" si="281"/>
-        <v>0.19</v>
-      </c>
-      <c r="BE31" s="9">
-        <f t="shared" ref="BE31:BF31" si="282">BE16/BE15</f>
-        <v>0.19000000000000003</v>
-      </c>
-      <c r="BF31" s="9">
-        <f t="shared" si="282"/>
-        <v>0.19000000000000003</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.3">
@@ -8311,27 +8468,27 @@
       </c>
       <c r="Y43" s="25"/>
       <c r="Z43" s="25">
-        <f t="shared" ref="Z43:AE43" si="283">SUM(Z34:Z42)</f>
+        <f t="shared" ref="Z43:AE43" si="279">SUM(Z34:Z42)</f>
         <v>364840</v>
       </c>
       <c r="AA43" s="25">
-        <f t="shared" si="283"/>
+        <f t="shared" si="279"/>
         <v>359784</v>
       </c>
       <c r="AB43" s="25">
-        <f t="shared" si="283"/>
+        <f t="shared" si="279"/>
         <v>364552</v>
       </c>
       <c r="AC43" s="25">
-        <f t="shared" si="283"/>
+        <f t="shared" si="279"/>
         <v>380088</v>
       </c>
       <c r="AD43" s="25">
-        <f t="shared" si="283"/>
+        <f t="shared" si="279"/>
         <v>411976</v>
       </c>
       <c r="AE43" s="25">
-        <f t="shared" si="283"/>
+        <f t="shared" si="279"/>
         <v>445785</v>
       </c>
     </row>
@@ -8539,27 +8696,27 @@
       </c>
       <c r="Y52" s="25"/>
       <c r="Z52" s="25">
-        <f t="shared" ref="Z52:AE52" si="284">SUM(Z45:Z51)</f>
+        <f t="shared" ref="Z52:AE52" si="280">SUM(Z45:Z51)</f>
         <v>198298</v>
       </c>
       <c r="AA52" s="25">
-        <f t="shared" si="284"/>
+        <f t="shared" si="280"/>
         <v>186308</v>
       </c>
       <c r="AB52" s="25">
-        <f t="shared" si="284"/>
+        <f t="shared" si="280"/>
         <v>181416</v>
       </c>
       <c r="AC52" s="25">
-        <f t="shared" si="284"/>
+        <f t="shared" si="280"/>
         <v>185405</v>
       </c>
       <c r="AD52" s="25">
-        <f t="shared" si="284"/>
+        <f t="shared" si="280"/>
         <v>205753</v>
       </c>
       <c r="AE52" s="25">
-        <f t="shared" si="284"/>
+        <f t="shared" si="280"/>
         <v>225071</v>
       </c>
     </row>
@@ -8595,27 +8752,27 @@
       </c>
       <c r="Y54" s="25"/>
       <c r="Z54" s="25">
-        <f t="shared" ref="Z54:AE54" si="285">Z52+Z53</f>
+        <f t="shared" ref="Z54:AE54" si="281">Z52+Z53</f>
         <v>364840</v>
       </c>
       <c r="AA54" s="25">
-        <f t="shared" si="285"/>
+        <f t="shared" si="281"/>
         <v>359874</v>
       </c>
       <c r="AB54" s="25">
-        <f t="shared" si="285"/>
+        <f t="shared" si="281"/>
         <v>364552</v>
       </c>
       <c r="AC54" s="25">
-        <f t="shared" si="285"/>
+        <f t="shared" si="281"/>
         <v>380088</v>
       </c>
       <c r="AD54" s="25">
-        <f t="shared" si="285"/>
+        <f t="shared" si="281"/>
         <v>411976</v>
       </c>
       <c r="AE54" s="25">
-        <f t="shared" si="285"/>
+        <f t="shared" si="281"/>
         <v>445785</v>
       </c>
     </row>

--- a/Financial Analysis/MSFT.xlsx
+++ b/Financial Analysis/MSFT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93D2327-2A19-4A7A-B7FB-7A8CF3BDAAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6452824F-285E-4AE2-8267-55AFF8FF603A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{61E89E8F-0FF3-456B-A54B-AD32D916470B}"/>
   </bookViews>
@@ -748,14 +748,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
@@ -772,7 +772,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27889200" y="0"/>
+          <a:off x="28620720" y="0"/>
           <a:ext cx="0" cy="6088380"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1188,17 +1188,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="19">
-        <v>520.79999999999995</v>
+        <v>527.70000000000005</v>
       </c>
       <c r="E3" s="2">
-        <v>45887</v>
+        <v>45960</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45887</v>
+        <v>45960</v>
       </c>
       <c r="G3" s="2">
-        <v>45960</v>
+        <v>46057</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>43</v>
@@ -1219,10 +1219,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>7432</v>
+        <f>7432.4</f>
+        <v>7432.4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F4" s="1"/>
       <c r="I4" s="13"/>
@@ -1243,7 +1244,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>3870585.5999999996</v>
+        <v>3922077.48</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1339,7 +1340,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>3803766.5999999996</v>
+        <v>3855258.48</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1826,7 +1827,9 @@
       <c r="AL3" s="4">
         <v>17136</v>
       </c>
-      <c r="AM3" s="4"/>
+      <c r="AM3" s="4">
+        <v>15922</v>
+      </c>
       <c r="AN3" s="4"/>
       <c r="AO3" s="4"/>
       <c r="AP3" s="4"/>
@@ -2020,7 +2023,9 @@
       <c r="AL4" s="4">
         <v>59305</v>
       </c>
-      <c r="AM4" s="4"/>
+      <c r="AM4" s="4">
+        <v>61751</v>
+      </c>
       <c r="AN4" s="4"/>
       <c r="AO4" s="4"/>
       <c r="AP4" s="4"/>
@@ -2062,44 +2067,44 @@
         <v>217778</v>
       </c>
       <c r="BB4" s="5">
-        <f>BA4*1.15</f>
-        <v>250444.69999999998</v>
+        <f>BA4*1.18</f>
+        <v>256978.03999999998</v>
       </c>
       <c r="BC4" s="5">
-        <f>BB4*1.08</f>
-        <v>270480.27600000001</v>
+        <f>BB4*1.09</f>
+        <v>280106.06359999999</v>
       </c>
       <c r="BD4" s="5">
         <f>BC4*1.06</f>
-        <v>286709.09256000002</v>
+        <v>296912.42741599999</v>
       </c>
       <c r="BE4" s="5">
         <f>BD4*1.05</f>
-        <v>301044.54718800006</v>
+        <v>311758.04878680001</v>
       </c>
       <c r="BF4" s="5">
         <f>BE4*1.04</f>
-        <v>313086.32907552004</v>
+        <v>324228.37073827203</v>
       </c>
       <c r="BG4" s="5">
         <f>BF4*1.03</f>
-        <v>322478.91894778563</v>
+        <v>333955.22186042019</v>
       </c>
       <c r="BH4" s="5">
         <f>BG4*1.03</f>
-        <v>332153.2865162192</v>
+        <v>343973.87851623283</v>
       </c>
       <c r="BI4" s="5">
         <f>BH4*1.02</f>
-        <v>338796.35224654357</v>
+        <v>350853.3560865575</v>
       </c>
       <c r="BJ4" s="5">
         <f t="shared" ref="BJ4:BK4" si="1">BI4*1.02</f>
-        <v>345572.27929147444</v>
+        <v>357870.42320828867</v>
       </c>
       <c r="BK4" s="5">
         <f t="shared" si="1"/>
-        <v>352483.72487730393</v>
+        <v>365027.83167245443</v>
       </c>
     </row>
     <row r="5" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2250,86 +2255,89 @@
         <f t="shared" si="10"/>
         <v>76441</v>
       </c>
-      <c r="AM5" s="7"/>
+      <c r="AM5" s="7">
+        <f t="shared" ref="AM5" si="11">AM3+AM4</f>
+        <v>77673</v>
+      </c>
       <c r="AN5" s="7"/>
       <c r="AO5" s="7"/>
       <c r="AP5" s="7"/>
       <c r="AQ5" s="7"/>
       <c r="AS5" s="7">
-        <f t="shared" ref="AS5:AW5" si="11">AS3+AS4</f>
+        <f t="shared" ref="AS5:AW5" si="12">AS3+AS4</f>
         <v>96301</v>
       </c>
       <c r="AT5" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>110360</v>
       </c>
       <c r="AU5" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>125843</v>
       </c>
       <c r="AV5" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>143015</v>
       </c>
       <c r="AW5" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>168088</v>
       </c>
       <c r="AX5" s="7">
-        <f t="shared" ref="AX5:AY5" si="12">AX3+AX4</f>
+        <f t="shared" ref="AX5:AY5" si="13">AX3+AX4</f>
         <v>198270</v>
       </c>
       <c r="AY5" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>211915</v>
       </c>
       <c r="AZ5" s="7">
-        <f t="shared" ref="AZ5" si="13">AZ3+AZ4</f>
+        <f t="shared" ref="AZ5" si="14">AZ3+AZ4</f>
         <v>239781</v>
       </c>
       <c r="BA5" s="7">
-        <f t="shared" ref="BA5:BF5" si="14">BA3+BA4</f>
+        <f t="shared" ref="BA5:BF5" si="15">BA3+BA4</f>
         <v>281724</v>
       </c>
       <c r="BB5" s="7">
-        <f t="shared" si="14"/>
-        <v>315030.15999999997</v>
+        <f t="shared" si="15"/>
+        <v>321563.5</v>
       </c>
       <c r="BC5" s="7">
-        <f t="shared" si="14"/>
-        <v>335711.5906</v>
+        <f t="shared" si="15"/>
+        <v>345337.37819999998</v>
       </c>
       <c r="BD5" s="7">
-        <f t="shared" si="14"/>
-        <v>352592.72030600003</v>
+        <f t="shared" si="15"/>
+        <v>362796.055162</v>
       </c>
       <c r="BE5" s="7">
-        <f t="shared" si="14"/>
-        <v>367587.01121146005</v>
+        <f t="shared" si="15"/>
+        <v>378300.51281026</v>
       </c>
       <c r="BF5" s="7">
-        <f t="shared" si="14"/>
-        <v>380294.21773921466</v>
+        <f t="shared" si="15"/>
+        <v>391436.25940196664</v>
       </c>
       <c r="BG5" s="7">
-        <f t="shared" ref="BG5:BI5" si="15">BG3+BG4</f>
-        <v>390358.88649811718</v>
+        <f t="shared" ref="BG5:BI5" si="16">BG3+BG4</f>
+        <v>401835.18941075174</v>
       </c>
       <c r="BH5" s="7">
-        <f t="shared" si="15"/>
-        <v>400712.05374205403</v>
+        <f t="shared" si="16"/>
+        <v>412532.64574206766</v>
       </c>
       <c r="BI5" s="7">
-        <f t="shared" si="15"/>
-        <v>408040.70714463678</v>
+        <f t="shared" si="16"/>
+        <v>420097.71098465071</v>
       </c>
       <c r="BJ5" s="7">
-        <f t="shared" ref="BJ5:BK5" si="16">BJ3+BJ4</f>
-        <v>415509.07773854857</v>
+        <f t="shared" ref="BJ5:BK5" si="17">BJ3+BJ4</f>
+        <v>427807.22165536281</v>
       </c>
       <c r="BK5" s="7">
-        <f t="shared" si="16"/>
-        <v>423119.8913088488</v>
+        <f t="shared" si="17"/>
+        <v>435663.9981039993</v>
       </c>
     </row>
     <row r="6" spans="2:63" x14ac:dyDescent="0.3">
@@ -2444,7 +2452,9 @@
       <c r="AL6" s="5">
         <v>3314</v>
       </c>
-      <c r="AM6" s="5"/>
+      <c r="AM6" s="5">
+        <v>2922</v>
+      </c>
       <c r="AN6" s="5"/>
       <c r="AO6" s="5"/>
       <c r="AP6" s="5"/>
@@ -2486,43 +2496,43 @@
         <v>13501</v>
       </c>
       <c r="BB6" s="5">
-        <f t="shared" ref="BB6:BI6" si="17">BB3*0.23</f>
+        <f t="shared" ref="BB6:BI6" si="18">BB3*0.23</f>
         <v>14854.6558</v>
       </c>
       <c r="BC6" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15003.202358</v>
       </c>
       <c r="BD6" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15153.23438158</v>
       </c>
       <c r="BE6" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15304.766725395799</v>
       </c>
       <c r="BF6" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15457.814392649758</v>
       </c>
       <c r="BG6" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15612.392536576253</v>
       </c>
       <c r="BH6" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15768.516461942016</v>
       </c>
       <c r="BI6" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15926.201626561437</v>
       </c>
       <c r="BJ6" s="5">
-        <f t="shared" ref="BJ6:BK6" si="18">BJ3*0.23</f>
+        <f t="shared" ref="BJ6:BK6" si="19">BJ3*0.23</f>
         <v>16085.463642827048</v>
       </c>
       <c r="BK6" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>16246.318279255318</v>
       </c>
     </row>
@@ -2638,7 +2648,9 @@
       <c r="AL7" s="5">
         <v>20700</v>
       </c>
-      <c r="AM7" s="5"/>
+      <c r="AM7" s="5">
+        <v>21121</v>
+      </c>
       <c r="AN7" s="5"/>
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
@@ -2681,43 +2693,43 @@
       </c>
       <c r="BB7" s="5">
         <f>BB4*0.33</f>
-        <v>82646.751000000004</v>
+        <v>84802.753199999992</v>
       </c>
       <c r="BC7" s="5">
-        <f t="shared" ref="BC7:BK7" si="19">BC4*0.33</f>
-        <v>89258.491080000007</v>
+        <f t="shared" ref="BC7:BK7" si="20">BC4*0.33</f>
+        <v>92435.000988</v>
       </c>
       <c r="BD7" s="5">
-        <f t="shared" si="19"/>
-        <v>94614.000544800016</v>
+        <f t="shared" si="20"/>
+        <v>97981.101047279997</v>
       </c>
       <c r="BE7" s="5">
-        <f t="shared" si="19"/>
-        <v>99344.700572040019</v>
+        <f t="shared" si="20"/>
+        <v>102880.15609964401</v>
       </c>
       <c r="BF7" s="5">
-        <f t="shared" si="19"/>
-        <v>103318.48859492163</v>
+        <f t="shared" si="20"/>
+        <v>106995.36234362978</v>
       </c>
       <c r="BG7" s="5">
-        <f t="shared" si="19"/>
-        <v>106418.04325276926</v>
+        <f t="shared" si="20"/>
+        <v>110205.22321393866</v>
       </c>
       <c r="BH7" s="5">
-        <f t="shared" si="19"/>
-        <v>109610.58455035235</v>
+        <f t="shared" si="20"/>
+        <v>113511.37991035685</v>
       </c>
       <c r="BI7" s="5">
-        <f t="shared" si="19"/>
-        <v>111802.79624135938</v>
+        <f t="shared" si="20"/>
+        <v>115781.60750856397</v>
       </c>
       <c r="BJ7" s="5">
-        <f t="shared" si="19"/>
-        <v>114038.85216618657</v>
+        <f t="shared" si="20"/>
+        <v>118097.23965873527</v>
       </c>
       <c r="BK7" s="5">
-        <f t="shared" si="19"/>
-        <v>116319.6292095103</v>
+        <f t="shared" si="20"/>
+        <v>120459.18445190997</v>
       </c>
     </row>
     <row r="8" spans="2:63" x14ac:dyDescent="0.3">
@@ -2725,229 +2737,232 @@
         <v>27</v>
       </c>
       <c r="C8" s="5">
-        <f t="shared" ref="C8:R8" si="20">C6+C7</f>
+        <f t="shared" ref="C8:R8" si="21">C6+C7</f>
         <v>7844</v>
       </c>
       <c r="D8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9901</v>
       </c>
       <c r="E8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>8060</v>
       </c>
       <c r="F8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>8456</v>
       </c>
       <c r="G8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>8278</v>
       </c>
       <c r="H8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>11064</v>
       </c>
       <c r="I8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9269</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9742</v>
       </c>
       <c r="K8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9905</v>
       </c>
       <c r="L8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12423</v>
       </c>
       <c r="M8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10170</v>
       </c>
       <c r="N8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10412</v>
       </c>
       <c r="O8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10406</v>
       </c>
       <c r="P8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12358</v>
       </c>
       <c r="Q8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10975</v>
       </c>
       <c r="R8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12339</v>
       </c>
       <c r="S8" s="5">
-        <f t="shared" ref="S8:V8" si="21">S6+S7</f>
+        <f t="shared" ref="S8:V8" si="22">S6+S7</f>
         <v>11002</v>
       </c>
       <c r="T8" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14194</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13045</v>
       </c>
       <c r="V8" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13991</v>
       </c>
       <c r="W8" s="5">
-        <f t="shared" ref="W8:X8" si="22">W6+W7</f>
+        <f t="shared" ref="W8:X8" si="23">W6+W7</f>
         <v>13646</v>
       </c>
       <c r="X8" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>18129</v>
       </c>
       <c r="Y8" s="5">
-        <f t="shared" ref="Y8" si="23">Y6+Y7</f>
+        <f t="shared" ref="Y8" si="24">Y6+Y7</f>
         <v>15615</v>
       </c>
       <c r="Z8" s="5">
-        <f t="shared" ref="Z8" si="24">Z6+Z7</f>
+        <f t="shared" ref="Z8" si="25">Z6+Z7</f>
         <v>16429</v>
       </c>
       <c r="AA8" s="5">
-        <f t="shared" ref="AA8" si="25">AA6+AA7</f>
+        <f t="shared" ref="AA8" si="26">AA6+AA7</f>
         <v>15452</v>
       </c>
       <c r="AB8" s="5">
-        <f t="shared" ref="AB8:AC8" si="26">AB6+AB7</f>
+        <f t="shared" ref="AB8:AC8" si="27">AB6+AB7</f>
         <v>17488</v>
       </c>
       <c r="AC8" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16128</v>
       </c>
       <c r="AD8" s="5">
-        <f t="shared" ref="AD8:AE8" si="27">AD6+AD7</f>
+        <f t="shared" ref="AD8:AE8" si="28">AD6+AD7</f>
         <v>16795</v>
       </c>
       <c r="AE8" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>16302</v>
       </c>
       <c r="AF8" s="5">
-        <f t="shared" ref="AF8:AG8" si="28">AF6+AF7</f>
+        <f t="shared" ref="AF8:AG8" si="29">AF6+AF7</f>
         <v>16302</v>
       </c>
       <c r="AG8" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>19623</v>
       </c>
       <c r="AH8" s="5">
-        <f t="shared" ref="AH8:AI8" si="29">AH6+AH7</f>
+        <f t="shared" ref="AH8:AI8" si="30">AH6+AH7</f>
         <v>19684</v>
       </c>
       <c r="AI8" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>20099</v>
       </c>
       <c r="AJ8" s="5">
-        <f t="shared" ref="AJ8:AL8" si="30">AJ6+AJ7</f>
+        <f t="shared" ref="AJ8:AL8" si="31">AJ6+AJ7</f>
         <v>21799</v>
       </c>
       <c r="AK8" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>21919</v>
       </c>
       <c r="AL8" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>24014</v>
       </c>
-      <c r="AM8" s="5"/>
+      <c r="AM8" s="5">
+        <f t="shared" ref="AM8" si="32">AM6+AM7</f>
+        <v>24043</v>
+      </c>
       <c r="AN8" s="5"/>
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
       <c r="AQ8" s="5"/>
       <c r="AS8" s="5">
-        <f t="shared" ref="AS8:AZ8" si="31">AS6+AS7</f>
+        <f t="shared" ref="AS8:AZ8" si="33">AS6+AS7</f>
         <v>34261</v>
       </c>
       <c r="AT8" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>38353</v>
       </c>
       <c r="AU8" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>42910</v>
       </c>
       <c r="AV8" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>46078</v>
       </c>
       <c r="AW8" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>52232</v>
       </c>
       <c r="AX8" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>63819</v>
       </c>
       <c r="AY8" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>65863</v>
       </c>
       <c r="AZ8" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>71911</v>
       </c>
       <c r="BA8" s="5">
-        <f t="shared" ref="BA8:BI8" si="32">BA6+BA7</f>
+        <f t="shared" ref="BA8:BI8" si="34">BA6+BA7</f>
         <v>87831</v>
       </c>
       <c r="BB8" s="5">
-        <f t="shared" si="32"/>
-        <v>97501.406799999997</v>
+        <f t="shared" si="34"/>
+        <v>99657.408999999985</v>
       </c>
       <c r="BC8" s="5">
-        <f t="shared" si="32"/>
-        <v>104261.693438</v>
+        <f t="shared" si="34"/>
+        <v>107438.20334599999</v>
       </c>
       <c r="BD8" s="5">
-        <f t="shared" si="32"/>
-        <v>109767.23492638001</v>
+        <f t="shared" si="34"/>
+        <v>113134.33542885999</v>
       </c>
       <c r="BE8" s="5">
-        <f t="shared" si="32"/>
-        <v>114649.46729743583</v>
+        <f t="shared" si="34"/>
+        <v>118184.9228250398</v>
       </c>
       <c r="BF8" s="5">
-        <f t="shared" si="32"/>
-        <v>118776.30298757138</v>
+        <f t="shared" si="34"/>
+        <v>122453.17673627954</v>
       </c>
       <c r="BG8" s="5">
-        <f t="shared" si="32"/>
-        <v>122030.43578934552</v>
+        <f t="shared" si="34"/>
+        <v>125817.61575051492</v>
       </c>
       <c r="BH8" s="5">
-        <f t="shared" si="32"/>
-        <v>125379.10101229436</v>
+        <f t="shared" si="34"/>
+        <v>129279.89637229886</v>
       </c>
       <c r="BI8" s="5">
-        <f t="shared" si="32"/>
-        <v>127728.99786792081</v>
+        <f t="shared" si="34"/>
+        <v>131707.80913512543</v>
       </c>
       <c r="BJ8" s="5">
-        <f t="shared" ref="BJ8:BK8" si="33">BJ6+BJ7</f>
-        <v>130124.31580901361</v>
+        <f t="shared" ref="BJ8:BK8" si="35">BJ6+BJ7</f>
+        <v>134182.70330156232</v>
       </c>
       <c r="BK8" s="5">
-        <f t="shared" si="33"/>
-        <v>132565.94748876561</v>
+        <f t="shared" si="35"/>
+        <v>136705.5027311653</v>
       </c>
     </row>
     <row r="9" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2955,229 +2970,232 @@
         <v>32</v>
       </c>
       <c r="C9" s="7">
-        <f t="shared" ref="C9:R9" si="34">C5-C8</f>
+        <f t="shared" ref="C9:R9" si="36">C5-C8</f>
         <v>13814</v>
       </c>
       <c r="D9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>15925</v>
       </c>
       <c r="E9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>15152</v>
       </c>
       <c r="F9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>17149</v>
       </c>
       <c r="G9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>16260</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>17854</v>
       </c>
       <c r="I9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>17550</v>
       </c>
       <c r="J9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>20343</v>
       </c>
       <c r="K9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>19179</v>
       </c>
       <c r="L9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>20048</v>
       </c>
       <c r="M9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>20401</v>
       </c>
       <c r="N9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>23305</v>
       </c>
       <c r="O9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>22649</v>
       </c>
       <c r="P9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>24548</v>
       </c>
       <c r="Q9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>24046</v>
       </c>
       <c r="R9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>25694</v>
       </c>
       <c r="S9" s="7">
-        <f t="shared" ref="S9:V9" si="35">S5-S8</f>
+        <f t="shared" ref="S9:V9" si="37">S5-S8</f>
         <v>26152</v>
       </c>
       <c r="T9" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>28882</v>
       </c>
       <c r="U9" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>28661</v>
       </c>
       <c r="V9" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>32161</v>
       </c>
       <c r="W9" s="7">
-        <f t="shared" ref="W9:X9" si="36">W5-W8</f>
+        <f t="shared" ref="W9:X9" si="38">W5-W8</f>
         <v>31671</v>
       </c>
       <c r="X9" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>33599</v>
       </c>
       <c r="Y9" s="7">
-        <f t="shared" ref="Y9" si="37">Y5-Y8</f>
+        <f t="shared" ref="Y9" si="39">Y5-Y8</f>
         <v>33745</v>
       </c>
       <c r="Z9" s="7">
-        <f t="shared" ref="Z9" si="38">Z5-Z8</f>
+        <f t="shared" ref="Z9" si="40">Z5-Z8</f>
         <v>35436</v>
       </c>
       <c r="AA9" s="7">
-        <f t="shared" ref="AA9" si="39">AA5-AA8</f>
+        <f t="shared" ref="AA9" si="41">AA5-AA8</f>
         <v>34670</v>
       </c>
       <c r="AB9" s="7">
-        <f t="shared" ref="AB9:AC9" si="40">AB5-AB8</f>
+        <f t="shared" ref="AB9:AC9" si="42">AB5-AB8</f>
         <v>35259</v>
       </c>
       <c r="AC9" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>36729</v>
       </c>
       <c r="AD9" s="7">
-        <f t="shared" ref="AD9:AE9" si="41">AD5-AD8</f>
+        <f t="shared" ref="AD9:AE9" si="43">AD5-AD8</f>
         <v>39394</v>
       </c>
       <c r="AE9" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>40215</v>
       </c>
       <c r="AF9" s="7">
-        <f t="shared" ref="AF9:AG9" si="42">AF5-AF8</f>
+        <f t="shared" ref="AF9:AG9" si="44">AF5-AF8</f>
         <v>40215</v>
       </c>
       <c r="AG9" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>42397</v>
       </c>
       <c r="AH9" s="7">
-        <f t="shared" ref="AH9:AI9" si="43">AH5-AH8</f>
+        <f t="shared" ref="AH9:AI9" si="45">AH5-AH8</f>
         <v>45043</v>
       </c>
       <c r="AI9" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>45486</v>
       </c>
       <c r="AJ9" s="7">
-        <f t="shared" ref="AJ9:AL9" si="44">AJ5-AJ8</f>
+        <f t="shared" ref="AJ9:AL9" si="46">AJ5-AJ8</f>
         <v>47833</v>
       </c>
       <c r="AK9" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>48147</v>
       </c>
       <c r="AL9" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>52427</v>
       </c>
-      <c r="AM9" s="7"/>
+      <c r="AM9" s="7">
+        <f t="shared" ref="AM9" si="47">AM5-AM8</f>
+        <v>53630</v>
+      </c>
       <c r="AN9" s="7"/>
       <c r="AO9" s="7"/>
       <c r="AP9" s="7"/>
       <c r="AQ9" s="7"/>
       <c r="AS9" s="7">
-        <f t="shared" ref="AS9:AZ9" si="45">AS5-AS8</f>
+        <f t="shared" ref="AS9:AZ9" si="48">AS5-AS8</f>
         <v>62040</v>
       </c>
       <c r="AT9" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>72007</v>
       </c>
       <c r="AU9" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>82933</v>
       </c>
       <c r="AV9" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>96937</v>
       </c>
       <c r="AW9" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>115856</v>
       </c>
       <c r="AX9" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>134451</v>
       </c>
       <c r="AY9" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>146052</v>
       </c>
       <c r="AZ9" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>167870</v>
       </c>
       <c r="BA9" s="7">
-        <f t="shared" ref="BA9:BI9" si="46">BA5-BA8</f>
+        <f t="shared" ref="BA9:BI9" si="49">BA5-BA8</f>
         <v>193893</v>
       </c>
       <c r="BB9" s="7">
-        <f t="shared" si="46"/>
-        <v>217528.75319999998</v>
+        <f t="shared" si="49"/>
+        <v>221906.09100000001</v>
       </c>
       <c r="BC9" s="7">
-        <f t="shared" si="46"/>
-        <v>231449.89716200001</v>
+        <f t="shared" si="49"/>
+        <v>237899.17485399998</v>
       </c>
       <c r="BD9" s="7">
-        <f t="shared" si="46"/>
-        <v>242825.48537962002</v>
+        <f t="shared" si="49"/>
+        <v>249661.71973314002</v>
       </c>
       <c r="BE9" s="7">
-        <f t="shared" si="46"/>
-        <v>252937.54391402422</v>
+        <f t="shared" si="49"/>
+        <v>260115.5899852202</v>
       </c>
       <c r="BF9" s="7">
-        <f t="shared" si="46"/>
-        <v>261517.91475164326</v>
+        <f t="shared" si="49"/>
+        <v>268983.08266568708</v>
       </c>
       <c r="BG9" s="7">
-        <f t="shared" si="46"/>
-        <v>268328.45070877165</v>
+        <f t="shared" si="49"/>
+        <v>276017.57366023684</v>
       </c>
       <c r="BH9" s="7">
-        <f t="shared" si="46"/>
-        <v>275332.95272975968</v>
+        <f t="shared" si="49"/>
+        <v>283252.74936976878</v>
       </c>
       <c r="BI9" s="7">
-        <f t="shared" si="46"/>
-        <v>280311.70927671599</v>
+        <f t="shared" si="49"/>
+        <v>288389.90184952528</v>
       </c>
       <c r="BJ9" s="7">
-        <f t="shared" ref="BJ9:BK9" si="47">BJ5-BJ8</f>
-        <v>285384.76192953496</v>
+        <f t="shared" ref="BJ9:BK9" si="50">BJ5-BJ8</f>
+        <v>293624.51835380052</v>
       </c>
       <c r="BK9" s="7">
-        <f t="shared" si="47"/>
-        <v>290553.94382008316</v>
+        <f t="shared" si="50"/>
+        <v>298958.49537283403</v>
       </c>
     </row>
     <row r="10" spans="2:63" x14ac:dyDescent="0.3">
@@ -3292,7 +3310,9 @@
       <c r="AL10" s="5">
         <v>8829</v>
       </c>
-      <c r="AM10" s="5"/>
+      <c r="AM10" s="5">
+        <v>8146</v>
+      </c>
       <c r="AN10" s="5"/>
       <c r="AO10" s="5"/>
       <c r="AP10" s="5"/>
@@ -3346,31 +3366,31 @@
         <v>36531.066624000006</v>
       </c>
       <c r="BE10" s="5">
-        <f t="shared" ref="BE10:BI10" si="48">BD10*1.01</f>
+        <f t="shared" ref="BE10:BI10" si="51">BD10*1.01</f>
         <v>36896.377290240009</v>
       </c>
       <c r="BF10" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>37265.341063142412</v>
       </c>
       <c r="BG10" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>37637.994473773833</v>
       </c>
       <c r="BH10" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>38014.374418511572</v>
       </c>
       <c r="BI10" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>38394.518162696688</v>
       </c>
       <c r="BJ10" s="5">
-        <f t="shared" ref="BJ10" si="49">BI10*1.01</f>
+        <f t="shared" ref="BJ10" si="52">BI10*1.01</f>
         <v>38778.463344323653</v>
       </c>
       <c r="BK10" s="5">
-        <f t="shared" ref="BK10" si="50">BJ10*1.01</f>
+        <f t="shared" ref="BK10" si="53">BJ10*1.01</f>
         <v>39166.247977766892</v>
       </c>
     </row>
@@ -3486,7 +3506,9 @@
       <c r="AL11" s="5">
         <v>7285</v>
       </c>
-      <c r="AM11" s="5"/>
+      <c r="AM11" s="5">
+        <v>5717</v>
+      </c>
       <c r="AN11" s="5"/>
       <c r="AO11" s="5"/>
       <c r="AP11" s="5"/>
@@ -3532,39 +3554,39 @@
         <v>26167.08</v>
       </c>
       <c r="BC11" s="5">
-        <f t="shared" ref="BC11:BI11" si="51">BB11*1.02</f>
+        <f t="shared" ref="BC11:BI11" si="54">BB11*1.02</f>
         <v>26690.421600000001</v>
       </c>
       <c r="BD11" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>27224.230032000003</v>
       </c>
       <c r="BE11" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>27768.714632640003</v>
       </c>
       <c r="BF11" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>28324.088925292803</v>
       </c>
       <c r="BG11" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>28890.570703798658</v>
       </c>
       <c r="BH11" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>29468.382117874633</v>
       </c>
       <c r="BI11" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>30057.749760232127</v>
       </c>
       <c r="BJ11" s="5">
-        <f t="shared" ref="BJ11" si="52">BI11*1.02</f>
+        <f t="shared" ref="BJ11" si="55">BI11*1.02</f>
         <v>30658.904755436772</v>
       </c>
       <c r="BK11" s="5">
-        <f t="shared" ref="BK11" si="53">BJ11*1.02</f>
+        <f t="shared" ref="BK11" si="56">BJ11*1.02</f>
         <v>31272.082850545507</v>
       </c>
     </row>
@@ -3680,7 +3702,9 @@
       <c r="AL12" s="5">
         <v>1990</v>
       </c>
-      <c r="AM12" s="5"/>
+      <c r="AM12" s="5">
+        <v>1806</v>
+      </c>
       <c r="AN12" s="5"/>
       <c r="AO12" s="5"/>
       <c r="AP12" s="5"/>
@@ -3746,19 +3770,19 @@
         <v>8536.8803637499223</v>
       </c>
       <c r="BH12" s="5">
-        <f t="shared" ref="BH12:BK12" si="54">BG12*1.01</f>
+        <f t="shared" ref="BH12:BK12" si="57">BG12*1.01</f>
         <v>8622.249167387421</v>
       </c>
       <c r="BI12" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>8708.4716590612952</v>
       </c>
       <c r="BJ12" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>8795.5563756519077</v>
       </c>
       <c r="BK12" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>8883.5119394084268</v>
       </c>
     </row>
@@ -3767,150 +3791,153 @@
         <v>36</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:R13" si="55">C9-C10-C11-C12</f>
+        <f t="shared" ref="C13:R13" si="58">C9-C10-C11-C12</f>
         <v>6445</v>
       </c>
       <c r="D13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>7905</v>
       </c>
       <c r="E13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>6723</v>
       </c>
       <c r="F13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>7988</v>
       </c>
       <c r="G13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>7708</v>
       </c>
       <c r="H13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>8679</v>
       </c>
       <c r="I13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>8292</v>
       </c>
       <c r="J13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>10379</v>
       </c>
       <c r="K13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>9955</v>
       </c>
       <c r="L13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>10258</v>
       </c>
       <c r="M13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>10341</v>
       </c>
       <c r="N13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>12405</v>
       </c>
       <c r="O13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>12686</v>
       </c>
       <c r="P13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>13891</v>
       </c>
       <c r="Q13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>12975</v>
       </c>
       <c r="R13" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>13407</v>
       </c>
       <c r="S13" s="7">
-        <f t="shared" ref="S13:V13" si="56">S9-S10-S11-S12</f>
+        <f t="shared" ref="S13:V13" si="59">S9-S10-S11-S12</f>
         <v>15876</v>
       </c>
       <c r="T13" s="7">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>17897</v>
       </c>
       <c r="U13" s="7">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>17048</v>
       </c>
       <c r="V13" s="7">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>19095</v>
       </c>
       <c r="W13" s="7">
-        <f t="shared" ref="W13:X13" si="57">W9-W10-W11-W12</f>
+        <f t="shared" ref="W13:X13" si="60">W9-W10-W11-W12</f>
         <v>20238</v>
       </c>
       <c r="X13" s="7">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>21078</v>
       </c>
       <c r="Y13" s="7">
-        <f t="shared" ref="Y13" si="58">Y9-Y10-Y11-Y12</f>
+        <f t="shared" ref="Y13" si="61">Y9-Y10-Y11-Y12</f>
         <v>20364</v>
       </c>
       <c r="Z13" s="7">
-        <f t="shared" ref="Z13" si="59">Z9-Z10-Z11-Z12</f>
+        <f t="shared" ref="Z13" si="62">Z9-Z10-Z11-Z12</f>
         <v>20534</v>
       </c>
       <c r="AA13" s="7">
-        <f t="shared" ref="AA13" si="60">AA9-AA10-AA11-AA12</f>
+        <f t="shared" ref="AA13" si="63">AA9-AA10-AA11-AA12</f>
         <v>21518</v>
       </c>
       <c r="AB13" s="7">
-        <f t="shared" ref="AB13:AC13" si="61">AB9-AB10-AB11-AB12</f>
+        <f t="shared" ref="AB13:AC13" si="64">AB9-AB10-AB11-AB12</f>
         <v>20399</v>
       </c>
       <c r="AC13" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>22352</v>
       </c>
       <c r="AD13" s="7">
-        <f t="shared" ref="AD13:AE13" si="62">AD9-AD10-AD11-AD12</f>
+        <f t="shared" ref="AD13:AE13" si="65">AD9-AD10-AD11-AD12</f>
         <v>24254</v>
       </c>
       <c r="AE13" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>26895</v>
       </c>
       <c r="AF13" s="7">
-        <f t="shared" ref="AF13:AG13" si="63">AF9-AF10-AF11-AF12</f>
+        <f t="shared" ref="AF13:AG13" si="66">AF9-AF10-AF11-AF12</f>
         <v>26895</v>
       </c>
       <c r="AG13" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>27032</v>
       </c>
       <c r="AH13" s="7">
-        <f t="shared" ref="AH13:AL13" si="64">AH9-AH10-AH11-AH12</f>
+        <f t="shared" ref="AH13:AL13" si="67">AH9-AH10-AH11-AH12</f>
         <v>27925</v>
       </c>
       <c r="AI13" s="7">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>30552</v>
       </c>
       <c r="AJ13" s="7">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>31653</v>
       </c>
       <c r="AK13" s="7">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>32000</v>
       </c>
       <c r="AL13" s="7">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>34323</v>
       </c>
-      <c r="AM13" s="7"/>
+      <c r="AM13" s="7">
+        <f t="shared" ref="AM13" si="68">AM9-AM10-AM11-AM12</f>
+        <v>37961</v>
+      </c>
       <c r="AN13" s="7"/>
       <c r="AO13" s="7"/>
       <c r="AP13" s="7"/>
@@ -3932,64 +3959,64 @@
         <v>52959</v>
       </c>
       <c r="AW13" s="7">
-        <f t="shared" ref="AW13:BF13" si="65">AW9-AW10-AW11-AW12</f>
+        <f t="shared" ref="AW13:BF13" si="69">AW9-AW10-AW11-AW12</f>
         <v>69916</v>
       </c>
       <c r="AX13" s="7">
-        <f t="shared" ref="AX13:AY13" si="66">AX9-AX10-AX11-AX12</f>
+        <f t="shared" ref="AX13:AY13" si="70">AX9-AX10-AX11-AX12</f>
         <v>82214</v>
       </c>
       <c r="AY13" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>88523</v>
       </c>
       <c r="AZ13" s="7">
-        <f t="shared" ref="AZ13" si="67">AZ9-AZ10-AZ11-AZ12</f>
+        <f t="shared" ref="AZ13" si="71">AZ9-AZ10-AZ11-AZ12</f>
         <v>108747</v>
       </c>
       <c r="BA13" s="7">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>128528</v>
       </c>
       <c r="BB13" s="7">
-        <f t="shared" si="65"/>
-        <v>149340.2432</v>
+        <f t="shared" si="69"/>
+        <v>153717.58100000003</v>
       </c>
       <c r="BC13" s="7">
-        <f t="shared" si="65"/>
-        <v>161057.18836199999</v>
+        <f t="shared" si="69"/>
+        <v>167506.46605399996</v>
       </c>
       <c r="BD13" s="7">
-        <f t="shared" si="65"/>
-        <v>170946.04724362004</v>
+        <f t="shared" si="69"/>
+        <v>177782.28159714004</v>
       </c>
       <c r="BE13" s="7">
-        <f t="shared" si="65"/>
-        <v>179985.82768154421</v>
+        <f t="shared" si="69"/>
+        <v>187163.87375274018</v>
       </c>
       <c r="BF13" s="7">
-        <f t="shared" si="65"/>
-        <v>187476.12796741605</v>
+        <f t="shared" si="69"/>
+        <v>194941.29588145987</v>
       </c>
       <c r="BG13" s="7">
-        <f t="shared" ref="BG13:BI13" si="68">BG9-BG10-BG11-BG12</f>
-        <v>193263.00516744924</v>
+        <f t="shared" ref="BG13:BI13" si="72">BG9-BG10-BG11-BG12</f>
+        <v>200952.12811891444</v>
       </c>
       <c r="BH13" s="7">
-        <f t="shared" si="68"/>
-        <v>199227.94702598604</v>
+        <f t="shared" si="72"/>
+        <v>207147.74366599513</v>
       </c>
       <c r="BI13" s="7">
-        <f t="shared" si="68"/>
-        <v>203150.96969472588</v>
+        <f t="shared" si="72"/>
+        <v>211229.16226753517</v>
       </c>
       <c r="BJ13" s="7">
-        <f t="shared" ref="BJ13:BK13" si="69">BJ9-BJ10-BJ11-BJ12</f>
-        <v>207151.83745412261</v>
+        <f t="shared" ref="BJ13:BK13" si="73">BJ9-BJ10-BJ11-BJ12</f>
+        <v>215391.59387838817</v>
       </c>
       <c r="BK13" s="7">
-        <f t="shared" si="69"/>
-        <v>211232.10105236233</v>
+        <f t="shared" si="73"/>
+        <v>219636.6526051132</v>
       </c>
     </row>
     <row r="14" spans="2:63" x14ac:dyDescent="0.3">
@@ -4105,7 +4132,9 @@
       <c r="AL14" s="5">
         <v>1707</v>
       </c>
-      <c r="AM14" s="5"/>
+      <c r="AM14" s="5">
+        <v>3660</v>
+      </c>
       <c r="AN14" s="5"/>
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
@@ -4147,43 +4176,43 @@
         <v>4901</v>
       </c>
       <c r="BB14" s="5">
-        <f t="shared" ref="BB14:BI14" si="70">BA14*1.01</f>
+        <f t="shared" ref="BB14:BI14" si="74">BA14*1.01</f>
         <v>4950.01</v>
       </c>
       <c r="BC14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>4999.5101000000004</v>
       </c>
       <c r="BD14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>5049.5052010000009</v>
       </c>
       <c r="BE14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>5100.000253010001</v>
       </c>
       <c r="BF14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>5151.0002555401006</v>
       </c>
       <c r="BG14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>5202.5102580955017</v>
       </c>
       <c r="BH14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>5254.5353606764565</v>
       </c>
       <c r="BI14" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>5307.0807142832209</v>
       </c>
       <c r="BJ14" s="5">
-        <f t="shared" ref="BJ14" si="71">BI14*1.01</f>
+        <f t="shared" ref="BJ14" si="75">BI14*1.01</f>
         <v>5360.1515214260535</v>
       </c>
       <c r="BK14" s="5">
-        <f t="shared" ref="BK14" si="72">BJ14*1.01</f>
+        <f t="shared" ref="BK14" si="76">BJ14*1.01</f>
         <v>5413.7530366403143</v>
       </c>
     </row>
@@ -4192,150 +4221,153 @@
         <v>38</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:R15" si="73">C13-C14</f>
+        <f t="shared" ref="C15:R15" si="77">C13-C14</f>
         <v>6557</v>
       </c>
       <c r="D15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>8022</v>
       </c>
       <c r="E15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>7094</v>
       </c>
       <c r="F15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>7958</v>
       </c>
       <c r="G15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>7984</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>9169</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>8641</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>10680</v>
       </c>
       <c r="K15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>10221</v>
       </c>
       <c r="L15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>10385</v>
       </c>
       <c r="M15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>10486</v>
       </c>
       <c r="N15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>12596</v>
       </c>
       <c r="O15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>12686</v>
       </c>
       <c r="P15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>14085</v>
       </c>
       <c r="Q15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>12843</v>
       </c>
       <c r="R15" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>13422</v>
       </c>
       <c r="S15" s="7">
-        <f t="shared" ref="S15:V15" si="74">S13-S14</f>
+        <f t="shared" ref="S15:V15" si="78">S13-S14</f>
         <v>16124</v>
       </c>
       <c r="T15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>18337</v>
       </c>
       <c r="U15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>17236</v>
       </c>
       <c r="V15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>19405</v>
       </c>
       <c r="W15" s="7">
-        <f t="shared" ref="W15:X15" si="75">W13-W14</f>
+        <f t="shared" ref="W15:X15" si="79">W13-W14</f>
         <v>20524</v>
       </c>
       <c r="X15" s="7">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>21346</v>
       </c>
       <c r="Y15" s="7">
-        <f t="shared" ref="Y15" si="76">Y13-Y14</f>
+        <f t="shared" ref="Y15" si="80">Y13-Y14</f>
         <v>20190</v>
       </c>
       <c r="Z15" s="7">
-        <f t="shared" ref="Z15" si="77">Z13-Z14</f>
+        <f t="shared" ref="Z15" si="81">Z13-Z14</f>
         <v>20487</v>
       </c>
       <c r="AA15" s="7">
-        <f t="shared" ref="AA15" si="78">AA13-AA14</f>
+        <f t="shared" ref="AA15" si="82">AA13-AA14</f>
         <v>21572</v>
       </c>
       <c r="AB15" s="7">
-        <f t="shared" ref="AB15:AC15" si="79">AB13-AB14</f>
+        <f t="shared" ref="AB15:AC15" si="83">AB13-AB14</f>
         <v>20339</v>
       </c>
       <c r="AC15" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>22673</v>
       </c>
       <c r="AD15" s="7">
-        <f t="shared" ref="AD15:AE15" si="80">AD13-AD14</f>
+        <f t="shared" ref="AD15:AE15" si="84">AD13-AD14</f>
         <v>24727</v>
       </c>
       <c r="AE15" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>27284</v>
       </c>
       <c r="AF15" s="7">
-        <f t="shared" ref="AF15:AG15" si="81">AF13-AF14</f>
+        <f t="shared" ref="AF15:AG15" si="85">AF13-AF14</f>
         <v>27284</v>
       </c>
       <c r="AG15" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>26526</v>
       </c>
       <c r="AH15" s="7">
-        <f t="shared" ref="AH15:AL15" si="82">AH13-AH14</f>
+        <f t="shared" ref="AH15:AL15" si="86">AH13-AH14</f>
         <v>27250</v>
       </c>
       <c r="AI15" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>30269</v>
       </c>
       <c r="AJ15" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>29365</v>
       </c>
       <c r="AK15" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>31377</v>
       </c>
       <c r="AL15" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>32616</v>
       </c>
-      <c r="AM15" s="7"/>
+      <c r="AM15" s="7">
+        <f t="shared" ref="AM15" si="87">AM13-AM14</f>
+        <v>34301</v>
+      </c>
       <c r="AN15" s="7"/>
       <c r="AO15" s="7"/>
       <c r="AP15" s="7"/>
@@ -4357,64 +4389,64 @@
         <v>53036</v>
       </c>
       <c r="AW15" s="7">
-        <f t="shared" ref="AW15:BF15" si="83">AW13-AW14</f>
+        <f t="shared" ref="AW15:BF15" si="88">AW13-AW14</f>
         <v>71102</v>
       </c>
       <c r="AX15" s="7">
-        <f t="shared" ref="AX15:AY15" si="84">AX13-AX14</f>
+        <f t="shared" ref="AX15:AY15" si="89">AX13-AX14</f>
         <v>82547</v>
       </c>
       <c r="AY15" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="89"/>
         <v>89311</v>
       </c>
       <c r="AZ15" s="7">
-        <f t="shared" ref="AZ15" si="85">AZ13-AZ14</f>
+        <f t="shared" ref="AZ15" si="90">AZ13-AZ14</f>
         <v>108344</v>
       </c>
       <c r="BA15" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>123627</v>
       </c>
       <c r="BB15" s="7">
-        <f t="shared" si="83"/>
-        <v>144390.23319999999</v>
+        <f t="shared" si="88"/>
+        <v>148767.57100000003</v>
       </c>
       <c r="BC15" s="7">
-        <f t="shared" si="83"/>
-        <v>156057.67826199997</v>
+        <f t="shared" si="88"/>
+        <v>162506.95595399995</v>
       </c>
       <c r="BD15" s="7">
-        <f t="shared" si="83"/>
-        <v>165896.54204262004</v>
+        <f t="shared" si="88"/>
+        <v>172732.77639614005</v>
       </c>
       <c r="BE15" s="7">
-        <f t="shared" si="83"/>
-        <v>174885.82742853422</v>
+        <f t="shared" si="88"/>
+        <v>182063.87349973019</v>
       </c>
       <c r="BF15" s="7">
-        <f t="shared" si="83"/>
-        <v>182325.12771187595</v>
+        <f t="shared" si="88"/>
+        <v>189790.29562591977</v>
       </c>
       <c r="BG15" s="7">
-        <f t="shared" ref="BG15:BI15" si="86">BG13-BG14</f>
-        <v>188060.49490935373</v>
+        <f t="shared" ref="BG15:BI15" si="91">BG13-BG14</f>
+        <v>195749.61786081892</v>
       </c>
       <c r="BH15" s="7">
-        <f t="shared" si="86"/>
-        <v>193973.41166530957</v>
+        <f t="shared" si="91"/>
+        <v>201893.20830531867</v>
       </c>
       <c r="BI15" s="7">
-        <f t="shared" si="86"/>
-        <v>197843.88898044266</v>
+        <f t="shared" si="91"/>
+        <v>205922.08155325195</v>
       </c>
       <c r="BJ15" s="7">
-        <f t="shared" ref="BJ15:BK15" si="87">BJ13-BJ14</f>
-        <v>201791.68593269656</v>
+        <f t="shared" ref="BJ15:BK15" si="92">BJ13-BJ14</f>
+        <v>210031.44235696213</v>
       </c>
       <c r="BK15" s="7">
-        <f t="shared" si="87"/>
-        <v>205818.348015722</v>
+        <f t="shared" si="92"/>
+        <v>214222.89956847287</v>
       </c>
     </row>
     <row r="16" spans="2:63" x14ac:dyDescent="0.3">
@@ -4530,7 +4562,9 @@
       <c r="AL16" s="5">
         <v>5383</v>
       </c>
-      <c r="AM16" s="5"/>
+      <c r="AM16" s="5">
+        <v>6554</v>
+      </c>
       <c r="AN16" s="5"/>
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
@@ -4572,44 +4606,44 @@
         <v>21795</v>
       </c>
       <c r="BB16" s="5">
-        <f t="shared" ref="BB16:BI16" si="88">BB15*0.19</f>
-        <v>27434.144307999999</v>
+        <f t="shared" ref="BB16:BI16" si="93">BB15*0.19</f>
+        <v>28265.838490000006</v>
       </c>
       <c r="BC16" s="5">
-        <f t="shared" si="88"/>
-        <v>29650.958869779995</v>
+        <f t="shared" si="93"/>
+        <v>30876.321631259991</v>
       </c>
       <c r="BD16" s="5">
-        <f t="shared" si="88"/>
-        <v>31520.342988097807</v>
+        <f t="shared" si="93"/>
+        <v>32819.227515266612</v>
       </c>
       <c r="BE16" s="5">
-        <f t="shared" si="88"/>
-        <v>33228.307211421503</v>
+        <f t="shared" si="93"/>
+        <v>34592.135964948735</v>
       </c>
       <c r="BF16" s="5">
-        <f t="shared" si="88"/>
-        <v>34641.774265256427</v>
+        <f t="shared" si="93"/>
+        <v>36060.156168924754</v>
       </c>
       <c r="BG16" s="5">
-        <f t="shared" si="88"/>
-        <v>35731.494032777206</v>
+        <f t="shared" si="93"/>
+        <v>37192.427393555598</v>
       </c>
       <c r="BH16" s="5">
-        <f t="shared" si="88"/>
-        <v>36854.948216408819</v>
+        <f t="shared" si="93"/>
+        <v>38359.709578010545</v>
       </c>
       <c r="BI16" s="5">
-        <f t="shared" si="88"/>
-        <v>37590.338906284109</v>
+        <f t="shared" si="93"/>
+        <v>39125.19549511787</v>
       </c>
       <c r="BJ16" s="5">
-        <f t="shared" ref="BJ16:BK16" si="89">BJ15*0.19</f>
-        <v>38340.420327212349</v>
+        <f t="shared" ref="BJ16:BK16" si="94">BJ15*0.19</f>
+        <v>39905.974047822805</v>
       </c>
       <c r="BK16" s="5">
-        <f t="shared" si="89"/>
-        <v>39105.486122987182</v>
+        <f t="shared" si="94"/>
+        <v>40702.350918009848</v>
       </c>
     </row>
     <row r="17" spans="2:184" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4617,150 +4651,153 @@
         <v>40</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:R17" si="90">C15-C16</f>
+        <f t="shared" ref="C17:R17" si="95">C15-C16</f>
         <v>5397</v>
       </c>
       <c r="D17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>6267</v>
       </c>
       <c r="E17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>5486</v>
       </c>
       <c r="F17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>8069</v>
       </c>
       <c r="G17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>6576</v>
       </c>
       <c r="H17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>-6302</v>
       </c>
       <c r="I17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>7424</v>
       </c>
       <c r="J17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>8873</v>
       </c>
       <c r="K17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>8824</v>
       </c>
       <c r="L17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>8420</v>
       </c>
       <c r="M17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>8809</v>
       </c>
       <c r="N17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>13187</v>
       </c>
       <c r="O17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>10678</v>
       </c>
       <c r="P17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>11649</v>
       </c>
       <c r="Q17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>10752</v>
       </c>
       <c r="R17" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>11202</v>
       </c>
       <c r="S17" s="7">
-        <f t="shared" ref="S17:V17" si="91">S15-S16</f>
+        <f t="shared" ref="S17:V17" si="96">S15-S16</f>
         <v>13893</v>
       </c>
       <c r="T17" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="96"/>
         <v>15463</v>
       </c>
       <c r="U17" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="96"/>
         <v>15457</v>
       </c>
       <c r="V17" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="96"/>
         <v>16458</v>
       </c>
       <c r="W17" s="7">
-        <f t="shared" ref="W17:X17" si="92">W15-W16</f>
+        <f t="shared" ref="W17:X17" si="97">W15-W16</f>
         <v>20505</v>
       </c>
       <c r="X17" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="97"/>
         <v>17596</v>
       </c>
       <c r="Y17" s="7">
-        <f t="shared" ref="Y17" si="93">Y15-Y16</f>
+        <f t="shared" ref="Y17" si="98">Y15-Y16</f>
         <v>16728</v>
       </c>
       <c r="Z17" s="7">
-        <f t="shared" ref="Z17" si="94">Z15-Z16</f>
+        <f t="shared" ref="Z17" si="99">Z15-Z16</f>
         <v>16740</v>
       </c>
       <c r="AA17" s="7">
-        <f t="shared" ref="AA17" si="95">AA15-AA16</f>
+        <f t="shared" ref="AA17" si="100">AA15-AA16</f>
         <v>17556</v>
       </c>
       <c r="AB17" s="7">
-        <f t="shared" ref="AB17:AC17" si="96">AB15-AB16</f>
+        <f t="shared" ref="AB17:AC17" si="101">AB15-AB16</f>
         <v>16425</v>
       </c>
       <c r="AC17" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>18299</v>
       </c>
       <c r="AD17" s="7">
-        <f t="shared" ref="AD17:AE17" si="97">AD15-AD16</f>
+        <f t="shared" ref="AD17:AE17" si="102">AD15-AD16</f>
         <v>20081</v>
       </c>
       <c r="AE17" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>22291</v>
       </c>
       <c r="AF17" s="7">
-        <f t="shared" ref="AF17:AG17" si="98">AF15-AF16</f>
+        <f t="shared" ref="AF17:AG17" si="103">AF15-AF16</f>
         <v>22291</v>
       </c>
       <c r="AG17" s="7">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>21870</v>
       </c>
       <c r="AH17" s="7">
-        <f t="shared" ref="AH17:AI17" si="99">AH15-AH16</f>
+        <f t="shared" ref="AH17:AI17" si="104">AH15-AH16</f>
         <v>22036</v>
       </c>
       <c r="AI17" s="7">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>24667</v>
       </c>
       <c r="AJ17" s="7">
-        <f t="shared" ref="AJ17:AL17" si="100">AJ15-AJ16</f>
+        <f t="shared" ref="AJ17:AL17" si="105">AJ15-AJ16</f>
         <v>24108</v>
       </c>
       <c r="AK17" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="105"/>
         <v>25824</v>
       </c>
       <c r="AL17" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="105"/>
         <v>27233</v>
       </c>
-      <c r="AM17" s="7"/>
+      <c r="AM17" s="7">
+        <f t="shared" ref="AM17" si="106">AM15-AM16</f>
+        <v>27747</v>
+      </c>
       <c r="AN17" s="7"/>
       <c r="AO17" s="7"/>
       <c r="AP17" s="7"/>
@@ -4782,548 +4819,548 @@
         <v>44281</v>
       </c>
       <c r="AW17" s="7">
-        <f t="shared" ref="AW17:BF17" si="101">AW15-AW16</f>
+        <f t="shared" ref="AW17:BF17" si="107">AW15-AW16</f>
         <v>61271</v>
       </c>
       <c r="AX17" s="7">
-        <f t="shared" ref="AX17:AY17" si="102">AX15-AX16</f>
+        <f t="shared" ref="AX17:AY17" si="108">AX15-AX16</f>
         <v>71569</v>
       </c>
       <c r="AY17" s="7">
-        <f t="shared" si="102"/>
+        <f t="shared" si="108"/>
         <v>72361</v>
       </c>
       <c r="AZ17" s="7">
-        <f t="shared" ref="AZ17" si="103">AZ15-AZ16</f>
+        <f t="shared" ref="AZ17" si="109">AZ15-AZ16</f>
         <v>88488</v>
       </c>
       <c r="BA17" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="107"/>
         <v>101832</v>
       </c>
       <c r="BB17" s="7">
-        <f t="shared" si="101"/>
-        <v>116956.08889199999</v>
+        <f t="shared" si="107"/>
+        <v>120501.73251000002</v>
       </c>
       <c r="BC17" s="7">
-        <f t="shared" si="101"/>
-        <v>126406.71939221998</v>
+        <f t="shared" si="107"/>
+        <v>131630.63432273996</v>
       </c>
       <c r="BD17" s="7">
-        <f t="shared" si="101"/>
-        <v>134376.19905452224</v>
+        <f t="shared" si="107"/>
+        <v>139913.54888087342</v>
       </c>
       <c r="BE17" s="7">
-        <f t="shared" si="101"/>
-        <v>141657.52021711273</v>
+        <f t="shared" si="107"/>
+        <v>147471.73753478145</v>
       </c>
       <c r="BF17" s="7">
-        <f t="shared" si="101"/>
-        <v>147683.35344661953</v>
+        <f t="shared" si="107"/>
+        <v>153730.13945699501</v>
       </c>
       <c r="BG17" s="7">
-        <f t="shared" ref="BG17:BI17" si="104">BG15-BG16</f>
-        <v>152329.00087657652</v>
+        <f t="shared" ref="BG17:BI17" si="110">BG15-BG16</f>
+        <v>158557.19046726334</v>
       </c>
       <c r="BH17" s="7">
-        <f t="shared" si="104"/>
-        <v>157118.46344890076</v>
+        <f t="shared" si="110"/>
+        <v>163533.49872730812</v>
       </c>
       <c r="BI17" s="7">
-        <f t="shared" si="104"/>
-        <v>160253.55007415856</v>
+        <f t="shared" si="110"/>
+        <v>166796.88605813409</v>
       </c>
       <c r="BJ17" s="7">
-        <f t="shared" ref="BJ17:BK17" si="105">BJ15-BJ16</f>
-        <v>163451.26560548422</v>
+        <f t="shared" ref="BJ17:BK17" si="111">BJ15-BJ16</f>
+        <v>170125.46830913931</v>
       </c>
       <c r="BK17" s="7">
-        <f t="shared" si="105"/>
-        <v>166712.86189273483</v>
+        <f t="shared" si="111"/>
+        <v>173520.54865046302</v>
       </c>
       <c r="BL17" s="6">
         <f>BK17*(1+$BN$21)</f>
-        <v>165045.73327380748</v>
+        <v>171785.3431639584</v>
       </c>
       <c r="BM17" s="6">
-        <f t="shared" ref="BM17:DX17" si="106">BL17*(1+$BN$21)</f>
-        <v>163395.27594106941</v>
+        <f t="shared" ref="BM17:DX17" si="112">BL17*(1+$BN$21)</f>
+        <v>170067.48973231882</v>
       </c>
       <c r="BN17" s="6">
-        <f t="shared" si="106"/>
-        <v>161761.32318165872</v>
+        <f t="shared" si="112"/>
+        <v>168366.81483499563</v>
       </c>
       <c r="BO17" s="6">
-        <f t="shared" si="106"/>
-        <v>160143.70994984213</v>
+        <f t="shared" si="112"/>
+        <v>166683.14668664566</v>
       </c>
       <c r="BP17" s="6">
-        <f t="shared" si="106"/>
-        <v>158542.2728503437</v>
+        <f t="shared" si="112"/>
+        <v>165016.31521977921</v>
       </c>
       <c r="BQ17" s="6">
-        <f t="shared" si="106"/>
-        <v>156956.85012184025</v>
+        <f t="shared" si="112"/>
+        <v>163366.15206758142</v>
       </c>
       <c r="BR17" s="6">
-        <f t="shared" si="106"/>
-        <v>155387.28162062186</v>
+        <f t="shared" si="112"/>
+        <v>161732.49054690561</v>
       </c>
       <c r="BS17" s="6">
-        <f t="shared" si="106"/>
-        <v>153833.40880441564</v>
+        <f t="shared" si="112"/>
+        <v>160115.16564143656</v>
       </c>
       <c r="BT17" s="6">
-        <f t="shared" si="106"/>
-        <v>152295.07471637148</v>
+        <f t="shared" si="112"/>
+        <v>158514.0139850222</v>
       </c>
       <c r="BU17" s="6">
-        <f t="shared" si="106"/>
-        <v>150772.12396920778</v>
+        <f t="shared" si="112"/>
+        <v>156928.87384517197</v>
       </c>
       <c r="BV17" s="6">
-        <f t="shared" si="106"/>
-        <v>149264.40272951571</v>
+        <f t="shared" si="112"/>
+        <v>155359.58510672025</v>
       </c>
       <c r="BW17" s="6">
-        <f t="shared" si="106"/>
-        <v>147771.75870222057</v>
+        <f t="shared" si="112"/>
+        <v>153805.98925565305</v>
       </c>
       <c r="BX17" s="6">
-        <f t="shared" si="106"/>
-        <v>146294.04111519837</v>
+        <f t="shared" si="112"/>
+        <v>152267.92936309651</v>
       </c>
       <c r="BY17" s="6">
-        <f t="shared" si="106"/>
-        <v>144831.10070404637</v>
+        <f t="shared" si="112"/>
+        <v>150745.25006946555</v>
       </c>
       <c r="BZ17" s="6">
-        <f t="shared" si="106"/>
-        <v>143382.78969700591</v>
+        <f t="shared" si="112"/>
+        <v>149237.79756877088</v>
       </c>
       <c r="CA17" s="6">
-        <f t="shared" si="106"/>
-        <v>141948.96180003585</v>
+        <f t="shared" si="112"/>
+        <v>147745.41959308318</v>
       </c>
       <c r="CB17" s="6">
-        <f t="shared" si="106"/>
-        <v>140529.47218203548</v>
+        <f t="shared" si="112"/>
+        <v>146267.96539715235</v>
       </c>
       <c r="CC17" s="6">
-        <f t="shared" si="106"/>
-        <v>139124.17746021511</v>
+        <f t="shared" si="112"/>
+        <v>144805.28574318084</v>
       </c>
       <c r="CD17" s="6">
-        <f t="shared" si="106"/>
-        <v>137732.93568561296</v>
+        <f t="shared" si="112"/>
+        <v>143357.23288574902</v>
       </c>
       <c r="CE17" s="6">
-        <f t="shared" si="106"/>
-        <v>136355.60632875684</v>
+        <f t="shared" si="112"/>
+        <v>141923.66055689153</v>
       </c>
       <c r="CF17" s="6">
-        <f t="shared" si="106"/>
-        <v>134992.05026546927</v>
+        <f t="shared" si="112"/>
+        <v>140504.42395132262</v>
       </c>
       <c r="CG17" s="6">
-        <f t="shared" si="106"/>
-        <v>133642.12976281458</v>
+        <f t="shared" si="112"/>
+        <v>139099.37971180939</v>
       </c>
       <c r="CH17" s="6">
-        <f t="shared" si="106"/>
-        <v>132305.70846518644</v>
+        <f t="shared" si="112"/>
+        <v>137708.38591469129</v>
       </c>
       <c r="CI17" s="6">
-        <f t="shared" si="106"/>
-        <v>130982.65138053457</v>
+        <f t="shared" si="112"/>
+        <v>136331.30205554437</v>
       </c>
       <c r="CJ17" s="6">
-        <f t="shared" si="106"/>
-        <v>129672.82486672922</v>
+        <f t="shared" si="112"/>
+        <v>134967.98903498892</v>
       </c>
       <c r="CK17" s="6">
-        <f t="shared" si="106"/>
-        <v>128376.09661806193</v>
+        <f t="shared" si="112"/>
+        <v>133618.30914463903</v>
       </c>
       <c r="CL17" s="6">
-        <f t="shared" si="106"/>
-        <v>127092.33565188131</v>
+        <f t="shared" si="112"/>
+        <v>132282.12605319265</v>
       </c>
       <c r="CM17" s="6">
-        <f t="shared" si="106"/>
-        <v>125821.41229536249</v>
+        <f t="shared" si="112"/>
+        <v>130959.30479266073</v>
       </c>
       <c r="CN17" s="6">
-        <f t="shared" si="106"/>
-        <v>124563.19817240887</v>
+        <f t="shared" si="112"/>
+        <v>129649.71174473412</v>
       </c>
       <c r="CO17" s="6">
-        <f t="shared" si="106"/>
-        <v>123317.56619068478</v>
+        <f t="shared" si="112"/>
+        <v>128353.21462728677</v>
       </c>
       <c r="CP17" s="6">
-        <f t="shared" si="106"/>
-        <v>122084.39052877793</v>
+        <f t="shared" si="112"/>
+        <v>127069.68248101389</v>
       </c>
       <c r="CQ17" s="6">
-        <f t="shared" si="106"/>
-        <v>120863.54662349015</v>
+        <f t="shared" si="112"/>
+        <v>125798.98565620376</v>
       </c>
       <c r="CR17" s="6">
-        <f t="shared" si="106"/>
-        <v>119654.91115725525</v>
+        <f t="shared" si="112"/>
+        <v>124540.99579964172</v>
       </c>
       <c r="CS17" s="6">
-        <f t="shared" si="106"/>
-        <v>118458.36204568269</v>
+        <f t="shared" si="112"/>
+        <v>123295.5858416453</v>
       </c>
       <c r="CT17" s="6">
-        <f t="shared" si="106"/>
-        <v>117273.77842522586</v>
+        <f t="shared" si="112"/>
+        <v>122062.62998322885</v>
       </c>
       <c r="CU17" s="6">
-        <f t="shared" si="106"/>
-        <v>116101.0406409736</v>
+        <f t="shared" si="112"/>
+        <v>120842.00368339656</v>
       </c>
       <c r="CV17" s="6">
-        <f t="shared" si="106"/>
-        <v>114940.03023456386</v>
+        <f t="shared" si="112"/>
+        <v>119633.58364656259</v>
       </c>
       <c r="CW17" s="6">
-        <f t="shared" si="106"/>
-        <v>113790.62993221822</v>
+        <f t="shared" si="112"/>
+        <v>118437.24781009696</v>
       </c>
       <c r="CX17" s="6">
-        <f t="shared" si="106"/>
-        <v>112652.72363289603</v>
+        <f t="shared" si="112"/>
+        <v>117252.87533199599</v>
       </c>
       <c r="CY17" s="6">
-        <f t="shared" si="106"/>
-        <v>111526.19639656707</v>
+        <f t="shared" si="112"/>
+        <v>116080.34657867604</v>
       </c>
       <c r="CZ17" s="6">
-        <f t="shared" si="106"/>
-        <v>110410.9344326014</v>
+        <f t="shared" si="112"/>
+        <v>114919.54311288927</v>
       </c>
       <c r="DA17" s="6">
-        <f t="shared" si="106"/>
-        <v>109306.82508827538</v>
+        <f t="shared" si="112"/>
+        <v>113770.34768176038</v>
       </c>
       <c r="DB17" s="6">
-        <f t="shared" si="106"/>
-        <v>108213.75683739262</v>
+        <f t="shared" si="112"/>
+        <v>112632.64420494277</v>
       </c>
       <c r="DC17" s="6">
-        <f t="shared" si="106"/>
-        <v>107131.61926901869</v>
+        <f t="shared" si="112"/>
+        <v>111506.31776289335</v>
       </c>
       <c r="DD17" s="6">
-        <f t="shared" si="106"/>
-        <v>106060.30307632851</v>
+        <f t="shared" si="112"/>
+        <v>110391.25458526441</v>
       </c>
       <c r="DE17" s="6">
-        <f t="shared" si="106"/>
-        <v>104999.70004556522</v>
+        <f t="shared" si="112"/>
+        <v>109287.34203941177</v>
       </c>
       <c r="DF17" s="6">
-        <f t="shared" si="106"/>
-        <v>103949.70304510956</v>
+        <f t="shared" si="112"/>
+        <v>108194.46861901766</v>
       </c>
       <c r="DG17" s="6">
-        <f t="shared" si="106"/>
-        <v>102910.20601465847</v>
+        <f t="shared" si="112"/>
+        <v>107112.52393282748</v>
       </c>
       <c r="DH17" s="6">
-        <f t="shared" si="106"/>
-        <v>101881.10395451188</v>
+        <f t="shared" si="112"/>
+        <v>106041.3986934992</v>
       </c>
       <c r="DI17" s="6">
-        <f t="shared" si="106"/>
-        <v>100862.29291496676</v>
+        <f t="shared" si="112"/>
+        <v>104980.98470656421</v>
       </c>
       <c r="DJ17" s="6">
-        <f t="shared" si="106"/>
-        <v>99853.66998581709</v>
+        <f t="shared" si="112"/>
+        <v>103931.17485949857</v>
       </c>
       <c r="DK17" s="6">
-        <f t="shared" si="106"/>
-        <v>98855.133285958917</v>
+        <f t="shared" si="112"/>
+        <v>102891.86311090358</v>
       </c>
       <c r="DL17" s="6">
-        <f t="shared" si="106"/>
-        <v>97866.581953099332</v>
+        <f t="shared" si="112"/>
+        <v>101862.94447979455</v>
       </c>
       <c r="DM17" s="6">
-        <f t="shared" si="106"/>
-        <v>96887.916133568331</v>
+        <f t="shared" si="112"/>
+        <v>100844.3150349966</v>
       </c>
       <c r="DN17" s="6">
-        <f t="shared" si="106"/>
-        <v>95919.036972232643</v>
+        <f t="shared" si="112"/>
+        <v>99835.871884646636</v>
       </c>
       <c r="DO17" s="6">
-        <f t="shared" si="106"/>
-        <v>94959.846602510312</v>
+        <f t="shared" si="112"/>
+        <v>98837.513165800163</v>
       </c>
       <c r="DP17" s="6">
-        <f t="shared" si="106"/>
-        <v>94010.248136485214</v>
+        <f t="shared" si="112"/>
+        <v>97849.138034142161</v>
       </c>
       <c r="DQ17" s="6">
-        <f t="shared" si="106"/>
-        <v>93070.145655120359</v>
+        <f t="shared" si="112"/>
+        <v>96870.646653800737</v>
       </c>
       <c r="DR17" s="6">
-        <f t="shared" si="106"/>
-        <v>92139.444198569152</v>
+        <f t="shared" si="112"/>
+        <v>95901.940187262735</v>
       </c>
       <c r="DS17" s="6">
-        <f t="shared" si="106"/>
-        <v>91218.049756583467</v>
+        <f t="shared" si="112"/>
+        <v>94942.920785390103</v>
       </c>
       <c r="DT17" s="6">
-        <f t="shared" si="106"/>
-        <v>90305.869259017636</v>
+        <f t="shared" si="112"/>
+        <v>93993.491577536202</v>
       </c>
       <c r="DU17" s="6">
-        <f t="shared" si="106"/>
-        <v>89402.810566427463</v>
+        <f t="shared" si="112"/>
+        <v>93053.556661760842</v>
       </c>
       <c r="DV17" s="6">
-        <f t="shared" si="106"/>
-        <v>88508.782460763192</v>
+        <f t="shared" si="112"/>
+        <v>92123.021095143238</v>
       </c>
       <c r="DW17" s="6">
-        <f t="shared" si="106"/>
-        <v>87623.69463615556</v>
+        <f t="shared" si="112"/>
+        <v>91201.790884191811</v>
       </c>
       <c r="DX17" s="6">
-        <f t="shared" si="106"/>
-        <v>86747.457689793999</v>
+        <f t="shared" si="112"/>
+        <v>90289.772975349886</v>
       </c>
       <c r="DY17" s="6">
-        <f t="shared" ref="DY17:GB17" si="107">DX17*(1+$BN$21)</f>
-        <v>85879.983112896065</v>
+        <f t="shared" ref="DY17:GB17" si="113">DX17*(1+$BN$21)</f>
+        <v>89386.875245596384</v>
       </c>
       <c r="DZ17" s="6">
-        <f t="shared" si="107"/>
-        <v>85021.183281767109</v>
+        <f t="shared" si="113"/>
+        <v>88493.006493140419</v>
       </c>
       <c r="EA17" s="6">
-        <f t="shared" si="107"/>
-        <v>84170.971448949436</v>
+        <f t="shared" si="113"/>
+        <v>87608.076428209009</v>
       </c>
       <c r="EB17" s="6">
-        <f t="shared" si="107"/>
-        <v>83329.261734459942</v>
+        <f t="shared" si="113"/>
+        <v>86731.995663926922</v>
       </c>
       <c r="EC17" s="6">
-        <f t="shared" si="107"/>
-        <v>82495.969117115339</v>
+        <f t="shared" si="113"/>
+        <v>85864.67570728765</v>
       </c>
       <c r="ED17" s="6">
-        <f t="shared" si="107"/>
-        <v>81671.009425944183</v>
+        <f t="shared" si="113"/>
+        <v>85006.028950214779</v>
       </c>
       <c r="EE17" s="6">
-        <f t="shared" si="107"/>
-        <v>80854.299331684742</v>
+        <f t="shared" si="113"/>
+        <v>84155.968660712635</v>
       </c>
       <c r="EF17" s="6">
-        <f t="shared" si="107"/>
-        <v>80045.756338367893</v>
+        <f t="shared" si="113"/>
+        <v>83314.408974105507</v>
       </c>
       <c r="EG17" s="6">
-        <f t="shared" si="107"/>
-        <v>79245.298774984214</v>
+        <f t="shared" si="113"/>
+        <v>82481.264884364457</v>
       </c>
       <c r="EH17" s="6">
-        <f t="shared" si="107"/>
-        <v>78452.845787234372</v>
+        <f t="shared" si="113"/>
+        <v>81656.452235520817</v>
       </c>
       <c r="EI17" s="6">
-        <f t="shared" si="107"/>
-        <v>77668.31732936202</v>
+        <f t="shared" si="113"/>
+        <v>80839.887713165605</v>
       </c>
       <c r="EJ17" s="6">
-        <f t="shared" si="107"/>
-        <v>76891.634156068394</v>
+        <f t="shared" si="113"/>
+        <v>80031.488836033954</v>
       </c>
       <c r="EK17" s="6">
-        <f t="shared" si="107"/>
-        <v>76122.717814507705</v>
+        <f t="shared" si="113"/>
+        <v>79231.173947673611</v>
       </c>
       <c r="EL17" s="6">
-        <f t="shared" si="107"/>
-        <v>75361.490636362621</v>
+        <f t="shared" si="113"/>
+        <v>78438.862208196879</v>
       </c>
       <c r="EM17" s="6">
-        <f t="shared" si="107"/>
-        <v>74607.875729998996</v>
+        <f t="shared" si="113"/>
+        <v>77654.473586114909</v>
       </c>
       <c r="EN17" s="6">
-        <f t="shared" si="107"/>
-        <v>73861.796972699012</v>
+        <f t="shared" si="113"/>
+        <v>76877.928850253753</v>
       </c>
       <c r="EO17" s="6">
-        <f t="shared" si="107"/>
-        <v>73123.179002972029</v>
+        <f t="shared" si="113"/>
+        <v>76109.149561751212</v>
       </c>
       <c r="EP17" s="6">
-        <f t="shared" si="107"/>
-        <v>72391.947212942308</v>
+        <f t="shared" si="113"/>
+        <v>75348.058066133701</v>
       </c>
       <c r="EQ17" s="6">
-        <f t="shared" si="107"/>
-        <v>71668.02774081289</v>
+        <f t="shared" si="113"/>
+        <v>74594.577485472357</v>
       </c>
       <c r="ER17" s="6">
-        <f t="shared" si="107"/>
-        <v>70951.34746340476</v>
+        <f t="shared" si="113"/>
+        <v>73848.631710617628</v>
       </c>
       <c r="ES17" s="6">
-        <f t="shared" si="107"/>
-        <v>70241.833988770712</v>
+        <f t="shared" si="113"/>
+        <v>73110.145393511455</v>
       </c>
       <c r="ET17" s="6">
-        <f t="shared" si="107"/>
-        <v>69539.415648883005</v>
+        <f t="shared" si="113"/>
+        <v>72379.043939576339</v>
       </c>
       <c r="EU17" s="6">
-        <f t="shared" si="107"/>
-        <v>68844.021492394168</v>
+        <f t="shared" si="113"/>
+        <v>71655.253500180581</v>
       </c>
       <c r="EV17" s="6">
-        <f t="shared" si="107"/>
-        <v>68155.581277470221</v>
+        <f t="shared" si="113"/>
+        <v>70938.700965178781</v>
       </c>
       <c r="EW17" s="6">
-        <f t="shared" si="107"/>
-        <v>67474.025464695515</v>
+        <f t="shared" si="113"/>
+        <v>70229.313955526988</v>
       </c>
       <c r="EX17" s="6">
-        <f t="shared" si="107"/>
-        <v>66799.285210048562</v>
+        <f t="shared" si="113"/>
+        <v>69527.020815971715</v>
       </c>
       <c r="EY17" s="6">
-        <f t="shared" si="107"/>
-        <v>66131.29235794807</v>
+        <f t="shared" si="113"/>
+        <v>68831.750607811991</v>
       </c>
       <c r="EZ17" s="6">
-        <f t="shared" si="107"/>
-        <v>65469.979434368586</v>
+        <f t="shared" si="113"/>
+        <v>68143.43310173387</v>
       </c>
       <c r="FA17" s="6">
-        <f t="shared" si="107"/>
-        <v>64815.279640024899</v>
+        <f t="shared" si="113"/>
+        <v>67461.998770716527</v>
       </c>
       <c r="FB17" s="6">
-        <f t="shared" si="107"/>
-        <v>64167.126843624646</v>
+        <f t="shared" si="113"/>
+        <v>66787.378783009364</v>
       </c>
       <c r="FC17" s="6">
-        <f t="shared" si="107"/>
-        <v>63525.455575188396</v>
+        <f t="shared" si="113"/>
+        <v>66119.504995179275</v>
       </c>
       <c r="FD17" s="6">
-        <f t="shared" si="107"/>
-        <v>62890.201019436514</v>
+        <f t="shared" si="113"/>
+        <v>65458.309945227484</v>
       </c>
       <c r="FE17" s="6">
-        <f t="shared" si="107"/>
-        <v>62261.299009242146</v>
+        <f t="shared" si="113"/>
+        <v>64803.726845775207</v>
       </c>
       <c r="FF17" s="6">
-        <f t="shared" si="107"/>
-        <v>61638.686019149725</v>
+        <f t="shared" si="113"/>
+        <v>64155.689577317455</v>
       </c>
       <c r="FG17" s="6">
-        <f t="shared" si="107"/>
-        <v>61022.299158958231</v>
+        <f t="shared" si="113"/>
+        <v>63514.132681544281</v>
       </c>
       <c r="FH17" s="6">
-        <f t="shared" si="107"/>
-        <v>60412.07616736865</v>
+        <f t="shared" si="113"/>
+        <v>62878.991354728838</v>
       </c>
       <c r="FI17" s="6">
-        <f t="shared" si="107"/>
-        <v>59807.955405694964</v>
+        <f t="shared" si="113"/>
+        <v>62250.201441181547</v>
       </c>
       <c r="FJ17" s="6">
-        <f t="shared" si="107"/>
-        <v>59209.875851638011</v>
+        <f t="shared" si="113"/>
+        <v>61627.69942676973</v>
       </c>
       <c r="FK17" s="6">
-        <f t="shared" si="107"/>
-        <v>58617.777093121629</v>
+        <f t="shared" si="113"/>
+        <v>61011.422432502033</v>
       </c>
       <c r="FL17" s="6">
-        <f t="shared" si="107"/>
-        <v>58031.599322190414</v>
+        <f t="shared" si="113"/>
+        <v>60401.308208177012</v>
       </c>
       <c r="FM17" s="6">
-        <f t="shared" si="107"/>
-        <v>57451.283328968508</v>
+        <f t="shared" si="113"/>
+        <v>59797.29512609524</v>
       </c>
       <c r="FN17" s="6">
-        <f t="shared" si="107"/>
-        <v>56876.770495678822</v>
+        <f t="shared" si="113"/>
+        <v>59199.322174834284</v>
       </c>
       <c r="FO17" s="6">
-        <f t="shared" si="107"/>
-        <v>56308.002790722036</v>
+        <f t="shared" si="113"/>
+        <v>58607.32895308594</v>
       </c>
       <c r="FP17" s="6">
-        <f t="shared" si="107"/>
-        <v>55744.922762814815</v>
+        <f t="shared" si="113"/>
+        <v>58021.255663555079</v>
       </c>
       <c r="FQ17" s="6">
-        <f t="shared" si="107"/>
-        <v>55187.473535186669</v>
+        <f t="shared" si="113"/>
+        <v>57441.043106919526</v>
       </c>
       <c r="FR17" s="6">
-        <f t="shared" si="107"/>
-        <v>54635.598799834799</v>
+        <f t="shared" si="113"/>
+        <v>56866.632675850327</v>
       </c>
       <c r="FS17" s="6">
-        <f t="shared" si="107"/>
-        <v>54089.242811836448</v>
+        <f t="shared" si="113"/>
+        <v>56297.966349091825</v>
       </c>
       <c r="FT17" s="6">
-        <f t="shared" si="107"/>
-        <v>53548.350383718083</v>
+        <f t="shared" si="113"/>
+        <v>55734.986685600903</v>
       </c>
       <c r="FU17" s="6">
-        <f t="shared" si="107"/>
-        <v>53012.866879880901</v>
+        <f t="shared" si="113"/>
+        <v>55177.636818744897</v>
       </c>
       <c r="FV17" s="6">
-        <f t="shared" si="107"/>
-        <v>52482.738211082091</v>
+        <f t="shared" si="113"/>
+        <v>54625.860450557448</v>
       </c>
       <c r="FW17" s="6">
-        <f t="shared" si="107"/>
-        <v>51957.910828971268</v>
+        <f t="shared" si="113"/>
+        <v>54079.601846051875</v>
       </c>
       <c r="FX17" s="6">
-        <f t="shared" si="107"/>
-        <v>51438.331720681555</v>
+        <f t="shared" si="113"/>
+        <v>53538.805827591357</v>
       </c>
       <c r="FY17" s="6">
-        <f t="shared" si="107"/>
-        <v>50923.948403474737</v>
+        <f t="shared" si="113"/>
+        <v>53003.417769315442</v>
       </c>
       <c r="FZ17" s="6">
-        <f t="shared" si="107"/>
-        <v>50414.708919439989</v>
+        <f t="shared" si="113"/>
+        <v>52473.383591622289</v>
       </c>
       <c r="GA17" s="6">
-        <f t="shared" si="107"/>
-        <v>49910.561830245591</v>
+        <f t="shared" si="113"/>
+        <v>51948.649755706065</v>
       </c>
       <c r="GB17" s="6">
-        <f t="shared" si="107"/>
-        <v>49411.456211943136</v>
+        <f t="shared" si="113"/>
+        <v>51429.163258149005</v>
       </c>
     </row>
     <row r="18" spans="2:184" x14ac:dyDescent="0.3">
@@ -5439,7 +5476,9 @@
       <c r="AL18" s="5">
         <v>7432</v>
       </c>
-      <c r="AM18" s="5"/>
+      <c r="AM18" s="5">
+        <v>7432</v>
+      </c>
       <c r="AN18" s="5"/>
       <c r="AO18" s="5"/>
       <c r="AP18" s="5"/>
@@ -5507,150 +5546,153 @@
         <v>41</v>
       </c>
       <c r="C19" s="8">
-        <f t="shared" ref="C19:R19" si="108">C17/C18</f>
+        <f t="shared" ref="C19:R19" si="114">C17/C18</f>
         <v>0.71322849213691031</v>
       </c>
       <c r="D19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>0.82820140081934712</v>
       </c>
       <c r="E19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>0.72499008854235492</v>
       </c>
       <c r="F19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>1.0663406898374521</v>
       </c>
       <c r="G19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>0.86903660631690238</v>
       </c>
       <c r="H19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>-0.83282674772036469</v>
       </c>
       <c r="I19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>0.98110215409012824</v>
       </c>
       <c r="J19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>1.172591515792256</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>1.1661160301308313</v>
       </c>
       <c r="L19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>1.1127263116162283</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>1.1641337386018238</v>
       </c>
       <c r="N19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>1.7426985595348223</v>
       </c>
       <c r="O19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>1.4111272631161622</v>
       </c>
       <c r="P19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>1.5394476014272498</v>
       </c>
       <c r="Q19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>1.4209065679925994</v>
       </c>
       <c r="R19" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="114"/>
         <v>1.4803753138628255</v>
       </c>
       <c r="S19" s="8">
-        <f t="shared" ref="S19:V19" si="109">S17/S18</f>
+        <f t="shared" ref="S19:V19" si="115">S17/S18</f>
         <v>1.8359984141667769</v>
       </c>
       <c r="T19" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>2.0434782608695654</v>
       </c>
       <c r="U19" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>2.052286366774656</v>
       </c>
       <c r="V19" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="115"/>
         <v>2.1851930532688937</v>
       </c>
       <c r="W19" s="8">
-        <f t="shared" ref="W19:X19" si="110">W17/W18</f>
+        <f t="shared" ref="W19:X19" si="116">W17/W18</f>
         <v>2.7589037041023641</v>
       </c>
       <c r="X19" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="116"/>
         <v>2.3675040027985954</v>
       </c>
       <c r="Y19" s="8">
-        <f t="shared" ref="Y19" si="111">Y17/Y18</f>
+        <f t="shared" ref="Y19" si="117">Y17/Y18</f>
         <v>2.2507164673115994</v>
       </c>
       <c r="Z19" s="8">
-        <f t="shared" ref="Z19" si="112">Z17/Z18</f>
+        <f t="shared" ref="Z19" si="118">Z17/Z18</f>
         <v>2.252331041534922</v>
       </c>
       <c r="AA19" s="8">
-        <f t="shared" ref="AA19" si="113">AA17/AA18</f>
+        <f t="shared" ref="AA19" si="119">AA17/AA18</f>
         <v>2.3621220887208536</v>
       </c>
       <c r="AB19" s="8">
-        <f t="shared" ref="AB19:AC19" si="114">AB17/AB18</f>
+        <f t="shared" ref="AB19:AC19" si="120">AB17/AB18</f>
         <v>2.2099484681727057</v>
       </c>
       <c r="AC19" s="8">
-        <f t="shared" si="114"/>
+        <f t="shared" si="120"/>
         <v>2.4620911427149066</v>
       </c>
       <c r="AD19" s="8">
-        <f t="shared" ref="AD19:AE19" si="115">AD17/AD18</f>
+        <f t="shared" ref="AD19:AE19" si="121">AD17/AD18</f>
         <v>2.7018554148783016</v>
       </c>
       <c r="AE19" s="8">
-        <f t="shared" si="115"/>
+        <f t="shared" si="121"/>
         <v>2.9992061676735329</v>
       </c>
       <c r="AF19" s="8">
-        <f t="shared" ref="AF19:AG19" si="116">AF17/AF18</f>
+        <f t="shared" ref="AF19:AG19" si="122">AF17/AF18</f>
         <v>2.9992061676735329</v>
       </c>
       <c r="AG19" s="8">
-        <f t="shared" si="116"/>
+        <f t="shared" si="122"/>
         <v>2.9425615220053012</v>
       </c>
       <c r="AH19" s="8">
-        <f t="shared" ref="AH19:AI19" si="117">AH17/AH18</f>
+        <f t="shared" ref="AH19:AI19" si="123">AH17/AH18</f>
         <v>2.9646172474101977</v>
       </c>
       <c r="AI19" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="123"/>
         <v>3.3185793084891699</v>
       </c>
       <c r="AJ19" s="8">
-        <f t="shared" ref="AJ19:AL19" si="118">AJ17/AJ18</f>
+        <f t="shared" ref="AJ19:AL19" si="124">AJ17/AJ18</f>
         <v>3.2429378531073447</v>
       </c>
       <c r="AK19" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="124"/>
         <v>3.474470232088799</v>
       </c>
       <c r="AL19" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="124"/>
         <v>3.6642895586652315</v>
       </c>
-      <c r="AM19" s="8"/>
+      <c r="AM19" s="8">
+        <f t="shared" ref="AM19" si="125">AM17/AM18</f>
+        <v>3.7334499461786868</v>
+      </c>
       <c r="AN19" s="8"/>
       <c r="AO19" s="8"/>
       <c r="AP19" s="8"/>
@@ -5672,64 +5714,64 @@
         <v>5.8518567463988367</v>
       </c>
       <c r="AW19" s="8">
-        <f t="shared" ref="AW19:BF19" si="119">AW17/AW18</f>
+        <f t="shared" ref="AW19:BF19" si="126">AW17/AW18</f>
         <v>8.135190397790641</v>
       </c>
       <c r="AX19" s="8">
-        <f t="shared" ref="AX19:AY19" si="120">AX17/AX18</f>
+        <f t="shared" ref="AX19:AY19" si="127">AX17/AX18</f>
         <v>9.6294552157474804</v>
       </c>
       <c r="AY19" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="127"/>
         <v>9.7360171144867671</v>
       </c>
       <c r="AZ19" s="8">
-        <f t="shared" ref="AZ19" si="121">AZ17/AZ18</f>
+        <f t="shared" ref="AZ19" si="128">AZ17/AZ18</f>
         <v>11.904749091887529</v>
       </c>
       <c r="BA19" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="126"/>
         <v>13.701829924650161</v>
       </c>
       <c r="BB19" s="8">
-        <f t="shared" si="119"/>
-        <v>15.736825738966628</v>
+        <f t="shared" si="126"/>
+        <v>16.213903728471475</v>
       </c>
       <c r="BC19" s="8">
-        <f t="shared" si="119"/>
-        <v>17.008439100137242</v>
+        <f t="shared" si="126"/>
+        <v>17.711334004674377</v>
       </c>
       <c r="BD19" s="8">
-        <f t="shared" si="119"/>
-        <v>18.080758753299548</v>
+        <f t="shared" si="126"/>
+        <v>18.825827352108909</v>
       </c>
       <c r="BE19" s="8">
-        <f t="shared" si="119"/>
-        <v>19.060484421032392</v>
+        <f t="shared" si="126"/>
+        <v>19.84280644978222</v>
       </c>
       <c r="BF19" s="8">
-        <f t="shared" si="119"/>
-        <v>19.871280065476256</v>
+        <f t="shared" si="126"/>
+        <v>20.684894975376078</v>
       </c>
       <c r="BG19" s="8">
-        <f t="shared" ref="BG19:BI19" si="122">BG17/BG18</f>
-        <v>20.496367179302545</v>
+        <f t="shared" ref="BG19:BI19" si="129">BG17/BG18</f>
+        <v>21.334390536499374</v>
       </c>
       <c r="BH19" s="8">
-        <f t="shared" si="122"/>
-        <v>21.14080509269386</v>
+        <f t="shared" si="129"/>
+        <v>22.003969150606583</v>
       </c>
       <c r="BI19" s="8">
-        <f t="shared" si="122"/>
-        <v>21.562641290925534</v>
+        <f t="shared" si="129"/>
+        <v>22.443068629996514</v>
       </c>
       <c r="BJ19" s="8">
-        <f t="shared" ref="BJ19:BK19" si="123">BJ17/BJ18</f>
-        <v>21.992904414085604</v>
+        <f t="shared" ref="BJ19:BK19" si="130">BJ17/BJ18</f>
+        <v>22.890940299938013</v>
       </c>
       <c r="BK19" s="8">
-        <f t="shared" si="123"/>
-        <v>22.431762902682298</v>
+        <f t="shared" si="130"/>
+        <v>23.347759506251752</v>
       </c>
     </row>
     <row r="21" spans="2:184" x14ac:dyDescent="0.3">
@@ -5737,208 +5779,211 @@
         <v>99</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" ref="G21:V22" si="124">G3/C3-1</f>
+        <f t="shared" ref="G21:V22" si="131">G3/C3-1</f>
         <v>-2.7214587018641989E-2</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>-1.898976632189564E-2</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>4.141114862537032E-2</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>6.8630503830105161E-2</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.20988949503427046</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>-9.5224813120606933E-2</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>2.2098716421860454E-2</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>-3.2635934495016672E-3</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>-8.8502225562171244E-2</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.12553178371046303</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>2.7382185396167769E-2</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>6.1041922469742049E-2</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>2.2196854388634168E-3</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>6.6009312517118612E-2</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>6.3134018020288618E-2</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>4.3588471923734051E-2</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" ref="W21:X23" si="125">W3/S3-1</f>
+        <f t="shared" ref="W21:X23" si="132">W3/S3-1</f>
         <v>5.2395114851610414E-2</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="132"/>
         <v>6.7780061664953761E-2</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" ref="Y21:Y23" si="126">Y3/U3-1</f>
+        <f t="shared" ref="Y21:Y23" si="133">Y3/U3-1</f>
         <v>2.9218277721803965E-2</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" ref="Z21:Z23" si="127">Z3/V3-1</f>
+        <f t="shared" ref="Z21:Z23" si="134">Z3/V3-1</f>
         <v>-5.1853416411447917E-2</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" ref="AA21:AA23" si="128">AA3/W3-1</f>
+        <f t="shared" ref="AA21:AA23" si="135">AA3/W3-1</f>
         <v>-5.3514521075100685E-2</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" ref="AB21:AL23" si="129">AB3/X3-1</f>
+        <f t="shared" ref="AB21:AM23" si="136">AB3/X3-1</f>
         <v>-0.20511092930362385</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>-0.10238396867442123</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>-6.142793495210519E-2</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>-1.3086843275522564E-2</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>-5.9453895985953853E-2</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.21510136002052871</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>-0.2157479380525722</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>-1.6929514000643686E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>4.4029610556807208E-2</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>-0.1912253840874294</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.29651206779148076</v>
       </c>
-      <c r="AM21" s="9"/>
+      <c r="AM21" s="9">
+        <f t="shared" si="136"/>
+        <v>4.2561550550026084E-2</v>
+      </c>
       <c r="AN21" s="9"/>
       <c r="AO21" s="9"/>
       <c r="AP21" s="9"/>
       <c r="AQ21" s="9"/>
       <c r="AT21" s="9">
-        <f t="shared" ref="AT21:BI21" si="130">AT3/AS3-1</f>
+        <f t="shared" ref="AT21:BI21" si="137">AT3/AS3-1</f>
         <v>1.5045403755055808E-2</v>
       </c>
       <c r="AU21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>2.4373226661705161E-2</v>
       </c>
       <c r="AV21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>2.984758358685613E-2</v>
       </c>
       <c r="AW21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>4.457606443173967E-2</v>
       </c>
       <c r="AX21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>2.3327799195205001E-2</v>
       </c>
       <c r="AY21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>-0.11044657097288679</v>
       </c>
       <c r="AZ21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>-2.2736054653085813E-2</v>
       </c>
       <c r="BA21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>1.1355728474726323E-2</v>
       </c>
       <c r="BB21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI21" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="137"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BJ21" s="9">
-        <f t="shared" ref="BJ21:BJ23" si="131">BJ3/BI3-1</f>
+        <f t="shared" ref="BJ21:BJ23" si="138">BJ3/BI3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK21" s="9">
-        <f t="shared" ref="BK21:BK23" si="132">BK3/BJ3-1</f>
+        <f t="shared" ref="BK21:BK23" si="139">BK3/BJ3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BM21" t="s">
@@ -5953,208 +5998,211 @@
         <v>85</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.47126436781609193</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.45531576856878053</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.34555696057018048</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.35379136992040228</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.15087890625</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.47852983988355158</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.29201196070055535</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.28531641652483364</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.46686465846414937</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.147612601525966</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.26628314487866156</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.19694233778740822</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.23508995198704219</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.26620556538523399</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.29676240208877291</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="131"/>
         <v>0.36850045257970421</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="132"/>
         <v>0.34354362793311788</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="132"/>
         <v>0.31050982384823844</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="133"/>
         <v>0.2883662867957959</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="134"/>
         <v>0.24601308150216794</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="135"/>
         <v>0.19852889911455063</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.17063556173058902</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.16487466399950002</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.16004600548526948</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.19199557895349173</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.13116202042506209</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.15589363814430213</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.30948749237339834</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.22768532526475038</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.30332829046898646</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.27085122681585005</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.15132983886623963</v>
       </c>
-      <c r="AM22" s="9"/>
+      <c r="AM22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.22733687118637325</v>
+      </c>
       <c r="AN22" s="9"/>
       <c r="AO22" s="9"/>
       <c r="AP22" s="9"/>
       <c r="AQ22" s="9"/>
       <c r="AT22" s="9">
-        <f t="shared" ref="AT22:BI22" si="133">AT4/AS4-1</f>
+        <f t="shared" ref="AT22:BI22" si="140">AT4/AS4-1</f>
         <v>0.39996947496947488</v>
       </c>
       <c r="AU22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>0.30331639884002359</v>
       </c>
       <c r="AV22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>0.25429116338207258</v>
       </c>
       <c r="AW22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>0.29396857577293467</v>
       </c>
       <c r="AX22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>0.29401941987754343</v>
       </c>
       <c r="AY22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>0.17268078191463943</v>
       </c>
       <c r="AZ22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>0.19927861102054134</v>
       </c>
       <c r="BA22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>0.23349928916529317</v>
       </c>
       <c r="BB22" s="9">
-        <f t="shared" si="133"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="140"/>
+        <v>0.17999999999999994</v>
       </c>
       <c r="BC22" s="9">
-        <f t="shared" si="133"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="140"/>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="BD22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BE22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BF22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BG22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BH22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BI22" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="140"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BJ22" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="138"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BK22" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="139"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BM22" t="s">
@@ -6173,19 +6221,19 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="9">
-        <f t="shared" ref="G23:J23" si="134">G5/C5-1</f>
+        <f t="shared" ref="G23:J23" si="141">G5/C5-1</f>
         <v>0.13297626743004898</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="141"/>
         <v>0.11972430883605667</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="141"/>
         <v>0.15539376184732046</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="141"/>
         <v>0.17496582698691654</v>
       </c>
       <c r="K23" s="9">
@@ -6193,114 +6241,117 @@
         <v>0.18526367267095933</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" ref="L23:V23" si="135">L5/H5-1</f>
+        <f t="shared" ref="L23:V23" si="142">L5/H5-1</f>
         <v>0.12286465177398154</v>
       </c>
       <c r="M23" s="9">
+        <f t="shared" si="142"/>
+        <v>0.13990081658525666</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="142"/>
+        <v>0.12072461359481479</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" si="142"/>
+        <v>0.13653555219364599</v>
+      </c>
+      <c r="P23" s="9">
+        <f t="shared" si="142"/>
+        <v>0.13658341289150311</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" si="142"/>
+        <v>0.14556278826338698</v>
+      </c>
+      <c r="R23" s="9">
+        <f t="shared" si="142"/>
+        <v>0.12800664353293589</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" si="142"/>
+        <v>0.12400544546967174</v>
+      </c>
+      <c r="T23" s="9">
+        <f t="shared" si="142"/>
+        <v>0.16718148810491518</v>
+      </c>
+      <c r="U23" s="9">
+        <f t="shared" si="142"/>
+        <v>0.19088546871876866</v>
+      </c>
+      <c r="V23" s="9">
+        <f t="shared" si="142"/>
+        <v>0.21347251071437956</v>
+      </c>
+      <c r="W23" s="9">
+        <f t="shared" si="132"/>
+        <v>0.21970716477364483</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" si="132"/>
+        <v>0.2008543040208004</v>
+      </c>
+      <c r="Y23" s="9">
+        <f t="shared" si="133"/>
+        <v>0.18352275451973332</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" si="134"/>
+        <v>0.12378661813139202</v>
+      </c>
+      <c r="AA23" s="9">
         <f t="shared" si="135"/>
-        <v>0.13990081658525666</v>
-      </c>
-      <c r="N23" s="9">
-        <f t="shared" si="135"/>
-        <v>0.12072461359481479</v>
-      </c>
-      <c r="O23" s="9">
-        <f t="shared" si="135"/>
-        <v>0.13653555219364599</v>
-      </c>
-      <c r="P23" s="9">
-        <f t="shared" si="135"/>
-        <v>0.13658341289150311</v>
-      </c>
-      <c r="Q23" s="9">
-        <f t="shared" si="135"/>
-        <v>0.14556278826338698</v>
-      </c>
-      <c r="R23" s="9">
-        <f t="shared" si="135"/>
-        <v>0.12800664353293589</v>
-      </c>
-      <c r="S23" s="9">
-        <f t="shared" si="135"/>
-        <v>0.12400544546967174</v>
-      </c>
-      <c r="T23" s="9">
-        <f t="shared" si="135"/>
-        <v>0.16718148810491518</v>
-      </c>
-      <c r="U23" s="9">
-        <f t="shared" si="135"/>
-        <v>0.19088546871876866</v>
-      </c>
-      <c r="V23" s="9">
-        <f t="shared" si="135"/>
-        <v>0.21347251071437956</v>
-      </c>
-      <c r="W23" s="9">
-        <f t="shared" si="125"/>
-        <v>0.21970716477364483</v>
-      </c>
-      <c r="X23" s="9">
-        <f t="shared" si="125"/>
-        <v>0.2008543040208004</v>
-      </c>
-      <c r="Y23" s="9">
-        <f t="shared" si="126"/>
-        <v>0.18352275451973332</v>
-      </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="127"/>
-        <v>0.12378661813139202</v>
-      </c>
-      <c r="AA23" s="9">
-        <f t="shared" si="128"/>
         <v>0.1060308493501334</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>1.9699195793380753E-2</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>7.0846839546191198E-2</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>8.3370288248336921E-2</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.12758868361198683</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>7.1473259142700085E-2</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.17335452257979078</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.15195144957198026</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.16044729904276589</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.23205407222605579</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.12973234440503068</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="136"/>
         <v>0.18097548163826538</v>
       </c>
-      <c r="AM23" s="9"/>
+      <c r="AM23" s="9">
+        <f t="shared" si="136"/>
+        <v>0.18431043683769155</v>
+      </c>
       <c r="AN23" s="9"/>
       <c r="AO23" s="9"/>
       <c r="AP23" s="9"/>
@@ -6310,79 +6361,79 @@
         <v>0.14599017663367975</v>
       </c>
       <c r="AU23" s="9">
-        <f t="shared" ref="AU23:BI23" si="136">AU5/AT5-1</f>
+        <f t="shared" ref="AU23:BI23" si="143">AU5/AT5-1</f>
         <v>0.14029539688292858</v>
       </c>
       <c r="AV23" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="143"/>
         <v>0.13645574247276371</v>
       </c>
       <c r="AW23" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="143"/>
         <v>0.17531727441177503</v>
       </c>
       <c r="AX23" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="143"/>
         <v>0.17956070629670173</v>
       </c>
       <c r="AY23" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="143"/>
         <v>6.8820295556564215E-2</v>
       </c>
       <c r="AZ23" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="143"/>
         <v>0.13149611872684797</v>
       </c>
       <c r="BA23" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="143"/>
         <v>0.17492211643124356</v>
       </c>
       <c r="BB23" s="9">
-        <f t="shared" si="136"/>
-        <v>0.11822265763655193</v>
+        <f t="shared" si="143"/>
+        <v>0.14141322713009896</v>
       </c>
       <c r="BC23" s="9">
-        <f t="shared" si="136"/>
-        <v>6.5649049602108045E-2</v>
+        <f t="shared" si="143"/>
+        <v>7.3932141552135011E-2</v>
       </c>
       <c r="BD23" s="9">
-        <f t="shared" si="136"/>
-        <v>5.0284619830460064E-2</v>
+        <f t="shared" si="143"/>
+        <v>5.0555422216383761E-2</v>
       </c>
       <c r="BE23" s="9">
-        <f t="shared" si="136"/>
-        <v>4.2525809643622514E-2</v>
+        <f t="shared" si="143"/>
+        <v>4.2736014980473636E-2</v>
       </c>
       <c r="BF23" s="9">
-        <f t="shared" si="136"/>
-        <v>3.4569247933639913E-2</v>
+        <f t="shared" si="143"/>
+        <v>3.4723047278275798E-2</v>
       </c>
       <c r="BG23" s="9">
-        <f t="shared" si="136"/>
-        <v>2.646547933001786E-2</v>
+        <f t="shared" si="143"/>
+        <v>2.6566087732067922E-2</v>
       </c>
       <c r="BH23" s="9">
-        <f t="shared" si="136"/>
-        <v>2.6522176392125729E-2</v>
+        <f t="shared" si="143"/>
+        <v>2.6621502081494164E-2</v>
       </c>
       <c r="BI23" s="9">
-        <f t="shared" si="136"/>
-        <v>1.828907649306788E-2</v>
+        <f t="shared" si="143"/>
+        <v>1.8338100804058621E-2</v>
       </c>
       <c r="BJ23" s="9">
-        <f t="shared" si="131"/>
-        <v>1.8303003752183189E-2</v>
+        <f t="shared" si="138"/>
+        <v>1.83517083505218E-2</v>
       </c>
       <c r="BK23" s="9">
-        <f t="shared" si="132"/>
-        <v>1.8316840661395162E-2</v>
+        <f t="shared" si="139"/>
+        <v>1.8365226323752593E-2</v>
       </c>
       <c r="BM23" t="s">
         <v>88</v>
       </c>
       <c r="BN23" s="23">
         <f>NPV(BN22,BB17:GB17)</f>
-        <v>2803246.2306998842</v>
+        <v>2916685.9620076721</v>
       </c>
     </row>
     <row r="24" spans="2:184" x14ac:dyDescent="0.3">
@@ -6394,224 +6445,227 @@
         <v>0.75636140971560761</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" ref="D24:V24" si="137">(D3-D6)/D3</f>
+        <f t="shared" ref="D24:V24" si="144">(D3-D6)/D3</f>
         <v>0.70568598478629674</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.78812099497002686</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.8043843806439559</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.79157924185200723</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.69329465580720739</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.77338891094349604</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.79503467568040098</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.78906295161570028</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.63715395523768414</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.77725271879854996</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.80716833304098701</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.79039827498731607</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.72796494111202414</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.78728498519311951</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.75918884664131814</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.77238499019173579</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.68869475847893113</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.74651810584958223</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="144"/>
         <v>0.7736297391488014</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" ref="W24:X24" si="138">(W3-W6)/W3</f>
+        <f t="shared" ref="W24:X24" si="145">(W3-W6)/W3</f>
         <v>0.77199206301485179</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="145"/>
         <v>0.69531738774724483</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" ref="Y24:Y25" si="139">(Y3-Y6)/Y3</f>
+        <f t="shared" ref="Y24:Y25" si="146">(Y3-Y6)/Y3</f>
         <v>0.73603593228146957</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24" si="140">(Z3-Z6)/Z3</f>
+        <f t="shared" ref="Z24" si="147">(Z3-Z6)/Z3</f>
         <v>0.75735130318556476</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" ref="AA24:AA25" si="141">(AA3-AA6)/AA3</f>
+        <f t="shared" ref="AA24:AA25" si="148">(AA3-AA6)/AA3</f>
         <v>0.72670097198399086</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" ref="AB24:AC24" si="142">(AB3-AB6)/AB3</f>
+        <f t="shared" ref="AB24:AC24" si="149">(AB3-AB6)/AB3</f>
         <v>0.65550644790216139</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="149"/>
         <v>0.74717731588401337</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" ref="AD24:AE24" si="143">(AD3-AD6)/AD3</f>
+        <f t="shared" ref="AD24:AE24" si="150">(AD3-AD6)/AD3</f>
         <v>0.77030795704028954</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="150"/>
         <v>0.77270679111683294</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" ref="AF24:AG24" si="144">(AF3-AF6)/AF3</f>
+        <f t="shared" ref="AF24:AG24" si="151">(AF3-AF6)/AF3</f>
         <v>0.77270679111683294</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="151"/>
         <v>0.68512750118789922</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" ref="AH24:AI24" si="145">(AH3-AH6)/AH3</f>
+        <f t="shared" ref="AH24:AI24" si="152">(AH3-AH6)/AH3</f>
         <v>0.89120072633729286</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="152"/>
         <v>0.78431115767417492</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" ref="AJ24:AL24" si="146">(AJ3-AJ6)/AJ3</f>
+        <f t="shared" ref="AJ24:AL24" si="153">(AJ3-AJ6)/AJ3</f>
         <v>0.76225414637153954</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="153"/>
         <v>0.80174946145309745</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="153"/>
         <v>0.8066059757236228</v>
       </c>
-      <c r="AM24" s="9"/>
+      <c r="AM24" s="9">
+        <f t="shared" ref="AM24" si="154">(AM3-AM6)/AM3</f>
+        <v>0.81648034166561989</v>
+      </c>
       <c r="AN24" s="9"/>
       <c r="AO24" s="9"/>
       <c r="AP24" s="9"/>
       <c r="AQ24" s="9"/>
       <c r="AS24" s="9">
-        <f t="shared" ref="AS24:AW24" si="147">(AS3-AS6)/AS3</f>
+        <f t="shared" ref="AS24:AW24" si="155">(AS3-AS6)/AS3</f>
         <v>0.76117782219354435</v>
       </c>
       <c r="AT24" s="9">
-        <f t="shared" si="147"/>
+        <f t="shared" si="155"/>
         <v>0.76091911251686128</v>
       </c>
       <c r="AU24" s="9">
-        <f t="shared" si="147"/>
+        <f t="shared" si="155"/>
         <v>0.75369689264254036</v>
       </c>
       <c r="AV24" s="9">
-        <f t="shared" si="147"/>
+        <f t="shared" si="155"/>
         <v>0.76459781602269217</v>
       </c>
       <c r="AW24" s="9">
-        <f t="shared" si="147"/>
+        <f t="shared" si="155"/>
         <v>0.74366153586402906</v>
       </c>
       <c r="AX24" s="9">
-        <f t="shared" ref="AX24:AY24" si="148">(AX3-AX6)/AX3</f>
+        <f t="shared" ref="AX24:AY24" si="156">(AX3-AX6)/AX3</f>
         <v>0.73788703734257277</v>
       </c>
       <c r="AY24" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="156"/>
         <v>0.72481800336944935</v>
       </c>
       <c r="AZ24" s="9">
-        <f t="shared" ref="AZ24:BI24" si="149">(AZ3-AZ6)/AZ3</f>
+        <f t="shared" ref="AZ24:BI24" si="157">(AZ3-AZ6)/AZ3</f>
         <v>0.7712405896121971</v>
       </c>
       <c r="BA24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="157"/>
         <v>0.78886873299346327</v>
       </c>
       <c r="BB24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="157"/>
         <v>0.77</v>
       </c>
       <c r="BC24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="157"/>
         <v>0.76999999999999991</v>
       </c>
       <c r="BD24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="157"/>
         <v>0.77</v>
       </c>
       <c r="BE24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="157"/>
         <v>0.77</v>
       </c>
       <c r="BF24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="157"/>
         <v>0.77</v>
       </c>
       <c r="BG24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="157"/>
         <v>0.77</v>
       </c>
       <c r="BH24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="157"/>
         <v>0.76999999999999991</v>
       </c>
       <c r="BI24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="157"/>
         <v>0.77</v>
       </c>
       <c r="BJ24" s="9">
-        <f t="shared" ref="BJ24:BK24" si="150">(BJ3-BJ6)/BJ3</f>
+        <f t="shared" ref="BJ24:BK24" si="158">(BJ3-BJ6)/BJ3</f>
         <v>0.77</v>
       </c>
       <c r="BK24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="158"/>
         <v>0.77</v>
       </c>
       <c r="BM24" t="s">
@@ -6627,236 +6681,239 @@
         <v>96</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:V25" si="151">(C4-C7)/C4</f>
+        <f t="shared" ref="C25:V25" si="159">(C4-C7)/C4</f>
         <v>0.38750000000000001</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.40116509996028066</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.42694562593401542</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.44333891914537077</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.48261718749999999</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.49363173216885009</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.50072618539085856</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.51841250193408639</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.46915570640644888</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.59771105094757571</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.55504860146796275</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.57180690983507887</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.58922890032972752</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.60366736368023166</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.60318537859007837</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.59926581514633415</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.65317783710364852</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.65548780487804881</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.64692143518704948</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="159"/>
         <v>0.64341882854413168</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" ref="W25:X25" si="152">(W4-W7)/W4</f>
+        <f t="shared" ref="W25:X25" si="160">(W4-W7)/W4</f>
         <v>0.65648748518441047</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="160"/>
         <v>0.618792206533329</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="146"/>
         <v>0.65521660311308372</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" ref="Z25" si="153">(Z4-Z7)/Z4</f>
+        <f t="shared" ref="Z25" si="161">(Z4-Z7)/Z4</f>
         <v>0.64398832168450859</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="148"/>
         <v>0.67569296995433525</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" ref="AB25:AC25" si="154">(AB4-AB7)/AB4</f>
+        <f t="shared" ref="AB25:AC25" si="162">(AB4-AB7)/AB4</f>
         <v>0.67435826662986476</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="162"/>
         <v>0.67299900721779493</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" ref="AD25:AE25" si="155">(AD4-AD7)/AD4</f>
+        <f t="shared" ref="AD25:AE25" si="163">(AD4-AD7)/AD4</f>
         <v>0.67144600366076879</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="163"/>
         <v>0.68837538431506518</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" ref="AF25:AG25" si="156">(AF4-AF7)/AF4</f>
+        <f t="shared" ref="AF25:AG25" si="164">(AF4-AF7)/AF4</f>
         <v>0.68837538431506518</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="156"/>
+        <f t="shared" si="164"/>
         <v>0.68293135866663568</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" ref="AH25:AI25" si="157">(AH4-AH7)/AH4</f>
+        <f t="shared" ref="AH25:AI25" si="165">(AH4-AH7)/AH4</f>
         <v>0.64577751892836344</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="165"/>
         <v>0.66599089698487468</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" ref="AJ25:AL25" si="158">(AJ4-AJ7)/AJ4</f>
+        <f t="shared" ref="AJ25:AL25" si="166">(AJ4-AJ7)/AJ4</f>
         <v>0.66407054462396797</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="166"/>
         <v>0.65510438928160453</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="166"/>
         <v>0.65095691762920493</v>
       </c>
-      <c r="AM25" s="9"/>
+      <c r="AM25" s="9">
+        <f t="shared" ref="AM25" si="167">(AM4-AM7)/AM4</f>
+        <v>0.65796505319751908</v>
+      </c>
       <c r="AN25" s="9"/>
       <c r="AO25" s="9"/>
       <c r="AP25" s="9"/>
       <c r="AQ25" s="9"/>
       <c r="AS25" s="9">
-        <f t="shared" ref="AS25:AW25" si="159">(AS4-AS7)/AS4</f>
+        <f t="shared" ref="AS25:AW25" si="168">(AS4-AS7)/AS4</f>
         <v>0.41739926739926742</v>
       </c>
       <c r="AT25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="168"/>
         <v>0.4999672938970412</v>
       </c>
       <c r="AU25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="168"/>
         <v>0.55437146585471941</v>
       </c>
       <c r="AV25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="168"/>
         <v>0.59904766985888447</v>
       </c>
       <c r="AW25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="168"/>
         <v>0.64940111736450412</v>
       </c>
       <c r="AX25" s="9">
-        <f t="shared" ref="AX25:AY25" si="160">(AX4-AX7)/AX4</f>
+        <f t="shared" ref="AX25:AY25" si="169">(AX4-AX7)/AX4</f>
         <v>0.64349440010196113</v>
       </c>
       <c r="AY25" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="169"/>
         <v>0.67354771220519505</v>
       </c>
       <c r="AZ25" s="9">
-        <f t="shared" ref="AZ25:BI25" si="161">(AZ4-AZ7)/AZ4</f>
+        <f t="shared" ref="AZ25:BI25" si="170">(AZ4-AZ7)/AZ4</f>
         <v>0.67461895294897278</v>
       </c>
       <c r="BA25" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="170"/>
         <v>0.65868912378660838</v>
       </c>
       <c r="BB25" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="170"/>
+        <v>0.67</v>
+      </c>
+      <c r="BC25" s="9">
+        <f t="shared" si="170"/>
         <v>0.66999999999999993</v>
       </c>
-      <c r="BC25" s="9">
-        <f t="shared" si="161"/>
+      <c r="BD25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.66999999999999993</v>
+      </c>
+      <c r="BE25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.66999999999999993</v>
+      </c>
+      <c r="BF25" s="9">
+        <f t="shared" si="170"/>
         <v>0.67</v>
       </c>
-      <c r="BD25" s="9">
-        <f t="shared" si="161"/>
+      <c r="BG25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.67</v>
+      </c>
+      <c r="BH25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.67</v>
+      </c>
+      <c r="BI25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.67</v>
+      </c>
+      <c r="BJ25" s="9">
+        <f t="shared" ref="BJ25:BK25" si="171">(BJ4-BJ7)/BJ4</f>
         <v>0.66999999999999993</v>
       </c>
-      <c r="BE25" s="9">
-        <f t="shared" si="161"/>
-        <v>0.67</v>
-      </c>
-      <c r="BF25" s="9">
-        <f t="shared" si="161"/>
+      <c r="BK25" s="9">
+        <f t="shared" si="171"/>
         <v>0.66999999999999993</v>
-      </c>
-      <c r="BG25" s="9">
-        <f t="shared" si="161"/>
-        <v>0.66999999999999993</v>
-      </c>
-      <c r="BH25" s="9">
-        <f t="shared" si="161"/>
-        <v>0.66999999999999993</v>
-      </c>
-      <c r="BI25" s="9">
-        <f t="shared" si="161"/>
-        <v>0.67</v>
-      </c>
-      <c r="BJ25" s="9">
-        <f t="shared" ref="BJ25:BK25" si="162">(BJ4-BJ7)/BJ4</f>
-        <v>0.67</v>
-      </c>
-      <c r="BK25" s="9">
-        <f t="shared" si="162"/>
-        <v>0.67</v>
       </c>
       <c r="BM25" t="s">
         <v>89</v>
       </c>
       <c r="BN25" s="23">
         <f>BN23+BN24</f>
-        <v>2870065.2306998842</v>
+        <v>2983504.9620076721</v>
       </c>
     </row>
     <row r="26" spans="2:184" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -6864,236 +6921,239 @@
         <v>42</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:F26" si="163">C9/C5</f>
+        <f t="shared" ref="C26:F26" si="172">C9/C5</f>
         <v>0.63782436051343616</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="172"/>
         <v>0.61662665530860372</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="172"/>
         <v>0.65276581078752371</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="172"/>
         <v>0.66975200156219483</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" ref="G26" si="164">G9/G5</f>
+        <f t="shared" ref="G26" si="173">G9/G5</f>
         <v>0.66264569239546822</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ref="H26:V26" si="165">H9/H5</f>
+        <f t="shared" ref="H26:V26" si="174">H9/H5</f>
         <v>0.6174009267584204</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.65438681531749876</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.67618414492271894</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.65943474075092834</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.61741246034923469</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.66733178502502366</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.69119435299700449</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.6851913477537438</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.66514929821709212</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.68661660146769077</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.67557121447164303</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.70388114334930285</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.67048936762930633</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.68721526878626582</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="174"/>
         <v>0.69684954064829263</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" ref="W26:X26" si="166">W9/W5</f>
+        <f t="shared" ref="W26:X26" si="175">W9/W5</f>
         <v>0.6988768012004325</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="166"/>
+        <f t="shared" si="175"/>
         <v>0.64953216826476956</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" ref="Y26" si="167">Y9/Y5</f>
+        <f t="shared" ref="Y26" si="176">Y9/Y5</f>
         <v>0.68365072933549431</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" ref="Z26" si="168">Z9/Z5</f>
+        <f t="shared" ref="Z26" si="177">Z9/Z5</f>
         <v>0.68323532247180174</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" ref="AA26" si="169">AA9/AA5</f>
+        <f t="shared" ref="AA26" si="178">AA9/AA5</f>
         <v>0.69171222217788597</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" ref="AB26:AC26" si="170">AB9/AB5</f>
+        <f t="shared" ref="AB26:AC26" si="179">AB9/AB5</f>
         <v>0.66845507801391546</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="179"/>
         <v>0.69487485101311086</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" ref="AD26:AE26" si="171">AD9/AD5</f>
+        <f t="shared" ref="AD26:AE26" si="180">AD9/AD5</f>
         <v>0.70109807969531401</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="171"/>
+        <f t="shared" si="180"/>
         <v>0.71155581506449384</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" ref="AF26:AG26" si="172">AF9/AF5</f>
+        <f t="shared" ref="AF26:AG26" si="181">AF9/AF5</f>
         <v>0.71155581506449384</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="181"/>
         <v>0.68360206385037081</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" ref="AH26:AI26" si="173">AH9/AH5</f>
+        <f t="shared" ref="AH26:AI26" si="182">AH9/AH5</f>
         <v>0.69589197707293715</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="173"/>
+        <f t="shared" si="182"/>
         <v>0.69354273080734929</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" ref="AJ26:AL26" si="174">AJ9/AJ5</f>
+        <f t="shared" ref="AJ26:AL26" si="183">AJ9/AJ5</f>
         <v>0.68693991268382348</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="183"/>
         <v>0.6871663859789342</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="183"/>
         <v>0.68584921704320978</v>
       </c>
-      <c r="AM26" s="9"/>
+      <c r="AM26" s="9">
+        <f t="shared" ref="AM26" si="184">AM9/AM5</f>
+        <v>0.69045871795862135</v>
+      </c>
       <c r="AN26" s="9"/>
       <c r="AO26" s="9"/>
       <c r="AP26" s="9"/>
       <c r="AQ26" s="9"/>
       <c r="AS26" s="9">
-        <f t="shared" ref="AS26:AU26" si="175">AS9/AS5</f>
+        <f t="shared" ref="AS26:AU26" si="185">AS9/AS5</f>
         <v>0.64423007030041224</v>
       </c>
       <c r="AT26" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="185"/>
         <v>0.65247372236317502</v>
       </c>
       <c r="AU26" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="185"/>
         <v>0.65901957200638894</v>
       </c>
       <c r="AV26" s="9">
-        <f t="shared" ref="AV26:BF26" si="176">AV9/AV5</f>
+        <f t="shared" ref="AV26:BF26" si="186">AV9/AV5</f>
         <v>0.67781001992797962</v>
       </c>
       <c r="AW26" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="186"/>
         <v>0.68925800771024703</v>
       </c>
       <c r="AX26" s="9">
-        <f t="shared" ref="AX26" si="177">AX9/AX5</f>
+        <f t="shared" ref="AX26" si="187">AX9/AX5</f>
         <v>0.67812074443940085</v>
       </c>
       <c r="AY26" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="186"/>
         <v>0.68920085883491022</v>
       </c>
       <c r="AZ26" s="9">
-        <f t="shared" ref="AZ26" si="178">AZ9/AZ5</f>
+        <f t="shared" ref="AZ26" si="188">AZ9/AZ5</f>
         <v>0.70009717200278587</v>
       </c>
       <c r="BA26" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="186"/>
         <v>0.68823742386165188</v>
       </c>
       <c r="BB26" s="9">
-        <f t="shared" si="176"/>
-        <v>0.69050135771127441</v>
+        <f t="shared" si="186"/>
+        <v>0.6900848230598311</v>
       </c>
       <c r="BC26" s="9">
-        <f t="shared" si="176"/>
-        <v>0.68943076033908024</v>
+        <f t="shared" si="186"/>
+        <v>0.68888915556723251</v>
       </c>
       <c r="BD26" s="9">
-        <f t="shared" si="176"/>
-        <v>0.68868547589094364</v>
+        <f t="shared" si="186"/>
+        <v>0.68815996254881573</v>
       </c>
       <c r="BE26" s="9">
-        <f t="shared" si="176"/>
-        <v>0.68810250688786723</v>
+        <f t="shared" si="186"/>
+        <v>0.68758984240574761</v>
       </c>
       <c r="BF26" s="9">
-        <f t="shared" si="176"/>
-        <v>0.68767260334990998</v>
+        <f t="shared" si="186"/>
+        <v>0.68716956133966078</v>
       </c>
       <c r="BG26" s="9">
-        <f t="shared" ref="BG26:BI26" si="179">BG9/BG5</f>
-        <v>0.68738911803937086</v>
+        <f t="shared" ref="BG26:BI26" si="189">BG9/BG5</f>
+        <v>0.68689248959252935</v>
       </c>
       <c r="BH26" s="9">
-        <f t="shared" si="179"/>
-        <v>0.68710923506932176</v>
+        <f t="shared" si="189"/>
+        <v>0.68661899195941456</v>
       </c>
       <c r="BI26" s="9">
-        <f t="shared" si="179"/>
-        <v>0.68696996247816733</v>
+        <f t="shared" si="189"/>
+        <v>0.68648291649478255</v>
       </c>
       <c r="BJ26" s="9">
-        <f t="shared" ref="BJ26:BK26" si="180">BJ9/BJ5</f>
-        <v>0.68683159338604882</v>
+        <f t="shared" ref="BJ26:BK26" si="190">BJ9/BJ5</f>
+        <v>0.68634773676247451</v>
       </c>
       <c r="BK26" s="9">
-        <f t="shared" si="180"/>
-        <v>0.68669412567985022</v>
+        <f t="shared" si="190"/>
+        <v>0.68621345044322046</v>
       </c>
       <c r="BM26" t="s">
         <v>90</v>
       </c>
       <c r="BN26" s="19">
         <f>BN25/BF18</f>
-        <v>386.1766995021373</v>
+        <v>401.44038778359419</v>
       </c>
     </row>
     <row r="27" spans="2:184" x14ac:dyDescent="0.3">
@@ -7101,19 +7161,19 @@
         <v>76</v>
       </c>
       <c r="C27" s="9">
-        <f t="shared" ref="C27:F27" si="181">C13/C5</f>
+        <f t="shared" ref="C27:F27" si="191">C13/C5</f>
         <v>0.29758057068981436</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="191"/>
         <v>0.30608688918144505</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="191"/>
         <v>0.28963467172152335</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="191"/>
         <v>0.31197031829720756</v>
       </c>
       <c r="G27" s="9">
@@ -7121,216 +7181,219 @@
         <v>0.3141250305648382</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:V27" si="182">H13/H5</f>
+        <f t="shared" ref="H27:V27" si="192">H13/H5</f>
         <v>0.30012448993706342</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.30918378761325926</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.3449891972743892</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.34228441754916794</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.3159126605278556</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.3382617513329626</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.3679152949550672</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.38378460142187265</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.37638866309001245</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.37049199051997372</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.35250966266137301</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.42730257845723207</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.41547497446373849</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.40876612477820939</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="192"/>
         <v>0.41374154966198645</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" ref="W27:X27" si="183">W13/W5</f>
+        <f t="shared" ref="W27:X27" si="193">W13/W5</f>
         <v>0.44658737339188381</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="183"/>
+        <f t="shared" si="193"/>
         <v>0.40747757500773274</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" ref="Y27" si="184">Y13/Y5</f>
+        <f t="shared" ref="Y27" si="194">Y13/Y5</f>
         <v>0.41256077795786061</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" ref="Z27" si="185">Z13/Z5</f>
+        <f t="shared" ref="Z27" si="195">Z13/Z5</f>
         <v>0.3959124650535043</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" ref="AA27" si="186">AA13/AA5</f>
+        <f t="shared" ref="AA27" si="196">AA13/AA5</f>
         <v>0.42931247755476637</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" ref="AB27:AC27" si="187">AB13/AB5</f>
+        <f t="shared" ref="AB27:AC27" si="197">AB13/AB5</f>
         <v>0.3867328947617874</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="187"/>
+        <f t="shared" si="197"/>
         <v>0.42287681858599618</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" ref="AD27:AE27" si="188">AD13/AD5</f>
+        <f t="shared" ref="AD27:AE27" si="198">AD13/AD5</f>
         <v>0.4316503230169606</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="188"/>
+        <f t="shared" si="198"/>
         <v>0.47587451563246458</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" ref="AF27:AG27" si="189">AF13/AF5</f>
+        <f t="shared" ref="AF27:AG27" si="199">AF13/AF5</f>
         <v>0.47587451563246458</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="189"/>
+        <f t="shared" si="199"/>
         <v>0.43585940019348596</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" ref="AH27:AI27" si="190">AH13/AH5</f>
+        <f t="shared" ref="AH27:AI27" si="200">AH13/AH5</f>
         <v>0.43142737960974553</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="200"/>
         <v>0.46583822520393381</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" ref="AJ27:AL27" si="191">AJ13/AJ5</f>
+        <f t="shared" ref="AJ27:AL27" si="201">AJ13/AJ5</f>
         <v>0.45457548253676472</v>
       </c>
       <c r="AK27" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="201"/>
         <v>0.45671224274255701</v>
       </c>
       <c r="AL27" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="201"/>
         <v>0.44901296424693554</v>
       </c>
-      <c r="AM27" s="9"/>
+      <c r="AM27" s="9">
+        <f t="shared" ref="AM27" si="202">AM13/AM5</f>
+        <v>0.48872838695557014</v>
+      </c>
       <c r="AN27" s="9"/>
       <c r="AO27" s="9"/>
       <c r="AP27" s="9"/>
       <c r="AQ27" s="9"/>
       <c r="AS27" s="9">
-        <f t="shared" ref="AS27:AU27" si="192">AS13/AS5</f>
+        <f t="shared" ref="AS27:AU27" si="203">AS13/AS5</f>
         <v>0.30177256726306062</v>
       </c>
       <c r="AT27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="203"/>
         <v>0.31766944545125048</v>
       </c>
       <c r="AU27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="203"/>
         <v>0.3413698020549415</v>
       </c>
       <c r="AV27" s="9">
-        <f t="shared" ref="AV27:BF27" si="193">AV13/AV5</f>
+        <f t="shared" ref="AV27:BF27" si="204">AV13/AV5</f>
         <v>0.37030381428521486</v>
       </c>
       <c r="AW27" s="9">
-        <f t="shared" si="193"/>
+        <f t="shared" si="204"/>
         <v>0.41594878872971303</v>
       </c>
       <c r="AX27" s="9">
-        <f t="shared" ref="AX27" si="194">AX13/AX5</f>
+        <f t="shared" ref="AX27" si="205">AX13/AX5</f>
         <v>0.4146567811570081</v>
       </c>
       <c r="AY27" s="9">
-        <f t="shared" si="193"/>
+        <f t="shared" si="204"/>
         <v>0.41772880636104098</v>
       </c>
       <c r="AZ27" s="9">
-        <f t="shared" ref="AZ27" si="195">AZ13/AZ5</f>
+        <f t="shared" ref="AZ27" si="206">AZ13/AZ5</f>
         <v>0.45352634278779386</v>
       </c>
       <c r="BA27" s="9">
-        <f t="shared" si="193"/>
+        <f t="shared" si="204"/>
         <v>0.45621956240859851</v>
       </c>
       <c r="BB27" s="9">
-        <f t="shared" si="193"/>
-        <v>0.47405062169285633</v>
+        <f t="shared" si="204"/>
+        <v>0.47803180709253396</v>
       </c>
       <c r="BC27" s="9">
-        <f t="shared" si="193"/>
-        <v>0.47974866781975201</v>
+        <f t="shared" si="204"/>
+        <v>0.4850516527550332</v>
       </c>
       <c r="BD27" s="9">
-        <f t="shared" si="193"/>
-        <v>0.48482579871547921</v>
+        <f t="shared" si="204"/>
+        <v>0.49003366786266345</v>
       </c>
       <c r="BE27" s="9">
-        <f t="shared" si="193"/>
-        <v>0.48964142418515599</v>
+        <f t="shared" si="204"/>
+        <v>0.49474919386803445</v>
       </c>
       <c r="BF27" s="9">
-        <f t="shared" si="193"/>
-        <v>0.49297654085284331</v>
+        <f t="shared" si="204"/>
+        <v>0.49801542703092888</v>
       </c>
       <c r="BG27" s="9">
-        <f t="shared" ref="BG27:BI27" si="196">BG13/BG5</f>
-        <v>0.4950905739618186</v>
+        <f t="shared" ref="BG27:BI27" si="207">BG13/BG5</f>
+        <v>0.50008593924685696</v>
       </c>
       <c r="BH27" s="9">
-        <f t="shared" si="196"/>
-        <v>0.4971848118006274</v>
+        <f t="shared" si="207"/>
+        <v>0.50213660859100206</v>
       </c>
       <c r="BI27" s="9">
-        <f t="shared" si="196"/>
-        <v>0.4978693697408863</v>
+        <f t="shared" si="207"/>
+        <v>0.5028096005865953</v>
       </c>
       <c r="BJ27" s="9">
-        <f t="shared" ref="BJ27:BK27" si="197">BJ13/BJ5</f>
-        <v>0.49854948676829891</v>
+        <f t="shared" ref="BJ27:BK27" si="208">BJ13/BJ5</f>
+        <v>0.5034781625353334</v>
       </c>
       <c r="BK27" s="9">
-        <f t="shared" si="197"/>
-        <v>0.49922517326933519</v>
+        <f t="shared" si="208"/>
+        <v>0.50414230590768883</v>
       </c>
       <c r="BM27" t="s">
         <v>92</v>
       </c>
       <c r="BN27" s="19">
         <f>Main!D3</f>
-        <v>520.79999999999995</v>
+        <v>527.70000000000005</v>
       </c>
     </row>
     <row r="28" spans="2:184" x14ac:dyDescent="0.3">
@@ -7342,134 +7405,137 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9">
-        <f t="shared" ref="G28:G30" si="198">G10/C10-1</f>
+        <f t="shared" ref="G28:G30" si="209">G10/C10-1</f>
         <v>0.1506761107533805</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" ref="H28" si="199">H10/D10-1</f>
+        <f t="shared" ref="H28" si="210">H10/D10-1</f>
         <v>0.14435009797517973</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" ref="I28" si="200">I10/E10-1</f>
+        <f t="shared" ref="I28" si="211">I10/E10-1</f>
         <v>0.10730253353204167</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" ref="J28" si="201">J10/F10-1</f>
+        <f t="shared" ref="J28" si="212">J10/F10-1</f>
         <v>0.1192373363688104</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" ref="K28" si="202">K10/G10-1</f>
+        <f t="shared" ref="K28" si="213">K10/G10-1</f>
         <v>0.11275881365416907</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" ref="L28" si="203">L10/H10-1</f>
+        <f t="shared" ref="L28" si="214">L10/H10-1</f>
         <v>0.1615296803652968</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" ref="M28" si="204">M10/I10-1</f>
+        <f t="shared" ref="M28" si="215">M10/I10-1</f>
         <v>0.16177658142664875</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" ref="N28" si="205">N10/J10-1</f>
+        <f t="shared" ref="N28" si="216">N10/J10-1</f>
         <v>0.14747012458682929</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28" si="206">O10/K10-1</f>
+        <f t="shared" ref="O28" si="217">O10/K10-1</f>
         <v>0.14785013829519733</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" ref="P28" si="207">P10/L10-1</f>
+        <f t="shared" ref="P28" si="218">P10/L10-1</f>
         <v>0.13095823095823089</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" ref="Q28" si="208">Q10/M10-1</f>
+        <f t="shared" ref="Q28" si="219">Q10/M10-1</f>
         <v>0.13229842446709927</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" ref="R28" si="209">R10/N10-1</f>
+        <f t="shared" ref="R28" si="220">R10/N10-1</f>
         <v>0.15532904941280745</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" ref="S28" si="210">S10/O10-1</f>
+        <f t="shared" ref="S28" si="221">S10/O10-1</f>
         <v>7.9079956188389922E-2</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" ref="T28" si="211">T10/P10-1</f>
+        <f t="shared" ref="T28" si="222">T10/P10-1</f>
         <v>6.4305887464696898E-2</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" ref="U28" si="212">U10/Q10-1</f>
+        <f t="shared" ref="U28" si="223">U10/Q10-1</f>
         <v>6.4865970943319029E-2</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" ref="V28" si="213">V10/R10-1</f>
+        <f t="shared" ref="V28" si="224">V10/R10-1</f>
         <v>9.0717299578058963E-2</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" ref="W28:X28" si="214">W10/S10-1</f>
+        <f t="shared" ref="W28:X28" si="225">W10/S10-1</f>
         <v>0.13662200568412497</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="214"/>
+        <f t="shared" si="225"/>
         <v>0.17534190651153292</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" ref="Y28" si="215">Y10/U10-1</f>
+        <f t="shared" ref="Y28" si="226">Y10/U10-1</f>
         <v>0.21176018447348199</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" ref="Z28" si="216">Z10/V10-1</f>
+        <f t="shared" ref="Z28" si="227">Z10/V10-1</f>
         <v>0.20432565500263755</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" ref="AA28" si="217">AA10/W10-1</f>
+        <f t="shared" ref="AA28" si="228">AA10/W10-1</f>
         <v>0.18378281836042154</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" ref="AB28:AL28" si="218">AB10/X10-1</f>
+        <f t="shared" ref="AB28:AM28" si="229">AB10/X10-1</f>
         <v>0.18860715526224392</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="218"/>
+        <f t="shared" si="229"/>
         <v>0.1075166508087535</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="218"/>
+        <f t="shared" si="229"/>
         <v>-1.6060738793984508E-2</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="218"/>
+        <f t="shared" si="229"/>
         <v>4.6771273385637357E-3</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="218"/>
+        <f t="shared" si="229"/>
         <v>-2.7030976037405008E-2</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="218"/>
+        <f t="shared" si="229"/>
         <v>2.2623138602519965E-2</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="218"/>
+        <f t="shared" si="229"/>
         <v>0.19542958895978635</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="218"/>
+        <f t="shared" si="229"/>
         <v>0.13290283826400362</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="218"/>
+        <f t="shared" si="229"/>
         <v>0.18891725484306954</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" si="218"/>
+        <f t="shared" si="229"/>
         <v>0.14785774292915144</v>
       </c>
       <c r="AL28" s="9">
-        <f t="shared" si="218"/>
+        <f t="shared" si="229"/>
         <v>9.5953326713009046E-2</v>
       </c>
-      <c r="AM28" s="9"/>
+      <c r="AM28" s="9">
+        <f t="shared" si="229"/>
+        <v>7.9798515376458212E-2</v>
+      </c>
       <c r="AN28" s="9"/>
       <c r="AO28" s="9"/>
       <c r="AP28" s="9"/>
@@ -7480,71 +7546,71 @@
         <v>0.12955434532484467</v>
       </c>
       <c r="AU28" s="9">
-        <f t="shared" ref="AU28:BI28" si="219">AU10/AT10-1</f>
+        <f t="shared" ref="AU28:BI28" si="230">AU10/AT10-1</f>
         <v>0.14600027162841234</v>
       </c>
       <c r="AV28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>0.14179900450343674</v>
       </c>
       <c r="AW28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>7.5094711713114437E-2</v>
       </c>
       <c r="AX28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>0.1832400077234988</v>
       </c>
       <c r="AY28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>0.10945659268929497</v>
       </c>
       <c r="AZ28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>4.8575105717962863E-2</v>
       </c>
       <c r="BA28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>0.13929022303268335</v>
       </c>
       <c r="BB28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BC28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BD28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI28" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="230"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BJ28" s="9">
-        <f t="shared" ref="BJ28" si="220">BJ10/BI10-1</f>
+        <f t="shared" ref="BJ28" si="231">BJ10/BI10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK28" s="9">
-        <f t="shared" ref="BK28" si="221">BK10/BJ10-1</f>
+        <f t="shared" ref="BK28" si="232">BK10/BJ10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BM28" s="6" t="s">
@@ -7552,7 +7618,7 @@
       </c>
       <c r="BN28" s="18">
         <f>BN26/BN27-1</f>
-        <v>-0.25849328052584997</v>
+        <v>-0.23926399889407968</v>
       </c>
     </row>
     <row r="29" spans="2:184" x14ac:dyDescent="0.3">
@@ -7560,229 +7626,232 @@
         <v>77</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:F29" si="222">C11/C$5</f>
+        <f t="shared" ref="C29:F29" si="233">C11/C$5</f>
         <v>0.14858250992704775</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.1579416092310075</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.16681027054971567</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.16762351103300135</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" ref="G29:V29" si="223">G11/G$5</f>
+        <f t="shared" ref="G29:V29" si="234">G11/G$5</f>
         <v>0.15535088434265221</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.15775641468981258</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.16163913643312577</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.15821838125311616</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.14090221427589053</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.14129530966092821</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.14932452324098</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.14716611798202686</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.13120556648010892</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.13366390288841923</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.14023014762571029</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.14242894328609365</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.11387737524896377</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.11484353236140775</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.12185297079556898</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>0.12690674293638413</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" ref="W29:X29" si="224">W11/W$5</f>
+        <f t="shared" ref="W29:X29" si="235">W11/W$5</f>
         <v>0.100337621643092</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="224"/>
+        <f t="shared" si="235"/>
         <v>0.10398623569440149</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" ref="Y29" si="225">Y11/Y$5</f>
+        <f t="shared" ref="Y29" si="236">Y11/Y$5</f>
         <v>0.11335089141004863</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29" si="226">Z11/Z$5</f>
+        <f t="shared" ref="Z29" si="237">Z11/Z$5</f>
         <v>0.12154632218258941</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" ref="AA29" si="227">AA11/AA$5</f>
+        <f t="shared" ref="AA29" si="238">AA11/AA$5</f>
         <v>0.10227046007741111</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" ref="AB29:AC29" si="228">AB11/AB$5</f>
+        <f t="shared" ref="AB29:AC29" si="239">AB11/AB$5</f>
         <v>0.10766489089426887</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>0.10878407779480485</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" ref="AD29:AE29" si="229">AD11/AD$5</f>
+        <f t="shared" ref="AD29:AE29" si="240">AD11/AD$5</f>
         <v>0.11041307017387746</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="240"/>
         <v>9.1777695206751955E-2</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" ref="AF29:AG29" si="230">AF11/AF$5</f>
+        <f t="shared" ref="AF29:AG29" si="241">AF11/AF$5</f>
         <v>9.1777695206751955E-2</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="241"/>
         <v>0.10070944856497904</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" ref="AH29:AI29" si="231">AH11/AH$5</f>
+        <f t="shared" ref="AH29:AI29" si="242">AH11/AH$5</f>
         <v>0.10530381448236439</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="231"/>
+        <f t="shared" si="242"/>
         <v>8.716932225356408E-2</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" ref="AJ29:AL29" si="232">AJ11/AJ$5</f>
+        <f t="shared" ref="AJ29:AL29" si="243">AJ11/AJ$5</f>
         <v>9.2486213235294115E-2</v>
       </c>
       <c r="AK29" s="9">
-        <f t="shared" si="232"/>
+        <f t="shared" si="243"/>
         <v>8.8659264122398884E-2</v>
       </c>
       <c r="AL29" s="9">
-        <f t="shared" si="232"/>
+        <f t="shared" si="243"/>
         <v>9.5302259258774738E-2</v>
       </c>
-      <c r="AM29" s="9"/>
+      <c r="AM29" s="9">
+        <f t="shared" ref="AM29" si="244">AM11/AM$5</f>
+        <v>7.3603440062827499E-2</v>
+      </c>
       <c r="AN29" s="9"/>
       <c r="AO29" s="9"/>
       <c r="AP29" s="9"/>
       <c r="AQ29" s="9"/>
       <c r="AS29" s="9">
-        <f t="shared" ref="AS29:AU29" si="233">AS11/AS$5</f>
+        <f t="shared" ref="AS29:AU29" si="245">AS11/AS$5</f>
         <v>0.16054869627522039</v>
       </c>
       <c r="AT29" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="245"/>
         <v>0.15829104748097136</v>
       </c>
       <c r="AU29" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="245"/>
         <v>0.14472795467368069</v>
       </c>
       <c r="AV29" s="9">
-        <f t="shared" ref="AV29:BF29" si="234">AV11/AV$5</f>
+        <f t="shared" ref="AV29:BF29" si="246">AV11/AV$5</f>
         <v>0.13703457679264414</v>
       </c>
       <c r="AW29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="246"/>
         <v>0.1196813573842273</v>
       </c>
       <c r="AX29" s="9">
-        <f t="shared" ref="AX29" si="235">AX11/AX$5</f>
+        <f t="shared" ref="AX29" si="247">AX11/AX$5</f>
         <v>0.11007716749886519</v>
       </c>
       <c r="AY29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="246"/>
         <v>0.10739683363612769</v>
       </c>
       <c r="AZ29" s="9">
-        <f t="shared" ref="AZ29" si="236">AZ11/AZ$5</f>
+        <f t="shared" ref="AZ29" si="248">AZ11/AZ$5</f>
         <v>9.7739187008144934E-2</v>
       </c>
       <c r="BA29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="246"/>
         <v>9.1060754497309424E-2</v>
       </c>
       <c r="BB29" s="9">
-        <f t="shared" si="234"/>
-        <v>8.3062142367575226E-2</v>
+        <f t="shared" si="246"/>
+        <v>8.1374534112235997E-2</v>
       </c>
       <c r="BC29" s="9">
-        <f t="shared" si="234"/>
-        <v>7.9504021747648299E-2</v>
+        <f t="shared" si="246"/>
+        <v>7.7287960368258801E-2</v>
       </c>
       <c r="BD29" s="9">
-        <f t="shared" si="234"/>
-        <v>7.7211548804448568E-2</v>
+        <f t="shared" si="246"/>
+        <v>7.5040038734278725E-2</v>
       </c>
       <c r="BE29" s="9">
-        <f t="shared" si="234"/>
-        <v>7.554324224112921E-2</v>
+        <f t="shared" si="246"/>
+        <v>7.3403851415257404E-2</v>
       </c>
       <c r="BF29" s="9">
-        <f t="shared" si="234"/>
-        <v>7.4479409899195312E-2</v>
+        <f t="shared" si="246"/>
+        <v>7.2359389926130321E-2</v>
       </c>
       <c r="BG29" s="9">
-        <f t="shared" ref="BG29:BI29" si="237">BG11/BG$5</f>
-        <v>7.4010280547149795E-2</v>
+        <f t="shared" ref="BG29:BI29" si="249">BG11/BG$5</f>
+        <v>7.1896567212452411E-2</v>
       </c>
       <c r="BH29" s="9">
-        <f t="shared" si="237"/>
-        <v>7.3540044135642579E-2</v>
+        <f t="shared" si="249"/>
+        <v>7.1432848823071021E-2</v>
       </c>
       <c r="BI29" s="9">
-        <f t="shared" si="237"/>
-        <v>7.3663605698971749E-2</v>
+        <f t="shared" si="249"/>
+        <v>7.1549425227242808E-2</v>
       </c>
       <c r="BJ29" s="9">
-        <f t="shared" ref="BJ29:BK29" si="238">BJ11/BJ$5</f>
-        <v>7.3786365684959415E-2</v>
+        <f t="shared" ref="BJ29:BK29" si="250">BJ11/BJ$5</f>
+        <v>7.1665234253888488E-2</v>
       </c>
       <c r="BK29" s="9">
-        <f t="shared" si="238"/>
-        <v>7.3908325968345956E-2</v>
+        <f t="shared" si="250"/>
+        <v>7.178027788993574E-2</v>
       </c>
       <c r="BM29" t="s">
         <v>94</v>
@@ -7800,209 +7869,212 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="209"/>
         <v>0.11578947368421044</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" ref="H30" si="239">H12/D12-1</f>
+        <f t="shared" ref="H30" si="251">H12/D12-1</f>
         <v>0.26166097838452784</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" ref="I30" si="240">I12/E12-1</f>
+        <f t="shared" ref="I30" si="252">I12/E12-1</f>
         <v>4.991680532445919E-3</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" ref="J30" si="241">J12/F12-1</f>
+        <f t="shared" ref="J30" si="253">J12/F12-1</f>
         <v>-6.199261992619931E-2</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" ref="K30" si="242">K12/G12-1</f>
+        <f t="shared" ref="K30" si="254">K12/G12-1</f>
         <v>-1.4579759862778707E-2</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" ref="L30" si="243">L12/H12-1</f>
+        <f t="shared" ref="L30" si="255">L12/H12-1</f>
         <v>2.0739404869251521E-2</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" ref="M30" si="244">M12/I12-1</f>
+        <f t="shared" ref="M30" si="256">M12/I12-1</f>
         <v>-2.4006622516556275E-2</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" ref="N30" si="245">N12/J12-1</f>
+        <f t="shared" ref="N30" si="257">N12/J12-1</f>
         <v>0.12116443745082606</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" ref="O30" si="246">O12/K12-1</f>
+        <f t="shared" ref="O30" si="258">O12/K12-1</f>
         <v>-7.6588337684943442E-2</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" ref="P30" si="247">P12/L12-1</f>
+        <f t="shared" ref="P30" si="259">P12/L12-1</f>
         <v>-9.7173144876324669E-3</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" ref="Q30" si="248">Q12/M12-1</f>
+        <f t="shared" ref="Q30" si="260">Q12/M12-1</f>
         <v>7.9728583545377374E-2</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" ref="R30" si="249">R12/N12-1</f>
+        <f t="shared" ref="R30" si="261">R12/N12-1</f>
         <v>0.16210526315789475</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" ref="S30" si="250">S12/O12-1</f>
+        <f t="shared" ref="S30" si="262">S12/O12-1</f>
         <v>5.4665409990575009E-2</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" ref="T30" si="251">T12/P12-1</f>
+        <f t="shared" ref="T30" si="263">T12/P12-1</f>
         <v>1.605709188224802E-2</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" ref="U30" si="252">U12/Q12-1</f>
+        <f t="shared" ref="U30" si="264">U12/Q12-1</f>
         <v>4.2419481539670123E-2</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" ref="V30" si="253">V12/R12-1</f>
+        <f t="shared" ref="V30" si="265">V12/R12-1</f>
         <v>-8.0917874396135292E-2</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" ref="W30:X30" si="254">W12/S12-1</f>
+        <f t="shared" ref="W30:X30" si="266">W12/S12-1</f>
         <v>0.15013404825737275</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="254"/>
+        <f t="shared" si="266"/>
         <v>0.21510096575943805</v>
       </c>
       <c r="Y30" s="9">
-        <f t="shared" ref="Y30" si="255">Y12/U12-1</f>
+        <f t="shared" ref="Y30" si="267">Y12/U12-1</f>
         <v>0.1152976639035419</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" ref="Z30" si="256">Z12/V12-1</f>
+        <f t="shared" ref="Z30" si="268">Z12/V12-1</f>
         <v>0.14914586070959257</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" ref="AA30" si="257">AA12/W12-1</f>
+        <f t="shared" ref="AA30" si="269">AA12/W12-1</f>
         <v>8.6247086247086324E-2</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" ref="AB30:AL30" si="258">AB12/X12-1</f>
+        <f t="shared" ref="AB30:AM30" si="270">AB12/X12-1</f>
         <v>0.68858381502890165</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="258"/>
+        <f t="shared" si="270"/>
         <v>0.11013513513513518</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="258"/>
+        <f t="shared" si="270"/>
         <v>0.25614636935391655</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="258"/>
+        <f t="shared" si="270"/>
         <v>5.4363376251788331E-2</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="258"/>
+        <f t="shared" si="270"/>
         <v>-0.36927685066324345</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="258"/>
+        <f t="shared" si="270"/>
         <v>0.20328667072428486</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="258"/>
+        <f t="shared" si="270"/>
         <v>2.2303140646335873E-2</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="258"/>
+        <f t="shared" si="270"/>
         <v>0.1350067842605156</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="258"/>
+        <f t="shared" si="270"/>
         <v>0.23677069199457268</v>
       </c>
       <c r="AK30" s="9">
-        <f t="shared" si="258"/>
+        <f t="shared" si="270"/>
         <v>-0.12139605462822456</v>
       </c>
       <c r="AL30" s="9">
-        <f t="shared" si="258"/>
+        <f t="shared" si="270"/>
         <v>-0.1139804096170971</v>
       </c>
-      <c r="AM30" s="9"/>
+      <c r="AM30" s="9">
+        <f t="shared" si="270"/>
+        <v>7.9497907949790836E-2</v>
+      </c>
       <c r="AN30" s="9"/>
       <c r="AO30" s="9"/>
       <c r="AP30" s="9"/>
       <c r="AQ30" s="9"/>
       <c r="AS30" s="9"/>
       <c r="AT30" s="9">
-        <f t="shared" ref="AT30:BI30" si="259">AT12/AS12-1</f>
+        <f t="shared" ref="AT30:BI30" si="271">AT12/AS12-1</f>
         <v>6.0923900914974238E-2</v>
       </c>
       <c r="AU30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>2.7555742532604066E-2</v>
       </c>
       <c r="AV30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>4.6264073694984642E-2</v>
       </c>
       <c r="AW30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>-7.8262570925458075E-4</v>
       </c>
       <c r="AX30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>0.15527707068729191</v>
       </c>
       <c r="AY30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>0.28389830508474567</v>
       </c>
       <c r="AZ30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>-5.3333333333333344E-2</v>
       </c>
       <c r="BA30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>7.2514293682890418E-3</v>
       </c>
       <c r="BB30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BC30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BD30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BE30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BG30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI30" s="9">
-        <f t="shared" si="259"/>
+        <f t="shared" si="271"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BJ30" s="9">
-        <f t="shared" ref="BJ30" si="260">BJ12/BI12-1</f>
+        <f t="shared" ref="BJ30" si="272">BJ12/BI12-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK30" s="9">
-        <f t="shared" ref="BK30" si="261">BK12/BJ12-1</f>
+        <f t="shared" ref="BK30" si="273">BK12/BJ12-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -8011,19 +8083,19 @@
         <v>78</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="262">C16/C15</f>
+        <f t="shared" ref="C31:F31" si="274">C16/C15</f>
         <v>0.17691017233490924</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="262"/>
+        <f t="shared" si="274"/>
         <v>0.21877337322363499</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="262"/>
+        <f t="shared" si="274"/>
         <v>0.22667042571186918</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="262"/>
+        <f t="shared" si="274"/>
         <v>-1.3948228198039708E-2</v>
       </c>
       <c r="G31" s="9">
@@ -8035,204 +8107,207 @@
         <v>0.18224451957683499</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" ref="I31:V31" si="263">I16/I15</f>
+        <f t="shared" ref="I31:V31" si="275">I16/I15</f>
         <v>0.14084018053466035</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.16919475655430713</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.13667938557871051</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.18921521425132404</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.15992752241083349</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>-4.6919657033979038E-2</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.15828472331704241</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.17294994675186368</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.16281242700303666</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.16540008940545373</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.13836516993301909</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.15673228990565524</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.10321420283128337</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="263"/>
+        <f t="shared" si="275"/>
         <v>0.15186807523834064</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" ref="W31:X31" si="264">W16/W15</f>
+        <f t="shared" ref="W31:X31" si="276">W16/W15</f>
         <v>9.2574546871954783E-4</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" si="264"/>
+        <f t="shared" si="276"/>
         <v>0.17567694181579688</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" ref="Y31" si="265">Y16/Y15</f>
+        <f t="shared" ref="Y31" si="277">Y16/Y15</f>
         <v>0.17147102526002972</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" ref="Z31" si="266">Z16/Z15</f>
+        <f t="shared" ref="Z31" si="278">Z16/Z15</f>
         <v>0.18289647093278666</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" ref="AA31" si="267">AA16/AA15</f>
+        <f t="shared" ref="AA31" si="279">AA16/AA15</f>
         <v>0.18616725384758021</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" ref="AB31:AC31" si="268">AB16/AB15</f>
+        <f t="shared" ref="AB31:AC31" si="280">AB16/AB15</f>
         <v>0.19243817296818919</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="268"/>
+        <f t="shared" si="280"/>
         <v>0.19291668504388479</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" ref="AD31:AE31" si="269">AD16/AD15</f>
+        <f t="shared" ref="AD31:AE31" si="281">AD16/AD15</f>
         <v>0.18789177821814212</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="269"/>
+        <f t="shared" si="281"/>
         <v>0.18300102624248643</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" ref="AF31:AG31" si="270">AF16/AF15</f>
+        <f t="shared" ref="AF31:AG31" si="282">AF16/AF15</f>
         <v>0.18300102624248643</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="282"/>
         <v>0.17552589911784663</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" ref="AH31:AI31" si="271">AH16/AH15</f>
+        <f t="shared" ref="AH31:AI31" si="283">AH16/AH15</f>
         <v>0.1913394495412844</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="283"/>
         <v>0.18507383791998414</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" ref="AJ31:AL31" si="272">AJ16/AJ15</f>
+        <f t="shared" ref="AJ31:AL31" si="284">AJ16/AJ15</f>
         <v>0.17902264600715137</v>
       </c>
       <c r="AK31" s="9">
-        <f t="shared" si="272"/>
+        <f t="shared" si="284"/>
         <v>0.17697676642126398</v>
       </c>
       <c r="AL31" s="9">
-        <f t="shared" si="272"/>
+        <f t="shared" si="284"/>
         <v>0.16504169732646554</v>
       </c>
-      <c r="AM31" s="9"/>
+      <c r="AM31" s="9">
+        <f t="shared" ref="AM31" si="285">AM16/AM15</f>
+        <v>0.19107314655549401</v>
+      </c>
       <c r="AN31" s="9"/>
       <c r="AO31" s="9"/>
       <c r="AP31" s="9"/>
       <c r="AQ31" s="9"/>
       <c r="AS31" s="9">
-        <f t="shared" ref="AS31:AU31" si="273">AS16/AS15</f>
+        <f t="shared" ref="AS31:AU31" si="286">AS16/AS15</f>
         <v>0.14889811346225237</v>
       </c>
       <c r="AT31" s="9">
-        <f t="shared" si="273"/>
+        <f t="shared" si="286"/>
         <v>0.16732466962768</v>
       </c>
       <c r="AU31" s="9">
-        <f t="shared" si="273"/>
+        <f t="shared" si="286"/>
         <v>0.10181285478850027</v>
       </c>
       <c r="AV31" s="9">
-        <f t="shared" ref="AV31:BF31" si="274">AV16/AV15</f>
+        <f t="shared" ref="AV31:BF31" si="287">AV16/AV15</f>
         <v>0.16507655177615205</v>
       </c>
       <c r="AW31" s="9">
-        <f t="shared" si="274"/>
+        <f t="shared" si="287"/>
         <v>0.13826615285083402</v>
       </c>
       <c r="AX31" s="9">
-        <f t="shared" ref="AX31" si="275">AX16/AX15</f>
+        <f t="shared" ref="AX31" si="288">AX16/AX15</f>
         <v>0.132990902152713</v>
       </c>
       <c r="AY31" s="9">
-        <f t="shared" si="274"/>
+        <f t="shared" si="287"/>
         <v>0.18978625253328257</v>
       </c>
       <c r="AZ31" s="9">
-        <f t="shared" ref="AZ31" si="276">AZ16/AZ15</f>
+        <f t="shared" ref="AZ31" si="289">AZ16/AZ15</f>
         <v>0.18326810898619214</v>
       </c>
       <c r="BA31" s="9">
-        <f t="shared" si="274"/>
+        <f t="shared" si="287"/>
         <v>0.17629644009803683</v>
       </c>
       <c r="BB31" s="9">
-        <f t="shared" si="274"/>
+        <f t="shared" si="287"/>
         <v>0.19</v>
       </c>
       <c r="BC31" s="9">
-        <f t="shared" si="274"/>
+        <f t="shared" si="287"/>
         <v>0.19</v>
       </c>
       <c r="BD31" s="9">
-        <f t="shared" si="274"/>
+        <f t="shared" si="287"/>
         <v>0.19</v>
       </c>
       <c r="BE31" s="9">
-        <f t="shared" si="274"/>
+        <f t="shared" si="287"/>
         <v>0.19</v>
       </c>
       <c r="BF31" s="9">
-        <f t="shared" si="274"/>
-        <v>0.18999999999999997</v>
+        <f t="shared" si="287"/>
+        <v>0.19</v>
       </c>
       <c r="BG31" s="9">
-        <f t="shared" ref="BG31:BI31" si="277">BG16/BG15</f>
-        <v>0.18999999999999997</v>
+        <f t="shared" ref="BG31:BI31" si="290">BG16/BG15</f>
+        <v>0.19</v>
       </c>
       <c r="BH31" s="9">
-        <f t="shared" si="277"/>
+        <f t="shared" si="290"/>
         <v>0.19</v>
       </c>
       <c r="BI31" s="9">
-        <f t="shared" si="277"/>
-        <v>0.19000000000000003</v>
+        <f t="shared" si="290"/>
+        <v>0.19</v>
       </c>
       <c r="BJ31" s="9">
-        <f t="shared" ref="BJ31:BK31" si="278">BJ16/BJ15</f>
+        <f t="shared" ref="BJ31:BK31" si="291">BJ16/BJ15</f>
         <v>0.19</v>
       </c>
       <c r="BK31" s="9">
-        <f t="shared" si="278"/>
+        <f t="shared" si="291"/>
         <v>0.19</v>
       </c>
     </row>
@@ -8468,27 +8543,27 @@
       </c>
       <c r="Y43" s="25"/>
       <c r="Z43" s="25">
-        <f t="shared" ref="Z43:AE43" si="279">SUM(Z34:Z42)</f>
+        <f t="shared" ref="Z43:AE43" si="292">SUM(Z34:Z42)</f>
         <v>364840</v>
       </c>
       <c r="AA43" s="25">
-        <f t="shared" si="279"/>
+        <f t="shared" si="292"/>
         <v>359784</v>
       </c>
       <c r="AB43" s="25">
-        <f t="shared" si="279"/>
+        <f t="shared" si="292"/>
         <v>364552</v>
       </c>
       <c r="AC43" s="25">
-        <f t="shared" si="279"/>
+        <f t="shared" si="292"/>
         <v>380088</v>
       </c>
       <c r="AD43" s="25">
-        <f t="shared" si="279"/>
+        <f t="shared" si="292"/>
         <v>411976</v>
       </c>
       <c r="AE43" s="25">
-        <f t="shared" si="279"/>
+        <f t="shared" si="292"/>
         <v>445785</v>
       </c>
     </row>
@@ -8696,27 +8771,27 @@
       </c>
       <c r="Y52" s="25"/>
       <c r="Z52" s="25">
-        <f t="shared" ref="Z52:AE52" si="280">SUM(Z45:Z51)</f>
+        <f t="shared" ref="Z52:AE52" si="293">SUM(Z45:Z51)</f>
         <v>198298</v>
       </c>
       <c r="AA52" s="25">
-        <f t="shared" si="280"/>
+        <f t="shared" si="293"/>
         <v>186308</v>
       </c>
       <c r="AB52" s="25">
-        <f t="shared" si="280"/>
+        <f t="shared" si="293"/>
         <v>181416</v>
       </c>
       <c r="AC52" s="25">
-        <f t="shared" si="280"/>
+        <f t="shared" si="293"/>
         <v>185405</v>
       </c>
       <c r="AD52" s="25">
-        <f t="shared" si="280"/>
+        <f t="shared" si="293"/>
         <v>205753</v>
       </c>
       <c r="AE52" s="25">
-        <f t="shared" si="280"/>
+        <f t="shared" si="293"/>
         <v>225071</v>
       </c>
     </row>
@@ -8752,27 +8827,27 @@
       </c>
       <c r="Y54" s="25"/>
       <c r="Z54" s="25">
-        <f t="shared" ref="Z54:AE54" si="281">Z52+Z53</f>
+        <f t="shared" ref="Z54:AE54" si="294">Z52+Z53</f>
         <v>364840</v>
       </c>
       <c r="AA54" s="25">
-        <f t="shared" si="281"/>
+        <f t="shared" si="294"/>
         <v>359874</v>
       </c>
       <c r="AB54" s="25">
-        <f t="shared" si="281"/>
+        <f t="shared" si="294"/>
         <v>364552</v>
       </c>
       <c r="AC54" s="25">
-        <f t="shared" si="281"/>
+        <f t="shared" si="294"/>
         <v>380088</v>
       </c>
       <c r="AD54" s="25">
-        <f t="shared" si="281"/>
+        <f t="shared" si="294"/>
         <v>411976</v>
       </c>
       <c r="AE54" s="25">
-        <f t="shared" si="281"/>
+        <f t="shared" si="294"/>
         <v>445785</v>
       </c>
     </row>

--- a/Financial Analysis/MSFT.xlsx
+++ b/Financial Analysis/MSFT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6452824F-285E-4AE2-8267-55AFF8FF603A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA4DF48-D52F-4EE8-BFF0-BEA2ED0D035D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{61E89E8F-0FF3-456B-A54B-AD32D916470B}"/>
   </bookViews>
@@ -491,9 +491,6 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
-  </si>
-  <si>
     <t>Q126</t>
   </si>
   <si>
@@ -504,6 +501,9 @@
   </si>
   <si>
     <t>Q426</t>
+  </si>
+  <si>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -748,14 +748,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
@@ -772,7 +772,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28620720" y="0"/>
+          <a:off x="29337000" y="0"/>
           <a:ext cx="0" cy="6088380"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1188,17 +1188,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="19">
-        <v>527.70000000000005</v>
+        <v>432.76</v>
       </c>
       <c r="E3" s="2">
-        <v>45960</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45960</v>
+        <v>46052</v>
       </c>
       <c r="G3" s="2">
-        <v>46057</v>
+        <v>46140</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>43</v>
@@ -1219,11 +1219,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>7432.4</f>
-        <v>7432.4</v>
+        <f>7425.6</f>
+        <v>7425.6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F4" s="1"/>
       <c r="I4" s="13"/>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>3922077.48</v>
+        <v>3213502.656</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>3855258.48</v>
+        <v>3146683.656</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1645,16 +1645,16 @@
         <v>134</v>
       </c>
       <c r="AM2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN2" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="AN2" s="3" t="s">
+      <c r="AO2" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="AO2" s="3" t="s">
+      <c r="AP2" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="AP2" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="AQ2" s="3"/>
       <c r="AS2">
@@ -1830,7 +1830,9 @@
       <c r="AM3" s="4">
         <v>15922</v>
       </c>
-      <c r="AN3" s="4"/>
+      <c r="AN3" s="4">
+        <v>16451</v>
+      </c>
       <c r="AO3" s="4"/>
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
@@ -2026,7 +2028,9 @@
       <c r="AM4" s="4">
         <v>61751</v>
       </c>
-      <c r="AN4" s="4"/>
+      <c r="AN4" s="4">
+        <v>64822</v>
+      </c>
       <c r="AO4" s="4"/>
       <c r="AP4" s="4"/>
       <c r="AQ4" s="4"/>
@@ -2256,10 +2260,13 @@
         <v>76441</v>
       </c>
       <c r="AM5" s="7">
-        <f t="shared" ref="AM5" si="11">AM3+AM4</f>
+        <f t="shared" ref="AM5:AN5" si="11">AM3+AM4</f>
         <v>77673</v>
       </c>
-      <c r="AN5" s="7"/>
+      <c r="AN5" s="7">
+        <f t="shared" si="11"/>
+        <v>81273</v>
+      </c>
       <c r="AO5" s="7"/>
       <c r="AP5" s="7"/>
       <c r="AQ5" s="7"/>
@@ -2455,7 +2462,9 @@
       <c r="AM6" s="5">
         <v>2922</v>
       </c>
-      <c r="AN6" s="5"/>
+      <c r="AN6" s="5">
+        <v>3505</v>
+      </c>
       <c r="AO6" s="5"/>
       <c r="AP6" s="5"/>
       <c r="AQ6" s="5"/>
@@ -2500,40 +2509,40 @@
         <v>14854.6558</v>
       </c>
       <c r="BC6" s="5">
-        <f t="shared" si="18"/>
-        <v>15003.202358</v>
+        <f>BC3*0.22</f>
+        <v>14350.889212</v>
       </c>
       <c r="BD6" s="5">
-        <f t="shared" si="18"/>
-        <v>15153.23438158</v>
+        <f t="shared" ref="BD6:BK6" si="19">BD3*0.22</f>
+        <v>14494.39810412</v>
       </c>
       <c r="BE6" s="5">
-        <f t="shared" si="18"/>
-        <v>15304.766725395799</v>
+        <f t="shared" si="19"/>
+        <v>14639.342085161199</v>
       </c>
       <c r="BF6" s="5">
-        <f t="shared" si="18"/>
-        <v>15457.814392649758</v>
+        <f t="shared" si="19"/>
+        <v>14785.735506012812</v>
       </c>
       <c r="BG6" s="5">
-        <f t="shared" si="18"/>
-        <v>15612.392536576253</v>
+        <f t="shared" si="19"/>
+        <v>14933.592861072939</v>
       </c>
       <c r="BH6" s="5">
-        <f t="shared" si="18"/>
-        <v>15768.516461942016</v>
+        <f t="shared" si="19"/>
+        <v>15082.928789683667</v>
       </c>
       <c r="BI6" s="5">
-        <f t="shared" si="18"/>
-        <v>15926.201626561437</v>
+        <f t="shared" si="19"/>
+        <v>15233.758077580504</v>
       </c>
       <c r="BJ6" s="5">
-        <f t="shared" ref="BJ6:BK6" si="19">BJ3*0.23</f>
-        <v>16085.463642827048</v>
+        <f t="shared" si="19"/>
+        <v>15386.095658356307</v>
       </c>
       <c r="BK6" s="5">
         <f t="shared" si="19"/>
-        <v>16246.318279255318</v>
+        <v>15539.956614939869</v>
       </c>
     </row>
     <row r="7" spans="2:63" x14ac:dyDescent="0.3">
@@ -2651,7 +2660,9 @@
       <c r="AM7" s="5">
         <v>21121</v>
       </c>
-      <c r="AN7" s="5"/>
+      <c r="AN7" s="5">
+        <v>22473</v>
+      </c>
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
       <c r="AQ7" s="5"/>
@@ -2692,44 +2703,44 @@
         <v>74330</v>
       </c>
       <c r="BB7" s="5">
-        <f>BB4*0.33</f>
-        <v>84802.753199999992</v>
+        <f>BB4*0.34</f>
+        <v>87372.533599999995</v>
       </c>
       <c r="BC7" s="5">
-        <f t="shared" ref="BC7:BK7" si="20">BC4*0.33</f>
-        <v>92435.000988</v>
+        <f t="shared" ref="BC7:BK7" si="20">BC4*0.34</f>
+        <v>95236.061624000009</v>
       </c>
       <c r="BD7" s="5">
         <f t="shared" si="20"/>
-        <v>97981.101047279997</v>
+        <v>100950.22532144</v>
       </c>
       <c r="BE7" s="5">
         <f t="shared" si="20"/>
-        <v>102880.15609964401</v>
+        <v>105997.73658751202</v>
       </c>
       <c r="BF7" s="5">
         <f t="shared" si="20"/>
-        <v>106995.36234362978</v>
+        <v>110237.6460510125</v>
       </c>
       <c r="BG7" s="5">
         <f t="shared" si="20"/>
-        <v>110205.22321393866</v>
+        <v>113544.77543254287</v>
       </c>
       <c r="BH7" s="5">
         <f t="shared" si="20"/>
-        <v>113511.37991035685</v>
+        <v>116951.11869551917</v>
       </c>
       <c r="BI7" s="5">
         <f t="shared" si="20"/>
-        <v>115781.60750856397</v>
+        <v>119290.14106942956</v>
       </c>
       <c r="BJ7" s="5">
         <f t="shared" si="20"/>
-        <v>118097.23965873527</v>
+        <v>121675.94389081816</v>
       </c>
       <c r="BK7" s="5">
         <f t="shared" si="20"/>
-        <v>120459.18445190997</v>
+        <v>124109.46276863452</v>
       </c>
     </row>
     <row r="8" spans="2:63" x14ac:dyDescent="0.3">
@@ -2881,10 +2892,13 @@
         <v>24014</v>
       </c>
       <c r="AM8" s="5">
-        <f t="shared" ref="AM8" si="32">AM6+AM7</f>
+        <f t="shared" ref="AM8:AN8" si="32">AM6+AM7</f>
         <v>24043</v>
       </c>
-      <c r="AN8" s="5"/>
+      <c r="AN8" s="5">
+        <f t="shared" si="32"/>
+        <v>25978</v>
+      </c>
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
       <c r="AQ8" s="5"/>
@@ -2926,43 +2940,43 @@
       </c>
       <c r="BB8" s="5">
         <f t="shared" si="34"/>
-        <v>99657.408999999985</v>
+        <v>102227.1894</v>
       </c>
       <c r="BC8" s="5">
         <f t="shared" si="34"/>
-        <v>107438.20334599999</v>
+        <v>109586.950836</v>
       </c>
       <c r="BD8" s="5">
         <f t="shared" si="34"/>
-        <v>113134.33542885999</v>
+        <v>115444.62342556</v>
       </c>
       <c r="BE8" s="5">
         <f t="shared" si="34"/>
-        <v>118184.9228250398</v>
+        <v>120637.07867267322</v>
       </c>
       <c r="BF8" s="5">
         <f t="shared" si="34"/>
-        <v>122453.17673627954</v>
+        <v>125023.38155702532</v>
       </c>
       <c r="BG8" s="5">
         <f t="shared" si="34"/>
-        <v>125817.61575051492</v>
+        <v>128478.36829361581</v>
       </c>
       <c r="BH8" s="5">
         <f t="shared" si="34"/>
-        <v>129279.89637229886</v>
+        <v>132034.04748520284</v>
       </c>
       <c r="BI8" s="5">
         <f t="shared" si="34"/>
-        <v>131707.80913512543</v>
+        <v>134523.89914701006</v>
       </c>
       <c r="BJ8" s="5">
         <f t="shared" ref="BJ8:BK8" si="35">BJ6+BJ7</f>
-        <v>134182.70330156232</v>
+        <v>137062.03954917446</v>
       </c>
       <c r="BK8" s="5">
         <f t="shared" si="35"/>
-        <v>136705.5027311653</v>
+        <v>139649.41938357439</v>
       </c>
     </row>
     <row r="9" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3114,10 +3128,13 @@
         <v>52427</v>
       </c>
       <c r="AM9" s="7">
-        <f t="shared" ref="AM9" si="47">AM5-AM8</f>
+        <f t="shared" ref="AM9:AN9" si="47">AM5-AM8</f>
         <v>53630</v>
       </c>
-      <c r="AN9" s="7"/>
+      <c r="AN9" s="7">
+        <f t="shared" si="47"/>
+        <v>55295</v>
+      </c>
       <c r="AO9" s="7"/>
       <c r="AP9" s="7"/>
       <c r="AQ9" s="7"/>
@@ -3159,43 +3176,43 @@
       </c>
       <c r="BB9" s="7">
         <f t="shared" si="49"/>
-        <v>221906.09100000001</v>
+        <v>219336.3106</v>
       </c>
       <c r="BC9" s="7">
         <f t="shared" si="49"/>
-        <v>237899.17485399998</v>
+        <v>235750.42736399997</v>
       </c>
       <c r="BD9" s="7">
         <f t="shared" si="49"/>
-        <v>249661.71973314002</v>
+        <v>247351.43173643999</v>
       </c>
       <c r="BE9" s="7">
         <f t="shared" si="49"/>
-        <v>260115.5899852202</v>
+        <v>257663.4341375868</v>
       </c>
       <c r="BF9" s="7">
         <f t="shared" si="49"/>
-        <v>268983.08266568708</v>
+        <v>266412.87784494134</v>
       </c>
       <c r="BG9" s="7">
         <f t="shared" si="49"/>
-        <v>276017.57366023684</v>
+        <v>273356.82111713593</v>
       </c>
       <c r="BH9" s="7">
         <f t="shared" si="49"/>
-        <v>283252.74936976878</v>
+        <v>280498.59825686482</v>
       </c>
       <c r="BI9" s="7">
         <f t="shared" si="49"/>
-        <v>288389.90184952528</v>
+        <v>285573.81183764065</v>
       </c>
       <c r="BJ9" s="7">
         <f t="shared" ref="BJ9:BK9" si="50">BJ5-BJ8</f>
-        <v>293624.51835380052</v>
+        <v>290745.18210618838</v>
       </c>
       <c r="BK9" s="7">
         <f t="shared" si="50"/>
-        <v>298958.49537283403</v>
+        <v>296014.57872042491</v>
       </c>
     </row>
     <row r="10" spans="2:63" x14ac:dyDescent="0.3">
@@ -3313,7 +3330,9 @@
       <c r="AM10" s="5">
         <v>8146</v>
       </c>
-      <c r="AN10" s="5"/>
+      <c r="AN10" s="5">
+        <v>8504</v>
+      </c>
       <c r="AO10" s="5"/>
       <c r="AP10" s="5"/>
       <c r="AQ10" s="5"/>
@@ -3509,7 +3528,9 @@
       <c r="AM11" s="5">
         <v>5717</v>
       </c>
-      <c r="AN11" s="5"/>
+      <c r="AN11" s="5">
+        <v>6584</v>
+      </c>
       <c r="AO11" s="5"/>
       <c r="AP11" s="5"/>
       <c r="AQ11" s="5"/>
@@ -3705,7 +3726,9 @@
       <c r="AM12" s="5">
         <v>1806</v>
       </c>
-      <c r="AN12" s="5"/>
+      <c r="AN12" s="5">
+        <v>1932</v>
+      </c>
       <c r="AO12" s="5"/>
       <c r="AP12" s="5"/>
       <c r="AQ12" s="5"/>
@@ -3746,44 +3769,44 @@
         <v>7223</v>
       </c>
       <c r="BB12" s="5">
-        <f>BA12*1.05</f>
-        <v>7584.1500000000005</v>
+        <f>BA12*1.06</f>
+        <v>7656.38</v>
       </c>
       <c r="BC12" s="5">
         <f>BB12*1.04</f>
-        <v>7887.5160000000005</v>
+        <v>7962.6352000000006</v>
       </c>
       <c r="BD12" s="5">
         <f>BC12*1.03</f>
-        <v>8124.1414800000011</v>
+        <v>8201.5142560000004</v>
       </c>
       <c r="BE12" s="5">
         <f>BD12*1.02</f>
-        <v>8286.6243096000017</v>
+        <v>8365.5445411199998</v>
       </c>
       <c r="BF12" s="5">
         <f>BE12*1.02</f>
-        <v>8452.3567957920022</v>
+        <v>8532.8554319424002</v>
       </c>
       <c r="BG12" s="5">
         <f>BF12*1.01</f>
-        <v>8536.8803637499223</v>
+        <v>8618.1839862618235</v>
       </c>
       <c r="BH12" s="5">
         <f t="shared" ref="BH12:BK12" si="57">BG12*1.01</f>
-        <v>8622.249167387421</v>
+        <v>8704.3658261244418</v>
       </c>
       <c r="BI12" s="5">
         <f t="shared" si="57"/>
-        <v>8708.4716590612952</v>
+        <v>8791.4094843856856</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="57"/>
-        <v>8795.5563756519077</v>
+        <v>8879.3235792295418</v>
       </c>
       <c r="BK12" s="5">
         <f t="shared" si="57"/>
-        <v>8883.5119394084268</v>
+        <v>8968.1168150218382</v>
       </c>
     </row>
     <row r="13" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3935,10 +3958,13 @@
         <v>34323</v>
       </c>
       <c r="AM13" s="7">
-        <f t="shared" ref="AM13" si="68">AM9-AM10-AM11-AM12</f>
+        <f t="shared" ref="AM13:AN13" si="68">AM9-AM10-AM11-AM12</f>
         <v>37961</v>
       </c>
-      <c r="AN13" s="7"/>
+      <c r="AN13" s="7">
+        <f t="shared" si="68"/>
+        <v>38275</v>
+      </c>
       <c r="AO13" s="7"/>
       <c r="AP13" s="7"/>
       <c r="AQ13" s="7"/>
@@ -3980,43 +4006,43 @@
       </c>
       <c r="BB13" s="7">
         <f t="shared" si="69"/>
-        <v>153717.58100000003</v>
+        <v>151075.57059999998</v>
       </c>
       <c r="BC13" s="7">
         <f t="shared" si="69"/>
-        <v>167506.46605399996</v>
+        <v>165282.59936399999</v>
       </c>
       <c r="BD13" s="7">
         <f t="shared" si="69"/>
-        <v>177782.28159714004</v>
+        <v>175394.62082444</v>
       </c>
       <c r="BE13" s="7">
         <f t="shared" si="69"/>
-        <v>187163.87375274018</v>
+        <v>184632.79767358676</v>
       </c>
       <c r="BF13" s="7">
         <f t="shared" si="69"/>
-        <v>194941.29588145987</v>
+        <v>192290.59242456371</v>
       </c>
       <c r="BG13" s="7">
         <f t="shared" ref="BG13:BI13" si="72">BG9-BG10-BG11-BG12</f>
-        <v>200952.12811891444</v>
+        <v>198210.07195330161</v>
       </c>
       <c r="BH13" s="7">
         <f t="shared" si="72"/>
-        <v>207147.74366599513</v>
+        <v>204311.47589435417</v>
       </c>
       <c r="BI13" s="7">
         <f t="shared" si="72"/>
-        <v>211229.16226753517</v>
+        <v>208330.13443032614</v>
       </c>
       <c r="BJ13" s="7">
         <f t="shared" ref="BJ13:BK13" si="73">BJ9-BJ10-BJ11-BJ12</f>
-        <v>215391.59387838817</v>
+        <v>212428.49042719841</v>
       </c>
       <c r="BK13" s="7">
         <f t="shared" si="73"/>
-        <v>219636.6526051132</v>
+        <v>216608.13107709066</v>
       </c>
     </row>
     <row r="14" spans="2:63" x14ac:dyDescent="0.3">
@@ -4135,7 +4161,9 @@
       <c r="AM14" s="5">
         <v>3660</v>
       </c>
-      <c r="AN14" s="5"/>
+      <c r="AN14" s="5">
+        <v>-9971</v>
+      </c>
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
       <c r="AQ14" s="5"/>
@@ -4365,10 +4393,13 @@
         <v>32616</v>
       </c>
       <c r="AM15" s="7">
-        <f t="shared" ref="AM15" si="87">AM13-AM14</f>
+        <f t="shared" ref="AM15:AN15" si="87">AM13-AM14</f>
         <v>34301</v>
       </c>
-      <c r="AN15" s="7"/>
+      <c r="AN15" s="7">
+        <f t="shared" si="87"/>
+        <v>48246</v>
+      </c>
       <c r="AO15" s="7"/>
       <c r="AP15" s="7"/>
       <c r="AQ15" s="7"/>
@@ -4410,43 +4441,43 @@
       </c>
       <c r="BB15" s="7">
         <f t="shared" si="88"/>
-        <v>148767.57100000003</v>
+        <v>146125.56059999997</v>
       </c>
       <c r="BC15" s="7">
         <f t="shared" si="88"/>
-        <v>162506.95595399995</v>
+        <v>160283.08926399998</v>
       </c>
       <c r="BD15" s="7">
         <f t="shared" si="88"/>
-        <v>172732.77639614005</v>
+        <v>170345.11562344001</v>
       </c>
       <c r="BE15" s="7">
         <f t="shared" si="88"/>
-        <v>182063.87349973019</v>
+        <v>179532.79742057677</v>
       </c>
       <c r="BF15" s="7">
         <f t="shared" si="88"/>
-        <v>189790.29562591977</v>
+        <v>187139.59216902361</v>
       </c>
       <c r="BG15" s="7">
         <f t="shared" ref="BG15:BI15" si="91">BG13-BG14</f>
-        <v>195749.61786081892</v>
+        <v>193007.5616952061</v>
       </c>
       <c r="BH15" s="7">
         <f t="shared" si="91"/>
-        <v>201893.20830531867</v>
+        <v>199056.9405336777</v>
       </c>
       <c r="BI15" s="7">
         <f t="shared" si="91"/>
-        <v>205922.08155325195</v>
+        <v>203023.05371604292</v>
       </c>
       <c r="BJ15" s="7">
         <f t="shared" ref="BJ15:BK15" si="92">BJ13-BJ14</f>
-        <v>210031.44235696213</v>
+        <v>207068.33890577237</v>
       </c>
       <c r="BK15" s="7">
         <f t="shared" si="92"/>
-        <v>214222.89956847287</v>
+        <v>211194.37804045033</v>
       </c>
     </row>
     <row r="16" spans="2:63" x14ac:dyDescent="0.3">
@@ -4565,7 +4596,9 @@
       <c r="AM16" s="5">
         <v>6554</v>
       </c>
-      <c r="AN16" s="5"/>
+      <c r="AN16" s="5">
+        <v>9788</v>
+      </c>
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
       <c r="AQ16" s="5"/>
@@ -4607,43 +4640,43 @@
       </c>
       <c r="BB16" s="5">
         <f t="shared" ref="BB16:BI16" si="93">BB15*0.19</f>
-        <v>28265.838490000006</v>
+        <v>27763.856513999996</v>
       </c>
       <c r="BC16" s="5">
         <f t="shared" si="93"/>
-        <v>30876.321631259991</v>
+        <v>30453.786960159996</v>
       </c>
       <c r="BD16" s="5">
         <f t="shared" si="93"/>
-        <v>32819.227515266612</v>
+        <v>32365.571968453602</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="93"/>
-        <v>34592.135964948735</v>
+        <v>34111.231509909587</v>
       </c>
       <c r="BF16" s="5">
         <f t="shared" si="93"/>
-        <v>36060.156168924754</v>
+        <v>35556.52251211449</v>
       </c>
       <c r="BG16" s="5">
         <f t="shared" si="93"/>
-        <v>37192.427393555598</v>
+        <v>36671.436722089158</v>
       </c>
       <c r="BH16" s="5">
         <f t="shared" si="93"/>
-        <v>38359.709578010545</v>
+        <v>37820.818701398763</v>
       </c>
       <c r="BI16" s="5">
         <f t="shared" si="93"/>
-        <v>39125.19549511787</v>
+        <v>38574.380206048154</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" ref="BJ16:BK16" si="94">BJ15*0.19</f>
-        <v>39905.974047822805</v>
+        <v>39342.984392096754</v>
       </c>
       <c r="BK16" s="5">
         <f t="shared" si="94"/>
-        <v>40702.350918009848</v>
+        <v>40126.931827685563</v>
       </c>
     </row>
     <row r="17" spans="2:184" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4795,10 +4828,13 @@
         <v>27233</v>
       </c>
       <c r="AM17" s="7">
-        <f t="shared" ref="AM17" si="106">AM15-AM16</f>
+        <f t="shared" ref="AM17:AN17" si="106">AM15-AM16</f>
         <v>27747</v>
       </c>
-      <c r="AN17" s="7"/>
+      <c r="AN17" s="7">
+        <f t="shared" si="106"/>
+        <v>38458</v>
+      </c>
       <c r="AO17" s="7"/>
       <c r="AP17" s="7"/>
       <c r="AQ17" s="7"/>
@@ -4840,527 +4876,527 @@
       </c>
       <c r="BB17" s="7">
         <f t="shared" si="107"/>
-        <v>120501.73251000002</v>
+        <v>118361.70408599997</v>
       </c>
       <c r="BC17" s="7">
         <f t="shared" si="107"/>
-        <v>131630.63432273996</v>
+        <v>129829.30230383998</v>
       </c>
       <c r="BD17" s="7">
         <f t="shared" si="107"/>
-        <v>139913.54888087342</v>
+        <v>137979.54365498642</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="107"/>
-        <v>147471.73753478145</v>
+        <v>145421.56591066718</v>
       </c>
       <c r="BF17" s="7">
         <f t="shared" si="107"/>
-        <v>153730.13945699501</v>
+        <v>151583.06965690912</v>
       </c>
       <c r="BG17" s="7">
         <f t="shared" ref="BG17:BI17" si="110">BG15-BG16</f>
-        <v>158557.19046726334</v>
+        <v>156336.12497311694</v>
       </c>
       <c r="BH17" s="7">
         <f t="shared" si="110"/>
-        <v>163533.49872730812</v>
+        <v>161236.12183227894</v>
       </c>
       <c r="BI17" s="7">
         <f t="shared" si="110"/>
-        <v>166796.88605813409</v>
+        <v>164448.67350999475</v>
       </c>
       <c r="BJ17" s="7">
         <f t="shared" ref="BJ17:BK17" si="111">BJ15-BJ16</f>
-        <v>170125.46830913931</v>
+        <v>167725.35451367561</v>
       </c>
       <c r="BK17" s="7">
         <f t="shared" si="111"/>
-        <v>173520.54865046302</v>
+        <v>171067.44621276477</v>
       </c>
       <c r="BL17" s="6">
         <f>BK17*(1+$BN$21)</f>
-        <v>171785.3431639584</v>
+        <v>169356.77175063713</v>
       </c>
       <c r="BM17" s="6">
         <f t="shared" ref="BM17:DX17" si="112">BL17*(1+$BN$21)</f>
-        <v>170067.48973231882</v>
+        <v>167663.20403313075</v>
       </c>
       <c r="BN17" s="6">
         <f t="shared" si="112"/>
-        <v>168366.81483499563</v>
+        <v>165986.57199279944</v>
       </c>
       <c r="BO17" s="6">
         <f t="shared" si="112"/>
-        <v>166683.14668664566</v>
+        <v>164326.70627287144</v>
       </c>
       <c r="BP17" s="6">
         <f t="shared" si="112"/>
-        <v>165016.31521977921</v>
+        <v>162683.43921014271</v>
       </c>
       <c r="BQ17" s="6">
         <f t="shared" si="112"/>
-        <v>163366.15206758142</v>
+        <v>161056.60481804129</v>
       </c>
       <c r="BR17" s="6">
         <f t="shared" si="112"/>
-        <v>161732.49054690561</v>
+        <v>159446.03876986087</v>
       </c>
       <c r="BS17" s="6">
         <f t="shared" si="112"/>
-        <v>160115.16564143656</v>
+        <v>157851.57838216226</v>
       </c>
       <c r="BT17" s="6">
         <f t="shared" si="112"/>
-        <v>158514.0139850222</v>
+        <v>156273.06259834065</v>
       </c>
       <c r="BU17" s="6">
         <f t="shared" si="112"/>
-        <v>156928.87384517197</v>
+        <v>154710.33197235723</v>
       </c>
       <c r="BV17" s="6">
         <f t="shared" si="112"/>
-        <v>155359.58510672025</v>
+        <v>153163.22865263367</v>
       </c>
       <c r="BW17" s="6">
         <f t="shared" si="112"/>
-        <v>153805.98925565305</v>
+        <v>151631.59636610732</v>
       </c>
       <c r="BX17" s="6">
         <f t="shared" si="112"/>
-        <v>152267.92936309651</v>
+        <v>150115.28040244625</v>
       </c>
       <c r="BY17" s="6">
         <f t="shared" si="112"/>
-        <v>150745.25006946555</v>
+        <v>148614.12759842179</v>
       </c>
       <c r="BZ17" s="6">
         <f t="shared" si="112"/>
-        <v>149237.79756877088</v>
+        <v>147127.98632243759</v>
       </c>
       <c r="CA17" s="6">
         <f t="shared" si="112"/>
-        <v>147745.41959308318</v>
+        <v>145656.70645921322</v>
       </c>
       <c r="CB17" s="6">
         <f t="shared" si="112"/>
-        <v>146267.96539715235</v>
+        <v>144200.1393946211</v>
       </c>
       <c r="CC17" s="6">
         <f t="shared" si="112"/>
-        <v>144805.28574318084</v>
+        <v>142758.1380006749</v>
       </c>
       <c r="CD17" s="6">
         <f t="shared" si="112"/>
-        <v>143357.23288574902</v>
+        <v>141330.55662066815</v>
       </c>
       <c r="CE17" s="6">
         <f t="shared" si="112"/>
-        <v>141923.66055689153</v>
+        <v>139917.25105446146</v>
       </c>
       <c r="CF17" s="6">
         <f t="shared" si="112"/>
-        <v>140504.42395132262</v>
+        <v>138518.07854391684</v>
       </c>
       <c r="CG17" s="6">
         <f t="shared" si="112"/>
-        <v>139099.37971180939</v>
+        <v>137132.89775847766</v>
       </c>
       <c r="CH17" s="6">
         <f t="shared" si="112"/>
-        <v>137708.38591469129</v>
+        <v>135761.56878089288</v>
       </c>
       <c r="CI17" s="6">
         <f t="shared" si="112"/>
-        <v>136331.30205554437</v>
+        <v>134403.95309308395</v>
       </c>
       <c r="CJ17" s="6">
         <f t="shared" si="112"/>
-        <v>134967.98903498892</v>
+        <v>133059.91356215312</v>
       </c>
       <c r="CK17" s="6">
         <f t="shared" si="112"/>
-        <v>133618.30914463903</v>
+        <v>131729.31442653158</v>
       </c>
       <c r="CL17" s="6">
         <f t="shared" si="112"/>
-        <v>132282.12605319265</v>
+        <v>130412.02128226626</v>
       </c>
       <c r="CM17" s="6">
         <f t="shared" si="112"/>
-        <v>130959.30479266073</v>
+        <v>129107.9010694436</v>
       </c>
       <c r="CN17" s="6">
         <f t="shared" si="112"/>
-        <v>129649.71174473412</v>
+        <v>127816.82205874917</v>
       </c>
       <c r="CO17" s="6">
         <f t="shared" si="112"/>
-        <v>128353.21462728677</v>
+        <v>126538.65383816167</v>
       </c>
       <c r="CP17" s="6">
         <f t="shared" si="112"/>
-        <v>127069.68248101389</v>
+        <v>125273.26729978005</v>
       </c>
       <c r="CQ17" s="6">
         <f t="shared" si="112"/>
-        <v>125798.98565620376</v>
+        <v>124020.53462678225</v>
       </c>
       <c r="CR17" s="6">
         <f t="shared" si="112"/>
-        <v>124540.99579964172</v>
+        <v>122780.32928051442</v>
       </c>
       <c r="CS17" s="6">
         <f t="shared" si="112"/>
-        <v>123295.5858416453</v>
+        <v>121552.52598770928</v>
       </c>
       <c r="CT17" s="6">
         <f t="shared" si="112"/>
-        <v>122062.62998322885</v>
+        <v>120337.00072783219</v>
       </c>
       <c r="CU17" s="6">
         <f t="shared" si="112"/>
-        <v>120842.00368339656</v>
+        <v>119133.63072055386</v>
       </c>
       <c r="CV17" s="6">
         <f t="shared" si="112"/>
-        <v>119633.58364656259</v>
+        <v>117942.29441334833</v>
       </c>
       <c r="CW17" s="6">
         <f t="shared" si="112"/>
-        <v>118437.24781009696</v>
+        <v>116762.87146921484</v>
       </c>
       <c r="CX17" s="6">
         <f t="shared" si="112"/>
-        <v>117252.87533199599</v>
+        <v>115595.24275452268</v>
       </c>
       <c r="CY17" s="6">
         <f t="shared" si="112"/>
-        <v>116080.34657867604</v>
+        <v>114439.29032697745</v>
       </c>
       <c r="CZ17" s="6">
         <f t="shared" si="112"/>
-        <v>114919.54311288927</v>
+        <v>113294.89742370768</v>
       </c>
       <c r="DA17" s="6">
         <f t="shared" si="112"/>
-        <v>113770.34768176038</v>
+        <v>112161.9484494706</v>
       </c>
       <c r="DB17" s="6">
         <f t="shared" si="112"/>
-        <v>112632.64420494277</v>
+        <v>111040.3289649759</v>
       </c>
       <c r="DC17" s="6">
         <f t="shared" si="112"/>
-        <v>111506.31776289335</v>
+        <v>109929.92567532613</v>
       </c>
       <c r="DD17" s="6">
         <f t="shared" si="112"/>
-        <v>110391.25458526441</v>
+        <v>108830.62641857287</v>
       </c>
       <c r="DE17" s="6">
         <f t="shared" si="112"/>
-        <v>109287.34203941177</v>
+        <v>107742.32015438714</v>
       </c>
       <c r="DF17" s="6">
         <f t="shared" si="112"/>
-        <v>108194.46861901766</v>
+        <v>106664.89695284326</v>
       </c>
       <c r="DG17" s="6">
         <f t="shared" si="112"/>
-        <v>107112.52393282748</v>
+        <v>105598.24798331482</v>
       </c>
       <c r="DH17" s="6">
         <f t="shared" si="112"/>
-        <v>106041.3986934992</v>
+        <v>104542.26550348167</v>
       </c>
       <c r="DI17" s="6">
         <f t="shared" si="112"/>
-        <v>104980.98470656421</v>
+        <v>103496.84284844685</v>
       </c>
       <c r="DJ17" s="6">
         <f t="shared" si="112"/>
-        <v>103931.17485949857</v>
+        <v>102461.87441996238</v>
       </c>
       <c r="DK17" s="6">
         <f t="shared" si="112"/>
-        <v>102891.86311090358</v>
+        <v>101437.25567576275</v>
       </c>
       <c r="DL17" s="6">
         <f t="shared" si="112"/>
-        <v>101862.94447979455</v>
+        <v>100422.88311900511</v>
       </c>
       <c r="DM17" s="6">
         <f t="shared" si="112"/>
-        <v>100844.3150349966</v>
+        <v>99418.654287815065</v>
       </c>
       <c r="DN17" s="6">
         <f t="shared" si="112"/>
-        <v>99835.871884646636</v>
+        <v>98424.467744936919</v>
       </c>
       <c r="DO17" s="6">
         <f t="shared" si="112"/>
-        <v>98837.513165800163</v>
+        <v>97440.223067487546</v>
       </c>
       <c r="DP17" s="6">
         <f t="shared" si="112"/>
-        <v>97849.138034142161</v>
+        <v>96465.820836812665</v>
       </c>
       <c r="DQ17" s="6">
         <f t="shared" si="112"/>
-        <v>96870.646653800737</v>
+        <v>95501.162628444537</v>
       </c>
       <c r="DR17" s="6">
         <f t="shared" si="112"/>
-        <v>95901.940187262735</v>
+        <v>94546.151002160084</v>
       </c>
       <c r="DS17" s="6">
         <f t="shared" si="112"/>
-        <v>94942.920785390103</v>
+        <v>93600.689492138481</v>
       </c>
       <c r="DT17" s="6">
         <f t="shared" si="112"/>
-        <v>93993.491577536202</v>
+        <v>92664.682597217092</v>
       </c>
       <c r="DU17" s="6">
         <f t="shared" si="112"/>
-        <v>93053.556661760842</v>
+        <v>91738.035771244919</v>
       </c>
       <c r="DV17" s="6">
         <f t="shared" si="112"/>
-        <v>92123.021095143238</v>
+        <v>90820.65541353247</v>
       </c>
       <c r="DW17" s="6">
         <f t="shared" si="112"/>
-        <v>91201.790884191811</v>
+        <v>89912.448859397147</v>
       </c>
       <c r="DX17" s="6">
         <f t="shared" si="112"/>
-        <v>90289.772975349886</v>
+        <v>89013.32437080318</v>
       </c>
       <c r="DY17" s="6">
         <f t="shared" ref="DY17:GB17" si="113">DX17*(1+$BN$21)</f>
-        <v>89386.875245596384</v>
+        <v>88123.191127095153</v>
       </c>
       <c r="DZ17" s="6">
         <f t="shared" si="113"/>
-        <v>88493.006493140419</v>
+        <v>87241.959215824201</v>
       </c>
       <c r="EA17" s="6">
         <f t="shared" si="113"/>
-        <v>87608.076428209009</v>
+        <v>86369.539623665958</v>
       </c>
       <c r="EB17" s="6">
         <f t="shared" si="113"/>
-        <v>86731.995663926922</v>
+        <v>85505.844227429305</v>
       </c>
       <c r="EC17" s="6">
         <f t="shared" si="113"/>
-        <v>85864.67570728765</v>
+        <v>84650.785785155007</v>
       </c>
       <c r="ED17" s="6">
         <f t="shared" si="113"/>
-        <v>85006.028950214779</v>
+        <v>83804.277927303454</v>
       </c>
       <c r="EE17" s="6">
         <f t="shared" si="113"/>
-        <v>84155.968660712635</v>
+        <v>82966.235148030421</v>
       </c>
       <c r="EF17" s="6">
         <f t="shared" si="113"/>
-        <v>83314.408974105507</v>
+        <v>82136.572796550114</v>
       </c>
       <c r="EG17" s="6">
         <f t="shared" si="113"/>
-        <v>82481.264884364457</v>
+        <v>81315.207068584612</v>
       </c>
       <c r="EH17" s="6">
         <f t="shared" si="113"/>
-        <v>81656.452235520817</v>
+        <v>80502.054997898769</v>
       </c>
       <c r="EI17" s="6">
         <f t="shared" si="113"/>
-        <v>80839.887713165605</v>
+        <v>79697.034447919781</v>
       </c>
       <c r="EJ17" s="6">
         <f t="shared" si="113"/>
-        <v>80031.488836033954</v>
+        <v>78900.064103440585</v>
       </c>
       <c r="EK17" s="6">
         <f t="shared" si="113"/>
-        <v>79231.173947673611</v>
+        <v>78111.063462406179</v>
       </c>
       <c r="EL17" s="6">
         <f t="shared" si="113"/>
-        <v>78438.862208196879</v>
+        <v>77329.952827782123</v>
       </c>
       <c r="EM17" s="6">
         <f t="shared" si="113"/>
-        <v>77654.473586114909</v>
+        <v>76556.653299504294</v>
       </c>
       <c r="EN17" s="6">
         <f t="shared" si="113"/>
-        <v>76877.928850253753</v>
+        <v>75791.086766509252</v>
       </c>
       <c r="EO17" s="6">
         <f t="shared" si="113"/>
-        <v>76109.149561751212</v>
+        <v>75033.175898844158</v>
       </c>
       <c r="EP17" s="6">
         <f t="shared" si="113"/>
-        <v>75348.058066133701</v>
+        <v>74282.844139855719</v>
       </c>
       <c r="EQ17" s="6">
         <f t="shared" si="113"/>
-        <v>74594.577485472357</v>
+        <v>73540.015698457166</v>
       </c>
       <c r="ER17" s="6">
         <f t="shared" si="113"/>
-        <v>73848.631710617628</v>
+        <v>72804.615541472594</v>
       </c>
       <c r="ES17" s="6">
         <f t="shared" si="113"/>
-        <v>73110.145393511455</v>
+        <v>72076.569386057861</v>
       </c>
       <c r="ET17" s="6">
         <f t="shared" si="113"/>
-        <v>72379.043939576339</v>
+        <v>71355.803692197282</v>
       </c>
       <c r="EU17" s="6">
         <f t="shared" si="113"/>
-        <v>71655.253500180581</v>
+        <v>70642.245655275314</v>
       </c>
       <c r="EV17" s="6">
         <f t="shared" si="113"/>
-        <v>70938.700965178781</v>
+        <v>69935.823198722559</v>
       </c>
       <c r="EW17" s="6">
         <f t="shared" si="113"/>
-        <v>70229.313955526988</v>
+        <v>69236.464966735337</v>
       </c>
       <c r="EX17" s="6">
         <f t="shared" si="113"/>
-        <v>69527.020815971715</v>
+        <v>68544.100317067976</v>
       </c>
       <c r="EY17" s="6">
         <f t="shared" si="113"/>
-        <v>68831.750607811991</v>
+        <v>67858.659313897297</v>
       </c>
       <c r="EZ17" s="6">
         <f t="shared" si="113"/>
-        <v>68143.43310173387</v>
+        <v>67180.072720758326</v>
       </c>
       <c r="FA17" s="6">
         <f t="shared" si="113"/>
-        <v>67461.998770716527</v>
+        <v>66508.271993550748</v>
       </c>
       <c r="FB17" s="6">
         <f t="shared" si="113"/>
-        <v>66787.378783009364</v>
+        <v>65843.189273615237</v>
       </c>
       <c r="FC17" s="6">
         <f t="shared" si="113"/>
-        <v>66119.504995179275</v>
+        <v>65184.757380879084</v>
       </c>
       <c r="FD17" s="6">
         <f t="shared" si="113"/>
-        <v>65458.309945227484</v>
+        <v>64532.909807070289</v>
       </c>
       <c r="FE17" s="6">
         <f t="shared" si="113"/>
-        <v>64803.726845775207</v>
+        <v>63887.580708999587</v>
       </c>
       <c r="FF17" s="6">
         <f t="shared" si="113"/>
-        <v>64155.689577317455</v>
+        <v>63248.704901909594</v>
       </c>
       <c r="FG17" s="6">
         <f t="shared" si="113"/>
-        <v>63514.132681544281</v>
+        <v>62616.217852890499</v>
       </c>
       <c r="FH17" s="6">
         <f t="shared" si="113"/>
-        <v>62878.991354728838</v>
+        <v>61990.055674361596</v>
       </c>
       <c r="FI17" s="6">
         <f t="shared" si="113"/>
-        <v>62250.201441181547</v>
+        <v>61370.155117617978</v>
       </c>
       <c r="FJ17" s="6">
         <f t="shared" si="113"/>
-        <v>61627.69942676973</v>
+        <v>60756.4535664418</v>
       </c>
       <c r="FK17" s="6">
         <f t="shared" si="113"/>
-        <v>61011.422432502033</v>
+        <v>60148.889030777384</v>
       </c>
       <c r="FL17" s="6">
         <f t="shared" si="113"/>
-        <v>60401.308208177012</v>
+        <v>59547.40014046961</v>
       </c>
       <c r="FM17" s="6">
         <f t="shared" si="113"/>
-        <v>59797.29512609524</v>
+        <v>58951.926139064912</v>
       </c>
       <c r="FN17" s="6">
         <f t="shared" si="113"/>
-        <v>59199.322174834284</v>
+        <v>58362.406877674264</v>
       </c>
       <c r="FO17" s="6">
         <f t="shared" si="113"/>
-        <v>58607.32895308594</v>
+        <v>57778.782808897522</v>
       </c>
       <c r="FP17" s="6">
         <f t="shared" si="113"/>
-        <v>58021.255663555079</v>
+        <v>57200.994980808544</v>
       </c>
       <c r="FQ17" s="6">
         <f t="shared" si="113"/>
-        <v>57441.043106919526</v>
+        <v>56628.985031000455</v>
       </c>
       <c r="FR17" s="6">
         <f t="shared" si="113"/>
-        <v>56866.632675850327</v>
+        <v>56062.695180690447</v>
       </c>
       <c r="FS17" s="6">
         <f t="shared" si="113"/>
-        <v>56297.966349091825</v>
+        <v>55502.068228883545</v>
       </c>
       <c r="FT17" s="6">
         <f t="shared" si="113"/>
-        <v>55734.986685600903</v>
+        <v>54947.047546594709</v>
       </c>
       <c r="FU17" s="6">
         <f t="shared" si="113"/>
-        <v>55177.636818744897</v>
+        <v>54397.577071128762</v>
       </c>
       <c r="FV17" s="6">
         <f t="shared" si="113"/>
-        <v>54625.860450557448</v>
+        <v>53853.601300417475</v>
       </c>
       <c r="FW17" s="6">
         <f t="shared" si="113"/>
-        <v>54079.601846051875</v>
+        <v>53315.065287413301</v>
       </c>
       <c r="FX17" s="6">
         <f t="shared" si="113"/>
-        <v>53538.805827591357</v>
+        <v>52781.914634539171</v>
       </c>
       <c r="FY17" s="6">
         <f t="shared" si="113"/>
-        <v>53003.417769315442</v>
+        <v>52254.09548819378</v>
       </c>
       <c r="FZ17" s="6">
         <f t="shared" si="113"/>
-        <v>52473.383591622289</v>
+        <v>51731.554533311843</v>
       </c>
       <c r="GA17" s="6">
         <f t="shared" si="113"/>
-        <v>51948.649755706065</v>
+        <v>51214.238987978722</v>
       </c>
       <c r="GB17" s="6">
         <f t="shared" si="113"/>
-        <v>51429.163258149005</v>
+        <v>50702.096598098935</v>
       </c>
     </row>
     <row r="18" spans="2:184" x14ac:dyDescent="0.3">
@@ -5479,9 +5515,18 @@
       <c r="AM18" s="5">
         <v>7432</v>
       </c>
-      <c r="AN18" s="5"/>
-      <c r="AO18" s="5"/>
-      <c r="AP18" s="5"/>
+      <c r="AN18" s="5">
+        <f>7425.6</f>
+        <v>7425.6</v>
+      </c>
+      <c r="AO18" s="5">
+        <f>7425.6</f>
+        <v>7425.6</v>
+      </c>
+      <c r="AP18" s="5">
+        <f>7425.6</f>
+        <v>7425.6</v>
+      </c>
       <c r="AQ18" s="5"/>
       <c r="AS18" s="5">
         <v>7567</v>
@@ -5511,34 +5556,44 @@
         <v>7432</v>
       </c>
       <c r="BB18" s="5">
-        <v>7432</v>
+        <f>7425.6</f>
+        <v>7425.6</v>
       </c>
       <c r="BC18" s="5">
-        <v>7432</v>
+        <f>7425.6</f>
+        <v>7425.6</v>
       </c>
       <c r="BD18" s="5">
-        <v>7432</v>
+        <f>7425.6</f>
+        <v>7425.6</v>
       </c>
       <c r="BE18" s="5">
-        <v>7432</v>
+        <f>7425.6</f>
+        <v>7425.6</v>
       </c>
       <c r="BF18" s="5">
-        <v>7432</v>
+        <f>7425.6</f>
+        <v>7425.6</v>
       </c>
       <c r="BG18" s="5">
-        <v>7432</v>
+        <f>7425.6</f>
+        <v>7425.6</v>
       </c>
       <c r="BH18" s="5">
-        <v>7432</v>
+        <f>7425.6</f>
+        <v>7425.6</v>
       </c>
       <c r="BI18" s="5">
-        <v>7432</v>
+        <f>7425.6</f>
+        <v>7425.6</v>
       </c>
       <c r="BJ18" s="5">
-        <v>7432</v>
+        <f>7425.6</f>
+        <v>7425.6</v>
       </c>
       <c r="BK18" s="5">
-        <v>7432</v>
+        <f>7425.6</f>
+        <v>7425.6</v>
       </c>
     </row>
     <row r="19" spans="2:184" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -5690,10 +5745,13 @@
         <v>3.6642895586652315</v>
       </c>
       <c r="AM19" s="8">
-        <f t="shared" ref="AM19" si="125">AM17/AM18</f>
+        <f t="shared" ref="AM19:AN19" si="125">AM17/AM18</f>
         <v>3.7334499461786868</v>
       </c>
-      <c r="AN19" s="8"/>
+      <c r="AN19" s="8">
+        <f t="shared" si="125"/>
+        <v>5.1791101055806932</v>
+      </c>
       <c r="AO19" s="8"/>
       <c r="AP19" s="8"/>
       <c r="AQ19" s="8"/>
@@ -5735,43 +5793,43 @@
       </c>
       <c r="BB19" s="8">
         <f t="shared" si="126"/>
-        <v>16.213903728471475</v>
+        <v>15.939682192146083</v>
       </c>
       <c r="BC19" s="8">
         <f t="shared" si="126"/>
-        <v>17.711334004674377</v>
+        <v>17.48401507000646</v>
       </c>
       <c r="BD19" s="8">
         <f t="shared" si="126"/>
-        <v>18.825827352108909</v>
+        <v>18.581601978962833</v>
       </c>
       <c r="BE19" s="8">
         <f t="shared" si="126"/>
-        <v>19.84280644978222</v>
+        <v>19.583813551856707</v>
       </c>
       <c r="BF19" s="8">
         <f t="shared" si="126"/>
-        <v>20.684894975376078</v>
+        <v>20.413578654507262</v>
       </c>
       <c r="BG19" s="8">
         <f t="shared" ref="BG19:BI19" si="129">BG17/BG18</f>
-        <v>21.334390536499374</v>
+        <v>21.053669060159034</v>
       </c>
       <c r="BH19" s="8">
         <f t="shared" si="129"/>
-        <v>22.003969150606583</v>
+        <v>21.713547973534656</v>
       </c>
       <c r="BI19" s="8">
         <f t="shared" si="129"/>
-        <v>22.443068629996514</v>
+        <v>22.146179906000153</v>
       </c>
       <c r="BJ19" s="8">
         <f t="shared" ref="BJ19:BK19" si="130">BJ17/BJ18</f>
-        <v>22.890940299938013</v>
+        <v>22.587448086844915</v>
       </c>
       <c r="BK19" s="8">
         <f t="shared" si="130"/>
-        <v>23.347759506251752</v>
+        <v>23.037525077133804</v>
       </c>
     </row>
     <row r="21" spans="2:184" x14ac:dyDescent="0.3">
@@ -5910,80 +5968,89 @@
         <f t="shared" si="136"/>
         <v>4.2561550550026084E-2</v>
       </c>
-      <c r="AN21" s="9"/>
-      <c r="AO21" s="9"/>
-      <c r="AP21" s="9"/>
+      <c r="AN21" s="9">
+        <f t="shared" ref="AN21:AN23" si="137">AN3/AJ3-1</f>
+        <v>1.4304211110426124E-2</v>
+      </c>
+      <c r="AO21" s="9">
+        <f t="shared" ref="AO21:AO23" si="138">AO3/AK3-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AP21" s="9">
+        <f t="shared" ref="AP21:AP23" si="139">AP3/AL3-1</f>
+        <v>-1</v>
+      </c>
       <c r="AQ21" s="9"/>
       <c r="AT21" s="9">
-        <f t="shared" ref="AT21:BI21" si="137">AT3/AS3-1</f>
+        <f t="shared" ref="AT21:BI21" si="140">AT3/AS3-1</f>
         <v>1.5045403755055808E-2</v>
       </c>
       <c r="AU21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>2.4373226661705161E-2</v>
       </c>
       <c r="AV21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>2.984758358685613E-2</v>
       </c>
       <c r="AW21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>4.457606443173967E-2</v>
       </c>
       <c r="AX21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>2.3327799195205001E-2</v>
       </c>
       <c r="AY21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>-0.11044657097288679</v>
       </c>
       <c r="AZ21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>-2.2736054653085813E-2</v>
       </c>
       <c r="BA21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>1.1355728474726323E-2</v>
       </c>
       <c r="BB21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI21" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BJ21" s="9">
-        <f t="shared" ref="BJ21:BJ23" si="138">BJ3/BI3-1</f>
+        <f t="shared" ref="BJ21:BJ23" si="141">BJ3/BI3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK21" s="9">
-        <f t="shared" ref="BK21:BK23" si="139">BK3/BJ3-1</f>
+        <f t="shared" ref="BK21:BK23" si="142">BK3/BJ3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BM21" t="s">
@@ -6129,80 +6196,89 @@
         <f t="shared" si="136"/>
         <v>0.22733687118637325</v>
       </c>
-      <c r="AN22" s="9"/>
-      <c r="AO22" s="9"/>
-      <c r="AP22" s="9"/>
+      <c r="AN22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.21359968546982944</v>
+      </c>
+      <c r="AO22" s="9">
+        <f t="shared" si="138"/>
+        <v>-1</v>
+      </c>
+      <c r="AP22" s="9">
+        <f t="shared" si="139"/>
+        <v>-1</v>
+      </c>
       <c r="AQ22" s="9"/>
       <c r="AT22" s="9">
-        <f t="shared" ref="AT22:BI22" si="140">AT4/AS4-1</f>
+        <f t="shared" ref="AT22:BI22" si="143">AT4/AS4-1</f>
         <v>0.39996947496947488</v>
       </c>
       <c r="AU22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>0.30331639884002359</v>
       </c>
       <c r="AV22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>0.25429116338207258</v>
       </c>
       <c r="AW22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>0.29396857577293467</v>
       </c>
       <c r="AX22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>0.29401941987754343</v>
       </c>
       <c r="AY22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>0.17268078191463943</v>
       </c>
       <c r="AZ22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>0.19927861102054134</v>
       </c>
       <c r="BA22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>0.23349928916529317</v>
       </c>
       <c r="BB22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>0.17999999999999994</v>
       </c>
       <c r="BC22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="BD22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BE22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BF22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BG22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BH22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BI22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BJ22" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="141"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BK22" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="142"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BM22" t="s">
@@ -6221,19 +6297,19 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="9">
-        <f t="shared" ref="G23:J23" si="141">G5/C5-1</f>
+        <f t="shared" ref="G23:J23" si="144">G5/C5-1</f>
         <v>0.13297626743004898</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>0.11972430883605667</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>0.15539376184732046</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>0.17496582698691654</v>
       </c>
       <c r="K23" s="9">
@@ -6241,47 +6317,47 @@
         <v>0.18526367267095933</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" ref="L23:V23" si="142">L5/H5-1</f>
+        <f t="shared" ref="L23:V23" si="145">L5/H5-1</f>
         <v>0.12286465177398154</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>0.13990081658525666</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>0.12072461359481479</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>0.13653555219364599</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>0.13658341289150311</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>0.14556278826338698</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>0.12800664353293589</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>0.12400544546967174</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>0.16718148810491518</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>0.19088546871876866</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>0.21347251071437956</v>
       </c>
       <c r="W23" s="9">
@@ -6352,80 +6428,89 @@
         <f t="shared" si="136"/>
         <v>0.18431043683769155</v>
       </c>
-      <c r="AN23" s="9"/>
-      <c r="AO23" s="9"/>
-      <c r="AP23" s="9"/>
+      <c r="AN23" s="9">
+        <f t="shared" si="137"/>
+        <v>0.16717888327205888</v>
+      </c>
+      <c r="AO23" s="9">
+        <f t="shared" si="138"/>
+        <v>-1</v>
+      </c>
+      <c r="AP23" s="9">
+        <f t="shared" si="139"/>
+        <v>-1</v>
+      </c>
       <c r="AQ23" s="9"/>
       <c r="AT23" s="9">
         <f>AT5/AS5-1</f>
         <v>0.14599017663367975</v>
       </c>
       <c r="AU23" s="9">
-        <f t="shared" ref="AU23:BI23" si="143">AU5/AT5-1</f>
+        <f t="shared" ref="AU23:BI23" si="146">AU5/AT5-1</f>
         <v>0.14029539688292858</v>
       </c>
       <c r="AV23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>0.13645574247276371</v>
       </c>
       <c r="AW23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>0.17531727441177503</v>
       </c>
       <c r="AX23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>0.17956070629670173</v>
       </c>
       <c r="AY23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>6.8820295556564215E-2</v>
       </c>
       <c r="AZ23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>0.13149611872684797</v>
       </c>
       <c r="BA23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>0.17492211643124356</v>
       </c>
       <c r="BB23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>0.14141322713009896</v>
       </c>
       <c r="BC23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>7.3932141552135011E-2</v>
       </c>
       <c r="BD23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>5.0555422216383761E-2</v>
       </c>
       <c r="BE23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>4.2736014980473636E-2</v>
       </c>
       <c r="BF23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>3.4723047278275798E-2</v>
       </c>
       <c r="BG23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>2.6566087732067922E-2</v>
       </c>
       <c r="BH23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>2.6621502081494164E-2</v>
       </c>
       <c r="BI23" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>1.8338100804058621E-2</v>
       </c>
       <c r="BJ23" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="141"/>
         <v>1.83517083505218E-2</v>
       </c>
       <c r="BK23" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="142"/>
         <v>1.8365226323752593E-2</v>
       </c>
       <c r="BM23" t="s">
@@ -6433,7 +6518,7 @@
       </c>
       <c r="BN23" s="23">
         <f>NPV(BN22,BB17:GB17)</f>
-        <v>2916685.9620076721</v>
+        <v>2875212.9930478651</v>
       </c>
     </row>
     <row r="24" spans="2:184" x14ac:dyDescent="0.3">
@@ -6445,228 +6530,237 @@
         <v>0.75636140971560761</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" ref="D24:V24" si="144">(D3-D6)/D3</f>
+        <f t="shared" ref="D24:V24" si="147">(D3-D6)/D3</f>
         <v>0.70568598478629674</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.78812099497002686</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.8043843806439559</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.79157924185200723</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.69329465580720739</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.77338891094349604</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.79503467568040098</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.78906295161570028</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.63715395523768414</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.77725271879854996</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.80716833304098701</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.79039827498731607</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.72796494111202414</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.78728498519311951</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.75918884664131814</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.77238499019173579</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.68869475847893113</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.74651810584958223</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>0.7736297391488014</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" ref="W24:X24" si="145">(W3-W6)/W3</f>
+        <f t="shared" ref="W24:X24" si="148">(W3-W6)/W3</f>
         <v>0.77199206301485179</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="148"/>
         <v>0.69531738774724483</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" ref="Y24:Y25" si="146">(Y3-Y6)/Y3</f>
+        <f t="shared" ref="Y24:Y25" si="149">(Y3-Y6)/Y3</f>
         <v>0.73603593228146957</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24" si="147">(Z3-Z6)/Z3</f>
+        <f t="shared" ref="Z24" si="150">(Z3-Z6)/Z3</f>
         <v>0.75735130318556476</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" ref="AA24:AA25" si="148">(AA3-AA6)/AA3</f>
+        <f t="shared" ref="AA24:AA25" si="151">(AA3-AA6)/AA3</f>
         <v>0.72670097198399086</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" ref="AB24:AC24" si="149">(AB3-AB6)/AB3</f>
+        <f t="shared" ref="AB24:AC24" si="152">(AB3-AB6)/AB3</f>
         <v>0.65550644790216139</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="152"/>
         <v>0.74717731588401337</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" ref="AD24:AE24" si="150">(AD3-AD6)/AD3</f>
+        <f t="shared" ref="AD24:AE24" si="153">(AD3-AD6)/AD3</f>
         <v>0.77030795704028954</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="153"/>
         <v>0.77270679111683294</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" ref="AF24:AG24" si="151">(AF3-AF6)/AF3</f>
+        <f t="shared" ref="AF24:AG24" si="154">(AF3-AF6)/AF3</f>
         <v>0.77270679111683294</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="154"/>
         <v>0.68512750118789922</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" ref="AH24:AI24" si="152">(AH3-AH6)/AH3</f>
+        <f t="shared" ref="AH24:AI24" si="155">(AH3-AH6)/AH3</f>
         <v>0.89120072633729286</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="155"/>
         <v>0.78431115767417492</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" ref="AJ24:AL24" si="153">(AJ3-AJ6)/AJ3</f>
+        <f t="shared" ref="AJ24:AL24" si="156">(AJ3-AJ6)/AJ3</f>
         <v>0.76225414637153954</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="156"/>
         <v>0.80174946145309745</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="156"/>
         <v>0.8066059757236228</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" ref="AM24" si="154">(AM3-AM6)/AM3</f>
+        <f t="shared" ref="AM24:AP24" si="157">(AM3-AM6)/AM3</f>
         <v>0.81648034166561989</v>
       </c>
-      <c r="AN24" s="9"/>
-      <c r="AO24" s="9"/>
-      <c r="AP24" s="9"/>
+      <c r="AN24" s="9">
+        <f t="shared" si="157"/>
+        <v>0.78694304297611084</v>
+      </c>
+      <c r="AO24" s="9" t="e">
+        <f t="shared" si="157"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AP24" s="9" t="e">
+        <f t="shared" si="157"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AQ24" s="9"/>
       <c r="AS24" s="9">
-        <f t="shared" ref="AS24:AW24" si="155">(AS3-AS6)/AS3</f>
+        <f t="shared" ref="AS24:AW24" si="158">(AS3-AS6)/AS3</f>
         <v>0.76117782219354435</v>
       </c>
       <c r="AT24" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="158"/>
         <v>0.76091911251686128</v>
       </c>
       <c r="AU24" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="158"/>
         <v>0.75369689264254036</v>
       </c>
       <c r="AV24" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="158"/>
         <v>0.76459781602269217</v>
       </c>
       <c r="AW24" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="158"/>
         <v>0.74366153586402906</v>
       </c>
       <c r="AX24" s="9">
-        <f t="shared" ref="AX24:AY24" si="156">(AX3-AX6)/AX3</f>
+        <f t="shared" ref="AX24:AY24" si="159">(AX3-AX6)/AX3</f>
         <v>0.73788703734257277</v>
       </c>
       <c r="AY24" s="9">
-        <f t="shared" si="156"/>
+        <f t="shared" si="159"/>
         <v>0.72481800336944935</v>
       </c>
       <c r="AZ24" s="9">
-        <f t="shared" ref="AZ24:BI24" si="157">(AZ3-AZ6)/AZ3</f>
+        <f t="shared" ref="AZ24:BI24" si="160">(AZ3-AZ6)/AZ3</f>
         <v>0.7712405896121971</v>
       </c>
       <c r="BA24" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="160"/>
         <v>0.78886873299346327</v>
       </c>
       <c r="BB24" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="160"/>
         <v>0.77</v>
       </c>
       <c r="BC24" s="9">
-        <f t="shared" si="157"/>
-        <v>0.76999999999999991</v>
+        <f t="shared" si="160"/>
+        <v>0.77999999999999992</v>
       </c>
       <c r="BD24" s="9">
-        <f t="shared" si="157"/>
-        <v>0.77</v>
+        <f t="shared" si="160"/>
+        <v>0.77999999999999992</v>
       </c>
       <c r="BE24" s="9">
-        <f t="shared" si="157"/>
-        <v>0.77</v>
+        <f t="shared" si="160"/>
+        <v>0.77999999999999992</v>
       </c>
       <c r="BF24" s="9">
-        <f t="shared" si="157"/>
-        <v>0.77</v>
+        <f t="shared" si="160"/>
+        <v>0.78</v>
       </c>
       <c r="BG24" s="9">
-        <f t="shared" si="157"/>
-        <v>0.77</v>
+        <f t="shared" si="160"/>
+        <v>0.78</v>
       </c>
       <c r="BH24" s="9">
-        <f t="shared" si="157"/>
-        <v>0.76999999999999991</v>
+        <f t="shared" si="160"/>
+        <v>0.77999999999999992</v>
       </c>
       <c r="BI24" s="9">
-        <f t="shared" si="157"/>
-        <v>0.77</v>
+        <f t="shared" si="160"/>
+        <v>0.78</v>
       </c>
       <c r="BJ24" s="9">
-        <f t="shared" ref="BJ24:BK24" si="158">(BJ3-BJ6)/BJ3</f>
-        <v>0.77</v>
+        <f t="shared" ref="BJ24:BK24" si="161">(BJ3-BJ6)/BJ3</f>
+        <v>0.77999999999999992</v>
       </c>
       <c r="BK24" s="9">
-        <f t="shared" si="158"/>
-        <v>0.77</v>
+        <f t="shared" si="161"/>
+        <v>0.78</v>
       </c>
       <c r="BM24" t="s">
         <v>91</v>
@@ -6681,239 +6775,248 @@
         <v>96</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:V25" si="159">(C4-C7)/C4</f>
+        <f t="shared" ref="C25:V25" si="162">(C4-C7)/C4</f>
         <v>0.38750000000000001</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.40116509996028066</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.42694562593401542</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.44333891914537077</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.48261718749999999</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.49363173216885009</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.50072618539085856</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.51841250193408639</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.46915570640644888</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.59771105094757571</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.55504860146796275</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.57180690983507887</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.58922890032972752</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.60366736368023166</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.60318537859007837</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.59926581514633415</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.65317783710364852</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.65548780487804881</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.64692143518704948</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="162"/>
         <v>0.64341882854413168</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" ref="W25:X25" si="160">(W4-W7)/W4</f>
+        <f t="shared" ref="W25:X25" si="163">(W4-W7)/W4</f>
         <v>0.65648748518441047</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="163"/>
         <v>0.618792206533329</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="149"/>
         <v>0.65521660311308372</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" ref="Z25" si="161">(Z4-Z7)/Z4</f>
+        <f t="shared" ref="Z25" si="164">(Z4-Z7)/Z4</f>
         <v>0.64398832168450859</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="151"/>
         <v>0.67569296995433525</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" ref="AB25:AC25" si="162">(AB4-AB7)/AB4</f>
+        <f t="shared" ref="AB25:AC25" si="165">(AB4-AB7)/AB4</f>
         <v>0.67435826662986476</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="165"/>
         <v>0.67299900721779493</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" ref="AD25:AE25" si="163">(AD4-AD7)/AD4</f>
+        <f t="shared" ref="AD25:AE25" si="166">(AD4-AD7)/AD4</f>
         <v>0.67144600366076879</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="166"/>
         <v>0.68837538431506518</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" ref="AF25:AG25" si="164">(AF4-AF7)/AF4</f>
+        <f t="shared" ref="AF25:AG25" si="167">(AF4-AF7)/AF4</f>
         <v>0.68837538431506518</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="167"/>
         <v>0.68293135866663568</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" ref="AH25:AI25" si="165">(AH4-AH7)/AH4</f>
+        <f t="shared" ref="AH25:AI25" si="168">(AH4-AH7)/AH4</f>
         <v>0.64577751892836344</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="168"/>
         <v>0.66599089698487468</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" ref="AJ25:AL25" si="166">(AJ4-AJ7)/AJ4</f>
+        <f t="shared" ref="AJ25:AL25" si="169">(AJ4-AJ7)/AJ4</f>
         <v>0.66407054462396797</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="166"/>
+        <f t="shared" si="169"/>
         <v>0.65510438928160453</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="166"/>
+        <f t="shared" si="169"/>
         <v>0.65095691762920493</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" ref="AM25" si="167">(AM4-AM7)/AM4</f>
+        <f t="shared" ref="AM25:AP25" si="170">(AM4-AM7)/AM4</f>
         <v>0.65796505319751908</v>
       </c>
-      <c r="AN25" s="9"/>
-      <c r="AO25" s="9"/>
-      <c r="AP25" s="9"/>
+      <c r="AN25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.65331214711054886</v>
+      </c>
+      <c r="AO25" s="9" t="e">
+        <f t="shared" si="170"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AP25" s="9" t="e">
+        <f t="shared" si="170"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AQ25" s="9"/>
       <c r="AS25" s="9">
-        <f t="shared" ref="AS25:AW25" si="168">(AS4-AS7)/AS4</f>
+        <f t="shared" ref="AS25:AW25" si="171">(AS4-AS7)/AS4</f>
         <v>0.41739926739926742</v>
       </c>
       <c r="AT25" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="171"/>
         <v>0.4999672938970412</v>
       </c>
       <c r="AU25" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="171"/>
         <v>0.55437146585471941</v>
       </c>
       <c r="AV25" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="171"/>
         <v>0.59904766985888447</v>
       </c>
       <c r="AW25" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="171"/>
         <v>0.64940111736450412</v>
       </c>
       <c r="AX25" s="9">
-        <f t="shared" ref="AX25:AY25" si="169">(AX4-AX7)/AX4</f>
+        <f t="shared" ref="AX25:AY25" si="172">(AX4-AX7)/AX4</f>
         <v>0.64349440010196113</v>
       </c>
       <c r="AY25" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="172"/>
         <v>0.67354771220519505</v>
       </c>
       <c r="AZ25" s="9">
-        <f t="shared" ref="AZ25:BI25" si="170">(AZ4-AZ7)/AZ4</f>
+        <f t="shared" ref="AZ25:BI25" si="173">(AZ4-AZ7)/AZ4</f>
         <v>0.67461895294897278</v>
       </c>
       <c r="BA25" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>0.65868912378660838</v>
       </c>
       <c r="BB25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.67</v>
+        <f t="shared" si="173"/>
+        <v>0.66</v>
       </c>
       <c r="BC25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.66999999999999993</v>
+        <f t="shared" si="173"/>
+        <v>0.65999999999999992</v>
       </c>
       <c r="BD25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.66999999999999993</v>
+        <f t="shared" si="173"/>
+        <v>0.66</v>
       </c>
       <c r="BE25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.66999999999999993</v>
+        <f t="shared" si="173"/>
+        <v>0.65999999999999992</v>
       </c>
       <c r="BF25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.67</v>
+        <f t="shared" si="173"/>
+        <v>0.65999999999999992</v>
       </c>
       <c r="BG25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.67</v>
+        <f t="shared" si="173"/>
+        <v>0.66</v>
       </c>
       <c r="BH25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.67</v>
+        <f t="shared" si="173"/>
+        <v>0.66</v>
       </c>
       <c r="BI25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.67</v>
+        <f t="shared" si="173"/>
+        <v>0.65999999999999992</v>
       </c>
       <c r="BJ25" s="9">
-        <f t="shared" ref="BJ25:BK25" si="171">(BJ4-BJ7)/BJ4</f>
-        <v>0.66999999999999993</v>
+        <f t="shared" ref="BJ25:BK25" si="174">(BJ4-BJ7)/BJ4</f>
+        <v>0.65999999999999992</v>
       </c>
       <c r="BK25" s="9">
-        <f t="shared" si="171"/>
-        <v>0.66999999999999993</v>
+        <f t="shared" si="174"/>
+        <v>0.65999999999999992</v>
       </c>
       <c r="BM25" t="s">
         <v>89</v>
       </c>
       <c r="BN25" s="23">
         <f>BN23+BN24</f>
-        <v>2983504.9620076721</v>
+        <v>2942031.9930478651</v>
       </c>
     </row>
     <row r="26" spans="2:184" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -6921,239 +7024,248 @@
         <v>42</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:F26" si="172">C9/C5</f>
+        <f t="shared" ref="C26:F26" si="175">C9/C5</f>
         <v>0.63782436051343616</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>0.61662665530860372</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>0.65276581078752371</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>0.66975200156219483</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" ref="G26" si="173">G9/G5</f>
+        <f t="shared" ref="G26" si="176">G9/G5</f>
         <v>0.66264569239546822</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ref="H26:V26" si="174">H9/H5</f>
+        <f t="shared" ref="H26:V26" si="177">H9/H5</f>
         <v>0.6174009267584204</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.65438681531749876</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.67618414492271894</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.65943474075092834</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.61741246034923469</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.66733178502502366</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.69119435299700449</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.6851913477537438</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.66514929821709212</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.68661660146769077</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.67557121447164303</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.70388114334930285</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.67048936762930633</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.68721526878626582</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0.69684954064829263</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" ref="W26:X26" si="175">W9/W5</f>
+        <f t="shared" ref="W26:X26" si="178">W9/W5</f>
         <v>0.6988768012004325</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="178"/>
         <v>0.64953216826476956</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" ref="Y26" si="176">Y9/Y5</f>
+        <f t="shared" ref="Y26" si="179">Y9/Y5</f>
         <v>0.68365072933549431</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" ref="Z26" si="177">Z9/Z5</f>
+        <f t="shared" ref="Z26" si="180">Z9/Z5</f>
         <v>0.68323532247180174</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" ref="AA26" si="178">AA9/AA5</f>
+        <f t="shared" ref="AA26" si="181">AA9/AA5</f>
         <v>0.69171222217788597</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" ref="AB26:AC26" si="179">AB9/AB5</f>
+        <f t="shared" ref="AB26:AC26" si="182">AB9/AB5</f>
         <v>0.66845507801391546</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0.69487485101311086</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" ref="AD26:AE26" si="180">AD9/AD5</f>
+        <f t="shared" ref="AD26:AE26" si="183">AD9/AD5</f>
         <v>0.70109807969531401</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="183"/>
         <v>0.71155581506449384</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" ref="AF26:AG26" si="181">AF9/AF5</f>
+        <f t="shared" ref="AF26:AG26" si="184">AF9/AF5</f>
         <v>0.71155581506449384</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>0.68360206385037081</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" ref="AH26:AI26" si="182">AH9/AH5</f>
+        <f t="shared" ref="AH26:AI26" si="185">AH9/AH5</f>
         <v>0.69589197707293715</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="185"/>
         <v>0.69354273080734929</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" ref="AJ26:AL26" si="183">AJ9/AJ5</f>
+        <f t="shared" ref="AJ26:AL26" si="186">AJ9/AJ5</f>
         <v>0.68693991268382348</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="183"/>
+        <f t="shared" si="186"/>
         <v>0.6871663859789342</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="183"/>
+        <f t="shared" si="186"/>
         <v>0.68584921704320978</v>
       </c>
       <c r="AM26" s="9">
-        <f t="shared" ref="AM26" si="184">AM9/AM5</f>
+        <f t="shared" ref="AM26:AP26" si="187">AM9/AM5</f>
         <v>0.69045871795862135</v>
       </c>
-      <c r="AN26" s="9"/>
-      <c r="AO26" s="9"/>
-      <c r="AP26" s="9"/>
+      <c r="AN26" s="9">
+        <f t="shared" si="187"/>
+        <v>0.68036125158416694</v>
+      </c>
+      <c r="AO26" s="9" t="e">
+        <f t="shared" si="187"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AP26" s="9" t="e">
+        <f t="shared" si="187"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AQ26" s="9"/>
       <c r="AS26" s="9">
-        <f t="shared" ref="AS26:AU26" si="185">AS9/AS5</f>
+        <f t="shared" ref="AS26:AU26" si="188">AS9/AS5</f>
         <v>0.64423007030041224</v>
       </c>
       <c r="AT26" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>0.65247372236317502</v>
       </c>
       <c r="AU26" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>0.65901957200638894</v>
       </c>
       <c r="AV26" s="9">
-        <f t="shared" ref="AV26:BF26" si="186">AV9/AV5</f>
+        <f t="shared" ref="AV26:BF26" si="189">AV9/AV5</f>
         <v>0.67781001992797962</v>
       </c>
       <c r="AW26" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="189"/>
         <v>0.68925800771024703</v>
       </c>
       <c r="AX26" s="9">
-        <f t="shared" ref="AX26" si="187">AX9/AX5</f>
+        <f t="shared" ref="AX26" si="190">AX9/AX5</f>
         <v>0.67812074443940085</v>
       </c>
       <c r="AY26" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="189"/>
         <v>0.68920085883491022</v>
       </c>
       <c r="AZ26" s="9">
-        <f t="shared" ref="AZ26" si="188">AZ9/AZ5</f>
+        <f t="shared" ref="AZ26" si="191">AZ9/AZ5</f>
         <v>0.70009717200278587</v>
       </c>
       <c r="BA26" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="189"/>
         <v>0.68823742386165188</v>
       </c>
       <c r="BB26" s="9">
-        <f t="shared" si="186"/>
-        <v>0.6900848230598311</v>
+        <f t="shared" si="189"/>
+        <v>0.68209330536581425</v>
       </c>
       <c r="BC26" s="9">
-        <f t="shared" si="186"/>
-        <v>0.68888915556723251</v>
+        <f t="shared" si="189"/>
+        <v>0.68266698668067893</v>
       </c>
       <c r="BD26" s="9">
-        <f t="shared" si="186"/>
-        <v>0.68815996254881573</v>
+        <f t="shared" si="189"/>
+        <v>0.68179195505857881</v>
       </c>
       <c r="BE26" s="9">
-        <f t="shared" si="186"/>
-        <v>0.68758984240574761</v>
+        <f t="shared" si="189"/>
+        <v>0.6811078108868972</v>
       </c>
       <c r="BF26" s="9">
-        <f t="shared" si="186"/>
-        <v>0.68716956133966078</v>
+        <f t="shared" si="189"/>
+        <v>0.68060347360759299</v>
       </c>
       <c r="BG26" s="9">
-        <f t="shared" ref="BG26:BI26" si="189">BG9/BG5</f>
-        <v>0.68689248959252935</v>
+        <f t="shared" ref="BG26:BI26" si="192">BG9/BG5</f>
+        <v>0.6802709875110351</v>
       </c>
       <c r="BH26" s="9">
-        <f t="shared" si="189"/>
-        <v>0.68661899195941456</v>
+        <f t="shared" si="192"/>
+        <v>0.67994279035129757</v>
       </c>
       <c r="BI26" s="9">
-        <f t="shared" si="189"/>
-        <v>0.68648291649478255</v>
+        <f t="shared" si="192"/>
+        <v>0.67977949979373908</v>
       </c>
       <c r="BJ26" s="9">
-        <f t="shared" ref="BJ26:BK26" si="190">BJ9/BJ5</f>
-        <v>0.68634773676247451</v>
+        <f t="shared" ref="BJ26:BK26" si="193">BJ9/BJ5</f>
+        <v>0.67961728411496936</v>
       </c>
       <c r="BK26" s="9">
-        <f t="shared" si="190"/>
-        <v>0.68621345044322046</v>
+        <f t="shared" si="193"/>
+        <v>0.67945614053186454</v>
       </c>
       <c r="BM26" t="s">
         <v>90</v>
       </c>
       <c r="BN26" s="19">
         <f>BN25/BF18</f>
-        <v>401.44038778359419</v>
+        <v>396.20124879442267</v>
       </c>
     </row>
     <row r="27" spans="2:184" x14ac:dyDescent="0.3">
@@ -7161,19 +7273,19 @@
         <v>76</v>
       </c>
       <c r="C27" s="9">
-        <f t="shared" ref="C27:F27" si="191">C13/C5</f>
+        <f t="shared" ref="C27:F27" si="194">C13/C5</f>
         <v>0.29758057068981436</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="194"/>
         <v>0.30608688918144505</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="194"/>
         <v>0.28963467172152335</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="194"/>
         <v>0.31197031829720756</v>
       </c>
       <c r="G27" s="9">
@@ -7181,219 +7293,228 @@
         <v>0.3141250305648382</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:V27" si="192">H13/H5</f>
+        <f t="shared" ref="H27:V27" si="195">H13/H5</f>
         <v>0.30012448993706342</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.30918378761325926</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.3449891972743892</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.34228441754916794</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.3159126605278556</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.3382617513329626</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.3679152949550672</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.38378460142187265</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.37638866309001245</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.37049199051997372</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.35250966266137301</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.42730257845723207</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.41547497446373849</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.40876612477820939</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>0.41374154966198645</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" ref="W27:X27" si="193">W13/W5</f>
+        <f t="shared" ref="W27:X27" si="196">W13/W5</f>
         <v>0.44658737339188381</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="193"/>
+        <f t="shared" si="196"/>
         <v>0.40747757500773274</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" ref="Y27" si="194">Y13/Y5</f>
+        <f t="shared" ref="Y27" si="197">Y13/Y5</f>
         <v>0.41256077795786061</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" ref="Z27" si="195">Z13/Z5</f>
+        <f t="shared" ref="Z27" si="198">Z13/Z5</f>
         <v>0.3959124650535043</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" ref="AA27" si="196">AA13/AA5</f>
+        <f t="shared" ref="AA27" si="199">AA13/AA5</f>
         <v>0.42931247755476637</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" ref="AB27:AC27" si="197">AB13/AB5</f>
+        <f t="shared" ref="AB27:AC27" si="200">AB13/AB5</f>
         <v>0.3867328947617874</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="200"/>
         <v>0.42287681858599618</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" ref="AD27:AE27" si="198">AD13/AD5</f>
+        <f t="shared" ref="AD27:AE27" si="201">AD13/AD5</f>
         <v>0.4316503230169606</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="201"/>
         <v>0.47587451563246458</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" ref="AF27:AG27" si="199">AF13/AF5</f>
+        <f t="shared" ref="AF27:AG27" si="202">AF13/AF5</f>
         <v>0.47587451563246458</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="202"/>
         <v>0.43585940019348596</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" ref="AH27:AI27" si="200">AH13/AH5</f>
+        <f t="shared" ref="AH27:AI27" si="203">AH13/AH5</f>
         <v>0.43142737960974553</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.46583822520393381</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" ref="AJ27:AL27" si="201">AJ13/AJ5</f>
+        <f t="shared" ref="AJ27:AL27" si="204">AJ13/AJ5</f>
         <v>0.45457548253676472</v>
       </c>
       <c r="AK27" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="204"/>
         <v>0.45671224274255701</v>
       </c>
       <c r="AL27" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="204"/>
         <v>0.44901296424693554</v>
       </c>
       <c r="AM27" s="9">
-        <f t="shared" ref="AM27" si="202">AM13/AM5</f>
+        <f t="shared" ref="AM27:AP27" si="205">AM13/AM5</f>
         <v>0.48872838695557014</v>
       </c>
-      <c r="AN27" s="9"/>
-      <c r="AO27" s="9"/>
-      <c r="AP27" s="9"/>
+      <c r="AN27" s="9">
+        <f t="shared" si="205"/>
+        <v>0.47094360980891564</v>
+      </c>
+      <c r="AO27" s="9" t="e">
+        <f t="shared" si="205"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AP27" s="9" t="e">
+        <f t="shared" si="205"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AQ27" s="9"/>
       <c r="AS27" s="9">
-        <f t="shared" ref="AS27:AU27" si="203">AS13/AS5</f>
+        <f t="shared" ref="AS27:AU27" si="206">AS13/AS5</f>
         <v>0.30177256726306062</v>
       </c>
       <c r="AT27" s="9">
-        <f t="shared" si="203"/>
+        <f t="shared" si="206"/>
         <v>0.31766944545125048</v>
       </c>
       <c r="AU27" s="9">
-        <f t="shared" si="203"/>
+        <f t="shared" si="206"/>
         <v>0.3413698020549415</v>
       </c>
       <c r="AV27" s="9">
-        <f t="shared" ref="AV27:BF27" si="204">AV13/AV5</f>
+        <f t="shared" ref="AV27:BF27" si="207">AV13/AV5</f>
         <v>0.37030381428521486</v>
       </c>
       <c r="AW27" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.41594878872971303</v>
       </c>
       <c r="AX27" s="9">
-        <f t="shared" ref="AX27" si="205">AX13/AX5</f>
+        <f t="shared" ref="AX27" si="208">AX13/AX5</f>
         <v>0.4146567811570081</v>
       </c>
       <c r="AY27" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.41772880636104098</v>
       </c>
       <c r="AZ27" s="9">
-        <f t="shared" ref="AZ27" si="206">AZ13/AZ5</f>
+        <f t="shared" ref="AZ27" si="209">AZ13/AZ5</f>
         <v>0.45352634278779386</v>
       </c>
       <c r="BA27" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.45621956240859851</v>
       </c>
       <c r="BB27" s="9">
-        <f t="shared" si="204"/>
-        <v>0.47803180709253396</v>
+        <f t="shared" si="207"/>
+        <v>0.46981566813397657</v>
       </c>
       <c r="BC27" s="9">
-        <f t="shared" si="204"/>
-        <v>0.4850516527550332</v>
+        <f t="shared" si="207"/>
+        <v>0.47861195977539855</v>
       </c>
       <c r="BD27" s="9">
-        <f t="shared" si="204"/>
-        <v>0.49003366786266345</v>
+        <f t="shared" si="207"/>
+        <v>0.48345239240851368</v>
       </c>
       <c r="BE27" s="9">
-        <f t="shared" si="204"/>
-        <v>0.49474919386803445</v>
+        <f t="shared" si="207"/>
+        <v>0.48805854452063879</v>
       </c>
       <c r="BF27" s="9">
-        <f t="shared" si="204"/>
-        <v>0.49801542703092888</v>
+        <f t="shared" si="207"/>
+        <v>0.49124368988796241</v>
       </c>
       <c r="BG27" s="9">
-        <f t="shared" ref="BG27:BI27" si="207">BG13/BG5</f>
-        <v>0.50008593924685696</v>
+        <f t="shared" ref="BG27:BI27" si="210">BG13/BG5</f>
+        <v>0.49326210639729051</v>
       </c>
       <c r="BH27" s="9">
-        <f t="shared" si="207"/>
-        <v>0.50213660859100206</v>
+        <f t="shared" si="210"/>
+        <v>0.49526135204848271</v>
       </c>
       <c r="BI27" s="9">
-        <f t="shared" si="207"/>
-        <v>0.5028096005865953</v>
+        <f t="shared" si="210"/>
+        <v>0.49590875880287288</v>
       </c>
       <c r="BJ27" s="9">
-        <f t="shared" ref="BJ27:BK27" si="208">BJ13/BJ5</f>
-        <v>0.5034781625353334</v>
+        <f t="shared" ref="BJ27:BK27" si="211">BJ13/BJ5</f>
+        <v>0.49655190392818721</v>
       </c>
       <c r="BK27" s="9">
-        <f t="shared" si="208"/>
-        <v>0.50414230590768883</v>
+        <f t="shared" si="211"/>
+        <v>0.49719079845882319</v>
       </c>
       <c r="BM27" t="s">
         <v>92</v>
       </c>
       <c r="BN27" s="19">
         <f>Main!D3</f>
-        <v>527.70000000000005</v>
+        <v>432.76</v>
       </c>
     </row>
     <row r="28" spans="2:184" x14ac:dyDescent="0.3">
@@ -7405,140 +7526,149 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9">
-        <f t="shared" ref="G28:G30" si="209">G10/C10-1</f>
+        <f t="shared" ref="G28:G30" si="212">G10/C10-1</f>
         <v>0.1506761107533805</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" ref="H28" si="210">H10/D10-1</f>
+        <f t="shared" ref="H28" si="213">H10/D10-1</f>
         <v>0.14435009797517973</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" ref="I28" si="211">I10/E10-1</f>
+        <f t="shared" ref="I28" si="214">I10/E10-1</f>
         <v>0.10730253353204167</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" ref="J28" si="212">J10/F10-1</f>
+        <f t="shared" ref="J28" si="215">J10/F10-1</f>
         <v>0.1192373363688104</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" ref="K28" si="213">K10/G10-1</f>
+        <f t="shared" ref="K28" si="216">K10/G10-1</f>
         <v>0.11275881365416907</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" ref="L28" si="214">L10/H10-1</f>
+        <f t="shared" ref="L28" si="217">L10/H10-1</f>
         <v>0.1615296803652968</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" ref="M28" si="215">M10/I10-1</f>
+        <f t="shared" ref="M28" si="218">M10/I10-1</f>
         <v>0.16177658142664875</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" ref="N28" si="216">N10/J10-1</f>
+        <f t="shared" ref="N28" si="219">N10/J10-1</f>
         <v>0.14747012458682929</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28" si="217">O10/K10-1</f>
+        <f t="shared" ref="O28" si="220">O10/K10-1</f>
         <v>0.14785013829519733</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" ref="P28" si="218">P10/L10-1</f>
+        <f t="shared" ref="P28" si="221">P10/L10-1</f>
         <v>0.13095823095823089</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" ref="Q28" si="219">Q10/M10-1</f>
+        <f t="shared" ref="Q28" si="222">Q10/M10-1</f>
         <v>0.13229842446709927</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" ref="R28" si="220">R10/N10-1</f>
+        <f t="shared" ref="R28" si="223">R10/N10-1</f>
         <v>0.15532904941280745</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" ref="S28" si="221">S10/O10-1</f>
+        <f t="shared" ref="S28" si="224">S10/O10-1</f>
         <v>7.9079956188389922E-2</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" ref="T28" si="222">T10/P10-1</f>
+        <f t="shared" ref="T28" si="225">T10/P10-1</f>
         <v>6.4305887464696898E-2</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" ref="U28" si="223">U10/Q10-1</f>
+        <f t="shared" ref="U28" si="226">U10/Q10-1</f>
         <v>6.4865970943319029E-2</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" ref="V28" si="224">V10/R10-1</f>
+        <f t="shared" ref="V28" si="227">V10/R10-1</f>
         <v>9.0717299578058963E-2</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" ref="W28:X28" si="225">W10/S10-1</f>
+        <f t="shared" ref="W28:X28" si="228">W10/S10-1</f>
         <v>0.13662200568412497</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="225"/>
+        <f t="shared" si="228"/>
         <v>0.17534190651153292</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" ref="Y28" si="226">Y10/U10-1</f>
+        <f t="shared" ref="Y28" si="229">Y10/U10-1</f>
         <v>0.21176018447348199</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" ref="Z28" si="227">Z10/V10-1</f>
+        <f t="shared" ref="Z28" si="230">Z10/V10-1</f>
         <v>0.20432565500263755</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" ref="AA28" si="228">AA10/W10-1</f>
+        <f t="shared" ref="AA28" si="231">AA10/W10-1</f>
         <v>0.18378281836042154</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" ref="AB28:AM28" si="229">AB10/X10-1</f>
+        <f t="shared" ref="AB28:AM28" si="232">AB10/X10-1</f>
         <v>0.18860715526224392</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>0.1075166508087535</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>-1.6060738793984508E-2</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>4.6771273385637357E-3</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>-2.7030976037405008E-2</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>2.2623138602519965E-2</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>0.19542958895978635</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>0.13290283826400362</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>0.18891725484306954</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>0.14785774292915144</v>
       </c>
       <c r="AL28" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>9.5953326713009046E-2</v>
       </c>
       <c r="AM28" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>7.9798515376458212E-2</v>
       </c>
-      <c r="AN28" s="9"/>
-      <c r="AO28" s="9"/>
-      <c r="AP28" s="9"/>
+      <c r="AN28" s="9">
+        <f t="shared" ref="AN28" si="233">AN10/AJ10-1</f>
+        <v>7.414424655803975E-2</v>
+      </c>
+      <c r="AO28" s="9">
+        <f t="shared" ref="AO28" si="234">AO10/AK10-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AP28" s="9">
+        <f t="shared" ref="AP28" si="235">AP10/AL10-1</f>
+        <v>-1</v>
+      </c>
       <c r="AQ28" s="9"/>
       <c r="AS28" s="9"/>
       <c r="AT28" s="9">
@@ -7546,71 +7676,71 @@
         <v>0.12955434532484467</v>
       </c>
       <c r="AU28" s="9">
-        <f t="shared" ref="AU28:BI28" si="230">AU10/AT10-1</f>
+        <f t="shared" ref="AU28:BI28" si="236">AU10/AT10-1</f>
         <v>0.14600027162841234</v>
       </c>
       <c r="AV28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>0.14179900450343674</v>
       </c>
       <c r="AW28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>7.5094711713114437E-2</v>
       </c>
       <c r="AX28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>0.1832400077234988</v>
       </c>
       <c r="AY28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>0.10945659268929497</v>
       </c>
       <c r="AZ28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>4.8575105717962863E-2</v>
       </c>
       <c r="BA28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>0.13929022303268335</v>
       </c>
       <c r="BB28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BC28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BD28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI28" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="236"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BJ28" s="9">
-        <f t="shared" ref="BJ28" si="231">BJ10/BI10-1</f>
+        <f t="shared" ref="BJ28" si="237">BJ10/BI10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK28" s="9">
-        <f t="shared" ref="BK28" si="232">BK10/BJ10-1</f>
+        <f t="shared" ref="BK28" si="238">BK10/BJ10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BM28" s="6" t="s">
@@ -7618,7 +7748,7 @@
       </c>
       <c r="BN28" s="18">
         <f>BN26/BN27-1</f>
-        <v>-0.23926399889407968</v>
+        <v>-8.4478119987007383E-2</v>
       </c>
     </row>
     <row r="29" spans="2:184" x14ac:dyDescent="0.3">
@@ -7626,238 +7756,247 @@
         <v>77</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:F29" si="233">C11/C$5</f>
+        <f t="shared" ref="C29:F29" si="239">C11/C$5</f>
         <v>0.14858250992704775</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="239"/>
         <v>0.1579416092310075</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="239"/>
         <v>0.16681027054971567</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="239"/>
         <v>0.16762351103300135</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" ref="G29:V29" si="234">G11/G$5</f>
+        <f t="shared" ref="G29:V29" si="240">G11/G$5</f>
         <v>0.15535088434265221</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.15775641468981258</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.16163913643312577</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.15821838125311616</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.14090221427589053</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.14129530966092821</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.14932452324098</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.14716611798202686</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.13120556648010892</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.13366390288841923</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.14023014762571029</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.14242894328609365</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.11387737524896377</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.11484353236140775</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.12185297079556898</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="240"/>
         <v>0.12690674293638413</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" ref="W29:X29" si="235">W11/W$5</f>
+        <f t="shared" ref="W29:X29" si="241">W11/W$5</f>
         <v>0.100337621643092</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="235"/>
+        <f t="shared" si="241"/>
         <v>0.10398623569440149</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" ref="Y29" si="236">Y11/Y$5</f>
+        <f t="shared" ref="Y29" si="242">Y11/Y$5</f>
         <v>0.11335089141004863</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29" si="237">Z11/Z$5</f>
+        <f t="shared" ref="Z29" si="243">Z11/Z$5</f>
         <v>0.12154632218258941</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" ref="AA29" si="238">AA11/AA$5</f>
+        <f t="shared" ref="AA29" si="244">AA11/AA$5</f>
         <v>0.10227046007741111</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" ref="AB29:AC29" si="239">AB11/AB$5</f>
+        <f t="shared" ref="AB29:AC29" si="245">AB11/AB$5</f>
         <v>0.10766489089426887</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="239"/>
+        <f t="shared" si="245"/>
         <v>0.10878407779480485</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" ref="AD29:AE29" si="240">AD11/AD$5</f>
+        <f t="shared" ref="AD29:AE29" si="246">AD11/AD$5</f>
         <v>0.11041307017387746</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="246"/>
         <v>9.1777695206751955E-2</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" ref="AF29:AG29" si="241">AF11/AF$5</f>
+        <f t="shared" ref="AF29:AG29" si="247">AF11/AF$5</f>
         <v>9.1777695206751955E-2</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="241"/>
+        <f t="shared" si="247"/>
         <v>0.10070944856497904</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" ref="AH29:AI29" si="242">AH11/AH$5</f>
+        <f t="shared" ref="AH29:AI29" si="248">AH11/AH$5</f>
         <v>0.10530381448236439</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="242"/>
+        <f t="shared" si="248"/>
         <v>8.716932225356408E-2</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" ref="AJ29:AL29" si="243">AJ11/AJ$5</f>
+        <f t="shared" ref="AJ29:AL29" si="249">AJ11/AJ$5</f>
         <v>9.2486213235294115E-2</v>
       </c>
       <c r="AK29" s="9">
-        <f t="shared" si="243"/>
+        <f t="shared" si="249"/>
         <v>8.8659264122398884E-2</v>
       </c>
       <c r="AL29" s="9">
-        <f t="shared" si="243"/>
+        <f t="shared" si="249"/>
         <v>9.5302259258774738E-2</v>
       </c>
       <c r="AM29" s="9">
-        <f t="shared" ref="AM29" si="244">AM11/AM$5</f>
+        <f t="shared" ref="AM29:AP29" si="250">AM11/AM$5</f>
         <v>7.3603440062827499E-2</v>
       </c>
-      <c r="AN29" s="9"/>
-      <c r="AO29" s="9"/>
-      <c r="AP29" s="9"/>
+      <c r="AN29" s="9">
+        <f t="shared" si="250"/>
+        <v>8.101091383362248E-2</v>
+      </c>
+      <c r="AO29" s="9" t="e">
+        <f t="shared" si="250"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AP29" s="9" t="e">
+        <f t="shared" si="250"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AQ29" s="9"/>
       <c r="AS29" s="9">
-        <f t="shared" ref="AS29:AU29" si="245">AS11/AS$5</f>
+        <f t="shared" ref="AS29:AU29" si="251">AS11/AS$5</f>
         <v>0.16054869627522039</v>
       </c>
       <c r="AT29" s="9">
-        <f t="shared" si="245"/>
+        <f t="shared" si="251"/>
         <v>0.15829104748097136</v>
       </c>
       <c r="AU29" s="9">
-        <f t="shared" si="245"/>
+        <f t="shared" si="251"/>
         <v>0.14472795467368069</v>
       </c>
       <c r="AV29" s="9">
-        <f t="shared" ref="AV29:BF29" si="246">AV11/AV$5</f>
+        <f t="shared" ref="AV29:BF29" si="252">AV11/AV$5</f>
         <v>0.13703457679264414</v>
       </c>
       <c r="AW29" s="9">
-        <f t="shared" si="246"/>
+        <f t="shared" si="252"/>
         <v>0.1196813573842273</v>
       </c>
       <c r="AX29" s="9">
-        <f t="shared" ref="AX29" si="247">AX11/AX$5</f>
+        <f t="shared" ref="AX29" si="253">AX11/AX$5</f>
         <v>0.11007716749886519</v>
       </c>
       <c r="AY29" s="9">
-        <f t="shared" si="246"/>
+        <f t="shared" si="252"/>
         <v>0.10739683363612769</v>
       </c>
       <c r="AZ29" s="9">
-        <f t="shared" ref="AZ29" si="248">AZ11/AZ$5</f>
+        <f t="shared" ref="AZ29" si="254">AZ11/AZ$5</f>
         <v>9.7739187008144934E-2</v>
       </c>
       <c r="BA29" s="9">
-        <f t="shared" si="246"/>
+        <f t="shared" si="252"/>
         <v>9.1060754497309424E-2</v>
       </c>
       <c r="BB29" s="9">
-        <f t="shared" si="246"/>
+        <f t="shared" si="252"/>
         <v>8.1374534112235997E-2</v>
       </c>
       <c r="BC29" s="9">
-        <f t="shared" si="246"/>
+        <f t="shared" si="252"/>
         <v>7.7287960368258801E-2</v>
       </c>
       <c r="BD29" s="9">
-        <f t="shared" si="246"/>
+        <f t="shared" si="252"/>
         <v>7.5040038734278725E-2</v>
       </c>
       <c r="BE29" s="9">
-        <f t="shared" si="246"/>
+        <f t="shared" si="252"/>
         <v>7.3403851415257404E-2</v>
       </c>
       <c r="BF29" s="9">
-        <f t="shared" si="246"/>
+        <f t="shared" si="252"/>
         <v>7.2359389926130321E-2</v>
       </c>
       <c r="BG29" s="9">
-        <f t="shared" ref="BG29:BI29" si="249">BG11/BG$5</f>
+        <f t="shared" ref="BG29:BI29" si="255">BG11/BG$5</f>
         <v>7.1896567212452411E-2</v>
       </c>
       <c r="BH29" s="9">
-        <f t="shared" si="249"/>
+        <f t="shared" si="255"/>
         <v>7.1432848823071021E-2</v>
       </c>
       <c r="BI29" s="9">
-        <f t="shared" si="249"/>
+        <f t="shared" si="255"/>
         <v>7.1549425227242808E-2</v>
       </c>
       <c r="BJ29" s="9">
-        <f t="shared" ref="BJ29:BK29" si="250">BJ11/BJ$5</f>
+        <f t="shared" ref="BJ29:BK29" si="256">BJ11/BJ$5</f>
         <v>7.1665234253888488E-2</v>
       </c>
       <c r="BK29" s="9">
-        <f t="shared" si="250"/>
+        <f t="shared" si="256"/>
         <v>7.178027788993574E-2</v>
       </c>
       <c r="BM29" t="s">
         <v>94</v>
       </c>
       <c r="BN29" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="2:184" x14ac:dyDescent="0.3">
@@ -7869,212 +8008,221 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9">
-        <f t="shared" si="209"/>
+        <f t="shared" si="212"/>
         <v>0.11578947368421044</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" ref="H30" si="251">H12/D12-1</f>
+        <f t="shared" ref="H30" si="257">H12/D12-1</f>
         <v>0.26166097838452784</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" ref="I30" si="252">I12/E12-1</f>
+        <f t="shared" ref="I30" si="258">I12/E12-1</f>
         <v>4.991680532445919E-3</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" ref="J30" si="253">J12/F12-1</f>
+        <f t="shared" ref="J30" si="259">J12/F12-1</f>
         <v>-6.199261992619931E-2</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" ref="K30" si="254">K12/G12-1</f>
+        <f t="shared" ref="K30" si="260">K12/G12-1</f>
         <v>-1.4579759862778707E-2</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" ref="L30" si="255">L12/H12-1</f>
+        <f t="shared" ref="L30" si="261">L12/H12-1</f>
         <v>2.0739404869251521E-2</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" ref="M30" si="256">M12/I12-1</f>
+        <f t="shared" ref="M30" si="262">M12/I12-1</f>
         <v>-2.4006622516556275E-2</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" ref="N30" si="257">N12/J12-1</f>
+        <f t="shared" ref="N30" si="263">N12/J12-1</f>
         <v>0.12116443745082606</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" ref="O30" si="258">O12/K12-1</f>
+        <f t="shared" ref="O30" si="264">O12/K12-1</f>
         <v>-7.6588337684943442E-2</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" ref="P30" si="259">P12/L12-1</f>
+        <f t="shared" ref="P30" si="265">P12/L12-1</f>
         <v>-9.7173144876324669E-3</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" ref="Q30" si="260">Q12/M12-1</f>
+        <f t="shared" ref="Q30" si="266">Q12/M12-1</f>
         <v>7.9728583545377374E-2</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" ref="R30" si="261">R12/N12-1</f>
+        <f t="shared" ref="R30" si="267">R12/N12-1</f>
         <v>0.16210526315789475</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" ref="S30" si="262">S12/O12-1</f>
+        <f t="shared" ref="S30" si="268">S12/O12-1</f>
         <v>5.4665409990575009E-2</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" ref="T30" si="263">T12/P12-1</f>
+        <f t="shared" ref="T30" si="269">T12/P12-1</f>
         <v>1.605709188224802E-2</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" ref="U30" si="264">U12/Q12-1</f>
+        <f t="shared" ref="U30" si="270">U12/Q12-1</f>
         <v>4.2419481539670123E-2</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" ref="V30" si="265">V12/R12-1</f>
+        <f t="shared" ref="V30" si="271">V12/R12-1</f>
         <v>-8.0917874396135292E-2</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" ref="W30:X30" si="266">W12/S12-1</f>
+        <f t="shared" ref="W30:X30" si="272">W12/S12-1</f>
         <v>0.15013404825737275</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="266"/>
+        <f t="shared" si="272"/>
         <v>0.21510096575943805</v>
       </c>
       <c r="Y30" s="9">
-        <f t="shared" ref="Y30" si="267">Y12/U12-1</f>
+        <f t="shared" ref="Y30" si="273">Y12/U12-1</f>
         <v>0.1152976639035419</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" ref="Z30" si="268">Z12/V12-1</f>
+        <f t="shared" ref="Z30" si="274">Z12/V12-1</f>
         <v>0.14914586070959257</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" ref="AA30" si="269">AA12/W12-1</f>
+        <f t="shared" ref="AA30" si="275">AA12/W12-1</f>
         <v>8.6247086247086324E-2</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" ref="AB30:AM30" si="270">AB12/X12-1</f>
+        <f t="shared" ref="AB30:AM30" si="276">AB12/X12-1</f>
         <v>0.68858381502890165</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="276"/>
         <v>0.11013513513513518</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="276"/>
         <v>0.25614636935391655</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="276"/>
         <v>5.4363376251788331E-2</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="276"/>
         <v>-0.36927685066324345</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="276"/>
         <v>0.20328667072428486</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="276"/>
         <v>2.2303140646335873E-2</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="276"/>
         <v>0.1350067842605156</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="276"/>
         <v>0.23677069199457268</v>
       </c>
       <c r="AK30" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="276"/>
         <v>-0.12139605462822456</v>
       </c>
       <c r="AL30" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="276"/>
         <v>-0.1139804096170971</v>
       </c>
       <c r="AM30" s="9">
-        <f t="shared" si="270"/>
+        <f t="shared" si="276"/>
         <v>7.9497907949790836E-2</v>
       </c>
-      <c r="AN30" s="9"/>
-      <c r="AO30" s="9"/>
-      <c r="AP30" s="9"/>
+      <c r="AN30" s="9">
+        <f t="shared" ref="AN30" si="277">AN12/AJ12-1</f>
+        <v>5.9791552386176727E-2</v>
+      </c>
+      <c r="AO30" s="9">
+        <f t="shared" ref="AO30" si="278">AO12/AK12-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AP30" s="9">
+        <f t="shared" ref="AP30" si="279">AP12/AL12-1</f>
+        <v>-1</v>
+      </c>
       <c r="AQ30" s="9"/>
       <c r="AS30" s="9"/>
       <c r="AT30" s="9">
-        <f t="shared" ref="AT30:BI30" si="271">AT12/AS12-1</f>
+        <f t="shared" ref="AT30:BI30" si="280">AT12/AS12-1</f>
         <v>6.0923900914974238E-2</v>
       </c>
       <c r="AU30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>2.7555742532604066E-2</v>
       </c>
       <c r="AV30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>4.6264073694984642E-2</v>
       </c>
       <c r="AW30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>-7.8262570925458075E-4</v>
       </c>
       <c r="AX30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>0.15527707068729191</v>
       </c>
       <c r="AY30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>0.28389830508474567</v>
       </c>
       <c r="AZ30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>-5.3333333333333344E-2</v>
       </c>
       <c r="BA30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>7.2514293682890418E-3</v>
       </c>
       <c r="BB30" s="9">
-        <f t="shared" si="271"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="280"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="BC30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BD30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BE30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BG30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI30" s="9">
-        <f t="shared" si="271"/>
+        <f t="shared" si="280"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BJ30" s="9">
-        <f t="shared" ref="BJ30" si="272">BJ12/BI12-1</f>
+        <f t="shared" ref="BJ30" si="281">BJ12/BI12-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK30" s="9">
-        <f t="shared" ref="BK30" si="273">BK12/BJ12-1</f>
+        <f t="shared" ref="BK30" si="282">BK12/BJ12-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -8083,19 +8231,19 @@
         <v>78</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="274">C16/C15</f>
+        <f t="shared" ref="C31:F31" si="283">C16/C15</f>
         <v>0.17691017233490924</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="274"/>
+        <f t="shared" si="283"/>
         <v>0.21877337322363499</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="274"/>
+        <f t="shared" si="283"/>
         <v>0.22667042571186918</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="274"/>
+        <f t="shared" si="283"/>
         <v>-1.3948228198039708E-2</v>
       </c>
       <c r="G31" s="9">
@@ -8107,207 +8255,216 @@
         <v>0.18224451957683499</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" ref="I31:V31" si="275">I16/I15</f>
+        <f t="shared" ref="I31:V31" si="284">I16/I15</f>
         <v>0.14084018053466035</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.16919475655430713</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.13667938557871051</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.18921521425132404</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.15992752241083349</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>-4.6919657033979038E-2</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.15828472331704241</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.17294994675186368</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.16281242700303666</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.16540008940545373</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.13836516993301909</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.15673228990565524</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.10321420283128337</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="275"/>
+        <f t="shared" si="284"/>
         <v>0.15186807523834064</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" ref="W31:X31" si="276">W16/W15</f>
+        <f t="shared" ref="W31:X31" si="285">W16/W15</f>
         <v>9.2574546871954783E-4</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" si="276"/>
+        <f t="shared" si="285"/>
         <v>0.17567694181579688</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" ref="Y31" si="277">Y16/Y15</f>
+        <f t="shared" ref="Y31" si="286">Y16/Y15</f>
         <v>0.17147102526002972</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" ref="Z31" si="278">Z16/Z15</f>
+        <f t="shared" ref="Z31" si="287">Z16/Z15</f>
         <v>0.18289647093278666</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" ref="AA31" si="279">AA16/AA15</f>
+        <f t="shared" ref="AA31" si="288">AA16/AA15</f>
         <v>0.18616725384758021</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" ref="AB31:AC31" si="280">AB16/AB15</f>
+        <f t="shared" ref="AB31:AC31" si="289">AB16/AB15</f>
         <v>0.19243817296818919</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="280"/>
+        <f t="shared" si="289"/>
         <v>0.19291668504388479</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" ref="AD31:AE31" si="281">AD16/AD15</f>
+        <f t="shared" ref="AD31:AE31" si="290">AD16/AD15</f>
         <v>0.18789177821814212</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="281"/>
+        <f t="shared" si="290"/>
         <v>0.18300102624248643</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" ref="AF31:AG31" si="282">AF16/AF15</f>
+        <f t="shared" ref="AF31:AG31" si="291">AF16/AF15</f>
         <v>0.18300102624248643</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="282"/>
+        <f t="shared" si="291"/>
         <v>0.17552589911784663</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" ref="AH31:AI31" si="283">AH16/AH15</f>
+        <f t="shared" ref="AH31:AI31" si="292">AH16/AH15</f>
         <v>0.1913394495412844</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="283"/>
+        <f t="shared" si="292"/>
         <v>0.18507383791998414</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" ref="AJ31:AL31" si="284">AJ16/AJ15</f>
+        <f t="shared" ref="AJ31:AL31" si="293">AJ16/AJ15</f>
         <v>0.17902264600715137</v>
       </c>
       <c r="AK31" s="9">
-        <f t="shared" si="284"/>
+        <f t="shared" si="293"/>
         <v>0.17697676642126398</v>
       </c>
       <c r="AL31" s="9">
-        <f t="shared" si="284"/>
+        <f t="shared" si="293"/>
         <v>0.16504169732646554</v>
       </c>
       <c r="AM31" s="9">
-        <f t="shared" ref="AM31" si="285">AM16/AM15</f>
+        <f t="shared" ref="AM31:AP31" si="294">AM16/AM15</f>
         <v>0.19107314655549401</v>
       </c>
-      <c r="AN31" s="9"/>
-      <c r="AO31" s="9"/>
-      <c r="AP31" s="9"/>
+      <c r="AN31" s="9">
+        <f t="shared" si="294"/>
+        <v>0.20287692243916594</v>
+      </c>
+      <c r="AO31" s="9" t="e">
+        <f t="shared" si="294"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AP31" s="9" t="e">
+        <f t="shared" si="294"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AQ31" s="9"/>
       <c r="AS31" s="9">
-        <f t="shared" ref="AS31:AU31" si="286">AS16/AS15</f>
+        <f t="shared" ref="AS31:AU31" si="295">AS16/AS15</f>
         <v>0.14889811346225237</v>
       </c>
       <c r="AT31" s="9">
-        <f t="shared" si="286"/>
+        <f t="shared" si="295"/>
         <v>0.16732466962768</v>
       </c>
       <c r="AU31" s="9">
-        <f t="shared" si="286"/>
+        <f t="shared" si="295"/>
         <v>0.10181285478850027</v>
       </c>
       <c r="AV31" s="9">
-        <f t="shared" ref="AV31:BF31" si="287">AV16/AV15</f>
+        <f t="shared" ref="AV31:BF31" si="296">AV16/AV15</f>
         <v>0.16507655177615205</v>
       </c>
       <c r="AW31" s="9">
-        <f t="shared" si="287"/>
+        <f t="shared" si="296"/>
         <v>0.13826615285083402</v>
       </c>
       <c r="AX31" s="9">
-        <f t="shared" ref="AX31" si="288">AX16/AX15</f>
+        <f t="shared" ref="AX31" si="297">AX16/AX15</f>
         <v>0.132990902152713</v>
       </c>
       <c r="AY31" s="9">
-        <f t="shared" si="287"/>
+        <f t="shared" si="296"/>
         <v>0.18978625253328257</v>
       </c>
       <c r="AZ31" s="9">
-        <f t="shared" ref="AZ31" si="289">AZ16/AZ15</f>
+        <f t="shared" ref="AZ31" si="298">AZ16/AZ15</f>
         <v>0.18326810898619214</v>
       </c>
       <c r="BA31" s="9">
-        <f t="shared" si="287"/>
+        <f t="shared" si="296"/>
         <v>0.17629644009803683</v>
       </c>
       <c r="BB31" s="9">
-        <f t="shared" si="287"/>
+        <f t="shared" si="296"/>
         <v>0.19</v>
       </c>
       <c r="BC31" s="9">
-        <f t="shared" si="287"/>
+        <f t="shared" si="296"/>
         <v>0.19</v>
       </c>
       <c r="BD31" s="9">
-        <f t="shared" si="287"/>
+        <f t="shared" si="296"/>
         <v>0.19</v>
       </c>
       <c r="BE31" s="9">
-        <f t="shared" si="287"/>
+        <f t="shared" si="296"/>
         <v>0.19</v>
       </c>
       <c r="BF31" s="9">
-        <f t="shared" si="287"/>
+        <f t="shared" si="296"/>
+        <v>0.19000000000000003</v>
+      </c>
+      <c r="BG31" s="9">
+        <f t="shared" ref="BG31:BI31" si="299">BG16/BG15</f>
         <v>0.19</v>
       </c>
-      <c r="BG31" s="9">
-        <f t="shared" ref="BG31:BI31" si="290">BG16/BG15</f>
+      <c r="BH31" s="9">
+        <f t="shared" si="299"/>
         <v>0.19</v>
       </c>
-      <c r="BH31" s="9">
-        <f t="shared" si="290"/>
+      <c r="BI31" s="9">
+        <f t="shared" si="299"/>
         <v>0.19</v>
       </c>
-      <c r="BI31" s="9">
-        <f t="shared" si="290"/>
-        <v>0.19</v>
-      </c>
       <c r="BJ31" s="9">
-        <f t="shared" ref="BJ31:BK31" si="291">BJ16/BJ15</f>
-        <v>0.19</v>
+        <f t="shared" ref="BJ31:BK31" si="300">BJ16/BJ15</f>
+        <v>0.19000000000000003</v>
       </c>
       <c r="BK31" s="9">
-        <f t="shared" si="291"/>
+        <f t="shared" si="300"/>
         <v>0.19</v>
       </c>
     </row>
@@ -8543,27 +8700,27 @@
       </c>
       <c r="Y43" s="25"/>
       <c r="Z43" s="25">
-        <f t="shared" ref="Z43:AE43" si="292">SUM(Z34:Z42)</f>
+        <f t="shared" ref="Z43:AE43" si="301">SUM(Z34:Z42)</f>
         <v>364840</v>
       </c>
       <c r="AA43" s="25">
-        <f t="shared" si="292"/>
+        <f t="shared" si="301"/>
         <v>359784</v>
       </c>
       <c r="AB43" s="25">
-        <f t="shared" si="292"/>
+        <f t="shared" si="301"/>
         <v>364552</v>
       </c>
       <c r="AC43" s="25">
-        <f t="shared" si="292"/>
+        <f t="shared" si="301"/>
         <v>380088</v>
       </c>
       <c r="AD43" s="25">
-        <f t="shared" si="292"/>
+        <f t="shared" si="301"/>
         <v>411976</v>
       </c>
       <c r="AE43" s="25">
-        <f t="shared" si="292"/>
+        <f t="shared" si="301"/>
         <v>445785</v>
       </c>
     </row>
@@ -8771,27 +8928,27 @@
       </c>
       <c r="Y52" s="25"/>
       <c r="Z52" s="25">
-        <f t="shared" ref="Z52:AE52" si="293">SUM(Z45:Z51)</f>
+        <f t="shared" ref="Z52:AE52" si="302">SUM(Z45:Z51)</f>
         <v>198298</v>
       </c>
       <c r="AA52" s="25">
-        <f t="shared" si="293"/>
+        <f t="shared" si="302"/>
         <v>186308</v>
       </c>
       <c r="AB52" s="25">
-        <f t="shared" si="293"/>
+        <f t="shared" si="302"/>
         <v>181416</v>
       </c>
       <c r="AC52" s="25">
-        <f t="shared" si="293"/>
+        <f t="shared" si="302"/>
         <v>185405</v>
       </c>
       <c r="AD52" s="25">
-        <f t="shared" si="293"/>
+        <f t="shared" si="302"/>
         <v>205753</v>
       </c>
       <c r="AE52" s="25">
-        <f t="shared" si="293"/>
+        <f t="shared" si="302"/>
         <v>225071</v>
       </c>
     </row>
@@ -8827,27 +8984,27 @@
       </c>
       <c r="Y54" s="25"/>
       <c r="Z54" s="25">
-        <f t="shared" ref="Z54:AE54" si="294">Z52+Z53</f>
+        <f t="shared" ref="Z54:AE54" si="303">Z52+Z53</f>
         <v>364840</v>
       </c>
       <c r="AA54" s="25">
-        <f t="shared" si="294"/>
+        <f t="shared" si="303"/>
         <v>359874</v>
       </c>
       <c r="AB54" s="25">
-        <f t="shared" si="294"/>
+        <f t="shared" si="303"/>
         <v>364552</v>
       </c>
       <c r="AC54" s="25">
-        <f t="shared" si="294"/>
+        <f t="shared" si="303"/>
         <v>380088</v>
       </c>
       <c r="AD54" s="25">
-        <f t="shared" si="294"/>
+        <f t="shared" si="303"/>
         <v>411976</v>
       </c>
       <c r="AE54" s="25">
-        <f t="shared" si="294"/>
+        <f t="shared" si="303"/>
         <v>445785</v>
       </c>
     </row>
